--- a/News_Dashboard/data/social_media_posts.xlsx
+++ b/News_Dashboard/data/social_media_posts.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,81 +425,81 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O423"/>
+  <dimension ref="A1:O460"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Base_Company</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Competitor</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Author/Handle</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Date Created</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Post Text</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Image URL</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Image Text</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Video URL</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Video Transcript</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Post URL</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Sentiment</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Alert Level</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>AI Summary</t>
         </is>
@@ -27012,6 +27024,2396 @@
         </is>
       </c>
     </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>Ramp</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>tryramp</t>
+        </is>
+      </c>
+      <c r="E424" t="inlineStr">
+        <is>
+          <t>Thu Jul 16 16:48:32 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F424" t="inlineStr">
+        <is>
+          <t>tell all the tokenmaxxers we’re comin https://t.co/boBI0pR9qR</t>
+        </is>
+      </c>
+      <c r="G424" t="inlineStr"/>
+      <c r="H424" t="inlineStr"/>
+      <c r="I424" t="inlineStr"/>
+      <c r="J424" t="inlineStr"/>
+      <c r="K424" t="inlineStr">
+        <is>
+          <t>https://x.com/tryramp/status/2077797543224770940</t>
+        </is>
+      </c>
+      <c r="L424" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M424" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N424" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O424" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>Ramp</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>tryramp</t>
+        </is>
+      </c>
+      <c r="E425" t="inlineStr">
+        <is>
+          <t>Thu Jul 16 16:45:16 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F425" t="inlineStr">
+        <is>
+          <t>@karimatiyeh Enjoy, this one’s on us
+https://t.co/mz7ueJHHVt https://t.co/DDEsoKWZx4</t>
+        </is>
+      </c>
+      <c r="G425" t="inlineStr"/>
+      <c r="H425" t="inlineStr"/>
+      <c r="I425" t="inlineStr"/>
+      <c r="J425" t="inlineStr"/>
+      <c r="K425" t="inlineStr">
+        <is>
+          <t>https://x.com/tryramp/status/2077796722911121449</t>
+        </is>
+      </c>
+      <c r="L425" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M425" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N425" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O425" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>Ramp</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>tryramp</t>
+        </is>
+      </c>
+      <c r="E426" t="inlineStr">
+        <is>
+          <t>Thu Jul 16 16:39:27 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F426" t="inlineStr">
+        <is>
+          <t>@restocc @eglyman https://t.co/1UhZOsi225</t>
+        </is>
+      </c>
+      <c r="G426" t="inlineStr"/>
+      <c r="H426" t="inlineStr"/>
+      <c r="I426" t="inlineStr"/>
+      <c r="J426" t="inlineStr"/>
+      <c r="K426" t="inlineStr">
+        <is>
+          <t>https://x.com/tryramp/status/2077795255747826093</t>
+        </is>
+      </c>
+      <c r="L426" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M426" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N426" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O426" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>Ramp</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>tryramp</t>
+        </is>
+      </c>
+      <c r="E427" t="inlineStr">
+        <is>
+          <t>Thu Jul 16 15:04:00 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F427" t="inlineStr">
+        <is>
+          <t>@pontusab https://t.co/5qd1ddh4Gh</t>
+        </is>
+      </c>
+      <c r="G427" t="inlineStr"/>
+      <c r="H427" t="inlineStr"/>
+      <c r="I427" t="inlineStr"/>
+      <c r="J427" t="inlineStr"/>
+      <c r="K427" t="inlineStr">
+        <is>
+          <t>https://x.com/tryramp/status/2077771237867086276</t>
+        </is>
+      </c>
+      <c r="L427" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M427" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N427" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O427" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>Ramp</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>tryramp</t>
+        </is>
+      </c>
+      <c r="E428" t="inlineStr">
+        <is>
+          <t>Thu Jul 16 14:37:23 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F428" t="inlineStr">
+        <is>
+          <t>We analyzed 110 trillion tokens and found 3 distinct spending profiles with different model choices, caching habits, prompts, and spend controls.
+See how you compare.
+https://t.co/5sx7blcao1</t>
+        </is>
+      </c>
+      <c r="G428" t="inlineStr"/>
+      <c r="H428" t="inlineStr"/>
+      <c r="I428" t="inlineStr"/>
+      <c r="J428" t="inlineStr"/>
+      <c r="K428" t="inlineStr">
+        <is>
+          <t>https://x.com/tryramp/status/2077764536048738685</t>
+        </is>
+      </c>
+      <c r="L428" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M428" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N428" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O428" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>Ramp</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>tryramp</t>
+        </is>
+      </c>
+      <c r="E429" t="inlineStr">
+        <is>
+          <t>Thu Jul 16 14:35:01 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F429" t="inlineStr">
+        <is>
+          <t>No more trying to wrangle AI spend in the dark. 
+Connect your business data. Measure your team trends. Maximize value per token.
+There's a light up ahead. https://t.co/ocsftjOd4p</t>
+        </is>
+      </c>
+      <c r="G429" t="inlineStr"/>
+      <c r="H429" t="inlineStr"/>
+      <c r="I429" t="inlineStr"/>
+      <c r="J429" t="inlineStr"/>
+      <c r="K429" t="inlineStr">
+        <is>
+          <t>https://x.com/tryramp/status/2077763942357619180</t>
+        </is>
+      </c>
+      <c r="L429" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M429" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N429" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O429" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>Ramp</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>tryramp</t>
+        </is>
+      </c>
+      <c r="E430" t="inlineStr">
+        <is>
+          <t>Thu Jul 16 14:21:48 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F430" t="inlineStr">
+        <is>
+          <t>@eglyman that's our CFO 💛 https://t.co/6eBcWiiPvI</t>
+        </is>
+      </c>
+      <c r="G430" t="inlineStr"/>
+      <c r="H430" t="inlineStr"/>
+      <c r="I430" t="inlineStr"/>
+      <c r="J430" t="inlineStr"/>
+      <c r="K430" t="inlineStr">
+        <is>
+          <t>https://x.com/tryramp/status/2077760617516044682</t>
+        </is>
+      </c>
+      <c r="L430" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M430" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N430" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O430" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>Brex</t>
+        </is>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>brexhq</t>
+        </is>
+      </c>
+      <c r="E431" t="inlineStr">
+        <is>
+          <t>Thu Jul 16 20:00:01 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F431" t="inlineStr">
+        <is>
+          <t>BREX DATA: Three of the 25 most-purchased founder books this year are from @stripepress, with two more just outside the list. A payments company that launched a press in 2018 is quietly becoming the startup bookshelf.</t>
+        </is>
+      </c>
+      <c r="G431" t="inlineStr"/>
+      <c r="H431" t="inlineStr"/>
+      <c r="I431" t="inlineStr"/>
+      <c r="J431" t="inlineStr"/>
+      <c r="K431" t="inlineStr">
+        <is>
+          <t>https://x.com/brexHQ/status/2077845729960194441</t>
+        </is>
+      </c>
+      <c r="L431" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M431" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N431" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O431" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>Brex</t>
+        </is>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>brexhq</t>
+        </is>
+      </c>
+      <c r="E432" t="inlineStr">
+        <is>
+          <t>Thu Jul 16 19:00:00 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F432" t="inlineStr">
+        <is>
+          <t>BREX DATA: A year ago, Atomic Habits was the #3 book founders bought on Brex. Today it's #11, down 31%. Meanwhile, High Output Management is up 59%, and The Hard Thing About Hard Things and The Philosopher in the Valley are in the top 10.</t>
+        </is>
+      </c>
+      <c r="G432" t="inlineStr"/>
+      <c r="H432" t="inlineStr"/>
+      <c r="I432" t="inlineStr"/>
+      <c r="J432" t="inlineStr"/>
+      <c r="K432" t="inlineStr">
+        <is>
+          <t>https://x.com/brexHQ/status/2077830629526294858</t>
+        </is>
+      </c>
+      <c r="L432" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M432" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N432" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O432" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>Brex</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>brexhq</t>
+        </is>
+      </c>
+      <c r="E433" t="inlineStr">
+        <is>
+          <t>Thu Jul 16 18:00:01 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F433" t="inlineStr">
+        <is>
+          <t>BREX DATA: Founder mode isn't just talk. It shows up in what founders buy. The most-purchased business book on Brex cards in H1 2026 is a brand-new biography of Alex Karp</t>
+        </is>
+      </c>
+      <c r="G433" t="inlineStr"/>
+      <c r="H433" t="inlineStr"/>
+      <c r="I433" t="inlineStr"/>
+      <c r="J433" t="inlineStr"/>
+      <c r="K433" t="inlineStr">
+        <is>
+          <t>https://x.com/brexHQ/status/2077815531114295744</t>
+        </is>
+      </c>
+      <c r="L433" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M433" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N433" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O433" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>Brex</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>brexhq</t>
+        </is>
+      </c>
+      <c r="E434" t="inlineStr">
+        <is>
+          <t>Thu Jul 16 16:16:58 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F434" t="inlineStr">
+        <is>
+          <t>@WineDiarist @wguidara @martinkl @patricklencioni Read the rest: https://t.co/Gnre75JSbD</t>
+        </is>
+      </c>
+      <c r="G434" t="inlineStr"/>
+      <c r="H434" t="inlineStr"/>
+      <c r="I434" t="inlineStr"/>
+      <c r="J434" t="inlineStr"/>
+      <c r="K434" t="inlineStr">
+        <is>
+          <t>https://x.com/brexHQ/status/2077789599401681369</t>
+        </is>
+      </c>
+      <c r="L434" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M434" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N434" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O434" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>Brex</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>brexhq</t>
+        </is>
+      </c>
+      <c r="E435" t="inlineStr">
+        <is>
+          <t>Thu Jul 16 16:15:07 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F435" t="inlineStr">
+        <is>
+          <t>The Philosopher in the Valley by Michael Steinberger @WineDiarist
+Unreasonable Hospitality by Will Guidara @wguidara
+Designing Data-Intensive Applications by @martinkl
+The Five Dysfunctions of a Team
+by @patricklencioni
+The Challenger Sale by Dixon &amp; Adamson
+Traction by @GinoWickman
+Never Split the Difference by @fbinegotiator
+Radical Candor by @kimballscott
+The Hard Thing About Hard Things by @bhorowitz
+The Scaling Era by @dwarkesh_sp and @gleech
+Atomic Habits by @JamesClear
+Scaling People by @chughesjohnson
+High Output Management by Andy Grove
+Crucial Conversations by Patterson et al.
+The Mom Test by @robfitz
+Dare to Lead by @BreneBrown
+AI Engineering by @chipro
+What the Heck Is EOS? by @GinoWickman
+Extreme Ownership by @LeifBabin and @jockowillink
+The Creative Act by @RickRubin
+The Origins of Efficiency by @_brianpotter
+The Coaching Habit by @mbs_works
+The Goal by Eliyahu Goldratt
+No Rules Rules by @reedhastings and @ErinMeyerINSEAD
+Who by Smart &amp; Street</t>
+        </is>
+      </c>
+      <c r="G435" t="inlineStr"/>
+      <c r="H435" t="inlineStr"/>
+      <c r="I435" t="inlineStr"/>
+      <c r="J435" t="inlineStr"/>
+      <c r="K435" t="inlineStr">
+        <is>
+          <t>https://x.com/brexHQ/status/2077789133028684257</t>
+        </is>
+      </c>
+      <c r="L435" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M435" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N435" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O435" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>Brex</t>
+        </is>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>brexhq</t>
+        </is>
+      </c>
+      <c r="E436" t="inlineStr">
+        <is>
+          <t>Thu Jul 16 16:15:06 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F436" t="inlineStr">
+        <is>
+          <t>Founder mode is back on the bookshelf.
+Book purchases across 35,000+ Brex customers. H1 2026's rankings show founder biographies reclaiming the top spot, @stripepress cementing itself as a startup staple, and management frameworks losing ground to AI. 
+See what's on the bookshelf in the comments.</t>
+        </is>
+      </c>
+      <c r="G436" t="inlineStr"/>
+      <c r="H436" t="inlineStr"/>
+      <c r="I436" t="inlineStr"/>
+      <c r="J436" t="inlineStr"/>
+      <c r="K436" t="inlineStr">
+        <is>
+          <t>https://x.com/brexHQ/status/2077789130646241494</t>
+        </is>
+      </c>
+      <c r="L436" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M436" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N436" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O436" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>AirBnb</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>Heartshare</t>
+        </is>
+      </c>
+      <c r="E437" t="inlineStr">
+        <is>
+          <t>2026-07-16T17:47:57.180Z</t>
+        </is>
+      </c>
+      <c r="F437" t="inlineStr">
+        <is>
+          <t>We're still beaming from an unforgettable experience at the World Cup! ⚽✨
+Thanks to Airbnb’s incredible generosity, 50 young people from Heartshare's foster care programs had the chance to attend a FIFA World Cup 2026 match—a once-in-a-lifetime experience they'll never forget. We're deeply grateful to Airbnb for investing in young people and making this opportunity possible.
+A special thank you as well to New York City Council Member Rita Joseph for recommending Heartshare for this initiative and for being such a dedicated champion for our youth. Together, we're making dreams come true!</t>
+        </is>
+      </c>
+      <c r="G437" t="inlineStr">
+        <is>
+          <t>https://media.licdn.com/dms/image/v2/D5622AQHBua3f7o1sBA/feedshare-image-high-res/B56Z9ici6JG0AY-/0/1784063078272?e=1785974400&amp;v=beta&amp;t=pFuPI_TvjxJjRLxaEg7wOWJCABmvbM18dUvKXjEXfYg</t>
+        </is>
+      </c>
+      <c r="H437" t="inlineStr">
+        <is>
+          <t>[easyocr not installed. Run 'pip install easyocr torch torchvision']</t>
+        </is>
+      </c>
+      <c r="I437" t="inlineStr"/>
+      <c r="J437" t="inlineStr"/>
+      <c r="K437" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/heartshare_were-still-beaming-from-an-unforgettable-ugcPost-7482902912327761920-1Gwk</t>
+        </is>
+      </c>
+      <c r="L437" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M437" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N437" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O437" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>Expedia</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>Expedia</t>
+        </is>
+      </c>
+      <c r="E438" t="inlineStr">
+        <is>
+          <t>Fri Jul 17 00:00:01 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F438" t="inlineStr">
+        <is>
+          <t>Planning a trip to Norway? 🇳🇴
+➡️ The Fjords: Glide through dark waters past towering cliffs and feel the cold mist from crashing waterfalls.
+➡️ The Light: Hike under the midnight sun and watch the sky turn brilliant shades of pink over rugged islands.
+➡️ The Stays: Skip standard hotels and warm up by the fire in a striking, repurposed red fisherman’s cabin right on the water
+🔗 Plan your travel: https://t.co/MZXIYNu96P</t>
+        </is>
+      </c>
+      <c r="G438" t="inlineStr"/>
+      <c r="H438" t="inlineStr"/>
+      <c r="I438" t="inlineStr"/>
+      <c r="J438" t="inlineStr"/>
+      <c r="K438" t="inlineStr">
+        <is>
+          <t>https://x.com/Expedia/status/2077906128151687668</t>
+        </is>
+      </c>
+      <c r="L438" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M438" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N438" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O438" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>Expedia</t>
+        </is>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>expedia</t>
+        </is>
+      </c>
+      <c r="E439" t="inlineStr">
+        <is>
+          <t>2026-07-16T18:31:04.000Z</t>
+        </is>
+      </c>
+      <c r="F439" t="inlineStr">
+        <is>
+          <t>#ExpediaAmbassador Planning a Big Sur road trip? Save this itinerary for your next California adventure. 🌊🚗 From Bixby Bridge and Point Lobos to McWay Falls, Nepenthe and a dreamy stay at Post Ranch Inn, these are the stops we'd recommend every time. Plus, when you book through Expedia, you can earn OneKeyCash on eligible bookings to use toward future trips and unlock perks for your next adventure. 📍 Big Sur, California 🎥 @elenataber @lindzoutside</t>
+        </is>
+      </c>
+      <c r="G439" t="inlineStr">
+        <is>
+          <t>https://scontent-iad3-1.cdninstagram.com/v/t51.82787-15/750903842_18614895811030381_7426509813236580429_n.jpg?stp=dst-jpg_e35_p1080x1080_sh2.08_tt6&amp;_nc_ht=scontent-iad3-1.cdninstagram.com&amp;_nc_cat=101&amp;_nc_oc=Q6cZ2gFralIk8b42zuwqIwCpNCPayNOUuCf0Ehnzqvi92LZNmQDgy382Fp-Nv1nt2MG8HR0&amp;_nc_ohc=2isfH9A2kUoQ7kNvwHb-Ayh&amp;_nc_gid=K7dxLpvqhl7FS4wWw3tmwA&amp;edm=ADp7STQBAAAA&amp;ccb=7-5&amp;oh=00_AQCf9icS_BgqASK7WNCVFc29KWio2RmfwT8SDiOIHKx-QQ&amp;oe=6A5FC4CC&amp;_nc_sid=c6f216</t>
+        </is>
+      </c>
+      <c r="H439" t="inlineStr">
+        <is>
+          <t>[easyocr not installed. Run 'pip install easyocr torch torchvision']</t>
+        </is>
+      </c>
+      <c r="I439" t="inlineStr">
+        <is>
+          <t>https://scontent-lga3-2.cdninstagram.com/o1/v/t2/f2/m86/AQPlOS0NSeJqLwuKXk3zXE72lItojvs6Wh16t6Vt8mnqy4a5SiccbDIHushV6o7z6Ki1OB_o0xs5j-YFJ81o-bhTzCTH1FR77XRUP5Y.mp4?_nc_cat=101&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-lga3-2.cdninstagram.com&amp;_nc_ohc=5qs0tyANkO8Q7kNvwGrkpqn&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uQ0xJUFMuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTg2MTQ4ODEzOTYwMzAzODEsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDA5OSwiZHVyYXRpb25fcyI6ODQsInVybGdlbl9zb3VyY2UiOiJ3d3cifQ%3D%3D&amp;ccb=17-1&amp;vs=788d87cbeb7d07d2&amp;_nc_vs=HBksFQIYUmlnX3hwdl9yZWVsc19wZXJtYW5lbnRfc3JfcHJvZC83RTRENzBFQTc0NUREMTk5MUMwQjc2MEVDNDMwRjVCNl92aWRlb19kYXNoaW5pdC5tcDQVAALIARIAFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyL0MzNDMwMjYyNzhEMzJGMDVEQkI5QThCODZDMzA1OTg3X2F1ZGlvX2Rhc2hpbml0Lm1wNBUCAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACba7quS2oiRQhUCKAJDMywXQFUGZmZmZmYYEmRhc2hfYmFzZWxpbmVfMV92MREAdf4HZeadAQA&amp;_nc_gid=ZzezLqO0fGZ-z_pbX0caZA&amp;_nc_ss=7ca8c&amp;_nc_zt=28&amp;oh=00_AQAPTV6Aq8eQZjl5nfWvkTYnDdEVh6Zfq22rL2mc3Kil4Q&amp;oe=6A5BCCF2</t>
+        </is>
+      </c>
+      <c r="J439" t="inlineStr">
+        <is>
+          <t>[faster-whisper not installed. Run 'pip install faster-whisper']</t>
+        </is>
+      </c>
+      <c r="K439" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Da3ScCRDnXH/</t>
+        </is>
+      </c>
+      <c r="L439" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M439" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N439" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O439" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E440" t="inlineStr">
+        <is>
+          <t>Fri Jul 17 09:56:31 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F440" t="inlineStr">
+        <is>
+          <t>Hi there, as much as we'd like to assist you, we're unable to assist with Flight reservations through social media, but if you need support, you can contact our Flights team using this link: https://t.co/OVuF5pCzba or call {US}+1 917 421 7240 / {UK}+44 2039019061 / {IE} +353 19075677 / {AUS} +61 282281537.</t>
+        </is>
+      </c>
+      <c r="G440" t="inlineStr"/>
+      <c r="H440" t="inlineStr"/>
+      <c r="I440" t="inlineStr"/>
+      <c r="J440" t="inlineStr"/>
+      <c r="K440" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2078056243231346794</t>
+        </is>
+      </c>
+      <c r="L440" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M440" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N440" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O440" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E441" t="inlineStr">
+        <is>
+          <t>Fri Jul 17 09:31:00 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F441" t="inlineStr">
+        <is>
+          <t>As you said that one of the flight team supervisors called you to provide an answer, it seems that the assistance was provided, but the outcome did not match your expectations. With that said, we confirm that we cannot assist with this query on social media as due to GDPR and security restrictions we do not have access to flight reservations. Please contact them once again if you are still seeking assistance. Regards</t>
+        </is>
+      </c>
+      <c r="G441" t="inlineStr"/>
+      <c r="H441" t="inlineStr"/>
+      <c r="I441" t="inlineStr"/>
+      <c r="J441" t="inlineStr"/>
+      <c r="K441" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2078049822532047176</t>
+        </is>
+      </c>
+      <c r="L441" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M441" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N441" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O441" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E442" t="inlineStr">
+        <is>
+          <t>Fri Jul 17 09:14:02 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F442" t="inlineStr">
+        <is>
+          <t>@roalpeje Entendemos lo importante que es para ti obtener una respuesta lo antes posible, Roberto. Te sugerimos que te pongas en contacto con el equipo especializado a través del enlace compartido o que los llames para que puedan brindarte la ayuda que necesitas. 
+Un saludo.</t>
+        </is>
+      </c>
+      <c r="G442" t="inlineStr"/>
+      <c r="H442" t="inlineStr"/>
+      <c r="I442" t="inlineStr"/>
+      <c r="J442" t="inlineStr"/>
+      <c r="K442" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2078045552772575585</t>
+        </is>
+      </c>
+      <c r="L442" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M442" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N442" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O442" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D443" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E443" t="inlineStr">
+        <is>
+          <t>Fri Jul 17 08:50:27 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F443" t="inlineStr">
+        <is>
+          <t>Hola Carles, gracias por contactarnos. Aquí te dejamos unos consejos con relación a tu reserva:
+- https://t.co/fGhmZE7riF nunca te pedirá los datos de tu tarjeta de crédito ni tus datos personales por teléfono ni por e-mail. Recopilamos y guardamos toda la información en nuestro sistema online seguro.
+- No te pediremos que realices transferencias bancarias distintas de las que aparecen en las condiciones de tu reserva que te son enviadas al email de confirmación para que revises.
+- En dicho email de confirmación también te enviamos el número de teléfono del alojamiento para que puedas contactarlos directamente.
+- Nosotros no ofrecemos asistencia por medio de WhatsApp.
+- No ofrecemos asistencia pre-reservas ni reservamos a nombre de clientes; nuestro sistema se basa en un sistema de autoservicio.
+- Nuestros únicos canales de comunicación son los que aparecen en nuestra página https://t.co/e2l7BRLpeA, nuestra aplicación, nuestras cuentas verificadas en redes sociales. 
+- Nuestros números de teléfono oficiales citados son: https://t.co/o8QyR8SaDb
+Siempre aconsejamos no abrir enlaces sospechosos ni compartir información personal ni financiera con desconocidos y si tienes alguna pregunta acerca de la información que te hemos compartido seguimos aquí. 
+Si aún deseas que revisemos tu reserva, envíanos un mensaje privado con los siguientes datos:
+- Número de confirmación
+- Código PIN
+- Nombre del huésped
+- Detalles de tu solicitud
+Un saludo.</t>
+        </is>
+      </c>
+      <c r="G443" t="inlineStr"/>
+      <c r="H443" t="inlineStr"/>
+      <c r="I443" t="inlineStr"/>
+      <c r="J443" t="inlineStr"/>
+      <c r="K443" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2078039616599294031</t>
+        </is>
+      </c>
+      <c r="L443" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M443" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N443" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O443" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D444" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E444" t="inlineStr">
+        <is>
+          <t>Fri Jul 17 08:29:01 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F444" t="inlineStr">
+        <is>
+          <t>@julien3181 Hi there, we just responded to your DM. Please, check. Thank you.</t>
+        </is>
+      </c>
+      <c r="G444" t="inlineStr"/>
+      <c r="H444" t="inlineStr"/>
+      <c r="I444" t="inlineStr"/>
+      <c r="J444" t="inlineStr"/>
+      <c r="K444" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2078034225056387424</t>
+        </is>
+      </c>
+      <c r="L444" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M444" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N444" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O444" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D445" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E445" t="inlineStr">
+        <is>
+          <t>Fri Jul 17 07:52:20 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F445" t="inlineStr">
+        <is>
+          <t>Hi Libby, we regret to hear you are still awaiting your refund.While we would love to assist you with this matter via social media, we regret to inform you that we cannot provide assistance with flights through this platform. You can reach our Flights team using this link: https://t.co/OVuF5pCzba or by calling {US}+1 917 421 7240 / {UK}+44 2039019061 / {IE} +353 19075677.</t>
+        </is>
+      </c>
+      <c r="G445" t="inlineStr"/>
+      <c r="H445" t="inlineStr"/>
+      <c r="I445" t="inlineStr"/>
+      <c r="J445" t="inlineStr"/>
+      <c r="K445" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2078024993359696188</t>
+        </is>
+      </c>
+      <c r="L445" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M445" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N445" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O445" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E446" t="inlineStr">
+        <is>
+          <t>Fri Jul 17 07:44:17 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F446" t="inlineStr">
+        <is>
+          <t>Hi Tom,
+You recently reached out to us in regards to your Car Rental reservation, but we haven't heard back from you. If you still need assistance, please provide us with the following details :
+- Booking number
+- Name of booker
+- Email address used to book
+- Your request
+Thank you.</t>
+        </is>
+      </c>
+      <c r="G446" t="inlineStr"/>
+      <c r="H446" t="inlineStr"/>
+      <c r="I446" t="inlineStr"/>
+      <c r="J446" t="inlineStr"/>
+      <c r="K446" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2078022965799657485</t>
+        </is>
+      </c>
+      <c r="L446" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M446" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N446" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O446" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E447" t="inlineStr">
+        <is>
+          <t>Fri Jul 17 07:43:49 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F447" t="inlineStr">
+        <is>
+          <t>Hi Marisa 
+You recently reached out to us in regards to your Car Rental reservation, but we haven't heard back from you. If you still need assistance, please provide us with the following details :
+- Booking number
+- Name of booker
+- Email address used to book
+- Your request
+Thank you.</t>
+        </is>
+      </c>
+      <c r="G447" t="inlineStr"/>
+      <c r="H447" t="inlineStr"/>
+      <c r="I447" t="inlineStr"/>
+      <c r="J447" t="inlineStr"/>
+      <c r="K447" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2078022846433902673</t>
+        </is>
+      </c>
+      <c r="L447" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M447" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N447" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O447" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D448" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E448" t="inlineStr">
+        <is>
+          <t>Fri Jul 17 06:46:45 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F448" t="inlineStr">
+        <is>
+          <t>Hola, Paola. Sentimos que no hayas obtenido respuesta aún a tu solicitud. Cuéntanos, ¿cómo podemos ayudarte?. Si tu consulta está relacionada con una reserva de alojamiento, envíanos un mensaje privado con los siguientes datos y te responderemos lo antes posible:
+- Número de confirmación:
+- Código PIN:
+- Nombre que aparece en la reserva:
+- Detalles de tu solicitud:
+Ten en cuenta que nuestro equipo de Redes Sociales no trabaja en tiempo real. Para recibir ayuda inmediata, llama a nuestro equipo de Atención al Cliente disponible 24/7; puedes encontrar nuestros datos de contacto aquí:  https://t.co/o8QyR8SaDb
+Además, por el momento solo ofrecemos soporte para reservas de alojamiento a través de las redes sociales. Para preguntas sobre Vuelos, Taxis o Seguros, puedes contactar con los equipos especializados aquí:  https://t.co/TBejpc4vOA.
+Un saludo.</t>
+        </is>
+      </c>
+      <c r="G448" t="inlineStr"/>
+      <c r="H448" t="inlineStr"/>
+      <c r="I448" t="inlineStr"/>
+      <c r="J448" t="inlineStr"/>
+      <c r="K448" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2078008488534405244</t>
+        </is>
+      </c>
+      <c r="L448" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M448" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N448" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O448" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D449" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E449" t="inlineStr">
+        <is>
+          <t>Fri Jul 17 06:25:33 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F449" t="inlineStr">
+        <is>
+          <t>Gracias por compartir tu situación. Por motivos de seguridad, no podemos ofrecer asistencia a nuestros colaboradores a través de las redes sociales. Sin embargo, puedes encontrar los datos de contacto de nuestro equipo de Ayuda para colaboradores aquí:  https://t.co/QpD1nP4Qdu?
+Un saludo.</t>
+        </is>
+      </c>
+      <c r="G449" t="inlineStr"/>
+      <c r="H449" t="inlineStr"/>
+      <c r="I449" t="inlineStr"/>
+      <c r="J449" t="inlineStr"/>
+      <c r="K449" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2078003152226308395</t>
+        </is>
+      </c>
+      <c r="L449" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M449" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N449" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O449" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D450" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E450" t="inlineStr">
+        <is>
+          <t>Fri Jul 17 06:23:33 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F450" t="inlineStr">
+        <is>
+          <t>@valarmorgulisse - Numéro de confirmation
+- Code confidentiel
+- Nom indiqué sur la réservation
+En alternative, pour une assistance immédiate, vous pouvez également nous appeler ici : https://t.co/aH74XgSLGq</t>
+        </is>
+      </c>
+      <c r="G450" t="inlineStr"/>
+      <c r="H450" t="inlineStr"/>
+      <c r="I450" t="inlineStr"/>
+      <c r="J450" t="inlineStr"/>
+      <c r="K450" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2078002648268042652</t>
+        </is>
+      </c>
+      <c r="L450" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M450" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N450" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O450" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D451" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E451" t="inlineStr">
+        <is>
+          <t>Fri Jul 17 06:23:13 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F451" t="inlineStr">
+        <is>
+          <t>@valarmorgulisse Nous regrettons de lire votre déception. Afin que nous puissions vous aider ici, pourriez-vous nous envoyer un message privé avec les informations suivantes :</t>
+        </is>
+      </c>
+      <c r="G451" t="inlineStr"/>
+      <c r="H451" t="inlineStr"/>
+      <c r="I451" t="inlineStr"/>
+      <c r="J451" t="inlineStr"/>
+      <c r="K451" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2078002563098579338</t>
+        </is>
+      </c>
+      <c r="L451" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M451" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N451" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O451" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C452" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D452" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E452" t="inlineStr">
+        <is>
+          <t>Fri Jul 17 06:22:57 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F452" t="inlineStr">
+        <is>
+          <t>@valarmorgulisse Bonjour, toutes nos excuses pour le délai de réponse. Nous recevons actuellement un volume important de demandes sur les réseaux sociaux et n’avons pas pu vous répondre plus tôt.</t>
+        </is>
+      </c>
+      <c r="G452" t="inlineStr"/>
+      <c r="H452" t="inlineStr"/>
+      <c r="I452" t="inlineStr"/>
+      <c r="J452" t="inlineStr"/>
+      <c r="K452" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2078002499441631324</t>
+        </is>
+      </c>
+      <c r="L452" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M452" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N452" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O452" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C453" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D453" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E453" t="inlineStr">
+        <is>
+          <t>Fri Jul 17 01:31:19 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F453" t="inlineStr">
+        <is>
+          <t>Hi Tawn, we regret to hear that your flight is delayed and we understand how important this is for you. As much as we would like to, we're unable to assist with Flight reservations through social media, but if you need support, you can contact our Flights team using this link: https://t.co/OVuF5pCzba, or call {US}+1 917 421 7240 / {UK}+44 2039019061 / {IE} +353 19075677</t>
+        </is>
+      </c>
+      <c r="G453" t="inlineStr"/>
+      <c r="H453" t="inlineStr"/>
+      <c r="I453" t="inlineStr"/>
+      <c r="J453" t="inlineStr"/>
+      <c r="K453" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2077929105236918439</t>
+        </is>
+      </c>
+      <c r="L453" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M453" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N453" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O453" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C454" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D454" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E454" t="inlineStr">
+        <is>
+          <t>Fri Jul 17 00:53:07 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F454" t="inlineStr">
+        <is>
+          <t>Hi there, thank you for sharing your concerns regarding the property at 40 Shaftesbury Avenue. We acknowledge your message and regret to hear about the issues that were summarized in recent reviews. It's important to know that we provide an online platform through which properties can advertise their service. By making a reservation, you enter into a direct (legally binding) contractual relationship with the accommodation provider and, from that point, we act solely as an intermediary between you and them.
+If you still need support, we'll be happy to check your case and assist you. Feel free to DM us the following details: 
+• Confirmation number:
+• Pin code:
+• Name on the reservation:</t>
+        </is>
+      </c>
+      <c r="G454" t="inlineStr"/>
+      <c r="H454" t="inlineStr"/>
+      <c r="I454" t="inlineStr"/>
+      <c r="J454" t="inlineStr"/>
+      <c r="K454" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2077919491325841739</t>
+        </is>
+      </c>
+      <c r="L454" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M454" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N454" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O454" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C455" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D455" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E455" t="inlineStr">
+        <is>
+          <t>Fri Jul 17 00:27:07 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F455" t="inlineStr">
+        <is>
+          <t>@tdog1410 We have sent you a private message; kindly check at your earliest convenience. Thank you.</t>
+        </is>
+      </c>
+      <c r="G455" t="inlineStr"/>
+      <c r="H455" t="inlineStr"/>
+      <c r="I455" t="inlineStr"/>
+      <c r="J455" t="inlineStr"/>
+      <c r="K455" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2077912949029568633</t>
+        </is>
+      </c>
+      <c r="L455" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M455" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N455" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O455" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C456" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D456" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E456" t="inlineStr">
+        <is>
+          <t>Fri Jul 17 00:22:03 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F456" t="inlineStr">
+        <is>
+          <t>Hi Lios, thank you for flagging this. The properties provide the information on our website and have to pass a verification procedure before becoming bookable. If we find that a property listed on our platform is providing false information, we investigate immediately, give them the opportunity to rectify, or we may remove them from our website accordingly.
+Feel free to DM us with a link to the property's https://t.co/fGhmZE7riF page, as well as some more information about the details you believe are listed incorrectly, and our partner support team can investigate further.</t>
+        </is>
+      </c>
+      <c r="G456" t="inlineStr"/>
+      <c r="H456" t="inlineStr"/>
+      <c r="I456" t="inlineStr"/>
+      <c r="J456" t="inlineStr"/>
+      <c r="K456" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2077911675949215879</t>
+        </is>
+      </c>
+      <c r="L456" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M456" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N456" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O456" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C457" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D457" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E457" t="inlineStr">
+        <is>
+          <t>Fri Jul 17 00:06:24 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F457" t="inlineStr">
+        <is>
+          <t>Hi Levi, we regret to hear about the challenges you're facing regarding your refund, and we want to help you resolve this issue. If you could please share more details about your concern, we would be more than happy to assist you in any way we can. If your request is related to an accommodation booking, please DM us the following details, and we'll get back to you as soon as possible: 
+• Confirmation number:
+• Pin code:
+• Name on the reservation:
+Please bear in mind that our Social Media Team doesn't work in real time. For immediate support, please call our 24/7 Customer Service Team - our contact details can be found here: https://t.co/o8QyR8SaDb.
+Also, at this time, we only offer support for accommodation bookings via social media. For questions about Flights, Taxis, or Insurance, you can reach out to the dedicated support team here: https://t.co/OVuF5pCzba.</t>
+        </is>
+      </c>
+      <c r="G457" t="inlineStr"/>
+      <c r="H457" t="inlineStr"/>
+      <c r="I457" t="inlineStr"/>
+      <c r="J457" t="inlineStr"/>
+      <c r="K457" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2077907733962010725</t>
+        </is>
+      </c>
+      <c r="L457" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M457" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N457" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O457" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C458" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D458" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E458" t="inlineStr">
+        <is>
+          <t>Thu Jul 16 23:56:34 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F458" t="inlineStr">
+        <is>
+          <t>Thank you for contacting us, Irfan, and we regret to hear about any inconvenience this has caused you regarding your booked reservation. However, it's important to know that we provide an online platform through which properties can advertise their services. By making a reservation, you enter into a direct (legally binding) contractual relationship with the accommodation provider and, from that point, we act solely as an intermediary between you and them.
+If you still need support, we’ll be happy to check your case and assist you. Feel free to DM us the following details:
+• Confirmation number: 
+• Pin code: 
+• Name on the reservation:</t>
+        </is>
+      </c>
+      <c r="G458" t="inlineStr"/>
+      <c r="H458" t="inlineStr"/>
+      <c r="I458" t="inlineStr"/>
+      <c r="J458" t="inlineStr"/>
+      <c r="K458" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2077905261033861602</t>
+        </is>
+      </c>
+      <c r="L458" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M458" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N458" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O458" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C459" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D459" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E459" t="inlineStr">
+        <is>
+          <t>Thu Jul 16 23:33:38 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F459" t="inlineStr">
+        <is>
+          <t>Hi there, we regret to hear about the difficulty you’ve experienced with your Prague booking. We understand how frustrating it must feel to cancel within minutes and still face a non‑refundable outcome, especially when you expected free cancellation. Please note that each accommodation provider manages their policies themselves, so whenever an out of policy cancellation is requested, only the accommodation provider can approve this as an exception, not https://t.co/fGhmZE7riF
+We'll be happy to reach out to the property on your behalf if you send us a private message with the following details:
+- Pin code:
+- Name on the reservation:</t>
+        </is>
+      </c>
+      <c r="G459" t="inlineStr"/>
+      <c r="H459" t="inlineStr"/>
+      <c r="I459" t="inlineStr"/>
+      <c r="J459" t="inlineStr"/>
+      <c r="K459" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2077899490606879081</t>
+        </is>
+      </c>
+      <c r="L459" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M459" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N459" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O459" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C460" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="D460" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E460" t="inlineStr">
+        <is>
+          <t>2026-07-16T15:35:38.000Z</t>
+        </is>
+      </c>
+      <c r="F460" t="inlineStr">
+        <is>
+          <t>No humans. No drama. Just an Easy purr-cation.</t>
+        </is>
+      </c>
+      <c r="G460" t="inlineStr">
+        <is>
+          <t>https://instagram.fagc3-1.fna.fbcdn.net/v/t51.71878-15/750376604_1749854193100334_7661202268487853117_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_ht=instagram.fagc3-1.fna.fbcdn.net&amp;_nc_cat=102&amp;_nc_oc=Q6cZ2gFLiniGhZ_Wn9P7WhV3FW01U9IWvazhlVjkIQ8fA_QSgNXaBo9aPk87-ABdAxbO6Rw_oX6YiajVGUyF8lZ1eR8q&amp;_nc_ohc=rSpQG2x4njUQ7kNvwHuHzMB&amp;_nc_gid=AMRCMOOXRzz-Xt6x2-h01w&amp;edm=ADp7STQBAAAA&amp;ccb=7-5&amp;oh=00_AQCFyttuIrMbYRhlsF460CmZRYAnDotng8ioTKF-eltSiQ&amp;oe=6A5FE49D&amp;_nc_sid=c6f216</t>
+        </is>
+      </c>
+      <c r="H460" t="inlineStr">
+        <is>
+          <t>[easyocr not installed. Run 'pip install easyocr torch torchvision']</t>
+        </is>
+      </c>
+      <c r="I460" t="inlineStr">
+        <is>
+          <t>https://scontent-atl3-3.cdninstagram.com/o1/v/t2/f2/m86/AQPgUW6PRwGNO-LWg9gTXbHYbEAdGZTdVygX-s5lkZY8xKYrF_oe61MFMa7AalMUjtamhOsKdLIyrOrTx-sqYCeujABRc26qDnBZlEI.mp4?_nc_cat=110&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-atl3-3.cdninstagram.com&amp;_nc_ohc=sXs7N1pEz9AQ7kNvwFaN2Vh&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uQ0xJUFMuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTk2MTk2NzAwMTQyNTgzNSwiYXNzZXRfYWdlX2RheXMiOjAsInZpX3VzZWNhc2VfaWQiOjEwMDk5LCJkdXJhdGlvbl9zIjozNiwidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=befb48259c2372c8&amp;_nc_vs=HBksFQIYUmlnX3hwdl9yZWVsc19wZXJtYW5lbnRfc3JfcHJvZC9DRTQ1RUFCNUY4RTM0MTM2MEY4QkE0RkVBNjc2MzlBRl92aWRlb19kYXNoaW5pdC5tcDQVAALIARIAFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyLzlBNDVEMUQyREYzQzRFNDUwQTQ2MERBQTI2NTZBN0FDX2F1ZGlvX2Rhc2hpbml0Lm1wNBUCAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbW3vKiwZn8BhUCKAJDMywXQEIVP3ztkWgYEmRhc2hfYmFzZWxpbmVfMV92MREAdf4HZeadAQA&amp;_nc_gid=o4UsAiXxfM5tPlMBZ0F6sA&amp;_nc_ss=7ca8c&amp;_nc_zt=28&amp;oh=00_AQCHr9CONJAjEm0E01hf3TPyurCEoDxJidRxNelX7HEQ7Q&amp;oe=6A5BED33</t>
+        </is>
+      </c>
+      <c r="J460" t="inlineStr">
+        <is>
+          <t>[faster-whisper not installed. Run 'pip install faster-whisper']</t>
+        </is>
+      </c>
+      <c r="K460" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Da2-Un9tc84/</t>
+        </is>
+      </c>
+      <c r="L460" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M460" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N460" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O460" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/News_Dashboard/data/social_media_posts.xlsx
+++ b/News_Dashboard/data/social_media_posts.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O460"/>
+  <dimension ref="A1:O467"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29414,6 +29414,484 @@
         </is>
       </c>
     </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>AirBnb</t>
+        </is>
+      </c>
+      <c r="C461" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="D461" t="inlineStr">
+        <is>
+          <t>airbnb</t>
+        </is>
+      </c>
+      <c r="E461" t="inlineStr">
+        <is>
+          <t>2026-07-16T13:54:36.000Z</t>
+        </is>
+      </c>
+      <c r="F461" t="inlineStr">
+        <is>
+          <t>@mattymatheson is still nowhere to be found
+but the show must go on. So me and Matty’s
+lookalike go and meet some fans in Episode 14
+of Welcome Matt. #airbnbpartner</t>
+        </is>
+      </c>
+      <c r="G461" t="inlineStr">
+        <is>
+          <t>https://instagram.fagc1-1.fna.fbcdn.net/v/t51.82787-15/749566815_18611598736061235_1473618225108775931_n.jpg?stp=dst-jpg_e35_p1080x1080_sh2.08_tt6&amp;_nc_ht=instagram.fagc1-1.fna.fbcdn.net&amp;_nc_cat=103&amp;_nc_oc=Q6cZ2gEgE-TpUY8TcnNem4Is9S_WjPp6BEAhOJFXG7bmM_hthf7qRoaXU1O94SGNzQNjSes&amp;_nc_ohc=nrEGXmdGQb4Q7kNvwEPAZmU&amp;_nc_gid=CSfihGhbIPD2pv_NAlXzZw&amp;edm=ADp7STQBAAAA&amp;ccb=7-5&amp;oh=00_AQC7blcwRDWxDYgWSDK4LI_iUXVInKXTdKmuV4VQtYAb4Q&amp;oe=6A5FC9C9&amp;_nc_sid=c6f216</t>
+        </is>
+      </c>
+      <c r="H461" t="inlineStr">
+        <is>
+          <t>[easyocr not installed. Run 'pip install easyocr torch torchvision']</t>
+        </is>
+      </c>
+      <c r="I461" t="inlineStr">
+        <is>
+          <t>https://scontent-msp1-1.cdninstagram.com/o1/v/t2/f2/m86/AQPgDONR_xz0RpOKvm7rIIoXiVcoUS9YGpZadTGwOJRGRTptJb1q7CM_EzzfuOB3cDajbb4FSNzQd6TkDeJwIORAvS_8QXpIAEvXabQ.mp4?_nc_cat=102&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-msp1-1.cdninstagram.com&amp;_nc_ohc=mM7Hn8bjIn4Q7kNvwFFgI-3&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uQ0xJUFMuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTAyNzE0MDQyMDA3MTkyOSwiYXNzZXRfYWdlX2RheXMiOjAsInZpX3VzZWNhc2VfaWQiOjEwMDk5LCJkdXJhdGlvbl9zIjo5NiwidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=4f81413b7aeb1879&amp;_nc_vs=HBksFQIYUmlnX3hwdl9yZWVsc19wZXJtYW5lbnRfc3JfcHJvZC9GMDQ5N0U4RDREODE3QThBQjhEQUI5NTFFNkUwNkM4QV92aWRlb19kYXNoaW5pdC5tcDQVAALIARIAFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyL0FCNDcwOEZDQjU5OTQ0QkY0MjREMjA5NkZCNTVDQjgzX2F1ZGlvX2Rhc2hpbml0Lm1wNBUCAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbyx_u9uIvTAxUCKAJDMywXQFgqbpeNT98YEmRhc2hfYmFzZWxpbmVfMV92MREAdf4HZeadAQA&amp;_nc_gid=t-ySioe-h1eBQ7SjbN1skg&amp;_nc_ss=72a8c&amp;_nc_zt=28&amp;oh=00_AQAMiXB6GFEJwStQC6NakJ4LzfIziFmlOEknNYZb-L5qKw&amp;oe=6A5BD573</t>
+        </is>
+      </c>
+      <c r="J461" t="inlineStr">
+        <is>
+          <t>[faster-whisper not installed. Run 'pip install faster-whisper']</t>
+        </is>
+      </c>
+      <c r="K461" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Da2ys8ntHUj/</t>
+        </is>
+      </c>
+      <c r="L461" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M461" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N461" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O461" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>Expedia</t>
+        </is>
+      </c>
+      <c r="C462" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D462" t="inlineStr">
+        <is>
+          <t>Expedia</t>
+        </is>
+      </c>
+      <c r="E462" t="inlineStr">
+        <is>
+          <t>2026-07-16T17:39:01.487Z</t>
+        </is>
+      </c>
+      <c r="F462" t="inlineStr">
+        <is>
+          <t>Why is Croatia the ultimate summer destination? 🇭🇷
+➡️ Plitvice Lakes: Arrive early to walk the boardwalks past stunning waterfalls before the crowds.
+➡️ Island hopping: Swap busy Hvar for Vis to enjoy authentic fishing villages and hidden coves.
+➡️ Currency: Croatia now uses the Euro, making cross-border travel easier than ever.
+Find out more about Croatia here: http://ms.spr.ly/6040vIiNi</t>
+        </is>
+      </c>
+      <c r="G462" t="inlineStr">
+        <is>
+          <t>https://media.licdn.com/dms/image/v2/D4D10AQFa0LscHeiFSA/image-shrink_1280/B4DZ9pJx08JAAg-/0/1784175599374?e=1784890800&amp;v=beta&amp;t=FJfNRR8VjxiErxSqwRCtm3xxuq_yh1M10tmPqrYVqSU</t>
+        </is>
+      </c>
+      <c r="H462" t="inlineStr">
+        <is>
+          <t>[easyocr not installed. Run 'pip install easyocr torch torchvision']</t>
+        </is>
+      </c>
+      <c r="I462" t="inlineStr"/>
+      <c r="J462" t="inlineStr"/>
+      <c r="K462" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/expedia_why-is-croatia-the-ultimate-summer-destination-activity-7483575936953561088-kQBn</t>
+        </is>
+      </c>
+      <c r="L462" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M462" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N462" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O462" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C463" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D463" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E463" t="inlineStr">
+        <is>
+          <t>Fri Jul 17 10:40:37 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F463" t="inlineStr">
+        <is>
+          <t>@jvalsan_mp3 Sentimos que el filtro en nuestra plataforma no cumpla con tus expectativas al no ser posible filtrar por la hora de entrada ni de salida. Valoramos tu opinión porque nos ayuda a mejorar la calidad de nuestros servicios. 
+Un saludo.</t>
+        </is>
+      </c>
+      <c r="G463" t="inlineStr"/>
+      <c r="H463" t="inlineStr"/>
+      <c r="I463" t="inlineStr"/>
+      <c r="J463" t="inlineStr"/>
+      <c r="K463" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2078067341292609640</t>
+        </is>
+      </c>
+      <c r="L463" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M463" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N463" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O463" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C464" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D464" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E464" t="inlineStr">
+        <is>
+          <t>Fri Jul 17 10:31:26 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F464" t="inlineStr">
+        <is>
+          <t>@revedusud Hi there, thanks for reaching out to us. Our apologies for the late response.
+We've sent you a private message. Please check it at your earliest convenience.</t>
+        </is>
+      </c>
+      <c r="G464" t="inlineStr"/>
+      <c r="H464" t="inlineStr"/>
+      <c r="I464" t="inlineStr"/>
+      <c r="J464" t="inlineStr"/>
+      <c r="K464" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2078065031061643590</t>
+        </is>
+      </c>
+      <c r="L464" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M464" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N464" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O464" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C465" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D465" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E465" t="inlineStr">
+        <is>
+          <t>Fri Jul 17 10:20:10 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F465" t="inlineStr">
+        <is>
+          <t>@roalpeje Lo sentimos, Roberto. Esperamos que pronto tengas noticias.
+Saludos.</t>
+        </is>
+      </c>
+      <c r="G465" t="inlineStr"/>
+      <c r="H465" t="inlineStr"/>
+      <c r="I465" t="inlineStr"/>
+      <c r="J465" t="inlineStr"/>
+      <c r="K465" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2078062193023557652</t>
+        </is>
+      </c>
+      <c r="L465" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M465" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N465" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O465" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B466" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C466" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D466" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E466" t="inlineStr">
+        <is>
+          <t>Fri Jul 17 10:17:41 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F466" t="inlineStr">
+        <is>
+          <t>Agradecemos mucho tus comentarios, Carles, y que te hayas tomado el tiempo en compartirlos por este medio. Estos son muy valiosos para nosotros, ya que siempre nos ayudan a mejorar nuestros servicios y el funcionamiento de la plataforma misma.
+Si en el futuro, necesitas asistencia con alguna reserva, por favor no dudes en contactarnos. Que tengas un buen día.</t>
+        </is>
+      </c>
+      <c r="G466" t="inlineStr"/>
+      <c r="H466" t="inlineStr"/>
+      <c r="I466" t="inlineStr"/>
+      <c r="J466" t="inlineStr"/>
+      <c r="K466" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2078061569959772187</t>
+        </is>
+      </c>
+      <c r="L466" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M466" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N466" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O466" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C467" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="D467" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E467" t="inlineStr">
+        <is>
+          <t>2026-07-16T15:29:56.000Z</t>
+        </is>
+      </c>
+      <c r="F467" t="inlineStr">
+        <is>
+          <t>It’s so easy, even a teapot figured it out.</t>
+        </is>
+      </c>
+      <c r="G467" t="inlineStr">
+        <is>
+          <t>https://scontent-ord5-3.cdninstagram.com/v/t51.71878-15/748745802_1323295810017600_7815082476634872487_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_ht=scontent-ord5-3.cdninstagram.com&amp;_nc_cat=100&amp;_nc_oc=Q6cZ2gG3Y-_vAimcQZiESwdoldfUkSqlOQ6TLNpYHsbIe6aKUJWG9nP4l65IE6wNNqiOD5K_vplHTmQyBGu-_bOwmp5k&amp;_nc_ohc=8hc5mepczvsQ7kNvwEDsXZ6&amp;_nc_gid=Qhs5g9kmpeUfkqQFAenfvA&amp;edm=ADp7STQBAAAA&amp;ccb=7-5&amp;oh=00_AQBv3ZPlnzGB-INQP4i25SYdbRgqjH5NOtxrFPFEtvdkNA&amp;oe=6A5FF287&amp;_nc_sid=c6f216</t>
+        </is>
+      </c>
+      <c r="H467" t="inlineStr">
+        <is>
+          <t>[easyocr not installed. Run 'pip install easyocr torch torchvision']</t>
+        </is>
+      </c>
+      <c r="I467" t="inlineStr">
+        <is>
+          <t>https://instagram.fmem1-2.fna.fbcdn.net/o1/v/t2/f2/m86/AQNoqvLWgA3FZJHwOwTkp1GsGxGzuqQnJzDBFwW8qvCWyJK82A4J6sl5T156wC59Td2_jpShNrnXqEjfVYtIM9ws_dAPRtXAIA-n6nA.mp4?_nc_cat=102&amp;_nc_oc=Adprx1BuBnyMSh2FPvA0MnFRrI_12BgUZ96lVLyoYAL61-OWa7TyfUr3dPQNnus4IdykgXgj4KREpkgPebquYqzI&amp;_nc_sid=5e9851&amp;_nc_ht=instagram.fmem1-2.fna.fbcdn.net&amp;_nc_ohc=_Sa6BEPlaJUQ7kNvwGBDag_&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uQ0xJUFMuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MzA4NTY5ODkyNDk3MzIzMSwiYXNzZXRfYWdlX2RheXMiOjAsInZpX3VzZWNhc2VfaWQiOjEwMDk5LCJkdXJhdGlvbl9zIjozMiwidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=5030272038583226&amp;_nc_vs=HBksFQIYUmlnX3hwdl9yZWVsc19wZXJtYW5lbnRfc3JfcHJvZC9BNzRDNEVDOEJFNzMyQkQ0MTdEOUM5QjJFRDNGQTk4RV92aWRlb19kYXNoaW5pdC5tcDQVAALIARIAFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyL0EyNEZGRjQwQzk5RTQ2OUE1NjhERDY0ODREQTc3QTlCX2F1ZGlvX2Rhc2hpbml0Lm1wNBUCAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbesvTEqJv7ChUCKAJDMywXQEARBiTdLxsYEmRhc2hfYmFzZWxpbmVfMV92MREAdf4HZeadAQA&amp;_nc_gid=D7kwO63AcdHvRQXWynG4gw&amp;_nc_ss=72689&amp;_nc_map=urlgen_bucketless&amp;_nc_zt=28&amp;oh=00_AQCaVjyJOg_nb7fMot1nxSe1sFQz8_Hn2DfenA3tctcY9A&amp;oe=6A5C025B</t>
+        </is>
+      </c>
+      <c r="J467" t="inlineStr">
+        <is>
+          <t>[faster-whisper not installed. Run 'pip install faster-whisper']</t>
+        </is>
+      </c>
+      <c r="K467" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Da29pUptA2J/</t>
+        </is>
+      </c>
+      <c r="L467" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M467" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N467" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O467" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/News_Dashboard/data/social_media_posts.xlsx
+++ b/News_Dashboard/data/social_media_posts.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O467"/>
+  <dimension ref="A1:O460"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29414,484 +29414,6 @@
         </is>
       </c>
     </row>
-    <row r="461">
-      <c r="A461" t="inlineStr">
-        <is>
-          <t>Abhee</t>
-        </is>
-      </c>
-      <c r="B461" t="inlineStr">
-        <is>
-          <t>AirBnb</t>
-        </is>
-      </c>
-      <c r="C461" t="inlineStr">
-        <is>
-          <t>Instagram</t>
-        </is>
-      </c>
-      <c r="D461" t="inlineStr">
-        <is>
-          <t>airbnb</t>
-        </is>
-      </c>
-      <c r="E461" t="inlineStr">
-        <is>
-          <t>2026-07-16T13:54:36.000Z</t>
-        </is>
-      </c>
-      <c r="F461" t="inlineStr">
-        <is>
-          <t>@mattymatheson is still nowhere to be found
-but the show must go on. So me and Matty’s
-lookalike go and meet some fans in Episode 14
-of Welcome Matt. #airbnbpartner</t>
-        </is>
-      </c>
-      <c r="G461" t="inlineStr">
-        <is>
-          <t>https://instagram.fagc1-1.fna.fbcdn.net/v/t51.82787-15/749566815_18611598736061235_1473618225108775931_n.jpg?stp=dst-jpg_e35_p1080x1080_sh2.08_tt6&amp;_nc_ht=instagram.fagc1-1.fna.fbcdn.net&amp;_nc_cat=103&amp;_nc_oc=Q6cZ2gEgE-TpUY8TcnNem4Is9S_WjPp6BEAhOJFXG7bmM_hthf7qRoaXU1O94SGNzQNjSes&amp;_nc_ohc=nrEGXmdGQb4Q7kNvwEPAZmU&amp;_nc_gid=CSfihGhbIPD2pv_NAlXzZw&amp;edm=ADp7STQBAAAA&amp;ccb=7-5&amp;oh=00_AQC7blcwRDWxDYgWSDK4LI_iUXVInKXTdKmuV4VQtYAb4Q&amp;oe=6A5FC9C9&amp;_nc_sid=c6f216</t>
-        </is>
-      </c>
-      <c r="H461" t="inlineStr">
-        <is>
-          <t>[easyocr not installed. Run 'pip install easyocr torch torchvision']</t>
-        </is>
-      </c>
-      <c r="I461" t="inlineStr">
-        <is>
-          <t>https://scontent-msp1-1.cdninstagram.com/o1/v/t2/f2/m86/AQPgDONR_xz0RpOKvm7rIIoXiVcoUS9YGpZadTGwOJRGRTptJb1q7CM_EzzfuOB3cDajbb4FSNzQd6TkDeJwIORAvS_8QXpIAEvXabQ.mp4?_nc_cat=102&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-msp1-1.cdninstagram.com&amp;_nc_ohc=mM7Hn8bjIn4Q7kNvwFFgI-3&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uQ0xJUFMuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTAyNzE0MDQyMDA3MTkyOSwiYXNzZXRfYWdlX2RheXMiOjAsInZpX3VzZWNhc2VfaWQiOjEwMDk5LCJkdXJhdGlvbl9zIjo5NiwidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=4f81413b7aeb1879&amp;_nc_vs=HBksFQIYUmlnX3hwdl9yZWVsc19wZXJtYW5lbnRfc3JfcHJvZC9GMDQ5N0U4RDREODE3QThBQjhEQUI5NTFFNkUwNkM4QV92aWRlb19kYXNoaW5pdC5tcDQVAALIARIAFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyL0FCNDcwOEZDQjU5OTQ0QkY0MjREMjA5NkZCNTVDQjgzX2F1ZGlvX2Rhc2hpbml0Lm1wNBUCAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbyx_u9uIvTAxUCKAJDMywXQFgqbpeNT98YEmRhc2hfYmFzZWxpbmVfMV92MREAdf4HZeadAQA&amp;_nc_gid=t-ySioe-h1eBQ7SjbN1skg&amp;_nc_ss=72a8c&amp;_nc_zt=28&amp;oh=00_AQAMiXB6GFEJwStQC6NakJ4LzfIziFmlOEknNYZb-L5qKw&amp;oe=6A5BD573</t>
-        </is>
-      </c>
-      <c r="J461" t="inlineStr">
-        <is>
-          <t>[faster-whisper not installed. Run 'pip install faster-whisper']</t>
-        </is>
-      </c>
-      <c r="K461" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/Da2ys8ntHUj/</t>
-        </is>
-      </c>
-      <c r="L461" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="M461" t="inlineStr">
-        <is>
-          <t>General Industry News</t>
-        </is>
-      </c>
-      <c r="N461" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="O461" t="inlineStr">
-        <is>
-          <t>Failed to analyze post via LLM.</t>
-        </is>
-      </c>
-    </row>
-    <row r="462">
-      <c r="A462" t="inlineStr">
-        <is>
-          <t>Abhee</t>
-        </is>
-      </c>
-      <c r="B462" t="inlineStr">
-        <is>
-          <t>Expedia</t>
-        </is>
-      </c>
-      <c r="C462" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D462" t="inlineStr">
-        <is>
-          <t>Expedia</t>
-        </is>
-      </c>
-      <c r="E462" t="inlineStr">
-        <is>
-          <t>2026-07-16T17:39:01.487Z</t>
-        </is>
-      </c>
-      <c r="F462" t="inlineStr">
-        <is>
-          <t>Why is Croatia the ultimate summer destination? 🇭🇷
-➡️ Plitvice Lakes: Arrive early to walk the boardwalks past stunning waterfalls before the crowds.
-➡️ Island hopping: Swap busy Hvar for Vis to enjoy authentic fishing villages and hidden coves.
-➡️ Currency: Croatia now uses the Euro, making cross-border travel easier than ever.
-Find out more about Croatia here: http://ms.spr.ly/6040vIiNi</t>
-        </is>
-      </c>
-      <c r="G462" t="inlineStr">
-        <is>
-          <t>https://media.licdn.com/dms/image/v2/D4D10AQFa0LscHeiFSA/image-shrink_1280/B4DZ9pJx08JAAg-/0/1784175599374?e=1784890800&amp;v=beta&amp;t=FJfNRR8VjxiErxSqwRCtm3xxuq_yh1M10tmPqrYVqSU</t>
-        </is>
-      </c>
-      <c r="H462" t="inlineStr">
-        <is>
-          <t>[easyocr not installed. Run 'pip install easyocr torch torchvision']</t>
-        </is>
-      </c>
-      <c r="I462" t="inlineStr"/>
-      <c r="J462" t="inlineStr"/>
-      <c r="K462" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/posts/expedia_why-is-croatia-the-ultimate-summer-destination-activity-7483575936953561088-kQBn</t>
-        </is>
-      </c>
-      <c r="L462" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="M462" t="inlineStr">
-        <is>
-          <t>General Industry News</t>
-        </is>
-      </c>
-      <c r="N462" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="O462" t="inlineStr">
-        <is>
-          <t>Failed to analyze post via LLM.</t>
-        </is>
-      </c>
-    </row>
-    <row r="463">
-      <c r="A463" t="inlineStr">
-        <is>
-          <t>Abhee</t>
-        </is>
-      </c>
-      <c r="B463" t="inlineStr">
-        <is>
-          <t>Booking.com</t>
-        </is>
-      </c>
-      <c r="C463" t="inlineStr">
-        <is>
-          <t>X (Twitter)</t>
-        </is>
-      </c>
-      <c r="D463" t="inlineStr">
-        <is>
-          <t>bookingcom</t>
-        </is>
-      </c>
-      <c r="E463" t="inlineStr">
-        <is>
-          <t>Fri Jul 17 10:40:37 +0000 2026</t>
-        </is>
-      </c>
-      <c r="F463" t="inlineStr">
-        <is>
-          <t>@jvalsan_mp3 Sentimos que el filtro en nuestra plataforma no cumpla con tus expectativas al no ser posible filtrar por la hora de entrada ni de salida. Valoramos tu opinión porque nos ayuda a mejorar la calidad de nuestros servicios. 
-Un saludo.</t>
-        </is>
-      </c>
-      <c r="G463" t="inlineStr"/>
-      <c r="H463" t="inlineStr"/>
-      <c r="I463" t="inlineStr"/>
-      <c r="J463" t="inlineStr"/>
-      <c r="K463" t="inlineStr">
-        <is>
-          <t>https://x.com/bookingcom/status/2078067341292609640</t>
-        </is>
-      </c>
-      <c r="L463" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="M463" t="inlineStr">
-        <is>
-          <t>General Industry News</t>
-        </is>
-      </c>
-      <c r="N463" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="O463" t="inlineStr">
-        <is>
-          <t>Failed to analyze post via LLM.</t>
-        </is>
-      </c>
-    </row>
-    <row r="464">
-      <c r="A464" t="inlineStr">
-        <is>
-          <t>Abhee</t>
-        </is>
-      </c>
-      <c r="B464" t="inlineStr">
-        <is>
-          <t>Booking.com</t>
-        </is>
-      </c>
-      <c r="C464" t="inlineStr">
-        <is>
-          <t>X (Twitter)</t>
-        </is>
-      </c>
-      <c r="D464" t="inlineStr">
-        <is>
-          <t>bookingcom</t>
-        </is>
-      </c>
-      <c r="E464" t="inlineStr">
-        <is>
-          <t>Fri Jul 17 10:31:26 +0000 2026</t>
-        </is>
-      </c>
-      <c r="F464" t="inlineStr">
-        <is>
-          <t>@revedusud Hi there, thanks for reaching out to us. Our apologies for the late response.
-We've sent you a private message. Please check it at your earliest convenience.</t>
-        </is>
-      </c>
-      <c r="G464" t="inlineStr"/>
-      <c r="H464" t="inlineStr"/>
-      <c r="I464" t="inlineStr"/>
-      <c r="J464" t="inlineStr"/>
-      <c r="K464" t="inlineStr">
-        <is>
-          <t>https://x.com/bookingcom/status/2078065031061643590</t>
-        </is>
-      </c>
-      <c r="L464" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="M464" t="inlineStr">
-        <is>
-          <t>General Industry News</t>
-        </is>
-      </c>
-      <c r="N464" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="O464" t="inlineStr">
-        <is>
-          <t>Failed to analyze post via LLM.</t>
-        </is>
-      </c>
-    </row>
-    <row r="465">
-      <c r="A465" t="inlineStr">
-        <is>
-          <t>Abhee</t>
-        </is>
-      </c>
-      <c r="B465" t="inlineStr">
-        <is>
-          <t>Booking.com</t>
-        </is>
-      </c>
-      <c r="C465" t="inlineStr">
-        <is>
-          <t>X (Twitter)</t>
-        </is>
-      </c>
-      <c r="D465" t="inlineStr">
-        <is>
-          <t>bookingcom</t>
-        </is>
-      </c>
-      <c r="E465" t="inlineStr">
-        <is>
-          <t>Fri Jul 17 10:20:10 +0000 2026</t>
-        </is>
-      </c>
-      <c r="F465" t="inlineStr">
-        <is>
-          <t>@roalpeje Lo sentimos, Roberto. Esperamos que pronto tengas noticias.
-Saludos.</t>
-        </is>
-      </c>
-      <c r="G465" t="inlineStr"/>
-      <c r="H465" t="inlineStr"/>
-      <c r="I465" t="inlineStr"/>
-      <c r="J465" t="inlineStr"/>
-      <c r="K465" t="inlineStr">
-        <is>
-          <t>https://x.com/bookingcom/status/2078062193023557652</t>
-        </is>
-      </c>
-      <c r="L465" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="M465" t="inlineStr">
-        <is>
-          <t>General Industry News</t>
-        </is>
-      </c>
-      <c r="N465" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="O465" t="inlineStr">
-        <is>
-          <t>Failed to analyze post via LLM.</t>
-        </is>
-      </c>
-    </row>
-    <row r="466">
-      <c r="A466" t="inlineStr">
-        <is>
-          <t>Abhee</t>
-        </is>
-      </c>
-      <c r="B466" t="inlineStr">
-        <is>
-          <t>Booking.com</t>
-        </is>
-      </c>
-      <c r="C466" t="inlineStr">
-        <is>
-          <t>X (Twitter)</t>
-        </is>
-      </c>
-      <c r="D466" t="inlineStr">
-        <is>
-          <t>bookingcom</t>
-        </is>
-      </c>
-      <c r="E466" t="inlineStr">
-        <is>
-          <t>Fri Jul 17 10:17:41 +0000 2026</t>
-        </is>
-      </c>
-      <c r="F466" t="inlineStr">
-        <is>
-          <t>Agradecemos mucho tus comentarios, Carles, y que te hayas tomado el tiempo en compartirlos por este medio. Estos son muy valiosos para nosotros, ya que siempre nos ayudan a mejorar nuestros servicios y el funcionamiento de la plataforma misma.
-Si en el futuro, necesitas asistencia con alguna reserva, por favor no dudes en contactarnos. Que tengas un buen día.</t>
-        </is>
-      </c>
-      <c r="G466" t="inlineStr"/>
-      <c r="H466" t="inlineStr"/>
-      <c r="I466" t="inlineStr"/>
-      <c r="J466" t="inlineStr"/>
-      <c r="K466" t="inlineStr">
-        <is>
-          <t>https://x.com/bookingcom/status/2078061569959772187</t>
-        </is>
-      </c>
-      <c r="L466" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="M466" t="inlineStr">
-        <is>
-          <t>General Industry News</t>
-        </is>
-      </c>
-      <c r="N466" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="O466" t="inlineStr">
-        <is>
-          <t>Failed to analyze post via LLM.</t>
-        </is>
-      </c>
-    </row>
-    <row r="467">
-      <c r="A467" t="inlineStr">
-        <is>
-          <t>Abhee</t>
-        </is>
-      </c>
-      <c r="B467" t="inlineStr">
-        <is>
-          <t>Booking.com</t>
-        </is>
-      </c>
-      <c r="C467" t="inlineStr">
-        <is>
-          <t>Instagram</t>
-        </is>
-      </c>
-      <c r="D467" t="inlineStr">
-        <is>
-          <t>bookingcom</t>
-        </is>
-      </c>
-      <c r="E467" t="inlineStr">
-        <is>
-          <t>2026-07-16T15:29:56.000Z</t>
-        </is>
-      </c>
-      <c r="F467" t="inlineStr">
-        <is>
-          <t>It’s so easy, even a teapot figured it out.</t>
-        </is>
-      </c>
-      <c r="G467" t="inlineStr">
-        <is>
-          <t>https://scontent-ord5-3.cdninstagram.com/v/t51.71878-15/748745802_1323295810017600_7815082476634872487_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_ht=scontent-ord5-3.cdninstagram.com&amp;_nc_cat=100&amp;_nc_oc=Q6cZ2gG3Y-_vAimcQZiESwdoldfUkSqlOQ6TLNpYHsbIe6aKUJWG9nP4l65IE6wNNqiOD5K_vplHTmQyBGu-_bOwmp5k&amp;_nc_ohc=8hc5mepczvsQ7kNvwEDsXZ6&amp;_nc_gid=Qhs5g9kmpeUfkqQFAenfvA&amp;edm=ADp7STQBAAAA&amp;ccb=7-5&amp;oh=00_AQBv3ZPlnzGB-INQP4i25SYdbRgqjH5NOtxrFPFEtvdkNA&amp;oe=6A5FF287&amp;_nc_sid=c6f216</t>
-        </is>
-      </c>
-      <c r="H467" t="inlineStr">
-        <is>
-          <t>[easyocr not installed. Run 'pip install easyocr torch torchvision']</t>
-        </is>
-      </c>
-      <c r="I467" t="inlineStr">
-        <is>
-          <t>https://instagram.fmem1-2.fna.fbcdn.net/o1/v/t2/f2/m86/AQNoqvLWgA3FZJHwOwTkp1GsGxGzuqQnJzDBFwW8qvCWyJK82A4J6sl5T156wC59Td2_jpShNrnXqEjfVYtIM9ws_dAPRtXAIA-n6nA.mp4?_nc_cat=102&amp;_nc_oc=Adprx1BuBnyMSh2FPvA0MnFRrI_12BgUZ96lVLyoYAL61-OWa7TyfUr3dPQNnus4IdykgXgj4KREpkgPebquYqzI&amp;_nc_sid=5e9851&amp;_nc_ht=instagram.fmem1-2.fna.fbcdn.net&amp;_nc_ohc=_Sa6BEPlaJUQ7kNvwGBDag_&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uQ0xJUFMuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MzA4NTY5ODkyNDk3MzIzMSwiYXNzZXRfYWdlX2RheXMiOjAsInZpX3VzZWNhc2VfaWQiOjEwMDk5LCJkdXJhdGlvbl9zIjozMiwidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=5030272038583226&amp;_nc_vs=HBksFQIYUmlnX3hwdl9yZWVsc19wZXJtYW5lbnRfc3JfcHJvZC9BNzRDNEVDOEJFNzMyQkQ0MTdEOUM5QjJFRDNGQTk4RV92aWRlb19kYXNoaW5pdC5tcDQVAALIARIAFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyL0EyNEZGRjQwQzk5RTQ2OUE1NjhERDY0ODREQTc3QTlCX2F1ZGlvX2Rhc2hpbml0Lm1wNBUCAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbesvTEqJv7ChUCKAJDMywXQEARBiTdLxsYEmRhc2hfYmFzZWxpbmVfMV92MREAdf4HZeadAQA&amp;_nc_gid=D7kwO63AcdHvRQXWynG4gw&amp;_nc_ss=72689&amp;_nc_map=urlgen_bucketless&amp;_nc_zt=28&amp;oh=00_AQCaVjyJOg_nb7fMot1nxSe1sFQz8_Hn2DfenA3tctcY9A&amp;oe=6A5C025B</t>
-        </is>
-      </c>
-      <c r="J467" t="inlineStr">
-        <is>
-          <t>[faster-whisper not installed. Run 'pip install faster-whisper']</t>
-        </is>
-      </c>
-      <c r="K467" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/Da29pUptA2J/</t>
-        </is>
-      </c>
-      <c r="L467" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="M467" t="inlineStr">
-        <is>
-          <t>General Industry News</t>
-        </is>
-      </c>
-      <c r="N467" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="O467" t="inlineStr">
-        <is>
-          <t>Failed to analyze post via LLM.</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/News_Dashboard/data/social_media_posts.xlsx
+++ b/News_Dashboard/data/social_media_posts.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O460"/>
+  <dimension ref="A1:O467"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29414,6 +29414,453 @@
         </is>
       </c>
     </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>Expedia</t>
+        </is>
+      </c>
+      <c r="C461" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D461" t="inlineStr">
+        <is>
+          <t>Expedia</t>
+        </is>
+      </c>
+      <c r="E461" t="inlineStr">
+        <is>
+          <t>2026-07-16T17:39:01.487Z</t>
+        </is>
+      </c>
+      <c r="F461" t="inlineStr">
+        <is>
+          <t>Why is Croatia the ultimate summer destination? 🇭🇷
+➡️ Plitvice Lakes: Arrive early to walk the boardwalks past stunning waterfalls before the crowds.
+➡️ Island hopping: Swap busy Hvar for Vis to enjoy authentic fishing villages and hidden coves.
+➡️ Currency: Croatia now uses the Euro, making cross-border travel easier than ever.
+Find out more about Croatia here: http://ms.spr.ly/6040vIiNi</t>
+        </is>
+      </c>
+      <c r="G461" t="inlineStr">
+        <is>
+          <t>https://media.licdn.com/dms/image/v2/D4D10AQFa0LscHeiFSA/image-shrink_1280/B4DZ9pJx08JAAg-/0/1784175599374?e=1784898000&amp;v=beta&amp;t=3ZvTGDsTmIgwRWuCeveMDNftNT2Tazj1GCbqETgT2S4</t>
+        </is>
+      </c>
+      <c r="H461" t="inlineStr">
+        <is>
+          <t>[easyocr not installed. Run 'pip install easyocr torch torchvision']</t>
+        </is>
+      </c>
+      <c r="I461" t="inlineStr"/>
+      <c r="J461" t="inlineStr"/>
+      <c r="K461" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/expedia_why-is-croatia-the-ultimate-summer-destination-activity-7483575936953561088-kQBn</t>
+        </is>
+      </c>
+      <c r="L461" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M461" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N461" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O461" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C462" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D462" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E462" t="inlineStr">
+        <is>
+          <t>Fri Jul 17 11:52:00 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F462" t="inlineStr">
+        <is>
+          <t>Hi there, we regret to hear the property wasn’t able to accommodate you. On https://t.co/fGhmZE7riF, room availability is managed directly by the property, and they’re responsible for keeping it accurate. 
+If a property can’t honor a booking, they should help you find an alternative place to stay. If they’re unable or unwilling to do so, they should inform us as soon as possible so we can help find a solution. Please send a private message with the following details:
+- Pin code:
+- Name on the reservation:
+Alternatively, for immediate support you can always give us a call here: https://t.co/o8QyR8SaDb</t>
+        </is>
+      </c>
+      <c r="G462" t="inlineStr"/>
+      <c r="H462" t="inlineStr"/>
+      <c r="I462" t="inlineStr"/>
+      <c r="J462" t="inlineStr"/>
+      <c r="K462" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2078085307304497427</t>
+        </is>
+      </c>
+      <c r="L462" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M462" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N462" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O462" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C463" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D463" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E463" t="inlineStr">
+        <is>
+          <t>Fri Jul 17 11:34:30 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F463" t="inlineStr">
+        <is>
+          <t>@sreeee0 Hi there, we understand your concern and have just DMed you back. Please, check. Thank you.</t>
+        </is>
+      </c>
+      <c r="G463" t="inlineStr"/>
+      <c r="H463" t="inlineStr"/>
+      <c r="I463" t="inlineStr"/>
+      <c r="J463" t="inlineStr"/>
+      <c r="K463" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2078080900877730171</t>
+        </is>
+      </c>
+      <c r="L463" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M463" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N463" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O463" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C464" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D464" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E464" t="inlineStr">
+        <is>
+          <t>Fri Jul 17 10:40:37 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F464" t="inlineStr">
+        <is>
+          <t>@jvalsan_mp3 Sentimos que el filtro en nuestra plataforma no cumpla con tus expectativas al no ser posible filtrar por la hora de entrada ni de salida. Valoramos tu opinión porque nos ayuda a mejorar la calidad de nuestros servicios. 
+Un saludo.</t>
+        </is>
+      </c>
+      <c r="G464" t="inlineStr"/>
+      <c r="H464" t="inlineStr"/>
+      <c r="I464" t="inlineStr"/>
+      <c r="J464" t="inlineStr"/>
+      <c r="K464" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2078067341292609640</t>
+        </is>
+      </c>
+      <c r="L464" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M464" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N464" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O464" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C465" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D465" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E465" t="inlineStr">
+        <is>
+          <t>Fri Jul 17 10:31:26 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F465" t="inlineStr">
+        <is>
+          <t>@revedusud Hi there, thanks for reaching out to us. Our apologies for the late response.
+We've sent you a private message. Please check it at your earliest convenience.</t>
+        </is>
+      </c>
+      <c r="G465" t="inlineStr"/>
+      <c r="H465" t="inlineStr"/>
+      <c r="I465" t="inlineStr"/>
+      <c r="J465" t="inlineStr"/>
+      <c r="K465" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2078065031061643590</t>
+        </is>
+      </c>
+      <c r="L465" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M465" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N465" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O465" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B466" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C466" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D466" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E466" t="inlineStr">
+        <is>
+          <t>Fri Jul 17 10:20:10 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F466" t="inlineStr">
+        <is>
+          <t>@roalpeje Lo sentimos, Roberto. Esperamos que pronto tengas noticias.
+Saludos.</t>
+        </is>
+      </c>
+      <c r="G466" t="inlineStr"/>
+      <c r="H466" t="inlineStr"/>
+      <c r="I466" t="inlineStr"/>
+      <c r="J466" t="inlineStr"/>
+      <c r="K466" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2078062193023557652</t>
+        </is>
+      </c>
+      <c r="L466" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M466" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N466" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O466" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C467" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D467" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E467" t="inlineStr">
+        <is>
+          <t>Fri Jul 17 10:17:41 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F467" t="inlineStr">
+        <is>
+          <t>Agradecemos mucho tus comentarios, Carles, y que te hayas tomado el tiempo en compartirlos por este medio. Estos son muy valiosos para nosotros, ya que siempre nos ayudan a mejorar nuestros servicios y el funcionamiento de la plataforma misma.
+Si en el futuro, necesitas asistencia con alguna reserva, por favor no dudes en contactarnos. Que tengas un buen día.</t>
+        </is>
+      </c>
+      <c r="G467" t="inlineStr"/>
+      <c r="H467" t="inlineStr"/>
+      <c r="I467" t="inlineStr"/>
+      <c r="J467" t="inlineStr"/>
+      <c r="K467" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2078061569959772187</t>
+        </is>
+      </c>
+      <c r="L467" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M467" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N467" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O467" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/News_Dashboard/data/social_media_posts.xlsx
+++ b/News_Dashboard/data/social_media_posts.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O467"/>
+  <dimension ref="A1:O490"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29861,6 +29861,1437 @@
         </is>
       </c>
     </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B468" t="inlineStr">
+        <is>
+          <t>Brex</t>
+        </is>
+      </c>
+      <c r="C468" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D468" t="inlineStr">
+        <is>
+          <t>brexhq</t>
+        </is>
+      </c>
+      <c r="E468" t="inlineStr">
+        <is>
+          <t>Sun Jul 19 21:49:23 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F468" t="inlineStr">
+        <is>
+          <t>Watch party goal(s) https://t.co/xKBnM9na2G</t>
+        </is>
+      </c>
+      <c r="G468" t="inlineStr"/>
+      <c r="H468" t="inlineStr"/>
+      <c r="I468" t="inlineStr"/>
+      <c r="J468" t="inlineStr"/>
+      <c r="K468" t="inlineStr">
+        <is>
+          <t>https://x.com/brexHQ/status/2078960415850025252</t>
+        </is>
+      </c>
+      <c r="L468" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M468" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N468" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O468" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>Brex</t>
+        </is>
+      </c>
+      <c r="C469" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D469" t="inlineStr">
+        <is>
+          <t>brexhq</t>
+        </is>
+      </c>
+      <c r="E469" t="inlineStr">
+        <is>
+          <t>Sun Jul 19 19:32:45 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F469" t="inlineStr">
+        <is>
+          <t>Spain or Argentina?
+📍Finance On Offense Finals Watch Party https://t.co/uQcqAFCsyh</t>
+        </is>
+      </c>
+      <c r="G469" t="inlineStr"/>
+      <c r="H469" t="inlineStr"/>
+      <c r="I469" t="inlineStr"/>
+      <c r="J469" t="inlineStr"/>
+      <c r="K469" t="inlineStr">
+        <is>
+          <t>https://x.com/brexHQ/status/2078926032279568482</t>
+        </is>
+      </c>
+      <c r="L469" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M469" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N469" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O469" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B470" t="inlineStr">
+        <is>
+          <t>AirBnb</t>
+        </is>
+      </c>
+      <c r="C470" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="D470" t="inlineStr">
+        <is>
+          <t>airbnb</t>
+        </is>
+      </c>
+      <c r="E470" t="inlineStr">
+        <is>
+          <t>2026-07-20T02:27:09.000Z</t>
+        </is>
+      </c>
+      <c r="F470" t="inlineStr">
+        <is>
+          <t>⭐⭐🇪🇸 What an epic finale to an incredible Copa Mundial de la FIFA™ – it kinda makes us want to celebrate with a copa de horchata española. Which reminds us: it’s never too late to GOOO(AL) to Spain! Felicidades, España – on an incredible win.</t>
+        </is>
+      </c>
+      <c r="G470" t="inlineStr">
+        <is>
+          <t>https://scontent-phx1-1.cdninstagram.com/v/t51.82787-15/743163821_18615191725063838_4176267332975842659_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk0NTExNDQxMzQ4NTM4NDY0Ng%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuNzIwLnNkci52aWRlb19kZWZhdWx0X2NvdmVyX2ZyYW1lLkMzIn0%3D&amp;_nc_ohc=0UllLJ1UblwQ7kNvwHCavqF&amp;_nc_oc=AdrNQv5w2Jn9kq7tMNupVEwxqG-58qCiBXnQVTf4tFFyt6sSRUYc_wroGMqJLNVMnqwAj1828YCCiOK7jpkV-9NH&amp;_nc_zt=23&amp;_nc_ht=scontent-phx1-1.cdninstagram.com&amp;_nc_gid=t07faA086sKy4MVqWYOWaA&amp;_nc_ss=72689&amp;oh=00_AQB8--WSe5cIEeyEw-Ns-YstkQH5t9tVPjLBHYFMBdBJwA&amp;oe=6A63E121</t>
+        </is>
+      </c>
+      <c r="H470" t="inlineStr">
+        <is>
+          <t>[easyocr not installed. Run 'pip install easyocr torch torchvision']</t>
+        </is>
+      </c>
+      <c r="I470" t="inlineStr"/>
+      <c r="J470" t="inlineStr"/>
+      <c r="K470" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Da_3ZUnEWip/</t>
+        </is>
+      </c>
+      <c r="L470" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M470" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N470" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O470" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C471" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D471" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E471" t="inlineStr">
+        <is>
+          <t>Mon Jul 20 12:21:16 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F471" t="inlineStr">
+        <is>
+          <t>@lindtchocol8 For security purposes, we are unable to offer support to our partners via social media. However, you can find the contact information for our Partner Support team here: https://t.co/N4c4HTAv4f?</t>
+        </is>
+      </c>
+      <c r="G471" t="inlineStr"/>
+      <c r="H471" t="inlineStr"/>
+      <c r="I471" t="inlineStr"/>
+      <c r="J471" t="inlineStr"/>
+      <c r="K471" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2079179833469214819</t>
+        </is>
+      </c>
+      <c r="L471" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M471" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N471" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O471" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C472" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D472" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E472" t="inlineStr">
+        <is>
+          <t>Mon Jul 20 12:19:07 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F472" t="inlineStr">
+        <is>
+          <t>Hey Mmohamed, we regret to hear of the situation and understand the inconvenience with awaiting confrimation.  
+While we appreciate you messaging us here, we're unable to assist with flight reservations through social media, but if you need support, you can contact our Flights team using this link: 
+* https://t.co/OVuF5pCzba
+or by calling either: {US}+1 917 421 7240 / {UK}+44 2039019061 / {IE}+353 19075677
+They will be able to review and address any questions you may have. 
+Many thanks.</t>
+        </is>
+      </c>
+      <c r="G472" t="inlineStr"/>
+      <c r="H472" t="inlineStr"/>
+      <c r="I472" t="inlineStr"/>
+      <c r="J472" t="inlineStr"/>
+      <c r="K472" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2079179292689207629</t>
+        </is>
+      </c>
+      <c r="L472" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M472" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N472" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O472" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C473" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D473" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E473" t="inlineStr">
+        <is>
+          <t>Mon Jul 20 12:11:49 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F473" t="inlineStr">
+        <is>
+          <t>Hello, we regret to learn about your pending refund. While we would like to help, as stated in our earlier message, we cannot assist with flight reservations via social media. Due to GDPR regulations, only our dedicated team has access to your information and the necessary tools to provide assistance. You can reach our Flights team here: https://t.co/TBejpc4vOA, or contact call US +1 917 421 7240 / UK +44 2039019061 / IE +353 19075677. Best regards.</t>
+        </is>
+      </c>
+      <c r="G473" t="inlineStr"/>
+      <c r="H473" t="inlineStr"/>
+      <c r="I473" t="inlineStr"/>
+      <c r="J473" t="inlineStr"/>
+      <c r="K473" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2079177457958035841</t>
+        </is>
+      </c>
+      <c r="L473" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M473" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N473" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O473" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C474" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D474" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E474" t="inlineStr">
+        <is>
+          <t>Mon Jul 20 12:06:33 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F474" t="inlineStr">
+        <is>
+          <t>Hi Lorand, 
+we regret to learn you opinion on our services.
+While we appreciate that you have reached out to us here, we are, unfortunately, unable to help via Social Media. Your inquiry can only be addressed directly with our specialized team at the previously shared details.  
+Best regards</t>
+        </is>
+      </c>
+      <c r="G474" t="inlineStr"/>
+      <c r="H474" t="inlineStr"/>
+      <c r="I474" t="inlineStr"/>
+      <c r="J474" t="inlineStr"/>
+      <c r="K474" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2079176129009643897</t>
+        </is>
+      </c>
+      <c r="L474" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M474" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N474" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O474" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C475" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D475" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E475" t="inlineStr">
+        <is>
+          <t>Mon Jul 20 11:58:30 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F475" t="inlineStr">
+        <is>
+          <t>@lakshaysharma30 Hello, Lakshay, we regret learning about this situation. We see that we have already been in contact with Jagriti for more details, and if you were in the same reservation, then we can continue through her profile to avoid any confusion.</t>
+        </is>
+      </c>
+      <c r="G475" t="inlineStr"/>
+      <c r="H475" t="inlineStr"/>
+      <c r="I475" t="inlineStr"/>
+      <c r="J475" t="inlineStr"/>
+      <c r="K475" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2079174104926634401</t>
+        </is>
+      </c>
+      <c r="L475" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M475" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N475" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O475" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C476" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D476" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E476" t="inlineStr">
+        <is>
+          <t>Mon Jul 20 11:46:27 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F476" t="inlineStr">
+        <is>
+          <t>@cansinoroyal Lo sentimos. Respondimos tu mensaje privado.
+Saludos.</t>
+        </is>
+      </c>
+      <c r="G476" t="inlineStr"/>
+      <c r="H476" t="inlineStr"/>
+      <c r="I476" t="inlineStr"/>
+      <c r="J476" t="inlineStr"/>
+      <c r="K476" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2079171074382545072</t>
+        </is>
+      </c>
+      <c r="L476" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M476" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N476" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O476" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C477" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D477" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E477" t="inlineStr">
+        <is>
+          <t>Mon Jul 20 11:35:27 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F477" t="inlineStr">
+        <is>
+          <t>Hi Sasha, we regret to hear about your concerns. Unfortunately, we are unable to transfer your case to a supervisor through this channel. If you'd like to speak to one, you can reach out to our customer service team here: https://t.co/o8QyR8SaDb, and request to speak to one. Alternatively, we'd be happy to look into what happened through social media. To proceed, kindly send us a DM with the following details:
+-email address associated with your account
+-the full name of the person reaching out to us
+And we'll get back to you as soon as possible.</t>
+        </is>
+      </c>
+      <c r="G477" t="inlineStr"/>
+      <c r="H477" t="inlineStr"/>
+      <c r="I477" t="inlineStr"/>
+      <c r="J477" t="inlineStr"/>
+      <c r="K477" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2079168303491174768</t>
+        </is>
+      </c>
+      <c r="L477" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M477" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N477" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O477" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B478" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C478" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D478" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E478" t="inlineStr">
+        <is>
+          <t>Mon Jul 20 11:10:48 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F478" t="inlineStr">
+        <is>
+          <t>@KatrinColourArt Hi Katrin, in order for us to be able to assist you, please send a private message with: 
+-pin code of the reservation
+Kind regards.</t>
+        </is>
+      </c>
+      <c r="G478" t="inlineStr"/>
+      <c r="H478" t="inlineStr"/>
+      <c r="I478" t="inlineStr"/>
+      <c r="J478" t="inlineStr"/>
+      <c r="K478" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2079162100295884945</t>
+        </is>
+      </c>
+      <c r="L478" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M478" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N478" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O478" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C479" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D479" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E479" t="inlineStr">
+        <is>
+          <t>Mon Jul 20 11:07:50 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F479" t="inlineStr">
+        <is>
+          <t>@HaticeM50582608 Hi there, we regret to hear that you still did not receive your check-in details. In order for us to be able to assist you, please send a private message with:
+-confirmation number
+-email address
+-name of the guest
+Kind regards.</t>
+        </is>
+      </c>
+      <c r="G479" t="inlineStr"/>
+      <c r="H479" t="inlineStr"/>
+      <c r="I479" t="inlineStr"/>
+      <c r="J479" t="inlineStr"/>
+      <c r="K479" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2079161355693650196</t>
+        </is>
+      </c>
+      <c r="L479" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M479" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N479" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O479" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C480" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D480" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E480" t="inlineStr">
+        <is>
+          <t>Mon Jul 20 10:53:49 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F480" t="inlineStr">
+        <is>
+          <t>@xaviervieira18 We sent you a private message.</t>
+        </is>
+      </c>
+      <c r="G480" t="inlineStr"/>
+      <c r="H480" t="inlineStr"/>
+      <c r="I480" t="inlineStr"/>
+      <c r="J480" t="inlineStr"/>
+      <c r="K480" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2079157827122151785</t>
+        </is>
+      </c>
+      <c r="L480" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M480" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N480" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O480" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C481" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D481" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E481" t="inlineStr">
+        <is>
+          <t>Mon Jul 20 10:27:14 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F481" t="inlineStr">
+        <is>
+          <t>@TheRealKajal We have replied in private, Kajal. Please check your DMs at your earliest convenience. https://t.co/Z89AAoEgD7</t>
+        </is>
+      </c>
+      <c r="G481" t="inlineStr"/>
+      <c r="H481" t="inlineStr"/>
+      <c r="I481" t="inlineStr"/>
+      <c r="J481" t="inlineStr"/>
+      <c r="K481" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2079151137525997886</t>
+        </is>
+      </c>
+      <c r="L481" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M481" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N481" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O481" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B482" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C482" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D482" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E482" t="inlineStr">
+        <is>
+          <t>Mon Jul 20 10:26:09 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F482" t="inlineStr">
+        <is>
+          <t>Hi Connor, thank you for contacting us. We'd like to help, however we can only assist with accommodation bookings via Social Media. For any flight related requests you will need to reach out to our dedicated flight support team here: https://t.co/TBejpc4vOA. Or call via +1 917 421 7240 [US], +44 2039019061 [UK], +353 19075677 [IE].</t>
+        </is>
+      </c>
+      <c r="G482" t="inlineStr"/>
+      <c r="H482" t="inlineStr"/>
+      <c r="I482" t="inlineStr"/>
+      <c r="J482" t="inlineStr"/>
+      <c r="K482" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2079150863608631515</t>
+        </is>
+      </c>
+      <c r="L482" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M482" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N482" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O482" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C483" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D483" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E483" t="inlineStr">
+        <is>
+          <t>Mon Jul 20 10:18:58 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F483" t="inlineStr">
+        <is>
+          <t>@patrosenjimu Hi Patrose, we've replied to your DM and look forward to your response. https://t.co/Z89AAoEgD7</t>
+        </is>
+      </c>
+      <c r="G483" t="inlineStr"/>
+      <c r="H483" t="inlineStr"/>
+      <c r="I483" t="inlineStr"/>
+      <c r="J483" t="inlineStr"/>
+      <c r="K483" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2079149057436418221</t>
+        </is>
+      </c>
+      <c r="L483" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M483" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N483" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O483" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C484" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D484" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E484" t="inlineStr">
+        <is>
+          <t>Mon Jul 20 10:09:53 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F484" t="inlineStr">
+        <is>
+          <t>@yosoygergely You can find the numbers once you click on Support, then Contact Customer Service. After you reply to the questions to understand your request, you will have the option to call the relevant team directly. Kind regards.</t>
+        </is>
+      </c>
+      <c r="G484" t="inlineStr"/>
+      <c r="H484" t="inlineStr"/>
+      <c r="I484" t="inlineStr"/>
+      <c r="J484" t="inlineStr"/>
+      <c r="K484" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2079146769665950073</t>
+        </is>
+      </c>
+      <c r="L484" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M484" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N484" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O484" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C485" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D485" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E485" t="inlineStr">
+        <is>
+          <t>Mon Jul 20 09:17:42 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F485" t="inlineStr">
+        <is>
+          <t>@murphy2para Hi David, we've sent you a DM.</t>
+        </is>
+      </c>
+      <c r="G485" t="inlineStr"/>
+      <c r="H485" t="inlineStr"/>
+      <c r="I485" t="inlineStr"/>
+      <c r="J485" t="inlineStr"/>
+      <c r="K485" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2079133640542257662</t>
+        </is>
+      </c>
+      <c r="L485" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M485" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N485" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O485" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C486" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D486" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E486" t="inlineStr">
+        <is>
+          <t>Mon Jul 20 08:12:50 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F486" t="inlineStr">
+        <is>
+          <t>@mohamedElh81508 Hi there, for security purposes, we are unable to offer support to our partners via social media. However, you can find the contact information for our Partner Support team here: https://t.co/N4c4HTAv4f?</t>
+        </is>
+      </c>
+      <c r="G486" t="inlineStr"/>
+      <c r="H486" t="inlineStr"/>
+      <c r="I486" t="inlineStr"/>
+      <c r="J486" t="inlineStr"/>
+      <c r="K486" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2079117316147523935</t>
+        </is>
+      </c>
+      <c r="L486" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M486" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N486" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O486" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C487" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D487" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E487" t="inlineStr">
+        <is>
+          <t>Mon Jul 20 08:09:50 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F487" t="inlineStr">
+        <is>
+          <t>@marcovoltaico Grazie, Marco. Ti auguriamo una buona giornata.</t>
+        </is>
+      </c>
+      <c r="G487" t="inlineStr"/>
+      <c r="H487" t="inlineStr"/>
+      <c r="I487" t="inlineStr"/>
+      <c r="J487" t="inlineStr"/>
+      <c r="K487" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2079116558215864465</t>
+        </is>
+      </c>
+      <c r="L487" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M487" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N487" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O487" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B488" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C488" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D488" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E488" t="inlineStr">
+        <is>
+          <t>Mon Jul 20 07:20:41 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F488" t="inlineStr">
+        <is>
+          <t>Hi there, we regret to hear that your flight time was changed. While we would love to assist you with this matter via social media, we regret to inform you that we cannot provide assistance with flights through this platform. You can reach our Flights team using this link: https://t.co/OVuF5pCzba or by calling {US}+1 917 421 7240 / {UK}+44 2039019061 / {IE} +353 19075677.</t>
+        </is>
+      </c>
+      <c r="G488" t="inlineStr"/>
+      <c r="H488" t="inlineStr"/>
+      <c r="I488" t="inlineStr"/>
+      <c r="J488" t="inlineStr"/>
+      <c r="K488" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2079104192287752409</t>
+        </is>
+      </c>
+      <c r="L488" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M488" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N488" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O488" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C489" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D489" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E489" t="inlineStr">
+        <is>
+          <t>Mon Jul 20 07:11:53 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F489" t="inlineStr">
+        <is>
+          <t>Entendemos totalmente lo que comentas, Belinda. Los horarios los establece cada alojamiento en función de su operativa, limpieza y preparación de habitaciones entre reservas. Siempre recomendamos revisar esta información antes de reservar y, si lo necesitas, contactar directamente con el alojamiento para consultar opciones de early check-in o late check-out, ya que en algunos casos pueden ofrecerlo según disponibilidad.
+Un saludo.</t>
+        </is>
+      </c>
+      <c r="G489" t="inlineStr"/>
+      <c r="H489" t="inlineStr"/>
+      <c r="I489" t="inlineStr"/>
+      <c r="J489" t="inlineStr"/>
+      <c r="K489" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2079101975812014339</t>
+        </is>
+      </c>
+      <c r="L489" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M489" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N489" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O489" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B490" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C490" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D490" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E490" t="inlineStr">
+        <is>
+          <t>Mon Jul 20 06:42:57 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F490" t="inlineStr">
+        <is>
+          <t>@PhilChose En alternative, pour une assistance immédiate, vous pouvez toujours nous appeler ici : https://t.co/aH74XgSLGq</t>
+        </is>
+      </c>
+      <c r="G490" t="inlineStr"/>
+      <c r="H490" t="inlineStr"/>
+      <c r="I490" t="inlineStr"/>
+      <c r="J490" t="inlineStr"/>
+      <c r="K490" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2079094694642852107</t>
+        </is>
+      </c>
+      <c r="L490" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M490" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N490" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O490" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/News_Dashboard/data/social_media_posts.xlsx
+++ b/News_Dashboard/data/social_media_posts.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O490"/>
+  <dimension ref="A1:O511"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31292,6 +31292,1335 @@
         </is>
       </c>
     </row>
+    <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>Navan</t>
+        </is>
+      </c>
+      <c r="C491" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D491" t="inlineStr">
+        <is>
+          <t>navan</t>
+        </is>
+      </c>
+      <c r="E491" t="inlineStr">
+        <is>
+          <t>Mon Jul 20 14:53:49 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F491" t="inlineStr">
+        <is>
+          <t>Read the full case study: https://t.co/e8N030ZPT2</t>
+        </is>
+      </c>
+      <c r="G491" t="inlineStr"/>
+      <c r="H491" t="inlineStr"/>
+      <c r="I491" t="inlineStr"/>
+      <c r="J491" t="inlineStr"/>
+      <c r="K491" t="inlineStr">
+        <is>
+          <t>https://x.com/Navan/status/2079218225833771034</t>
+        </is>
+      </c>
+      <c r="L491" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M491" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N491" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O491" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B492" t="inlineStr">
+        <is>
+          <t>Navan</t>
+        </is>
+      </c>
+      <c r="C492" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D492" t="inlineStr">
+        <is>
+          <t>navan</t>
+        </is>
+      </c>
+      <c r="E492" t="inlineStr">
+        <is>
+          <t>Mon Jul 20 14:53:23 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F492" t="inlineStr">
+        <is>
+          <t>Flying your entire global workforce of 4,500+ people to one city? For Navan customer @Adyen, that’s just "Connect Week."
+Before partnering with Navan, coordinating this massive corporate milestone was an absolute mountain of manual work, fragmented legacy platforms, and admin chaos.
+Today, Navan handles the enterprise heavy lifting—steering thousands of global employees toward preferred flights, hotel blocks, and pre-negotiated corporate rates seamlessly—so Adyen can focus on the IRL connecting.</t>
+        </is>
+      </c>
+      <c r="G492" t="inlineStr"/>
+      <c r="H492" t="inlineStr"/>
+      <c r="I492" t="inlineStr"/>
+      <c r="J492" t="inlineStr"/>
+      <c r="K492" t="inlineStr">
+        <is>
+          <t>https://x.com/Navan/status/2079218115951419648</t>
+        </is>
+      </c>
+      <c r="L492" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M492" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N492" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O492" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B493" t="inlineStr">
+        <is>
+          <t>Ramp</t>
+        </is>
+      </c>
+      <c r="C493" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D493" t="inlineStr">
+        <is>
+          <t>tryramp</t>
+        </is>
+      </c>
+      <c r="E493" t="inlineStr">
+        <is>
+          <t>Mon Jul 20 15:53:57 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F493" t="inlineStr">
+        <is>
+          <t>Watch how the talented folks at https://t.co/fbtuqs2GUh 3D animated our construction product launch video https://t.co/XhNifqPhhf</t>
+        </is>
+      </c>
+      <c r="G493" t="inlineStr"/>
+      <c r="H493" t="inlineStr"/>
+      <c r="I493" t="inlineStr"/>
+      <c r="J493" t="inlineStr"/>
+      <c r="K493" t="inlineStr">
+        <is>
+          <t>https://x.com/tryramp/status/2079233359633318268</t>
+        </is>
+      </c>
+      <c r="L493" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M493" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N493" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O493" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B494" t="inlineStr">
+        <is>
+          <t>Ramp</t>
+        </is>
+      </c>
+      <c r="C494" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D494" t="inlineStr">
+        <is>
+          <t>tryramp</t>
+        </is>
+      </c>
+      <c r="E494" t="inlineStr">
+        <is>
+          <t>Mon Jul 20 14:02:03 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F494" t="inlineStr">
+        <is>
+          <t>@iamjasonlevin Art</t>
+        </is>
+      </c>
+      <c r="G494" t="inlineStr"/>
+      <c r="H494" t="inlineStr"/>
+      <c r="I494" t="inlineStr"/>
+      <c r="J494" t="inlineStr"/>
+      <c r="K494" t="inlineStr">
+        <is>
+          <t>https://x.com/tryramp/status/2079205198958874890</t>
+        </is>
+      </c>
+      <c r="L494" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M494" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N494" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O494" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B495" t="inlineStr">
+        <is>
+          <t>Brex</t>
+        </is>
+      </c>
+      <c r="C495" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D495" t="inlineStr">
+        <is>
+          <t>brexhq</t>
+        </is>
+      </c>
+      <c r="E495" t="inlineStr">
+        <is>
+          <t>Mon Jul 20 16:42:13 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F495" t="inlineStr">
+        <is>
+          <t>@tobiwaldhecker otw!</t>
+        </is>
+      </c>
+      <c r="G495" t="inlineStr"/>
+      <c r="H495" t="inlineStr"/>
+      <c r="I495" t="inlineStr"/>
+      <c r="J495" t="inlineStr"/>
+      <c r="K495" t="inlineStr">
+        <is>
+          <t>https://x.com/brexHQ/status/2079245505716949420</t>
+        </is>
+      </c>
+      <c r="L495" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M495" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N495" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O495" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B496" t="inlineStr">
+        <is>
+          <t>Brex</t>
+        </is>
+      </c>
+      <c r="C496" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D496" t="inlineStr">
+        <is>
+          <t>brexhq</t>
+        </is>
+      </c>
+      <c r="E496" t="inlineStr">
+        <is>
+          <t>Mon Jul 20 16:37:13 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F496" t="inlineStr">
+        <is>
+          <t>Every day is doomsday when you're still doing manual expense reports</t>
+        </is>
+      </c>
+      <c r="G496" t="inlineStr"/>
+      <c r="H496" t="inlineStr"/>
+      <c r="I496" t="inlineStr"/>
+      <c r="J496" t="inlineStr"/>
+      <c r="K496" t="inlineStr">
+        <is>
+          <t>https://x.com/brexHQ/status/2079244245169295377</t>
+        </is>
+      </c>
+      <c r="L496" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M496" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N496" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O496" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B497" t="inlineStr">
+        <is>
+          <t>Brex</t>
+        </is>
+      </c>
+      <c r="C497" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D497" t="inlineStr">
+        <is>
+          <t>brexhq</t>
+        </is>
+      </c>
+      <c r="E497" t="inlineStr">
+        <is>
+          <t>Mon Jul 20 16:04:50 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F497" t="inlineStr">
+        <is>
+          <t>@anieasyy We were wondering where that went...</t>
+        </is>
+      </c>
+      <c r="G497" t="inlineStr"/>
+      <c r="H497" t="inlineStr"/>
+      <c r="I497" t="inlineStr"/>
+      <c r="J497" t="inlineStr"/>
+      <c r="K497" t="inlineStr">
+        <is>
+          <t>https://x.com/brexHQ/status/2079236098463559885</t>
+        </is>
+      </c>
+      <c r="L497" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M497" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N497" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O497" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B498" t="inlineStr">
+        <is>
+          <t>Brex</t>
+        </is>
+      </c>
+      <c r="C498" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D498" t="inlineStr">
+        <is>
+          <t>brexhq</t>
+        </is>
+      </c>
+      <c r="E498" t="inlineStr">
+        <is>
+          <t>Mon Jul 20 13:51:27 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F498" t="inlineStr">
+        <is>
+          <t>top of the morning</t>
+        </is>
+      </c>
+      <c r="G498" t="inlineStr"/>
+      <c r="H498" t="inlineStr"/>
+      <c r="I498" t="inlineStr"/>
+      <c r="J498" t="inlineStr"/>
+      <c r="K498" t="inlineStr">
+        <is>
+          <t>https://x.com/brexHQ/status/2079202529548685503</t>
+        </is>
+      </c>
+      <c r="L498" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M498" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N498" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O498" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B499" t="inlineStr">
+        <is>
+          <t>Brex</t>
+        </is>
+      </c>
+      <c r="C499" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D499" t="inlineStr">
+        <is>
+          <t>brexhq</t>
+        </is>
+      </c>
+      <c r="E499" t="inlineStr">
+        <is>
+          <t>Mon Jul 20 13:42:13 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F499" t="inlineStr">
+        <is>
+          <t>@PigPugHealth thanks for joining us</t>
+        </is>
+      </c>
+      <c r="G499" t="inlineStr"/>
+      <c r="H499" t="inlineStr"/>
+      <c r="I499" t="inlineStr"/>
+      <c r="J499" t="inlineStr"/>
+      <c r="K499" t="inlineStr">
+        <is>
+          <t>https://x.com/brexHQ/status/2079200207074435161</t>
+        </is>
+      </c>
+      <c r="L499" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M499" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N499" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O499" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B500" t="inlineStr">
+        <is>
+          <t>AirBnb</t>
+        </is>
+      </c>
+      <c r="C500" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D500" t="inlineStr">
+        <is>
+          <t>Airbnb</t>
+        </is>
+      </c>
+      <c r="E500" t="inlineStr">
+        <is>
+          <t>Mon Jul 20 17:59:22 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F500" t="inlineStr">
+        <is>
+          <t>@chefjoseandres A promise kept and a World Cup won ❤️💛</t>
+        </is>
+      </c>
+      <c r="G500" t="inlineStr"/>
+      <c r="H500" t="inlineStr"/>
+      <c r="I500" t="inlineStr"/>
+      <c r="J500" t="inlineStr"/>
+      <c r="K500" t="inlineStr">
+        <is>
+          <t>https://x.com/Airbnb/status/2079264921196380339</t>
+        </is>
+      </c>
+      <c r="L500" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M500" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N500" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O500" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B501" t="inlineStr">
+        <is>
+          <t>AirBnb</t>
+        </is>
+      </c>
+      <c r="C501" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="D501" t="inlineStr">
+        <is>
+          <t>airbnb</t>
+        </is>
+      </c>
+      <c r="E501" t="inlineStr">
+        <is>
+          <t>2026-07-19T22:05:55.000Z</t>
+        </is>
+      </c>
+      <c r="F501" t="inlineStr">
+        <is>
+          <t>For about 39 days, the whole world met. We shared stadiums, living rooms, and flooded the streets. We sang together, celebrated goals and felt at home no matter the color of our jerseys. And even though Spain is taking home the cup. It feels like we all won. Let’s keep it going. Meet you in Brazil in 2027.</t>
+        </is>
+      </c>
+      <c r="G501" t="inlineStr">
+        <is>
+          <t>https://scontent-lga3-3.cdninstagram.com/v/t51.82787-15/751076434_18615116800063838_7536267405804119357_n.jpg?stp=dst-jpg_e35_p1080x1080_sh2.08_tt6&amp;_nc_ht=scontent-lga3-3.cdninstagram.com&amp;_nc_cat=102&amp;_nc_oc=Q6cZ2gEjkm4pywfI1vP2vabzz3Q6gJUER5Yj1r9yX5E3F18qJOsCJUdfjuM5efdt3hbzKnDhty-Pgy9H2LFOmN50DME3&amp;_nc_ohc=C79__JGeJNIQ7kNvwG61jfN&amp;_nc_gid=izILC2XplMM1FKR79k3SMg&amp;edm=ADp7STQBAAAA&amp;ccb=7-5&amp;oh=00_AQAlLFeSTmfD2Zp2322ExAzF1PiWO7oKAJPg_Zk0XEvHZQ&amp;oe=6A642B3D&amp;_nc_sid=c6f216</t>
+        </is>
+      </c>
+      <c r="H501" t="inlineStr">
+        <is>
+          <t>[easyocr not installed. Run 'pip install easyocr torch torchvision']</t>
+        </is>
+      </c>
+      <c r="I501" t="inlineStr">
+        <is>
+          <t>https://scontent-sea1-1.cdninstagram.com/o1/v/t2/f2/m86/AQPw2Gp6FltXC06TaA9j2RDWR6ieTikHVT-60JmalPKTKytw5lxCFPhFL2mVJcKOWxKG6iA2GvHRSFHdpqkXCzIqlGhSKH6NTg3cf4E.mp4?_nc_cat=101&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-sea1-1.cdninstagram.com&amp;_nc_ohc=7tBG0Q_sSDEQ7kNvwEJlLft&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uQUQuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTI0MzQwNTY3MjE4ODAwNiwiYXNzZXRfYWdlX2RheXMiOjAsInZpX3VzZWNhc2VfaWQiOjEyMzc0LCJkdXJhdGlvbl9zIjozMCwidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=b9fdf00486abac46&amp;_nc_vs=HBksFQIYUmlnX3hwdl9yZWVsc19wZXJtYW5lbnRfc3JfcHJvZC8xQTQzRTI3REI5RTcyMEI3RkQxOEI5OTQ3RDVGQUE5OF92aWRlb19kYXNoaW5pdC5tcDQVAALIARIAFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyL0M2NDM2NzU0OTg0MUY0RUM3MUFGRkNCMDVGNERFQjk5X2F1ZGlvX2Rhc2hpbml0Lm1wNBUCAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbMobiW3re1BBUCKAJDMywXQD4AAAAAAAAYEmRhc2hfYmFzZWxpbmVfMV92MREAdfAHZazBAQA&amp;_nc_gid=LJeO1IMkmRT8J7NLWRhC1A&amp;_nc_ss=7ca8c&amp;_nc_zt=28&amp;oh=00_AQCmwOzJ1PsPj8GdEPNCLTcue5z4Rq7NZbEOx0g3tnSaSQ&amp;oe=6A602D82</t>
+        </is>
+      </c>
+      <c r="J501" t="inlineStr">
+        <is>
+          <t>[faster-whisper not installed. Run 'pip install faster-whisper']</t>
+        </is>
+      </c>
+      <c r="K501" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Da_ZGvhp56E/</t>
+        </is>
+      </c>
+      <c r="L501" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M501" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N501" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O501" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B502" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C502" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D502" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E502" t="inlineStr">
+        <is>
+          <t>Mon Jul 20 17:41:14 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F502" t="inlineStr">
+        <is>
+          <t>@Mandy60029581 Hi Mandy, we have sent you a private message. Please take a moment to check it. Thank you.</t>
+        </is>
+      </c>
+      <c r="G502" t="inlineStr"/>
+      <c r="H502" t="inlineStr"/>
+      <c r="I502" t="inlineStr"/>
+      <c r="J502" t="inlineStr"/>
+      <c r="K502" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2079260354870214825</t>
+        </is>
+      </c>
+      <c r="L502" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M502" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N502" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O502" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B503" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C503" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D503" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E503" t="inlineStr">
+        <is>
+          <t>Mon Jul 20 17:15:29 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F503" t="inlineStr">
+        <is>
+          <t>We understand how upsetting this situation must be, Nyayena. To help us investigate and assist you further, please send the details we previously requested via private message. 
+As soon as we receive the information, we'll review your case and do our best to help. Thank you for your cooperation.</t>
+        </is>
+      </c>
+      <c r="G503" t="inlineStr"/>
+      <c r="H503" t="inlineStr"/>
+      <c r="I503" t="inlineStr"/>
+      <c r="J503" t="inlineStr"/>
+      <c r="K503" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2079253877220606055</t>
+        </is>
+      </c>
+      <c r="L503" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M503" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N503" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O503" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B504" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C504" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D504" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E504" t="inlineStr">
+        <is>
+          <t>Mon Jul 20 17:09:01 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F504" t="inlineStr">
+        <is>
+          <t>Hi Alexander, thank you for reaching out to us. We regret to hear about your situation, and we'd like to see how we are able to assist. For us to help you here, please send us the following information via private message, and we'll get back to you soon.
+- Confirmation number
+- Pin code
+- Name on the reservation
+Keep in mind, our Social Media Team does not work in real time. For immediate support, you can call our 24/7 Customer Service Team here: https://t.co/tuuNbmGVaG.</t>
+        </is>
+      </c>
+      <c r="G504" t="inlineStr"/>
+      <c r="H504" t="inlineStr"/>
+      <c r="I504" t="inlineStr"/>
+      <c r="J504" t="inlineStr"/>
+      <c r="K504" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2079252249998430208</t>
+        </is>
+      </c>
+      <c r="L504" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M504" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N504" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O504" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B505" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C505" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D505" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E505" t="inlineStr">
+        <is>
+          <t>Mon Jul 20 15:21:29 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F505" t="inlineStr">
+        <is>
+          <t>@KatrinColourArt We regret to hear about your dissatisfaction, but we'd like to clarify that several of our partners accept various payment options, including online payments, as indicated on our website. Regarding your claim, we've provided an update via DM, so please have a look. Regards</t>
+        </is>
+      </c>
+      <c r="G505" t="inlineStr"/>
+      <c r="H505" t="inlineStr"/>
+      <c r="I505" t="inlineStr"/>
+      <c r="J505" t="inlineStr"/>
+      <c r="K505" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2079225186365120585</t>
+        </is>
+      </c>
+      <c r="L505" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M505" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N505" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O505" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B506" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C506" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D506" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E506" t="inlineStr">
+        <is>
+          <t>Mon Jul 20 14:32:50 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F506" t="inlineStr">
+        <is>
+          <t>Hi Mandy, we are here to help you in regard to your refund.
+If you have a https://t.co/fGhmZE7riF reservation, please share with us in a private message:
+- reservation number
+- PIN code
+- guest name on the booking.
+We will check and get back to you as soon as we can.
+Kind Regards</t>
+        </is>
+      </c>
+      <c r="G506" t="inlineStr"/>
+      <c r="H506" t="inlineStr"/>
+      <c r="I506" t="inlineStr"/>
+      <c r="J506" t="inlineStr"/>
+      <c r="K506" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2079212942537421087</t>
+        </is>
+      </c>
+      <c r="L506" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M506" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N506" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O506" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B507" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C507" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D507" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E507" t="inlineStr">
+        <is>
+          <t>Mon Jul 20 13:34:56 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F507" t="inlineStr">
+        <is>
+          <t>Hi there, we regret to hear that you are still waiting for a refund. In order for us to be able to look into this, kindly send us a DM with the following details:
+-email address associated with your account
+-the full name of the person reaching out to us
+And we'll get back to you as soon as possible.</t>
+        </is>
+      </c>
+      <c r="G507" t="inlineStr"/>
+      <c r="H507" t="inlineStr"/>
+      <c r="I507" t="inlineStr"/>
+      <c r="J507" t="inlineStr"/>
+      <c r="K507" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2079198372431331808</t>
+        </is>
+      </c>
+      <c r="L507" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M507" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N507" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O507" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B508" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C508" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D508" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E508" t="inlineStr">
+        <is>
+          <t>Mon Jul 20 13:08:17 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F508" t="inlineStr">
+        <is>
+          <t>@JihaneCHERQAOU3 Hi Jihane, we have responded to your DM to request additional information. If you still need support, please review and let us know.</t>
+        </is>
+      </c>
+      <c r="G508" t="inlineStr"/>
+      <c r="H508" t="inlineStr"/>
+      <c r="I508" t="inlineStr"/>
+      <c r="J508" t="inlineStr"/>
+      <c r="K508" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2079191666255102447</t>
+        </is>
+      </c>
+      <c r="L508" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M508" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N508" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O508" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C509" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D509" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E509" t="inlineStr">
+        <is>
+          <t>Mon Jul 20 12:59:28 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F509" t="inlineStr">
+        <is>
+          <t>Bonjour Jeremy, merci de nous interpeller ici, nous sommes navrés de lire que les conditions de votre séjour n'étaient pas satisfaisantes. Nous souhaitons toutefois préciser que les établissements sont entièrement responsables de la qualité de service et des prestations fournies, ainsi que de leur descriptif sur notre site.
+Nous pourrons bien sûr nous renseigner davantage sur ce qu'il s'est passé lorsque vous nous aurez communiqué par message privé pour des raisons de confidentialité :
+- le numéro de réservation
+- le code confidentiel
+- le nom complet du voyageur sur la réservation.
+Nous reviendrons ensuite au plus vite vers vous.</t>
+        </is>
+      </c>
+      <c r="G509" t="inlineStr"/>
+      <c r="H509" t="inlineStr"/>
+      <c r="I509" t="inlineStr"/>
+      <c r="J509" t="inlineStr"/>
+      <c r="K509" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2079189449070485873</t>
+        </is>
+      </c>
+      <c r="L509" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M509" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N509" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O509" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>Mondee</t>
+        </is>
+      </c>
+      <c r="B510" t="inlineStr">
+        <is>
+          <t>Sky Bird Travel</t>
+        </is>
+      </c>
+      <c r="C510" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D510" t="inlineStr">
+        <is>
+          <t>SkyBirdTravel</t>
+        </is>
+      </c>
+      <c r="E510" t="inlineStr">
+        <is>
+          <t>Mon Jul 20 16:47:11 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F510" t="inlineStr">
+        <is>
+          <t>Grow your Morocco, Africa, Europe, and Asia sales with Royal Air Maroc. New nonstop Los Angeles–Casablanca service starts June 7, operating three times weekly with connections through Casablanca and the oneworld alliance. 
+Agents can book via WINGS. https://t.co/ctFwiJyiud https://t.co/3Sr1Z3l3Ae</t>
+        </is>
+      </c>
+      <c r="G510" t="inlineStr"/>
+      <c r="H510" t="inlineStr"/>
+      <c r="I510" t="inlineStr"/>
+      <c r="J510" t="inlineStr"/>
+      <c r="K510" t="inlineStr">
+        <is>
+          <t>https://x.com/SkyBirdTravel/status/2079246752725733395</t>
+        </is>
+      </c>
+      <c r="L510" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M510" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N510" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O510" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>Mondee</t>
+        </is>
+      </c>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>Sky Bird Travel</t>
+        </is>
+      </c>
+      <c r="C511" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D511" t="inlineStr">
+        <is>
+          <t>Sky Bird Travel &amp; Tours</t>
+        </is>
+      </c>
+      <c r="E511" t="inlineStr">
+        <is>
+          <t>2026-07-20T16:47:41.908Z</t>
+        </is>
+      </c>
+      <c r="F511" t="inlineStr">
+        <is>
+          <t>Grow your Morocco, Africa, Europe, and Asia sales with Royal Air Maroc. New nonstop Los Angeles–Casablanca service starts June 7, operating three times weekly with connections through Casablanca and the oneworld alliance. 
+Agents can book via WINGS. https://bit.ly/4ahXS0u
+#TravelAgent #TravelAgents #SkyBird #AirMoroc</t>
+        </is>
+      </c>
+      <c r="G511" t="inlineStr">
+        <is>
+          <t>https://media.licdn.com/dms/image/v2/D4E22AQGLNldJWVXKlQ/feedshare-shrink_1280/B4EZ.AbRPIKQAM-/0/1784566060993?e=1785974400&amp;v=beta&amp;t=W3VofQ5EYuAqg8YaYGvvWSGUtSPW3t1C1rws69l6SUY</t>
+        </is>
+      </c>
+      <c r="H511" t="inlineStr">
+        <is>
+          <t>[easyocr not installed. Run 'pip install easyocr torch torchvision']</t>
+        </is>
+      </c>
+      <c r="I511" t="inlineStr"/>
+      <c r="J511" t="inlineStr"/>
+      <c r="K511" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/sky-bird-travel-tours_travelagent-travelagents-skybird-activity-7485012571725565952-8lId</t>
+        </is>
+      </c>
+      <c r="L511" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M511" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N511" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O511" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/News_Dashboard/data/social_media_posts.xlsx
+++ b/News_Dashboard/data/social_media_posts.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O511"/>
+  <dimension ref="A1:O548"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32621,6 +32621,2389 @@
         </is>
       </c>
     </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>Navan</t>
+        </is>
+      </c>
+      <c r="C512" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="D512" t="inlineStr">
+        <is>
+          <t>getnavan</t>
+        </is>
+      </c>
+      <c r="E512" t="inlineStr">
+        <is>
+          <t>2026-07-21T14:07:36.000Z</t>
+        </is>
+      </c>
+      <c r="F512" t="inlineStr">
+        <is>
+          <t>Opening a new office on the other side of the world calls for precision.
+For Senior Workplace Project &amp; Program Manager at @adyen, Navan removes the friction from coordinating so he can focus on the wow moment.
+Navan is for wherever your journey takes you.</t>
+        </is>
+      </c>
+      <c r="G512" t="inlineStr">
+        <is>
+          <t>https://scontent-det1-1.cdninstagram.com/v/t51.82787-15/750897127_18476123959110668_972594455671238207_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_ht=scontent-det1-1.cdninstagram.com&amp;_nc_cat=108&amp;_nc_oc=Q6cZ2gGYq3MD1mttyl4WoPUTtpj36G-9_i58wCzf4VEJP_9myzrbH_K-XtywNW1oK176SzJ3Yod3j9YHGyoWvjeFFTeF&amp;_nc_ohc=ixi3ByZW8wUQ7kNvwHRwNi9&amp;_nc_gid=zpxg3SaMXsWnNtBdFeZj7A&amp;edm=ADp7STQBAAAA&amp;ccb=7-5&amp;oh=00_AQCtueMMhZqViqv1t7CUgRWpKfDOWiKfHRtD1a4xa8R0uA&amp;oe=6A65729F&amp;_nc_sid=c6f216</t>
+        </is>
+      </c>
+      <c r="H512" t="inlineStr">
+        <is>
+          <t>[easyocr not installed. Run 'pip install easyocr torch torchvision']</t>
+        </is>
+      </c>
+      <c r="I512" t="inlineStr">
+        <is>
+          <t>https://scontent-dfw6-1.cdninstagram.com/o1/v/t2/f2/m86/AQPFDP2cMCKXpWqXFhDrkRFxL1T-47j2svufMxT7uGoYnWhxId24kxC5uIGNnEw-P3_pNfWPPNcbTmWU9_IGN6cPHl_uD3-3YvqfujA.mp4?_nc_cat=101&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-dfw6-1.cdninstagram.com&amp;_nc_ohc=6W_szM68CTUQ7kNvwGalXWB&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uQ0xJUFMuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTM2NTY2MzE5OTA4Mzc4MCwiYXNzZXRfYWdlX2RheXMiOjAsInZpX3VzZWNhc2VfaWQiOjEwMDk5LCJkdXJhdGlvbl9zIjozNywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=5480577a971b1f82&amp;_nc_vs=HBksFQIYUmlnX3hwdl9yZWVsc19wZXJtYW5lbnRfc3JfcHJvZC8xQzQzM0ZCMjVBRTAyNkY0MUFBRTk2QjA5MERBRjZBRl92aWRlb19kYXNoaW5pdC5tcDQVAALIARIAFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyLzk0NEUwQzI1OEU0QTgzOTU2NURCRTIxNEY1QjQyRTlCX2F1ZGlvX2Rhc2hpbml0Lm1wNBUCAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACaI9Ondh4TtBBUCKAJDMywXQEKJ--dsi0QYEmRhc2hfYmFzZWxpbmVfMV92MREAdf4HZeadAQA&amp;_nc_gid=s8QwSoYwjBjQ8bnC3hMUVQ&amp;_nc_ss=72a8c&amp;_nc_zt=28&amp;oh=00_AQCer-H8jHk9UR90EhpKZf0Fur59HlUVAG2A9CsLthloZw&amp;oe=6A61A772</t>
+        </is>
+      </c>
+      <c r="J512" t="inlineStr">
+        <is>
+          <t>[faster-whisper not installed. Run 'pip install faster-whisper']</t>
+        </is>
+      </c>
+      <c r="K512" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DbDsTUwJk6f/</t>
+        </is>
+      </c>
+      <c r="L512" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M512" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N512" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O512" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B513" t="inlineStr">
+        <is>
+          <t>Ramp</t>
+        </is>
+      </c>
+      <c r="C513" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D513" t="inlineStr">
+        <is>
+          <t>tryramp</t>
+        </is>
+      </c>
+      <c r="E513" t="inlineStr">
+        <is>
+          <t>Tue Jul 21 16:29:00 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F513" t="inlineStr">
+        <is>
+          <t>More than 1,000 businesses already use stablecoins to pay vendors on Ramp, and more than 70% of that payment volume moves outside traditional banking hours.
+Open a Stablecoin Account today.
+https://t.co/0EChITRU1J</t>
+        </is>
+      </c>
+      <c r="G513" t="inlineStr"/>
+      <c r="H513" t="inlineStr"/>
+      <c r="I513" t="inlineStr"/>
+      <c r="J513" t="inlineStr"/>
+      <c r="K513" t="inlineStr">
+        <is>
+          <t>https://x.com/tryramp/status/2079604568225194110</t>
+        </is>
+      </c>
+      <c r="L513" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M513" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N513" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O513" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B514" t="inlineStr">
+        <is>
+          <t>Ramp</t>
+        </is>
+      </c>
+      <c r="C514" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D514" t="inlineStr">
+        <is>
+          <t>tryramp</t>
+        </is>
+      </c>
+      <c r="E514" t="inlineStr">
+        <is>
+          <t>Tue Jul 21 16:25:21 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F514" t="inlineStr">
+        <is>
+          <t>STABLECOINS ARE NOW ON RAMP.
+Your business operates 24/7, but your money only operates Mon-Fri, unavailable on evenings, weekends, &amp; holidays.
+Now you can pay vendors faster across borders &amp; move money in USDC or USDT with the approvals &amp; accounting workflows you already use.
+---
+Ramp Business Corporation is a fintech company and is not a bank or a digital asset custodian. Stablecoin custody is provided by Bridge Building Inc. and affiliates.</t>
+        </is>
+      </c>
+      <c r="G514" t="inlineStr"/>
+      <c r="H514" t="inlineStr"/>
+      <c r="I514" t="inlineStr"/>
+      <c r="J514" t="inlineStr"/>
+      <c r="K514" t="inlineStr">
+        <is>
+          <t>https://x.com/tryramp/status/2079603646690423074</t>
+        </is>
+      </c>
+      <c r="L514" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M514" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N514" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O514" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B515" t="inlineStr">
+        <is>
+          <t>Ramp</t>
+        </is>
+      </c>
+      <c r="C515" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D515" t="inlineStr">
+        <is>
+          <t>tryramp</t>
+        </is>
+      </c>
+      <c r="E515" t="inlineStr">
+        <is>
+          <t>Mon Jul 20 18:41:51 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F515" t="inlineStr">
+        <is>
+          <t>@vral model the models the models the models the models the models the models the models the models the models the models the models the models the models the models the models the models the models the models the models the models the models the models the models the models the models</t>
+        </is>
+      </c>
+      <c r="G515" t="inlineStr"/>
+      <c r="H515" t="inlineStr"/>
+      <c r="I515" t="inlineStr"/>
+      <c r="J515" t="inlineStr"/>
+      <c r="K515" t="inlineStr">
+        <is>
+          <t>https://x.com/tryramp/status/2079275611990745559</t>
+        </is>
+      </c>
+      <c r="L515" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M515" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N515" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O515" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B516" t="inlineStr">
+        <is>
+          <t>Ramp</t>
+        </is>
+      </c>
+      <c r="C516" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D516" t="inlineStr">
+        <is>
+          <t>tryramp</t>
+        </is>
+      </c>
+      <c r="E516" t="inlineStr">
+        <is>
+          <t>Mon Jul 20 18:40:19 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F516" t="inlineStr">
+        <is>
+          <t>@sridvijay honored to serve/cut 🫡</t>
+        </is>
+      </c>
+      <c r="G516" t="inlineStr"/>
+      <c r="H516" t="inlineStr"/>
+      <c r="I516" t="inlineStr"/>
+      <c r="J516" t="inlineStr"/>
+      <c r="K516" t="inlineStr">
+        <is>
+          <t>https://x.com/tryramp/status/2079275227100438979</t>
+        </is>
+      </c>
+      <c r="L516" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M516" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N516" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O516" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B517" t="inlineStr">
+        <is>
+          <t>Ramp</t>
+        </is>
+      </c>
+      <c r="C517" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D517" t="inlineStr">
+        <is>
+          <t>tryramp</t>
+        </is>
+      </c>
+      <c r="E517" t="inlineStr">
+        <is>
+          <t>Mon Jul 20 18:37:37 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F517" t="inlineStr">
+        <is>
+          <t>We cut our own AI bill by 30% with a Router that chooses the right model for the right task. 
+Now you can too.</t>
+        </is>
+      </c>
+      <c r="G517" t="inlineStr"/>
+      <c r="H517" t="inlineStr"/>
+      <c r="I517" t="inlineStr"/>
+      <c r="J517" t="inlineStr"/>
+      <c r="K517" t="inlineStr">
+        <is>
+          <t>https://x.com/tryramp/status/2079274545307889981</t>
+        </is>
+      </c>
+      <c r="L517" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M517" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N517" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O517" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B518" t="inlineStr">
+        <is>
+          <t>Ramp</t>
+        </is>
+      </c>
+      <c r="C518" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D518" t="inlineStr">
+        <is>
+          <t>tryramp</t>
+        </is>
+      </c>
+      <c r="E518" t="inlineStr">
+        <is>
+          <t>Mon Jul 20 18:36:00 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F518" t="inlineStr">
+        <is>
+          <t>@rahulgs sharing is caring</t>
+        </is>
+      </c>
+      <c r="G518" t="inlineStr"/>
+      <c r="H518" t="inlineStr"/>
+      <c r="I518" t="inlineStr"/>
+      <c r="J518" t="inlineStr"/>
+      <c r="K518" t="inlineStr">
+        <is>
+          <t>https://x.com/tryramp/status/2079274140008145344</t>
+        </is>
+      </c>
+      <c r="L518" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M518" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N518" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O518" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B519" t="inlineStr">
+        <is>
+          <t>Brex</t>
+        </is>
+      </c>
+      <c r="C519" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D519" t="inlineStr">
+        <is>
+          <t>brexhq</t>
+        </is>
+      </c>
+      <c r="E519" t="inlineStr">
+        <is>
+          <t>Tue Jul 21 17:21:24 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F519" t="inlineStr">
+        <is>
+          <t>Learn how @vibedotco made it happen: https://t.co/wxF63RBPXG</t>
+        </is>
+      </c>
+      <c r="G519" t="inlineStr"/>
+      <c r="H519" t="inlineStr"/>
+      <c r="I519" t="inlineStr"/>
+      <c r="J519" t="inlineStr"/>
+      <c r="K519" t="inlineStr">
+        <is>
+          <t>https://x.com/brexHQ/status/2079617755389550737</t>
+        </is>
+      </c>
+      <c r="L519" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M519" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N519" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O519" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B520" t="inlineStr">
+        <is>
+          <t>Brex</t>
+        </is>
+      </c>
+      <c r="C520" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D520" t="inlineStr">
+        <is>
+          <t>brexhq</t>
+        </is>
+      </c>
+      <c r="E520" t="inlineStr">
+        <is>
+          <t>Tue Jul 21 17:00:00 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F520" t="inlineStr">
+        <is>
+          <t>$128,000 in OOH ads…paid for with points 🤯
+@vibedotco turned Brex Points into a viral out-of-home campaign, no extra spend required. https://t.co/H3pfzgtRlQ</t>
+        </is>
+      </c>
+      <c r="G520" t="inlineStr"/>
+      <c r="H520" t="inlineStr"/>
+      <c r="I520" t="inlineStr"/>
+      <c r="J520" t="inlineStr"/>
+      <c r="K520" t="inlineStr">
+        <is>
+          <t>https://x.com/brexHQ/status/2079612368598777954</t>
+        </is>
+      </c>
+      <c r="L520" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M520" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N520" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O520" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B521" t="inlineStr">
+        <is>
+          <t>Brex</t>
+        </is>
+      </c>
+      <c r="C521" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D521" t="inlineStr">
+        <is>
+          <t>brexhq</t>
+        </is>
+      </c>
+      <c r="E521" t="inlineStr">
+        <is>
+          <t>Tue Jul 21 13:48:50 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F521" t="inlineStr">
+        <is>
+          <t>@zachmoskow 🔥</t>
+        </is>
+      </c>
+      <c r="G521" t="inlineStr"/>
+      <c r="H521" t="inlineStr"/>
+      <c r="I521" t="inlineStr"/>
+      <c r="J521" t="inlineStr"/>
+      <c r="K521" t="inlineStr">
+        <is>
+          <t>https://x.com/brexHQ/status/2079564260208787611</t>
+        </is>
+      </c>
+      <c r="L521" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M521" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N521" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O521" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B522" t="inlineStr">
+        <is>
+          <t>Brex</t>
+        </is>
+      </c>
+      <c r="C522" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D522" t="inlineStr">
+        <is>
+          <t>brexhq</t>
+        </is>
+      </c>
+      <c r="E522" t="inlineStr">
+        <is>
+          <t>Tue Jul 21 13:46:32 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F522" t="inlineStr">
+        <is>
+          <t>@Fondocom Thanks for the shout 🤝</t>
+        </is>
+      </c>
+      <c r="G522" t="inlineStr"/>
+      <c r="H522" t="inlineStr"/>
+      <c r="I522" t="inlineStr"/>
+      <c r="J522" t="inlineStr"/>
+      <c r="K522" t="inlineStr">
+        <is>
+          <t>https://x.com/brexHQ/status/2079563680090304514</t>
+        </is>
+      </c>
+      <c r="L522" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M522" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N522" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O522" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B523" t="inlineStr">
+        <is>
+          <t>Brex</t>
+        </is>
+      </c>
+      <c r="C523" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D523" t="inlineStr">
+        <is>
+          <t>brexhq</t>
+        </is>
+      </c>
+      <c r="E523" t="inlineStr">
+        <is>
+          <t>Mon Jul 20 20:20:01 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F523" t="inlineStr">
+        <is>
+          <t>@ishaanprasad18 @telnyx We like to keep things afloat</t>
+        </is>
+      </c>
+      <c r="G523" t="inlineStr"/>
+      <c r="H523" t="inlineStr"/>
+      <c r="I523" t="inlineStr"/>
+      <c r="J523" t="inlineStr"/>
+      <c r="K523" t="inlineStr">
+        <is>
+          <t>https://x.com/brexHQ/status/2079300314214039957</t>
+        </is>
+      </c>
+      <c r="L523" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M523" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N523" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O523" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B524" t="inlineStr">
+        <is>
+          <t>AirBnb</t>
+        </is>
+      </c>
+      <c r="C524" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D524" t="inlineStr">
+        <is>
+          <t>Airbnb</t>
+        </is>
+      </c>
+      <c r="E524" t="inlineStr">
+        <is>
+          <t>2026-07-21T15:23:48.662Z</t>
+        </is>
+      </c>
+      <c r="F524" t="inlineStr">
+        <is>
+          <t>For about 39 days, the whole world met at the FIFA World Cup 2026™.
+We shared stadiums, living rooms, and flooded the streets. We sang together, celebrated goals and felt at home no matter the color of our jerseys. And even though Spain took home the cup, it feels like we all won. 
+Let’s keep it going. Meet you in Brazil in 2027.</t>
+        </is>
+      </c>
+      <c r="G524" t="inlineStr"/>
+      <c r="H524" t="inlineStr"/>
+      <c r="I524" t="inlineStr">
+        <is>
+          <t>https://dms.licdn.com/playlist/vid/v2/D4D05AQEX0-2wn5C8eA/mp4-720p-30fp-crf28/B4DZ.FRm6DHgB8-/0/1784647418788?e=1785265200&amp;v=beta&amp;t=xpG_cuyoD598DvSZaxjGjQmKYqFMAlW39ZLAzQO8Sq0</t>
+        </is>
+      </c>
+      <c r="J524" t="inlineStr">
+        <is>
+          <t>[faster-whisper not installed. Run 'pip install faster-whisper']</t>
+        </is>
+      </c>
+      <c r="K524" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/airbnb_for-about-39-days-the-whole-world-met-at-activity-7485353848627171331-69Gl</t>
+        </is>
+      </c>
+      <c r="L524" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M524" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N524" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O524" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B525" t="inlineStr">
+        <is>
+          <t>Expedia</t>
+        </is>
+      </c>
+      <c r="C525" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="D525" t="inlineStr">
+        <is>
+          <t>expedia</t>
+        </is>
+      </c>
+      <c r="E525" t="inlineStr">
+        <is>
+          <t>2026-07-21T17:08:03.000Z</t>
+        </is>
+      </c>
+      <c r="F525" t="inlineStr">
+        <is>
+          <t>Is it getting hot in here, or is it just this year’s Island Hot List? Say hello to the island getaways making waves this summer 🌊 🏝️ Which of these next wave destinations is on your summer vision board?</t>
+        </is>
+      </c>
+      <c r="G525" t="inlineStr">
+        <is>
+          <t>https://scontent-dfw5-2.cdninstagram.com/v/t51.82787-15/752845899_18616496278030381_6620855394887071408_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk0NjI4MzQ2NTEwNjA2MDcxNg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMjE2MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=hui_x0mdPG8Q7kNvwGBrT2E&amp;_nc_oc=AdqlQhAKwdolh7rtRXUMdyvejnY6j_3xganxTbMNXN_Vp7KDKnU9wKKFjwrLAbK6FeI&amp;_nc_zt=23&amp;_nc_ht=scontent-dfw5-2.cdninstagram.com&amp;_nc_gid=E1W2S1dsmO25LVBgNZHmIg&amp;_nc_ss=72a8c&amp;oh=00_AQADWYR0T3-qQ34VY7WRyndyV1KN2ug6xXRHZ4WZ79pxJg&amp;oe=6A659FE8</t>
+        </is>
+      </c>
+      <c r="H525" t="inlineStr">
+        <is>
+          <t>[easyocr not installed. Run 'pip install easyocr torch torchvision']</t>
+        </is>
+      </c>
+      <c r="I525" t="inlineStr"/>
+      <c r="J525" t="inlineStr"/>
+      <c r="K525" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DbEBAEfFPM8/</t>
+        </is>
+      </c>
+      <c r="L525" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M525" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N525" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O525" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B526" t="inlineStr">
+        <is>
+          <t>Expedia</t>
+        </is>
+      </c>
+      <c r="C526" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="D526" t="inlineStr">
+        <is>
+          <t>expedia</t>
+        </is>
+      </c>
+      <c r="E526" t="inlineStr">
+        <is>
+          <t>2026-07-21T13:00:53.000Z</t>
+        </is>
+      </c>
+      <c r="F526" t="inlineStr">
+        <is>
+          <t>Dreaming of swapping your daily routine for turquoise waters, hidden beaches and unforgettable adventures? Expedia's 2026 Island Hot List has arrived, and it's packed with the next wave of rising-star island destinations.
+Based on Expedia's search data, the list spotlights 10 incredible alternative islands that are rising in popularity thanks to their stunning scenery, vibrant culture and unforgettable experiences.
+We're giving one lucky Cosmo Club member the chance to make their dream trip a reality with £3,500 in Expedia OneKeyCash to spend on eligible flights, accommodation and activities to create an island escape that's right for you.
+Whether you're craving a romantic retreat, a girls' trip, a family adventure or the ultimate solo getaway, the choice is yours. Ready to ride the wave? Enter to win at the link in bio (UK residents only). Not a member yet? It’s completely FREE to join ✨</t>
+        </is>
+      </c>
+      <c r="G526" t="inlineStr">
+        <is>
+          <t>https://scontent-iad6-1.cdninstagram.com/v/t51.82787-15/752631722_18602071528020429_5280495065809548836_n.jpg?stp=dst-jpg_e35_p1080x1080_sh2.08_tt6&amp;_nc_ht=scontent-iad6-1.cdninstagram.com&amp;_nc_cat=109&amp;_nc_oc=Q6cZ2gFetGEwwF_CoOw39vFxqkqgosKbOiWxJqKmZHwSs3PwwpiQ84HExCmfrmgmbfc1Nv0&amp;_nc_ohc=EiuP96SZxv0Q7kNvwERlBGo&amp;_nc_gid=e7gs7QcYe5PqISGYGcJ9FA&amp;edm=ADp7STQBAAAA&amp;ccb=7-5&amp;oh=00_AQAA1jXpgyd0jUftuWHBj6mxLsmY5Baiq8VlTatlgeE18A&amp;oe=6A657CA1&amp;_nc_sid=c6f216</t>
+        </is>
+      </c>
+      <c r="H526" t="inlineStr">
+        <is>
+          <t>[easyocr not installed. Run 'pip install easyocr torch torchvision']</t>
+        </is>
+      </c>
+      <c r="I526" t="inlineStr"/>
+      <c r="J526" t="inlineStr"/>
+      <c r="K526" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DbDW5Ijlkgi/</t>
+        </is>
+      </c>
+      <c r="L526" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M526" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N526" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O526" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B527" t="inlineStr">
+        <is>
+          <t>Expedia</t>
+        </is>
+      </c>
+      <c r="C527" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D527" t="inlineStr">
+        <is>
+          <t>Expedia</t>
+        </is>
+      </c>
+      <c r="E527" t="inlineStr">
+        <is>
+          <t>2026-07-21T13:24:54.629Z</t>
+        </is>
+      </c>
+      <c r="F527" t="inlineStr">
+        <is>
+          <t>Introducing Expedia's 2026 Island Hot List: 10 fast-rising destinations offering stunning natural beauty, rich culture, and serious value. 🏝️ 
+From the volcanic peaks of St. Lucia to the golden beaches of Porto Santo, Madeira and a surprise entry fueled entirely by soccer fever ⚽ — the next wave of island travel is here. 
+The best part? Many of these destinations are even more affordable when you bundle flights + hotel on Expedia. 
+Explore the full list and start planning: http://ms.spr.ly/6040vfyUI</t>
+        </is>
+      </c>
+      <c r="G527" t="inlineStr"/>
+      <c r="H527" t="inlineStr"/>
+      <c r="I527" t="inlineStr"/>
+      <c r="J527" t="inlineStr"/>
+      <c r="K527" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/expedia_2026-island-hot-list-activity-7485323926324117505-3bZM</t>
+        </is>
+      </c>
+      <c r="L527" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M527" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N527" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O527" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B528" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C528" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D528" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E528" t="inlineStr">
+        <is>
+          <t>Tue Jul 21 18:02:57 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F528" t="inlineStr">
+        <is>
+          <t>Hi James, we appreciate you taking the time to let us know, and we understand how frustrating it can be when an issue remains unresolved, and you're left uncertain about the outcome. As previously communicated, for us to check this further and assist you, kindly send us a private message with the following details:
+• Email address linked to your account 
+• Name of the person reaching out to us 
+Once we receive these details, we'll look into this further.</t>
+        </is>
+      </c>
+      <c r="G528" t="inlineStr"/>
+      <c r="H528" t="inlineStr"/>
+      <c r="I528" t="inlineStr"/>
+      <c r="J528" t="inlineStr"/>
+      <c r="K528" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2079628208530481222</t>
+        </is>
+      </c>
+      <c r="L528" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M528" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N528" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O528" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B529" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C529" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D529" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E529" t="inlineStr">
+        <is>
+          <t>Tue Jul 21 14:05:26 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F529" t="inlineStr">
+        <is>
+          <t>Hi Germán, that does not sound good. We advise our guests to never share their personal details and sensitive information on unrecognized channels or the phone. 
+If you want us to look into this and see what happened, please DM the following: 
+- booking number 
+- pin code
+- guest name 
+We will get back to you asap. Kind regards.</t>
+        </is>
+      </c>
+      <c r="G529" t="inlineStr"/>
+      <c r="H529" t="inlineStr"/>
+      <c r="I529" t="inlineStr"/>
+      <c r="J529" t="inlineStr"/>
+      <c r="K529" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2079568436733133218</t>
+        </is>
+      </c>
+      <c r="L529" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M529" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N529" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O529" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B530" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C530" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D530" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E530" t="inlineStr">
+        <is>
+          <t>Tue Jul 21 13:42:01 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F530" t="inlineStr">
+        <is>
+          <t>Hi Ankit, thanks for your message; we regret learning this issue. In order to further assist you with this matters, please get back to us in private with the following info:
+• Full guest name provided during the booking process: 
+• Full name and email address linked to your account:
+Please do not share this information in public for security and privacy reasons — and we’ll get back to you as soon as we can.</t>
+        </is>
+      </c>
+      <c r="G530" t="inlineStr"/>
+      <c r="H530" t="inlineStr"/>
+      <c r="I530" t="inlineStr"/>
+      <c r="J530" t="inlineStr"/>
+      <c r="K530" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2079562542842556641</t>
+        </is>
+      </c>
+      <c r="L530" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M530" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N530" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O530" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B531" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C531" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D531" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E531" t="inlineStr">
+        <is>
+          <t>Tue Jul 21 13:18:31 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F531" t="inlineStr">
+        <is>
+          <t>Bonjour Adeline, merci de nous interpeller ici. Nous sommes navrés de lire que vous semblez être en attente d'un remboursement de notre part. Nous ne pouvons pas vous aider pour les réservations de vols via les réseaux sociaux, mais vous pouvez contacter notre équipe Vols ici:  https://t.co/TBejpc4vOA, ou appeler :
+{US} +1 917 421 7240 / {UK} +44 2039019061 / {IE} +353 19075677
+Cordialement.</t>
+        </is>
+      </c>
+      <c r="G531" t="inlineStr"/>
+      <c r="H531" t="inlineStr"/>
+      <c r="I531" t="inlineStr"/>
+      <c r="J531" t="inlineStr"/>
+      <c r="K531" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2079556629192724642</t>
+        </is>
+      </c>
+      <c r="L531" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M531" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N531" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O531" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B532" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C532" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D532" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E532" t="inlineStr">
+        <is>
+          <t>Tue Jul 21 12:13:39 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F532" t="inlineStr">
+        <is>
+          <t>Bonjour Judith, merci de nous avoir contactés.  
+Nous nous excusons de ne pas avoir répondu plus tôt, notre équipe dédiée aux réseaux sociaux a actuellement une disponibilité limitée. Si vous avez besoin d’une réponse plus rapide, nous vous invitons à contacter le service client (https://t.co/o8QyR8SaDb).
+Nous regrettons de lire votre déception concernant ce double prélèvement. Afin que nous puissions consulter votre réservation, merci de nous envoyer les informations suivantes par message privé :  
+- Numéro de confirmation  
+- Code confidentiel  
+- Nom complet du voyageur  
+Nous reviendrons vers vous dès que possible.</t>
+        </is>
+      </c>
+      <c r="G532" t="inlineStr"/>
+      <c r="H532" t="inlineStr"/>
+      <c r="I532" t="inlineStr"/>
+      <c r="J532" t="inlineStr"/>
+      <c r="K532" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2079540306849026328</t>
+        </is>
+      </c>
+      <c r="L532" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M532" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N532" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O532" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B533" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C533" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D533" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E533" t="inlineStr">
+        <is>
+          <t>Tue Jul 21 11:35:38 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F533" t="inlineStr">
+        <is>
+          <t>@iklswsk Hi there, we have replied to your private message regarding this.</t>
+        </is>
+      </c>
+      <c r="G533" t="inlineStr"/>
+      <c r="H533" t="inlineStr"/>
+      <c r="I533" t="inlineStr"/>
+      <c r="J533" t="inlineStr"/>
+      <c r="K533" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2079530740245504498</t>
+        </is>
+      </c>
+      <c r="L533" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M533" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N533" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O533" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B534" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C534" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D534" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E534" t="inlineStr">
+        <is>
+          <t>Tue Jul 21 11:29:55 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F534" t="inlineStr">
+        <is>
+          <t>Hola Mariana, gracias por escribirnos. Cuéntanos, ¿cómo podemos ayudarte? Si necesitas asistencia con una reserva de alojamiento, comparte con nosotros por mensaje privado la siguiente información y te responderemos lo antes posible: 
+- Número de confirmación
+- Código PIN
+- Nombre del huésped en la reserva
+Ten en cuenta que nuestro equipo de Redes Sociales no opera en tiempo real. Para asistencia inmediata puedes comunicarte con nuestro equipo de atención al cliente, disponible las 24 horas, aquí: https://t.co/tuuNbmGVaG
+Un saludo.</t>
+        </is>
+      </c>
+      <c r="G534" t="inlineStr"/>
+      <c r="H534" t="inlineStr"/>
+      <c r="I534" t="inlineStr"/>
+      <c r="J534" t="inlineStr"/>
+      <c r="K534" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2079529299053363491</t>
+        </is>
+      </c>
+      <c r="L534" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M534" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N534" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O534" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B535" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C535" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D535" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E535" t="inlineStr">
+        <is>
+          <t>Tue Jul 21 10:02:04 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F535" t="inlineStr">
+        <is>
+          <t>Hi there, we regret hearing this and would like to check your booking, please send us a private message with the following details, and we'll get back to you as soon as possible: 
+- Confirmation number
+- Pin code
+- Name on the reservation (meaning the name of the traveler)
+Please bear in mind that our Social Media Team doesn't work in real time. For immediate support, please call our 24/7 Customer Service Team - our contact details can be found here: https://t.co/o8QyR8SaDb
+Also, at this time, we only offer support for accommodation bookings via social media. For questions about Flights, Taxis, or Insurance, you can reach out to the dedicated support team here: https://t.co/UfRgpDJomK</t>
+        </is>
+      </c>
+      <c r="G535" t="inlineStr"/>
+      <c r="H535" t="inlineStr"/>
+      <c r="I535" t="inlineStr"/>
+      <c r="J535" t="inlineStr"/>
+      <c r="K535" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2079507189937455592</t>
+        </is>
+      </c>
+      <c r="L535" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M535" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N535" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O535" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B536" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C536" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D536" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E536" t="inlineStr">
+        <is>
+          <t>Tue Jul 21 09:40:22 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F536" t="inlineStr">
+        <is>
+          <t>Gracias por escribirnos. Aunque nos gustaría, no podemos ayudarte con reservas de Vuelos a través de las redes sociales, pero puedes contactar con nuestro equipo de Vuelos aquí: https://t.co/TBejpc4vOA, o llamar al +34918362949 desde España de lunes a domingo de 9:00-21:00 hora local.
+Un saludo.</t>
+        </is>
+      </c>
+      <c r="G536" t="inlineStr"/>
+      <c r="H536" t="inlineStr"/>
+      <c r="I536" t="inlineStr"/>
+      <c r="J536" t="inlineStr"/>
+      <c r="K536" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2079501731965112322</t>
+        </is>
+      </c>
+      <c r="L536" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M536" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N536" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O536" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B537" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C537" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D537" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E537" t="inlineStr">
+        <is>
+          <t>Tue Jul 21 09:38:58 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F537" t="inlineStr">
+        <is>
+          <t>Hi Prasanna, it's a pity to hear you can't get in touch with our Customer Care team. How can we assist you? If your request is about a booking, please send us these details in a direct message, and we will reply as soon as we can: 
+- Confirmation number: 
+- Pin code: 
+- Name on the reservation: 
+- Details about your request: 
+If you would rather call our team, you can find your local number here: https://t.co/o8QyR8SaDb</t>
+        </is>
+      </c>
+      <c r="G537" t="inlineStr"/>
+      <c r="H537" t="inlineStr"/>
+      <c r="I537" t="inlineStr"/>
+      <c r="J537" t="inlineStr"/>
+      <c r="K537" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2079501376640401842</t>
+        </is>
+      </c>
+      <c r="L537" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M537" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N537" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O537" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B538" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C538" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D538" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E538" t="inlineStr">
+        <is>
+          <t>Tue Jul 21 09:36:26 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F538" t="inlineStr">
+        <is>
+          <t>Hi Aditya, thank you for getting back to us. We regret hearing that you were charged twice. Please note that if we already facilitated the payment, we would not charge again, and neither should the accommodation. For verification purposes, kindly DM us your:
+- PIN-code, 
+- Name on the reservation,
+so we can look into this for you.
+Keep in mind, our Social Media Team does not work in real time, for immediate support you can call our 24/7 Customer Service Team here: https://t.co/tuuNbmGVaG.</t>
+        </is>
+      </c>
+      <c r="G538" t="inlineStr"/>
+      <c r="H538" t="inlineStr"/>
+      <c r="I538" t="inlineStr"/>
+      <c r="J538" t="inlineStr"/>
+      <c r="K538" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2079500740616192496</t>
+        </is>
+      </c>
+      <c r="L538" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M538" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N538" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O538" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B539" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C539" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D539" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E539" t="inlineStr">
+        <is>
+          <t>Tue Jul 21 09:33:46 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F539" t="inlineStr">
+        <is>
+          <t>@iklswsk Hello Ihar, as stated earlier, if you'd like us to review your booking, please DM us with the following information: 
+- Confirmation number: 
+- Pin code: 
+- Name on the reservation: 
+- Details regarding your request: https://t.co/Z89AAoEgD7</t>
+        </is>
+      </c>
+      <c r="G539" t="inlineStr"/>
+      <c r="H539" t="inlineStr"/>
+      <c r="I539" t="inlineStr"/>
+      <c r="J539" t="inlineStr"/>
+      <c r="K539" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2079500070500573543</t>
+        </is>
+      </c>
+      <c r="L539" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M539" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N539" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O539" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B540" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C540" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D540" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E540" t="inlineStr">
+        <is>
+          <t>Tue Jul 21 09:31:31 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F540" t="inlineStr">
+        <is>
+          <t>Hola Nala, lamentamos tu experiencia. Esperamos que hayas podido comunicar cualquier inconveniente directamente con el alojamiento mientras estabas allí, ya que son quienes están en mejor posición para abordar y resolver cualquier incidencia.
+Para que podamos ayudarte desde aquí, envíanos por favor un mensaje privado con la siguiente información:
+- Número de confirmación
+- Código PIN
+- Nombre del huésped
+- Detalles sobre tu estancia
+Te responderemos lo antes posible. Como alternativa, para recibir ayuda inmediata siempre puedes llamarnos aquí: https://t.co/o8QyR8SaDb</t>
+        </is>
+      </c>
+      <c r="G540" t="inlineStr"/>
+      <c r="H540" t="inlineStr"/>
+      <c r="I540" t="inlineStr"/>
+      <c r="J540" t="inlineStr"/>
+      <c r="K540" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2079499502944182600</t>
+        </is>
+      </c>
+      <c r="L540" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M540" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N540" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O540" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B541" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C541" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D541" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E541" t="inlineStr">
+        <is>
+          <t>Tue Jul 21 09:24:50 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F541" t="inlineStr">
+        <is>
+          <t>Ciao Diana, siamo dispiaciuti di apprendere che c'è un rimborso in sospeso. Se la tua richiesta riguarda una prenotazione di una struttura, inviaci un messaggio privato con i seguenti dati e ti risponderemo il prima possibile:
+- Numero di conferma
+- Codice PIN
+- Nome indicato sulla prenotazione</t>
+        </is>
+      </c>
+      <c r="G541" t="inlineStr"/>
+      <c r="H541" t="inlineStr"/>
+      <c r="I541" t="inlineStr"/>
+      <c r="J541" t="inlineStr"/>
+      <c r="K541" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2079497820332081329</t>
+        </is>
+      </c>
+      <c r="L541" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M541" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N541" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O541" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B542" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C542" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D542" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E542" t="inlineStr">
+        <is>
+          <t>Tue Jul 21 09:20:36 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F542" t="inlineStr">
+        <is>
+          <t>Merci pour votre réponse, Candice, et pardonnez notre retour tardif. Sachez que la sécurité de nos clients et partenaires est primordiale. Nous améliorons constamment nos mesures de sécurité pour assurer une protection optimale. Chaque hébergeur qui publie son établissement sur notre plateforme s’engage à respecter les lois locales et à se soumettre à des contrôles approfondis par nos équipes dédiées afin de vérifier sa légitimité et ses standards opérationnels.
+Nos protocoles incluent une surveillance 24/7 par des équipes spécialisées en sécurité et en lutte contre la fraude, utilisant des outils avancés pour détecter rapidement toute activité suspecte. Dans le cas rare où un incident imprévu surviendrait dans un établissement, notre service client est disponible à tout moment pour offrir une assistance.
+ Vous trouverez plus de conseils et de recommandations dans notre centre de ressources en matière de sécurité : https://t.co/ejRulr54aP 
+Nous restons à votre disposition pour toute aide complémentaire.
+Cordialement.</t>
+        </is>
+      </c>
+      <c r="G542" t="inlineStr"/>
+      <c r="H542" t="inlineStr"/>
+      <c r="I542" t="inlineStr"/>
+      <c r="J542" t="inlineStr"/>
+      <c r="K542" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2079496754492236277</t>
+        </is>
+      </c>
+      <c r="L542" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M542" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N542" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O542" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B543" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C543" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D543" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E543" t="inlineStr">
+        <is>
+          <t>Tue Jul 21 09:07:25 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F543" t="inlineStr">
+        <is>
+          <t>Hi there, we regret hearing about your experience. If our customer service team has already provided you with a resolution, we regret to inform you that we cannot change it. However, we can review your booking to ensure that all necessary procedures were adhered to. To proceed, please send us a direct message with the following information, and we will respond to you as quickly as we can:
+- Confirmation number:
+- Pin code:
+- Name on the reservation:
+- Details on your request:
+Please bear in mind that our Social Media Team doesn't work in real time. For immediate support, please call our 24/7 Customer Service Team - our contact details can be found here: https://t.co/o8QyR8SaDb
+Also, at this time, we only offer support for accommodation bookings via social media. For questions about Flights, Taxis, or Insurance, you can reach out to the dedicated support team here: https://t.co/UfRgpDJomK</t>
+        </is>
+      </c>
+      <c r="G543" t="inlineStr"/>
+      <c r="H543" t="inlineStr"/>
+      <c r="I543" t="inlineStr"/>
+      <c r="J543" t="inlineStr"/>
+      <c r="K543" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2079493439117226044</t>
+        </is>
+      </c>
+      <c r="L543" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M543" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N543" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O543" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B544" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C544" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D544" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E544" t="inlineStr">
+        <is>
+          <t>Tue Jul 21 08:39:07 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F544" t="inlineStr">
+        <is>
+          <t>@pablolozal Sentimos lo ocurrido con la reserva, Pablo. Respondimos tu mensaje privado.
+Saludos.</t>
+        </is>
+      </c>
+      <c r="G544" t="inlineStr"/>
+      <c r="H544" t="inlineStr"/>
+      <c r="I544" t="inlineStr"/>
+      <c r="J544" t="inlineStr"/>
+      <c r="K544" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2079486314743832823</t>
+        </is>
+      </c>
+      <c r="L544" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M544" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N544" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O544" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B545" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C545" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D545" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E545" t="inlineStr">
+        <is>
+          <t>Tue Jul 21 08:38:44 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F545" t="inlineStr">
+        <is>
+          <t>We understand your frustration, as said before, but you need to understand that we do not support our partner through social media channels, we do not have the tools to help you with your request. 
+We can only suggest you to get in contact with our colleagues through the methods provided before, either through the inbox section of your extranet or via phone.</t>
+        </is>
+      </c>
+      <c r="G545" t="inlineStr"/>
+      <c r="H545" t="inlineStr"/>
+      <c r="I545" t="inlineStr"/>
+      <c r="J545" t="inlineStr"/>
+      <c r="K545" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2079486220405448826</t>
+        </is>
+      </c>
+      <c r="L545" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M545" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N545" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O545" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B546" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C546" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D546" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E546" t="inlineStr">
+        <is>
+          <t>Tue Jul 21 08:37:03 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F546" t="inlineStr">
+        <is>
+          <t>Bonjour, merci de nous avoir contactés, veuillez pardonner notre réponse tardive. Nous sommes navrés de lire les difficultés rencontrées avec votre annonce. Nous comprenons que vous espériez obtenir une résolution en nous contactant et sachez que nous aimerions vous assister cependant pour des raisons de sécurité et de confidentialité, nous ne fournissons aucune assistance aux partenaires sur les réseaux sociaux.
+Seule notre équipe d'assistance partenaire sera en position de vous assister en toute sécurité afin de répondre à vos questions. Celle-ci est disponible 24h/24 et 7j/7, voici les informations nécessaires pour les contacter : https://t.co/NwbHxvAhmK
+Nous vous remercions pour votre compréhension.
+Passez une agréable journée.</t>
+        </is>
+      </c>
+      <c r="G546" t="inlineStr"/>
+      <c r="H546" t="inlineStr"/>
+      <c r="I546" t="inlineStr"/>
+      <c r="J546" t="inlineStr"/>
+      <c r="K546" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2079485795908415666</t>
+        </is>
+      </c>
+      <c r="L546" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M546" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N546" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O546" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B547" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C547" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D547" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E547" t="inlineStr">
+        <is>
+          <t>Tue Jul 21 08:12:28 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F547" t="inlineStr">
+        <is>
+          <t>@Michevwells Hello,
+For security purposes, we are unable to offer support to our partners via social media. However, you can find the contact information for our Partner Support team here: https://t.co/N4c4HTAv4f?</t>
+        </is>
+      </c>
+      <c r="G547" t="inlineStr"/>
+      <c r="H547" t="inlineStr"/>
+      <c r="I547" t="inlineStr"/>
+      <c r="J547" t="inlineStr"/>
+      <c r="K547" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2079479609460961281</t>
+        </is>
+      </c>
+      <c r="L547" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M547" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N547" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O547" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="inlineStr">
+        <is>
+          <t>Mondee</t>
+        </is>
+      </c>
+      <c r="B548" t="inlineStr">
+        <is>
+          <t>Booking.com for Travel Agents</t>
+        </is>
+      </c>
+      <c r="C548" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D548" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E548" t="inlineStr">
+        <is>
+          <t>Tue Jul 21 18:23:45 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F548" t="inlineStr">
+        <is>
+          <t>@Ameerat_alwardd We have sent you a private message; kindly check it at your earliest convenience. Thank you.</t>
+        </is>
+      </c>
+      <c r="G548" t="inlineStr"/>
+      <c r="H548" t="inlineStr"/>
+      <c r="I548" t="inlineStr"/>
+      <c r="J548" t="inlineStr"/>
+      <c r="K548" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2079633442929520797</t>
+        </is>
+      </c>
+      <c r="L548" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M548" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N548" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O548" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/News_Dashboard/data/social_media_posts.xlsx
+++ b/News_Dashboard/data/social_media_posts.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O548"/>
+  <dimension ref="A1:O588"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35004,6 +35004,2614 @@
         </is>
       </c>
     </row>
+    <row r="549">
+      <c r="A549" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B549" t="inlineStr">
+        <is>
+          <t>Navan</t>
+        </is>
+      </c>
+      <c r="C549" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D549" t="inlineStr">
+        <is>
+          <t>navan</t>
+        </is>
+      </c>
+      <c r="E549" t="inlineStr">
+        <is>
+          <t>Wed Jul 22 13:56:46 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F549" t="inlineStr">
+        <is>
+          <t>Navan is proud to have been named one of the World’s Top Fintech Companies by @CNBC and @Statista 🏆🌎
+Building the best travel agency on the planet is a big goal. Helping 12,500+ customers manage millions of bookings each year shows us we're on the right path, but we’re just getting started.
+To the incredible people who trust us to make human connections and travel seamless, thank you!
+Read more at https://t.co/DaoAPjX5jk</t>
+        </is>
+      </c>
+      <c r="G549" t="inlineStr"/>
+      <c r="H549" t="inlineStr"/>
+      <c r="I549" t="inlineStr"/>
+      <c r="J549" t="inlineStr"/>
+      <c r="K549" t="inlineStr">
+        <is>
+          <t>https://x.com/Navan/status/2079928645175439809</t>
+        </is>
+      </c>
+      <c r="L549" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M549" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N549" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O549" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B550" t="inlineStr">
+        <is>
+          <t>SAP Concur</t>
+        </is>
+      </c>
+      <c r="C550" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="D550" t="inlineStr">
+        <is>
+          <t>SAP Concur</t>
+        </is>
+      </c>
+      <c r="E550" t="inlineStr">
+        <is>
+          <t>2026-07-21T19:48:05.000Z</t>
+        </is>
+      </c>
+      <c r="F550" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Look again at employee experience with Concur Expense
+</t>
+        </is>
+      </c>
+      <c r="G550" t="inlineStr"/>
+      <c r="H550" t="inlineStr"/>
+      <c r="I550" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=S-UWVsRu8t8</t>
+        </is>
+      </c>
+      <c r="J550" t="inlineStr">
+        <is>
+          <t>[Failed to fetch]</t>
+        </is>
+      </c>
+      <c r="K550" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=S-UWVsRu8t8</t>
+        </is>
+      </c>
+      <c r="L550" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M550" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N550" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O550" t="inlineStr">
+        <is>
+          <t>Failed to analyze video transcript via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B551" t="inlineStr">
+        <is>
+          <t>SAP Concur</t>
+        </is>
+      </c>
+      <c r="C551" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="D551" t="inlineStr">
+        <is>
+          <t>SAP Concur</t>
+        </is>
+      </c>
+      <c r="E551" t="inlineStr">
+        <is>
+          <t>2026-07-21T21:03:31.000Z</t>
+        </is>
+      </c>
+      <c r="F551" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Look again at visibility and control with Concur Travel
+</t>
+        </is>
+      </c>
+      <c r="G551" t="inlineStr"/>
+      <c r="H551" t="inlineStr"/>
+      <c r="I551" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=NX53Hmqpepw</t>
+        </is>
+      </c>
+      <c r="J551" t="inlineStr">
+        <is>
+          <t>[Failed to fetch]</t>
+        </is>
+      </c>
+      <c r="K551" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=NX53Hmqpepw</t>
+        </is>
+      </c>
+      <c r="L551" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M551" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N551" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O551" t="inlineStr">
+        <is>
+          <t>Failed to analyze video transcript via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B552" t="inlineStr">
+        <is>
+          <t>SAP Concur</t>
+        </is>
+      </c>
+      <c r="C552" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="D552" t="inlineStr">
+        <is>
+          <t>SAP Concur</t>
+        </is>
+      </c>
+      <c r="E552" t="inlineStr">
+        <is>
+          <t>2026-07-22T17:21:59.000Z</t>
+        </is>
+      </c>
+      <c r="F552" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Guía para Principiantes sobre las Integraciones de SAP Concur
+</t>
+        </is>
+      </c>
+      <c r="G552" t="inlineStr"/>
+      <c r="H552" t="inlineStr"/>
+      <c r="I552" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=c5Dk-nO3wxI</t>
+        </is>
+      </c>
+      <c r="J552" t="inlineStr">
+        <is>
+          <t>[Failed to fetch]</t>
+        </is>
+      </c>
+      <c r="K552" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=c5Dk-nO3wxI</t>
+        </is>
+      </c>
+      <c r="L552" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M552" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N552" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O552" t="inlineStr">
+        <is>
+          <t>Failed to analyze video transcript via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B553" t="inlineStr">
+        <is>
+          <t>SAP Concur</t>
+        </is>
+      </c>
+      <c r="C553" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="D553" t="inlineStr">
+        <is>
+          <t>SAP Concur</t>
+        </is>
+      </c>
+      <c r="E553" t="inlineStr">
+        <is>
+          <t>2026-07-21T19:51:45.000Z</t>
+        </is>
+      </c>
+      <c r="F553" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Look again at AP efficiency with Concur Invoice
+</t>
+        </is>
+      </c>
+      <c r="G553" t="inlineStr"/>
+      <c r="H553" t="inlineStr"/>
+      <c r="I553" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=81CEsCFF20A</t>
+        </is>
+      </c>
+      <c r="J553" t="inlineStr">
+        <is>
+          <t>[Failed to fetch]</t>
+        </is>
+      </c>
+      <c r="K553" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=81CEsCFF20A</t>
+        </is>
+      </c>
+      <c r="L553" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M553" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N553" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O553" t="inlineStr">
+        <is>
+          <t>Failed to analyze video transcript via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B554" t="inlineStr">
+        <is>
+          <t>SAP Concur</t>
+        </is>
+      </c>
+      <c r="C554" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="D554" t="inlineStr">
+        <is>
+          <t>SAP Concur</t>
+        </is>
+      </c>
+      <c r="E554" t="inlineStr">
+        <is>
+          <t>2026-07-22T15:47:13.000Z</t>
+        </is>
+      </c>
+      <c r="F554" t="inlineStr">
+        <is>
+          <t xml:space="preserve">How Meteor Education used visibility, Verify, and AI to finally hit budget
+</t>
+        </is>
+      </c>
+      <c r="G554" t="inlineStr"/>
+      <c r="H554" t="inlineStr"/>
+      <c r="I554" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=N9vjga6h-dA</t>
+        </is>
+      </c>
+      <c r="J554" t="inlineStr">
+        <is>
+          <t>[Failed to fetch]</t>
+        </is>
+      </c>
+      <c r="K554" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=N9vjga6h-dA</t>
+        </is>
+      </c>
+      <c r="L554" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M554" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N554" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O554" t="inlineStr">
+        <is>
+          <t>Failed to analyze video transcript via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B555" t="inlineStr">
+        <is>
+          <t>Ramp</t>
+        </is>
+      </c>
+      <c r="C555" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D555" t="inlineStr">
+        <is>
+          <t>tryramp</t>
+        </is>
+      </c>
+      <c r="E555" t="inlineStr">
+        <is>
+          <t>Wed Jul 22 00:07:06 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F555" t="inlineStr">
+        <is>
+          <t>@zebriez @camillericketts https://t.co/WaRQaT5Ypz</t>
+        </is>
+      </c>
+      <c r="G555" t="inlineStr"/>
+      <c r="H555" t="inlineStr"/>
+      <c r="I555" t="inlineStr"/>
+      <c r="J555" t="inlineStr"/>
+      <c r="K555" t="inlineStr">
+        <is>
+          <t>https://x.com/tryramp/status/2079719852596433261</t>
+        </is>
+      </c>
+      <c r="L555" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M555" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N555" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O555" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B556" t="inlineStr">
+        <is>
+          <t>Ramp</t>
+        </is>
+      </c>
+      <c r="C556" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D556" t="inlineStr">
+        <is>
+          <t>tryramp</t>
+        </is>
+      </c>
+      <c r="E556" t="inlineStr">
+        <is>
+          <t>Tue Jul 21 21:11:52 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F556" t="inlineStr">
+        <is>
+          <t>@figma Design is Jimothy</t>
+        </is>
+      </c>
+      <c r="G556" t="inlineStr"/>
+      <c r="H556" t="inlineStr"/>
+      <c r="I556" t="inlineStr"/>
+      <c r="J556" t="inlineStr"/>
+      <c r="K556" t="inlineStr">
+        <is>
+          <t>https://x.com/tryramp/status/2079675751519932869</t>
+        </is>
+      </c>
+      <c r="L556" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M556" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N556" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O556" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B557" t="inlineStr">
+        <is>
+          <t>Ramp</t>
+        </is>
+      </c>
+      <c r="C557" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D557" t="inlineStr">
+        <is>
+          <t>tryramp</t>
+        </is>
+      </c>
+      <c r="E557" t="inlineStr">
+        <is>
+          <t>Tue Jul 21 20:27:26 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F557" t="inlineStr">
+        <is>
+          <t>@grebby SOURCES SAY THEY’RE STABLE</t>
+        </is>
+      </c>
+      <c r="G557" t="inlineStr"/>
+      <c r="H557" t="inlineStr"/>
+      <c r="I557" t="inlineStr"/>
+      <c r="J557" t="inlineStr"/>
+      <c r="K557" t="inlineStr">
+        <is>
+          <t>https://x.com/tryramp/status/2079664569211933182</t>
+        </is>
+      </c>
+      <c r="L557" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M557" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N557" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O557" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B558" t="inlineStr">
+        <is>
+          <t>Ramp</t>
+        </is>
+      </c>
+      <c r="C558" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D558" t="inlineStr">
+        <is>
+          <t>tryramp</t>
+        </is>
+      </c>
+      <c r="E558" t="inlineStr">
+        <is>
+          <t>Tue Jul 21 20:25:40 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F558" t="inlineStr">
+        <is>
+          <t>@damianplayer major 🔑</t>
+        </is>
+      </c>
+      <c r="G558" t="inlineStr"/>
+      <c r="H558" t="inlineStr"/>
+      <c r="I558" t="inlineStr"/>
+      <c r="J558" t="inlineStr"/>
+      <c r="K558" t="inlineStr">
+        <is>
+          <t>https://x.com/tryramp/status/2079664124296909293</t>
+        </is>
+      </c>
+      <c r="L558" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M558" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N558" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O558" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B559" t="inlineStr">
+        <is>
+          <t>Ramp</t>
+        </is>
+      </c>
+      <c r="C559" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D559" t="inlineStr">
+        <is>
+          <t>tryramp</t>
+        </is>
+      </c>
+      <c r="E559" t="inlineStr">
+        <is>
+          <t>Tue Jul 21 20:24:57 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F559" t="inlineStr">
+        <is>
+          <t>@solana This post has been fact checked by real global stablecoin enjoyers</t>
+        </is>
+      </c>
+      <c r="G559" t="inlineStr"/>
+      <c r="H559" t="inlineStr"/>
+      <c r="I559" t="inlineStr"/>
+      <c r="J559" t="inlineStr"/>
+      <c r="K559" t="inlineStr">
+        <is>
+          <t>https://x.com/tryramp/status/2079663943862124715</t>
+        </is>
+      </c>
+      <c r="L559" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M559" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N559" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O559" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B560" t="inlineStr">
+        <is>
+          <t>Brex</t>
+        </is>
+      </c>
+      <c r="C560" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D560" t="inlineStr">
+        <is>
+          <t>brexhq</t>
+        </is>
+      </c>
+      <c r="E560" t="inlineStr">
+        <is>
+          <t>Wed Jul 22 16:40:47 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F560" t="inlineStr">
+        <is>
+          <t>AI agents are getting their own corporate cards👀 
+@sumeetm breaks down why that's happening 7x faster than you'd think</t>
+        </is>
+      </c>
+      <c r="G560" t="inlineStr"/>
+      <c r="H560" t="inlineStr"/>
+      <c r="I560" t="inlineStr"/>
+      <c r="J560" t="inlineStr"/>
+      <c r="K560" t="inlineStr">
+        <is>
+          <t>https://x.com/brexHQ/status/2079969917999128765</t>
+        </is>
+      </c>
+      <c r="L560" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M560" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N560" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O560" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B561" t="inlineStr">
+        <is>
+          <t>Brex</t>
+        </is>
+      </c>
+      <c r="C561" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D561" t="inlineStr">
+        <is>
+          <t>brexhq</t>
+        </is>
+      </c>
+      <c r="E561" t="inlineStr">
+        <is>
+          <t>Wed Jul 22 16:14:17 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F561" t="inlineStr">
+        <is>
+          <t>Nobody wants to be the engineer manually doing a big, painful, and slow framework upgrade for a quarter. 
+Sofhia de Souza Gonçalves built a self-correcting agent pipeline in @cursor_ai instead, and accelerated that old, manual work model by 32x. 
+Full read below 👇</t>
+        </is>
+      </c>
+      <c r="G561" t="inlineStr"/>
+      <c r="H561" t="inlineStr"/>
+      <c r="I561" t="inlineStr"/>
+      <c r="J561" t="inlineStr"/>
+      <c r="K561" t="inlineStr">
+        <is>
+          <t>https://x.com/brexHQ/status/2079963251996041560</t>
+        </is>
+      </c>
+      <c r="L561" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M561" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N561" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O561" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B562" t="inlineStr">
+        <is>
+          <t>Brex</t>
+        </is>
+      </c>
+      <c r="C562" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D562" t="inlineStr">
+        <is>
+          <t>brexhq</t>
+        </is>
+      </c>
+      <c r="E562" t="inlineStr">
+        <is>
+          <t>Wed Jul 22 15:32:32 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F562" t="inlineStr">
+        <is>
+          <t>https://t.co/9GG6t0qQ1V</t>
+        </is>
+      </c>
+      <c r="G562" t="inlineStr"/>
+      <c r="H562" t="inlineStr"/>
+      <c r="I562" t="inlineStr"/>
+      <c r="J562" t="inlineStr"/>
+      <c r="K562" t="inlineStr">
+        <is>
+          <t>https://x.com/brexHQ/status/2079952745130258554</t>
+        </is>
+      </c>
+      <c r="L562" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M562" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N562" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O562" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B563" t="inlineStr">
+        <is>
+          <t>Brex</t>
+        </is>
+      </c>
+      <c r="C563" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="D563" t="inlineStr">
+        <is>
+          <t>brex</t>
+        </is>
+      </c>
+      <c r="E563" t="inlineStr">
+        <is>
+          <t>2026-07-22T02:57:26.000Z</t>
+        </is>
+      </c>
+      <c r="F563" t="inlineStr">
+        <is>
+          <t>❤️💜
+-
+-
+-
+-
+#accord #honda #hondaaccordsport #hondaaccord2021 #accordsport accordnation 10thgenaccord hondaaccord viral stancelife cars stance jdm jdmcars jdmculture hondaaccord turbo10thaccord genaccord accordsociety accord airsuspension gen yofer yoferdesign 10thgenaccord
+accord honda hondaaccordsport hondaaccord2021 accordsport accordnation 10thgenaccord hondaaccord staticlife viral staticlyfe stancelife statio bmw cars stance jdmcars jdmculture hondaaccord
+turbo10thaccord genaccord accordsociety accord airsuspension</t>
+        </is>
+      </c>
+      <c r="G563" t="inlineStr">
+        <is>
+          <t>https://scontent-ord5-1.cdninstagram.com/v/t51.82787-15/753396799_18148855300509920_4703080248097108738_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_ht=scontent-ord5-1.cdninstagram.com&amp;_nc_cat=108&amp;_nc_oc=Q6cZ2gEOWvjvMzSw-jJk_6VI2_SwoleSyTKqivualo4wyudb_5G649SBJQdenuKTBqISy7c&amp;_nc_ohc=mVXoPs0bvmsQ7kNvwF4RIET&amp;_nc_gid=Dfe285taFbenlWL7eYrY3w&amp;edm=ADp7STQBAAAA&amp;ccb=7-5&amp;oh=00_AQCTFftcE1LDc2tr3aazkHBM14cuNXq2R3QoyDI6DFxBWw&amp;oe=6A66E615&amp;_nc_sid=c6f216</t>
+        </is>
+      </c>
+      <c r="H563" t="inlineStr">
+        <is>
+          <t>[easyocr not installed. Run 'pip install easyocr torch torchvision']</t>
+        </is>
+      </c>
+      <c r="I563" t="inlineStr">
+        <is>
+          <t>https://instagram.fhnl3-2.fna.fbcdn.net/o1/v/t2/f2/m86/AQMxN34XeMnIHELcZzR3-pgsMU7ygnBDxu2_kQRcD9GKKLmAYYWUB82HzI2-KbT-4o1PhW1h9IXVyz22znkOmE-huQoY4IR8hkb8orM.mp4?_nc_cat=111&amp;_nc_oc=Ado60NrF9a-C0uwnAYr_8GKeiDKhS2pArPF5c3Nu_50jtPb8wN15lwFaGyqF1u--I7XUPoGTVm-8t05LE-_4B6_m&amp;_nc_sid=5e9851&amp;_nc_ht=instagram.fhnl3-2.fna.fbcdn.net&amp;_nc_ohc=-Pac6fHDS3cQ7kNvwHox74J&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uQ0xJUFMuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTQzNjQ0NzQ1MTY1MjIxMCwiYXNzZXRfYWdlX2RheXMiOjAsInZpX3VzZWNhc2VfaWQiOjEwMDk5LCJkdXJhdGlvbl9zIjoxMiwidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=d54a6f461c62368f&amp;_nc_vs=HBksFQIYUmlnX3hwdl9yZWVsc19wZXJtYW5lbnRfc3JfcHJvZC83RDQ4NTg2NDY3MkIwQ0I3RkVDOEMwQ0I0NUQxM0Q5RF92aWRlb19kYXNoaW5pdC5tcDQVAALIARIAFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyLzlENDYzMzYyQzI3NDk1NkNERERGRTQ4MDk3RDQ4Qjg1X2F1ZGlvX2Rhc2hpbml0Lm1wNBUCAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbkgcHBn5yNBRUCKAJDMywXQCgAAAAAAAAYEmRhc2hfYmFzZWxpbmVfMV92MREAdf4HZeadAQA&amp;_nc_gid=vGJF5Crc4RhT8sEnSfc29w&amp;_nc_ss=72689&amp;_nc_map=urlgen_bucketless&amp;_nc_zt=28&amp;oh=00_AQC8tUMOcmxtcNG8R_Et8ih10GkME9z-nWH7VJ53eQOVlw&amp;oe=6A62CA14</t>
+        </is>
+      </c>
+      <c r="J563" t="inlineStr">
+        <is>
+          <t>[faster-whisper not installed. Run 'pip install faster-whisper']</t>
+        </is>
+      </c>
+      <c r="K563" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DbFEUkXMGVK/</t>
+        </is>
+      </c>
+      <c r="L563" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M563" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N563" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O563" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B564" t="inlineStr">
+        <is>
+          <t>Expedia</t>
+        </is>
+      </c>
+      <c r="C564" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D564" t="inlineStr">
+        <is>
+          <t>Expedia</t>
+        </is>
+      </c>
+      <c r="E564" t="inlineStr">
+        <is>
+          <t>Wed Jul 22 00:00:00 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F564" t="inlineStr">
+        <is>
+          <t>Planning a trip to Paraguay? 🇵🇾
+➡️ The Ruins: Wander the towering red-brick Jesuit ruins of Trinidad as the fading sun casts long shadows over the grass
+➡️ The Culture: Sit in the shade of a lapacho tree and share ice-cold tereré from a traditional guampa horn
+➡️ The Stays: Skip standard hotels and sleep in a beautifully restored colonial estancia surrounded by vast, open ranchlands
+🔗 Plan your travel: https://t.co/ZZ2iWjM4c9</t>
+        </is>
+      </c>
+      <c r="G564" t="inlineStr"/>
+      <c r="H564" t="inlineStr"/>
+      <c r="I564" t="inlineStr"/>
+      <c r="J564" t="inlineStr"/>
+      <c r="K564" t="inlineStr">
+        <is>
+          <t>https://x.com/Expedia/status/2079718066015903979</t>
+        </is>
+      </c>
+      <c r="L564" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M564" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N564" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O564" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B565" t="inlineStr">
+        <is>
+          <t>Expedia</t>
+        </is>
+      </c>
+      <c r="C565" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D565" t="inlineStr">
+        <is>
+          <t>Expedia</t>
+        </is>
+      </c>
+      <c r="E565" t="inlineStr">
+        <is>
+          <t>Tue Jul 21 20:05:00 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F565" t="inlineStr">
+        <is>
+          <t>Planning a Disney trip? 🏰
+Get an extra 10% off Disney Theme Park tickets with code DISNEY10 and add more magic to your adventure. ©Disney 2026
+Book by 7/26/26, travel by 9/30/26. While supplies last, subject to availability. Terms apply. https://t.co/TJKo1EJglq</t>
+        </is>
+      </c>
+      <c r="G565" t="inlineStr"/>
+      <c r="H565" t="inlineStr"/>
+      <c r="I565" t="inlineStr"/>
+      <c r="J565" t="inlineStr"/>
+      <c r="K565" t="inlineStr">
+        <is>
+          <t>https://x.com/Expedia/status/2079658925066993994</t>
+        </is>
+      </c>
+      <c r="L565" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M565" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N565" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O565" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B566" t="inlineStr">
+        <is>
+          <t>Expedia</t>
+        </is>
+      </c>
+      <c r="C566" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D566" t="inlineStr">
+        <is>
+          <t>Expedia</t>
+        </is>
+      </c>
+      <c r="E566" t="inlineStr">
+        <is>
+          <t>2026-07-22T15:26:00.940Z</t>
+        </is>
+      </c>
+      <c r="F566" t="inlineStr">
+        <is>
+          <t>Set-jetting through Greece to discover the real places that inspired The Odyssey. 🏛️⛵
+From caves once believed to be home to Cyclops, to beaches tied to ancient Greek legends, sailing between islands and staying in a traditional stone villa this trip felt like stepping into mythology.
+➡️ Start planning now: http://ms.spr.ly/6042v4tXy</t>
+        </is>
+      </c>
+      <c r="G566" t="inlineStr"/>
+      <c r="H566" t="inlineStr"/>
+      <c r="I566" t="inlineStr">
+        <is>
+          <t>https://dms.licdn.com/playlist/vid/v2/D4E10AQFEfX0V6o1XoA/mp4-720p-30fp-crf28/B4EZ.G9VgZH8Bo-/0/1784675667738?e=1785351600&amp;v=beta&amp;t=MDi-GBU68f0VLzWANLullEf5_gazLhDYfpGdcZ5t2LI</t>
+        </is>
+      </c>
+      <c r="J566" t="inlineStr">
+        <is>
+          <t>[faster-whisper not installed. Run 'pip install faster-whisper']</t>
+        </is>
+      </c>
+      <c r="K566" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/expedia_odyssey-set-jet-activity-7485716791307030529-xYF6</t>
+        </is>
+      </c>
+      <c r="L566" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M566" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N566" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O566" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B567" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C567" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D567" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E567" t="inlineStr">
+        <is>
+          <t>Wed Jul 22 14:42:03 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F567" t="inlineStr">
+        <is>
+          <t>Hi Sachi, thank you for getting back to us. Please note that our Social Media Team operates separately from our customer service team and therefore is unable to see any previous communication due to privacy. If you'd like our team to look into this, then kindly share the booking details that we've requested before. Otherwise, we won't be able to help. Looking forward to your DM.</t>
+        </is>
+      </c>
+      <c r="G567" t="inlineStr"/>
+      <c r="H567" t="inlineStr"/>
+      <c r="I567" t="inlineStr"/>
+      <c r="J567" t="inlineStr"/>
+      <c r="K567" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2079940039950135796</t>
+        </is>
+      </c>
+      <c r="L567" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M567" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N567" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O567" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B568" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C568" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D568" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E568" t="inlineStr">
+        <is>
+          <t>Wed Jul 22 14:28:14 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F568" t="inlineStr">
+        <is>
+          <t>@LeoMrtn_ Bonjour! Nous avons bien reçu votre message privé et nous venons à l'instant de vous répondre, nous vous invitons à le consulter dès que vous aurez un moment.
+Merci à vous ! https://t.co/Z89AAoEgD7</t>
+        </is>
+      </c>
+      <c r="G568" t="inlineStr"/>
+      <c r="H568" t="inlineStr"/>
+      <c r="I568" t="inlineStr"/>
+      <c r="J568" t="inlineStr"/>
+      <c r="K568" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2079936563677384959</t>
+        </is>
+      </c>
+      <c r="L568" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M568" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N568" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O568" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B569" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C569" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D569" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E569" t="inlineStr">
+        <is>
+          <t>Wed Jul 22 13:40:19 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F569" t="inlineStr">
+        <is>
+          <t>@717_159 Hi there, thank you for contacting us. We regret to hear about your experience. We're here to help, feel free to drop us a DM with your booking information and we'll be happy to help. https://t.co/Z89AAoEgD7</t>
+        </is>
+      </c>
+      <c r="G569" t="inlineStr"/>
+      <c r="H569" t="inlineStr"/>
+      <c r="I569" t="inlineStr"/>
+      <c r="J569" t="inlineStr"/>
+      <c r="K569" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2079924502834679929</t>
+        </is>
+      </c>
+      <c r="L569" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M569" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N569" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O569" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B570" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C570" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D570" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E570" t="inlineStr">
+        <is>
+          <t>Wed Jul 22 13:10:08 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F570" t="inlineStr">
+        <is>
+          <t>Hi there, we regret to hear, that you did not receive your booking confirmation yet. 
+For us to be able to assist you we kindly ask you to DM us the following information: 
+- Name of the Accommodation
+- Dates of Stay
+- Email address used to make the booking
+- Name of the Guest 
+- full Name of the Person reaching out to us
+We'll than get back to you as soon as possible.</t>
+        </is>
+      </c>
+      <c r="G570" t="inlineStr"/>
+      <c r="H570" t="inlineStr"/>
+      <c r="I570" t="inlineStr"/>
+      <c r="J570" t="inlineStr"/>
+      <c r="K570" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2079916909839962231</t>
+        </is>
+      </c>
+      <c r="L570" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M570" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N570" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O570" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B571" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C571" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D571" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E571" t="inlineStr">
+        <is>
+          <t>Wed Jul 22 13:04:08 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F571" t="inlineStr">
+        <is>
+          <t>Hi Mike, thanks for your message.
+Rest assured that we don't hesitate to issue refunds if we have the accommodation's approval, and if we have received the money back from them. If you didn't get a refund so far, it means that we are still waiting for the accommodation.
+Our social media team can review your booking to confirm this, please DM us the:
+- Pin code, 
+- Full guest name,
+and we will get back to you as soon as possible.</t>
+        </is>
+      </c>
+      <c r="G571" t="inlineStr"/>
+      <c r="H571" t="inlineStr"/>
+      <c r="I571" t="inlineStr"/>
+      <c r="J571" t="inlineStr"/>
+      <c r="K571" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2079915396048486736</t>
+        </is>
+      </c>
+      <c r="L571" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M571" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N571" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O571" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B572" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C572" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D572" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E572" t="inlineStr">
+        <is>
+          <t>Wed Jul 22 12:30:57 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F572" t="inlineStr">
+        <is>
+          <t>Hi there, we regret to hear the hotel wasn’t able to accommodate you. On https://t.co/fGhmZE7riF, room availability is managed directly by the property, and they’re responsible for keeping it accurate. 
+If a property can’t honor a booking, they should help you find an alternative place to stay. If they’re unable or unwilling to do so, they should inform us as soon as possible so we can help find a solution. Please send a private message with the following details:
+- Confirmation number:
+- Pin code:
+- Name on the reservation:
+Alternatively, for immediate support you can always give us a call here: https://t.co/o8QyR8SaDb.</t>
+        </is>
+      </c>
+      <c r="G572" t="inlineStr"/>
+      <c r="H572" t="inlineStr"/>
+      <c r="I572" t="inlineStr"/>
+      <c r="J572" t="inlineStr"/>
+      <c r="K572" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2079907047680659776</t>
+        </is>
+      </c>
+      <c r="L572" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M572" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N572" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O572" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B573" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C573" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D573" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E573" t="inlineStr">
+        <is>
+          <t>Wed Jul 22 12:25:28 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F573" t="inlineStr">
+        <is>
+          <t>Hola Rob, gracias por contactarnos.
+Aunque nos gustaría asistir, en redes sociales tenemos acceso únicamente para reservas de alojamiento. En el siguiente enlace encontrarás la información de contacto de nuestro equipo de atención al cliente para reservas de vuelo: https://t.co/0VBK0krD8X
+Un saludo.</t>
+        </is>
+      </c>
+      <c r="G573" t="inlineStr"/>
+      <c r="H573" t="inlineStr"/>
+      <c r="I573" t="inlineStr"/>
+      <c r="J573" t="inlineStr"/>
+      <c r="K573" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2079905669222683034</t>
+        </is>
+      </c>
+      <c r="L573" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M573" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N573" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O573" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B574" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C574" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D574" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E574" t="inlineStr">
+        <is>
+          <t>Wed Jul 22 11:41:48 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F574" t="inlineStr">
+        <is>
+          <t>Thank you for reaching out, Neil. We understand how disappointing this situation must be, especially with your trip so close.
+If you still require assistance, please send us a private message with the following information so we can review your case and follow up:
+* Confirmation number
+* PIN code
+* Full name of the guest on the booking
+Once we've received these details, we'll look into the matter and get back to you as soon as possible.</t>
+        </is>
+      </c>
+      <c r="G574" t="inlineStr"/>
+      <c r="H574" t="inlineStr"/>
+      <c r="I574" t="inlineStr"/>
+      <c r="J574" t="inlineStr"/>
+      <c r="K574" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2079894678330126590</t>
+        </is>
+      </c>
+      <c r="L574" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M574" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N574" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O574" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B575" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C575" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D575" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E575" t="inlineStr">
+        <is>
+          <t>Wed Jul 22 11:29:37 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F575" t="inlineStr">
+        <is>
+          <t>@MaryOrtegaB Hi there, unfortunately we're unable to assist with Flight reservations through social media, but you can contact our Flights team here: https://t.co/Z8ou85LCWJ, or call {US}+1 917 421 7240 / {UK}+44 2039019061 / {IE} +353 19075677</t>
+        </is>
+      </c>
+      <c r="G575" t="inlineStr"/>
+      <c r="H575" t="inlineStr"/>
+      <c r="I575" t="inlineStr"/>
+      <c r="J575" t="inlineStr"/>
+      <c r="K575" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2079891610372825246</t>
+        </is>
+      </c>
+      <c r="L575" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M575" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N575" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O575" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B576" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C576" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D576" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E576" t="inlineStr">
+        <is>
+          <t>Wed Jul 22 11:14:38 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F576" t="inlineStr">
+        <is>
+          <t>Hi Darina, it is possible the booking did not go through. Refunds for incomplete bookings are automatically processed within 24 hours and take a few days to reach your account depending on your bank.
+If you think it's possible you may've made typo in your email address whilst booking, DM the following:
+-- Hotel name
+-- Name on the booking
+-- Dates of stay
+-- Correct Email address.
+and we can take a look to see if there are any confirmed bookings for you.</t>
+        </is>
+      </c>
+      <c r="G576" t="inlineStr"/>
+      <c r="H576" t="inlineStr"/>
+      <c r="I576" t="inlineStr"/>
+      <c r="J576" t="inlineStr"/>
+      <c r="K576" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2079887840758935937</t>
+        </is>
+      </c>
+      <c r="L576" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M576" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N576" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O576" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B577" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C577" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D577" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E577" t="inlineStr">
+        <is>
+          <t>Wed Jul 22 11:12:03 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F577" t="inlineStr">
+        <is>
+          <t>Hello Dominic, thank you for contacting us. We regret hearing about the difficulties you are experiencing. However, please note that our social media team operates independently from our customer service team. If you would like us to investigate the situation, please send us a direct message with the following information:
+- Reservation Number:
+- PIN Code:
+- Name associated with the Reservation.
+We hope you were able to discuss any issues directly with the property during your stay, as they are best equipped to handle and resolve any concerns.</t>
+        </is>
+      </c>
+      <c r="G577" t="inlineStr"/>
+      <c r="H577" t="inlineStr"/>
+      <c r="I577" t="inlineStr"/>
+      <c r="J577" t="inlineStr"/>
+      <c r="K577" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2079887190528520300</t>
+        </is>
+      </c>
+      <c r="L577" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M577" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N577" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O577" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B578" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C578" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D578" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E578" t="inlineStr">
+        <is>
+          <t>Wed Jul 22 11:08:56 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F578" t="inlineStr">
+        <is>
+          <t>@marcovoltaico We're glad to hear that you are satisfied with our assistance. Please do not hesitate to reach out to us for any further inquiries. Regards</t>
+        </is>
+      </c>
+      <c r="G578" t="inlineStr"/>
+      <c r="H578" t="inlineStr"/>
+      <c r="I578" t="inlineStr"/>
+      <c r="J578" t="inlineStr"/>
+      <c r="K578" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2079886405614907664</t>
+        </is>
+      </c>
+      <c r="L578" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M578" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N578" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O578" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B579" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C579" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D579" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E579" t="inlineStr">
+        <is>
+          <t>Wed Jul 22 11:01:33 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F579" t="inlineStr">
+        <is>
+          <t>Hello, we regret hearing about your dissatisfaction.
+If you need help, feel free to let us know and share more details regarding your inquiry.
+We can also take a look at your booking if you send us the following details via DM:
+- Confirmation number, 
+- Pin code, 
+- Full guest name,
+and we will get back to you as soon as possible.</t>
+        </is>
+      </c>
+      <c r="G579" t="inlineStr"/>
+      <c r="H579" t="inlineStr"/>
+      <c r="I579" t="inlineStr"/>
+      <c r="J579" t="inlineStr"/>
+      <c r="K579" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2079884550948159813</t>
+        </is>
+      </c>
+      <c r="L579" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M579" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N579" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O579" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B580" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C580" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D580" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E580" t="inlineStr">
+        <is>
+          <t>Wed Jul 22 10:59:48 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F580" t="inlineStr">
+        <is>
+          <t>Hi there, thank you for contacting us. We regret hearing that you're still waiting on a refund. If you need support with an accommodation booking, please DM us your: 
+- Confirmation number, 
+- PIN-code, 
+- Name on the reservation,
+so we can look into this for you.
+At this time, we only offer support for accommodation bookings via social media. For questions about Flights, Taxis, or Insurance, you can reach out to the dedicated support team here: https://t.co/TBejpc4vOA.</t>
+        </is>
+      </c>
+      <c r="G580" t="inlineStr"/>
+      <c r="H580" t="inlineStr"/>
+      <c r="I580" t="inlineStr"/>
+      <c r="J580" t="inlineStr"/>
+      <c r="K580" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2079884109770322263</t>
+        </is>
+      </c>
+      <c r="L580" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M580" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N580" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O580" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B581" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C581" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D581" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E581" t="inlineStr">
+        <is>
+          <t>Wed Jul 22 10:46:01 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F581" t="inlineStr">
+        <is>
+          <t>@tfoster2021 Hi Tiffany, we regret to hear about your experience. We'd like to look into this, and see how we can help you. To proceed, kindly send us a DM with the following information:
+-confirmation number
+-PIN code
+-full name of the guest
+And we'll get back to you as soon as possible.</t>
+        </is>
+      </c>
+      <c r="G581" t="inlineStr"/>
+      <c r="H581" t="inlineStr"/>
+      <c r="I581" t="inlineStr"/>
+      <c r="J581" t="inlineStr"/>
+      <c r="K581" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2079880641504518453</t>
+        </is>
+      </c>
+      <c r="L581" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M581" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N581" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O581" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B582" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C582" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D582" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E582" t="inlineStr">
+        <is>
+          <t>Wed Jul 22 10:43:06 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F582" t="inlineStr">
+        <is>
+          <t>@CarlosM41664303 Bonjour Carlos, merci de nous avoir contactés. Nous vous avons envoyé un message privé. Pourriez-vous le consulter dès que possible ?</t>
+        </is>
+      </c>
+      <c r="G582" t="inlineStr"/>
+      <c r="H582" t="inlineStr"/>
+      <c r="I582" t="inlineStr"/>
+      <c r="J582" t="inlineStr"/>
+      <c r="K582" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2079879905974628496</t>
+        </is>
+      </c>
+      <c r="L582" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M582" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N582" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O582" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B583" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C583" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D583" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E583" t="inlineStr">
+        <is>
+          <t>Wed Jul 22 10:37:10 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F583" t="inlineStr">
+        <is>
+          <t>@trailing_dev We are unable to provide support to partners from our side on the Social Media Team; however, you can reach out directly here for more guidance: 
+* https://t.co/N4c4HTAv4f?</t>
+        </is>
+      </c>
+      <c r="G583" t="inlineStr"/>
+      <c r="H583" t="inlineStr"/>
+      <c r="I583" t="inlineStr"/>
+      <c r="J583" t="inlineStr"/>
+      <c r="K583" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2079878411053322423</t>
+        </is>
+      </c>
+      <c r="L583" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M583" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N583" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O583" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B584" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C584" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D584" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E584" t="inlineStr">
+        <is>
+          <t>Wed Jul 22 10:26:33 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F584" t="inlineStr">
+        <is>
+          <t>Hi Marco,
+as mentioned, the invoice can only be issued by the accommodation, as they are the service provider.
+If you need help contacting the property for this request, you can send us a private message with these details: 
+- Confirmation number 
+- PIN code 
+- Guest name 
+Best Regards</t>
+        </is>
+      </c>
+      <c r="G584" t="inlineStr"/>
+      <c r="H584" t="inlineStr"/>
+      <c r="I584" t="inlineStr"/>
+      <c r="J584" t="inlineStr"/>
+      <c r="K584" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2079875738883281322</t>
+        </is>
+      </c>
+      <c r="L584" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M584" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N584" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O584" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B585" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C585" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D585" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E585" t="inlineStr">
+        <is>
+          <t>Wed Jul 22 10:04:53 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F585" t="inlineStr">
+        <is>
+          <t>@cpbimal Hi there. We regret to hear about the delay in response from our support, and we're here to help. Please send us a private message with the following details:
+- Confirmation number
+- PIN
+- Name on the reservation
+And we will get back to you as soon as possible. https://t.co/Z89AAoEgD7</t>
+        </is>
+      </c>
+      <c r="G585" t="inlineStr"/>
+      <c r="H585" t="inlineStr"/>
+      <c r="I585" t="inlineStr"/>
+      <c r="J585" t="inlineStr"/>
+      <c r="K585" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2079870286812283129</t>
+        </is>
+      </c>
+      <c r="L585" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M585" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N585" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O585" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B586" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C586" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D586" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E586" t="inlineStr">
+        <is>
+          <t>Wed Jul 22 10:01:54 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F586" t="inlineStr">
+        <is>
+          <t>Thank you for reaching out. We understand you have concerns regarding an additional charge request and that you have been unable to reach the team for further assistance.
+If you still require support, please send us a private message with more details about the charge, along with the following booking information:
+* Confirmation number
+* PIN code
+* Full name of the guest on the reservation
+Once we receive these details, we’ll review the matter and follow up with you accordingly.</t>
+        </is>
+      </c>
+      <c r="G586" t="inlineStr"/>
+      <c r="H586" t="inlineStr"/>
+      <c r="I586" t="inlineStr"/>
+      <c r="J586" t="inlineStr"/>
+      <c r="K586" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2079869537009197449</t>
+        </is>
+      </c>
+      <c r="L586" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M586" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N586" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O586" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" t="inlineStr">
+        <is>
+          <t>Mondee</t>
+        </is>
+      </c>
+      <c r="B587" t="inlineStr">
+        <is>
+          <t>Sky Bird Travel</t>
+        </is>
+      </c>
+      <c r="C587" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D587" t="inlineStr">
+        <is>
+          <t>SkyBirdTravel</t>
+        </is>
+      </c>
+      <c r="E587" t="inlineStr">
+        <is>
+          <t>Wed Jul 22 16:56:49 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F587" t="inlineStr">
+        <is>
+          <t>Boost every booking. Earn 25% commission on travel insurance while giving clients peace of mind. Add value, protect travelers, and grow your revenue—all in one step.
+Book now on WINGS! https://t.co/ctFwiJyiud
+#TravelAgent #TravelInsurance #TravelAdvisor #TravelProfessionals https://t.co/Q9gKa9cM44</t>
+        </is>
+      </c>
+      <c r="G587" t="inlineStr"/>
+      <c r="H587" t="inlineStr"/>
+      <c r="I587" t="inlineStr"/>
+      <c r="J587" t="inlineStr"/>
+      <c r="K587" t="inlineStr">
+        <is>
+          <t>https://x.com/SkyBirdTravel/status/2079973953804939333</t>
+        </is>
+      </c>
+      <c r="L587" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M587" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N587" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O587" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" t="inlineStr">
+        <is>
+          <t>Mondee</t>
+        </is>
+      </c>
+      <c r="B588" t="inlineStr">
+        <is>
+          <t>Sky Bird Travel</t>
+        </is>
+      </c>
+      <c r="C588" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D588" t="inlineStr">
+        <is>
+          <t>Sky Bird Travel &amp; Tours</t>
+        </is>
+      </c>
+      <c r="E588" t="inlineStr">
+        <is>
+          <t>2026-07-22T16:23:55.499Z</t>
+        </is>
+      </c>
+      <c r="F588" t="inlineStr">
+        <is>
+          <t>Turn every booking into a bigger opportunity. Earn 25% commission on travel insurance while giving your clients the peace of mind they deserve. It’s an easy way to add value to every itinerary, protect your travelers from the unexpected, and grow your revenue-all in one place. 
+Book now on WINGS! https://bit.ly/4ahXS0u
+#TravelAgent #TravelInsurance #TravelAdvisor #TravelProfessionals #TravelSales #Commission #TravelBusiness #WINGS #BookWithConfidence</t>
+        </is>
+      </c>
+      <c r="G588" t="inlineStr">
+        <is>
+          <t>https://media.licdn.com/dms/image/v2/D4E22AQGSC2jQrhwNvw/feedshare-shrink_1280/B4EZ.KpAbBJMAM-/0/1784737434258?e=1786579200&amp;v=beta&amp;t=e-xSQAGUBtAH_oZ0cZGYeFXTpsYtTQSa61r0IdHBA6w</t>
+        </is>
+      </c>
+      <c r="H588" t="inlineStr">
+        <is>
+          <t>[easyocr not installed. Run 'pip install easyocr torch torchvision']</t>
+        </is>
+      </c>
+      <c r="I588" t="inlineStr"/>
+      <c r="J588" t="inlineStr"/>
+      <c r="K588" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/sky-bird-travel-tours_travelagent-travelinsurance-traveladvisor-activity-7485731364663717888-lUKK</t>
+        </is>
+      </c>
+      <c r="L588" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M588" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N588" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O588" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/News_Dashboard/data/social_media_posts.xlsx
+++ b/News_Dashboard/data/social_media_posts.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O588"/>
+  <dimension ref="A1:O615"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37612,6 +37612,1764 @@
         </is>
       </c>
     </row>
+    <row r="589">
+      <c r="A589" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B589" t="inlineStr">
+        <is>
+          <t>Navan</t>
+        </is>
+      </c>
+      <c r="C589" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D589" t="inlineStr">
+        <is>
+          <t>navan</t>
+        </is>
+      </c>
+      <c r="E589" t="inlineStr">
+        <is>
+          <t>Wed Jul 22 21:10:19 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F589" t="inlineStr">
+        <is>
+          <t>Look who @arielcoco found! 😎</t>
+        </is>
+      </c>
+      <c r="G589" t="inlineStr"/>
+      <c r="H589" t="inlineStr"/>
+      <c r="I589" t="inlineStr"/>
+      <c r="J589" t="inlineStr"/>
+      <c r="K589" t="inlineStr">
+        <is>
+          <t>https://x.com/Navan/status/2080037749512384964</t>
+        </is>
+      </c>
+      <c r="L589" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M589" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N589" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O589" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B590" t="inlineStr">
+        <is>
+          <t>Navan</t>
+        </is>
+      </c>
+      <c r="C590" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="D590" t="inlineStr">
+        <is>
+          <t>getnavan</t>
+        </is>
+      </c>
+      <c r="E590" t="inlineStr">
+        <is>
+          <t>2026-07-23T16:03:25.000Z</t>
+        </is>
+      </c>
+      <c r="F590" t="inlineStr">
+        <is>
+          <t>What should you do if your journey takes you to San Francisco?
+Gary, SVP of Global Account Management at @adyen, has you covered with his 48-hour itinerary featuring all of the hits.</t>
+        </is>
+      </c>
+      <c r="G590" t="inlineStr">
+        <is>
+          <t>https://scontent-cdg4-1.cdninstagram.com/v/t51.82787-15/755464532_18476492350110668_6335843408885087884_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_ht=scontent-cdg4-1.cdninstagram.com&amp;_nc_cat=108&amp;_nc_oc=Q6cZ2gGt0NHBshPeFz-2gHDwLqHy9Ya7vKP9NHvYD-i0sAlKfr28Sp9aMlS5ylDkz4n5dsExaRLildd-bin6LesuvV08&amp;_nc_ohc=vQCJOqc99isQ7kNvwHZCb-F&amp;_nc_gid=EtpQVXgcw8WdwfzmgAEEHA&amp;edm=ADp7STQBAAAA&amp;ccb=7-5&amp;oh=00_AQAQFl_Ta_8U4C_fCybsuSVX0Nr5eSDKr6MicR5fYPb1SQ&amp;oe=6A683EC6&amp;_nc_sid=c6f216</t>
+        </is>
+      </c>
+      <c r="H590" t="inlineStr">
+        <is>
+          <t>[easyocr not installed. Run 'pip install easyocr torch torchvision']</t>
+        </is>
+      </c>
+      <c r="I590" t="inlineStr">
+        <is>
+          <t>https://scontent-cdg4-2.cdninstagram.com/o1/v/t2/f2/m86/AQNcoFo9-oj2Vi1-Br33QJoa5Ckx2CxrS7VIACPCJZ3C11dWmse5DBiai3WjEAzi2sqHfX1P15jiqNP-EbDv5OUhBgBzyv0KndPaekc.mp4?_nc_cat=100&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-cdg4-2.cdninstagram.com&amp;_nc_ohc=lctKKAjbPcIQ7kNvwGMElGD&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uQ0xJUFMuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTA2MjQyNDYxNjMzODUwNywiYXNzZXRfYWdlX2RheXMiOjAsInZpX3VzZWNhc2VfaWQiOjEwMDk5LCJkdXJhdGlvbl9zIjozMywidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=c4981eb01f7103c4&amp;_nc_vs=HBksFQIYUmlnX3hwdl9yZWVsc19wZXJtYW5lbnRfc3JfcHJvZC8yQjRFMTgyRjRBQTBBOThDQTQwMjA5Qzc4RUZGREU4MF92aWRlb19kYXNoaW5pdC5tcDQVAALIARIAFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyLzIwNDU0NEZERkY4REYyNDIzQzExMjcxMTZFNDMxREJGX2F1ZGlvX2Rhc2hpbml0Lm1wNBUCAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACaWkdydoJHjAxUCKAJDMywXQEC0OVgQYk4YEmRhc2hfYmFzZWxpbmVfMV92MREAdf4HZeadAQA&amp;_nc_gid=rFf4_WT8t6bI4yRqnUJi1w&amp;_nc_ss=72a8c&amp;_nc_zt=28&amp;oh=00_AQC_342vFAopvzTv8CLxtdLO7RAGB_tipU-gr9tWvS2UwA&amp;oe=6A6429F1</t>
+        </is>
+      </c>
+      <c r="J590" t="inlineStr">
+        <is>
+          <t>[faster-whisper not installed. Run 'pip install faster-whisper']</t>
+        </is>
+      </c>
+      <c r="K590" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DbJDHPep_0L/</t>
+        </is>
+      </c>
+      <c r="L590" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M590" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N590" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O590" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B591" t="inlineStr">
+        <is>
+          <t>TravelPerk</t>
+        </is>
+      </c>
+      <c r="C591" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D591" t="inlineStr">
+        <is>
+          <t>Perk</t>
+        </is>
+      </c>
+      <c r="E591" t="inlineStr">
+        <is>
+          <t>2026-07-23T11:00:51.106Z</t>
+        </is>
+      </c>
+      <c r="F591" t="inlineStr">
+        <is>
+          <t>Another week, another first: introducing Entry Ready. 🛂
+Perk is now the first AI-native travel and spend management platform to integrate visa applications and purchase at the point of booking.
+41% of people traveling for work needed a visa last year. Most were left to figure it out, pay out of pocket, and chase reimbursement after.
+Here’s how Entry Ready works:
+1. Check your visa requirements instantly before an international flight
+2. Perk guides you to the correct eVisa or travel authorization for your trip
+3. You pay for the eVisa or travel authorization directly in Perk
+4. Complete the application with our trusted partner Sherpa°
+Crossing borders, made simple.
+Learn more: https://okt.to/vxcd1V</t>
+        </is>
+      </c>
+      <c r="G591" t="inlineStr"/>
+      <c r="H591" t="inlineStr"/>
+      <c r="I591" t="inlineStr">
+        <is>
+          <t>https://dms.licdn.com/playlist/vid/v2/D4E10AQFwzhnRytMO1Q/mp4-720p-30fp-crf28/B4EZ.OoiHoHsBo-/0/1784804423279?e=1785438000&amp;v=beta&amp;t=-CS-g3zzNdwsbEFeCDcw2PnnbaD8V9-FO_hWm_rFe6k</t>
+        </is>
+      </c>
+      <c r="J591" t="inlineStr">
+        <is>
+          <t>[faster-whisper not installed. Run 'pip install faster-whisper']</t>
+        </is>
+      </c>
+      <c r="K591" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/perk_another-week-another-first-introducing-activity-7486012448492224513-smkW</t>
+        </is>
+      </c>
+      <c r="L591" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M591" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N591" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O591" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B592" t="inlineStr">
+        <is>
+          <t>SAP Concur</t>
+        </is>
+      </c>
+      <c r="C592" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="D592" t="inlineStr">
+        <is>
+          <t>SAP Concur</t>
+        </is>
+      </c>
+      <c r="E592" t="inlineStr">
+        <is>
+          <t>2026-07-22T18:09:59.000Z</t>
+        </is>
+      </c>
+      <c r="F592" t="inlineStr">
+        <is>
+          <t xml:space="preserve">How SAP Concur Transformed Travel Spend Reporting
+</t>
+        </is>
+      </c>
+      <c r="G592" t="inlineStr"/>
+      <c r="H592" t="inlineStr"/>
+      <c r="I592" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=B_SnjBhsBBY</t>
+        </is>
+      </c>
+      <c r="J592" t="inlineStr">
+        <is>
+          <t>[Failed to fetch]</t>
+        </is>
+      </c>
+      <c r="K592" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=B_SnjBhsBBY</t>
+        </is>
+      </c>
+      <c r="L592" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M592" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N592" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O592" t="inlineStr">
+        <is>
+          <t>Failed to analyze video transcript via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B593" t="inlineStr">
+        <is>
+          <t>Brex</t>
+        </is>
+      </c>
+      <c r="C593" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D593" t="inlineStr">
+        <is>
+          <t>brexhq</t>
+        </is>
+      </c>
+      <c r="E593" t="inlineStr">
+        <is>
+          <t>Wed Jul 22 20:53:06 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F593" t="inlineStr">
+        <is>
+          <t>@axrahman See you upstairs.</t>
+        </is>
+      </c>
+      <c r="G593" t="inlineStr"/>
+      <c r="H593" t="inlineStr"/>
+      <c r="I593" t="inlineStr"/>
+      <c r="J593" t="inlineStr"/>
+      <c r="K593" t="inlineStr">
+        <is>
+          <t>https://x.com/brexHQ/status/2080033415332602211</t>
+        </is>
+      </c>
+      <c r="L593" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M593" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N593" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O593" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B594" t="inlineStr">
+        <is>
+          <t>Brex</t>
+        </is>
+      </c>
+      <c r="C594" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D594" t="inlineStr">
+        <is>
+          <t>brexhq</t>
+        </is>
+      </c>
+      <c r="E594" t="inlineStr">
+        <is>
+          <t>Wed Jul 22 18:51:42 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F594" t="inlineStr">
+        <is>
+          <t>@n2parko Cursor 🤝 Brex</t>
+        </is>
+      </c>
+      <c r="G594" t="inlineStr"/>
+      <c r="H594" t="inlineStr"/>
+      <c r="I594" t="inlineStr"/>
+      <c r="J594" t="inlineStr"/>
+      <c r="K594" t="inlineStr">
+        <is>
+          <t>https://x.com/brexHQ/status/2080002865586680169</t>
+        </is>
+      </c>
+      <c r="L594" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M594" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N594" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O594" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B595" t="inlineStr">
+        <is>
+          <t>AirBnb</t>
+        </is>
+      </c>
+      <c r="C595" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="D595" t="inlineStr">
+        <is>
+          <t>airbnb</t>
+        </is>
+      </c>
+      <c r="E595" t="inlineStr">
+        <is>
+          <t>2026-07-22T21:00:07.000Z</t>
+        </is>
+      </c>
+      <c r="F595" t="inlineStr">
+        <is>
+          <t>Now you can get a rental car on Airbnb.</t>
+        </is>
+      </c>
+      <c r="G595" t="inlineStr">
+        <is>
+          <t>https://scontent-ams2-1.cdninstagram.com/v/t51.82787-15/753541413_18616000774063838_3275431657645551324_n.jpg?stp=dst-jpg_e35_p1080x1080_sh2.08_tt6&amp;_nc_ht=scontent-ams2-1.cdninstagram.com&amp;_nc_cat=102&amp;_nc_oc=Q6cZ2gEHOqY_AmzgG8WGDAEVCDSHYFj4V6ssPlH170R5DOwcuIiQfFTC5p9gLPLT_GzVlK8&amp;_nc_ohc=QtxolZ-4B-UQ7kNvwES07_L&amp;_nc_gid=iTYvR5sBCI_0iSmbiCYP6g&amp;edm=ADp7STQBAAAA&amp;ccb=7-5&amp;oh=00_AQAZDAdN8k7FjbiKdtrUa2B85EpY4OuxtgWGO_KzavH3AQ&amp;oe=6A681FD9&amp;_nc_sid=c6f216</t>
+        </is>
+      </c>
+      <c r="H595" t="inlineStr">
+        <is>
+          <t>[easyocr not installed. Run 'pip install easyocr torch torchvision']</t>
+        </is>
+      </c>
+      <c r="I595" t="inlineStr">
+        <is>
+          <t>https://scontent-ams2-1.cdninstagram.com/o1/v/t2/f2/m86/AQPAEL6jrWPOYO0l9jhNm4jm8M-mH4NvTerLkddP5x4mx9Oup6x7wKILnVCYfntJZ8aCDAhDqvyiT2ochwDXxKQCoJqwvtZzom5MqKk.mp4?_nc_cat=106&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-ams2-1.cdninstagram.com&amp;_nc_ohc=FWM4FUYtunQQ7kNvwFODY5L&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uQ0xJUFMuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTA2ODc4MTc1MjQ5OTc0MiwiYXNzZXRfYWdlX2RheXMiOjAsInZpX3VzZWNhc2VfaWQiOjEwMDk5LCJkdXJhdGlvbl9zIjoxMiwidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=2c327bb5d6a6ffa0&amp;_nc_vs=HBksFQIYUmlnX3hwdl9yZWVsc19wZXJtYW5lbnRfc3JfcHJvZC85MDRBN0IzMDM5RkU4Qjc1MzJERUM1OEMwNUIyRERBRF92aWRlb19kYXNoaW5pdC5tcDQVAALIARIAFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyL0NGNDBEQ0RCNEJGNDQ2QzMyQUUwNzkxNkQ4NzdGRjkyX2F1ZGlvX2Rhc2hpbml0Lm1wNBUCAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACa8-JnLpIPmAxUCKAJDMywXQChmZmZmZmYYEmRhc2hfYmFzZWxpbmVfMV92MREAdf4HZeadAQA&amp;_nc_gid=jTZNFE0ppn3l9lFBoy6KNg&amp;_nc_ss=7ca8c&amp;_nc_zt=28&amp;oh=00_AQDXl1bpLq4L9WKXdYHXMkmHXPRM3lFGfJHqGTnum8_bDQ&amp;oe=6A641DA7</t>
+        </is>
+      </c>
+      <c r="J595" t="inlineStr">
+        <is>
+          <t>[faster-whisper not installed. Run 'pip install faster-whisper']</t>
+        </is>
+      </c>
+      <c r="K595" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DbHAWsgB5Xd/</t>
+        </is>
+      </c>
+      <c r="L595" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M595" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N595" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O595" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B596" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C596" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D596" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E596" t="inlineStr">
+        <is>
+          <t>Thu Jul 23 17:00:14 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F596" t="inlineStr">
+        <is>
+          <t>@zd1tx Hi there, we have replied to your private message; kindly review it at your convenience. https://t.co/Z89AAoEgD7</t>
+        </is>
+      </c>
+      <c r="G596" t="inlineStr"/>
+      <c r="H596" t="inlineStr"/>
+      <c r="I596" t="inlineStr"/>
+      <c r="J596" t="inlineStr"/>
+      <c r="K596" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2080337203406700592</t>
+        </is>
+      </c>
+      <c r="L596" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M596" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N596" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O596" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B597" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C597" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D597" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E597" t="inlineStr">
+        <is>
+          <t>Thu Jul 23 16:57:37 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F597" t="inlineStr">
+        <is>
+          <t>Hi there, we regret to hear about the unfortunate accident you experienced. We understand your concerns regarding your travel insurance, and we are here to support you during this difficult time. If your request is related to an accommodation booking, or you need any help with an insurance you bought via https://t.co/fGhmZE7riF, feel free to DM us the following details, and we'll take a look into this for you. This information is needed in order for us to look into your reservation and be able to share further information regarding your query:
+- Confirmation number:
+- PIN code:
+- The name on the reservation:</t>
+        </is>
+      </c>
+      <c r="G597" t="inlineStr"/>
+      <c r="H597" t="inlineStr"/>
+      <c r="I597" t="inlineStr"/>
+      <c r="J597" t="inlineStr"/>
+      <c r="K597" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2080336545249218900</t>
+        </is>
+      </c>
+      <c r="L597" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M597" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N597" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O597" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B598" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C598" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D598" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E598" t="inlineStr">
+        <is>
+          <t>Thu Jul 23 13:55:44 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F598" t="inlineStr">
+        <is>
+          <t>Hi there, we regret to hear, that your still waiting for a response regarding your complaint. For us to be able to look into this, we kindly ask you to DM us the following booking details: 
+- Confirmation Number
+- Pin Code
+- Name of the Guest 
+We'll than get back to you as soon as possible.</t>
+        </is>
+      </c>
+      <c r="G598" t="inlineStr"/>
+      <c r="H598" t="inlineStr"/>
+      <c r="I598" t="inlineStr"/>
+      <c r="J598" t="inlineStr"/>
+      <c r="K598" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2080290772071465055</t>
+        </is>
+      </c>
+      <c r="L598" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M598" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N598" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O598" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B599" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C599" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D599" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E599" t="inlineStr">
+        <is>
+          <t>Thu Jul 23 13:42:38 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F599" t="inlineStr">
+        <is>
+          <t>@snimda Te sugerimos enviar la información requerida a través de un DM, y con mucho gusto la revisaremos para ofrecerte una respuesta. https://t.co/Z89AAoEgD7</t>
+        </is>
+      </c>
+      <c r="G599" t="inlineStr"/>
+      <c r="H599" t="inlineStr"/>
+      <c r="I599" t="inlineStr"/>
+      <c r="J599" t="inlineStr"/>
+      <c r="K599" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2080287474098577493</t>
+        </is>
+      </c>
+      <c r="L599" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M599" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N599" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O599" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B600" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C600" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D600" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E600" t="inlineStr">
+        <is>
+          <t>Thu Jul 23 13:41:11 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F600" t="inlineStr">
+        <is>
+          <t>Bonjour,  
+nous souhaiterions consulter plus en détail cette réservation pour vous. Merci de nous envoyer un message privé avec les informations suivantes :  
+- Numéro de confirmation  
+- Code confidentiel  
+- Nom complet du voyageur  
+Une fois que nous aurons reçu ces informations, nous pourrons consulter votre dossier et revenir vers vous.  
+Bien cordialement.</t>
+        </is>
+      </c>
+      <c r="G600" t="inlineStr"/>
+      <c r="H600" t="inlineStr"/>
+      <c r="I600" t="inlineStr"/>
+      <c r="J600" t="inlineStr"/>
+      <c r="K600" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2080287109160550886</t>
+        </is>
+      </c>
+      <c r="L600" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M600" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N600" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O600" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B601" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C601" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D601" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E601" t="inlineStr">
+        <is>
+          <t>Thu Jul 23 13:33:45 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F601" t="inlineStr">
+        <is>
+          <t>Hi there, thank you for contacting us. We regret hearing that your account was compromised and the credits were used without consent.
+We'd like to review what has happened and how we can help. Please DM us the following:
+- Your full name,
+- E-mail address linked to your account,
+so we can follow up.</t>
+        </is>
+      </c>
+      <c r="G601" t="inlineStr"/>
+      <c r="H601" t="inlineStr"/>
+      <c r="I601" t="inlineStr"/>
+      <c r="J601" t="inlineStr"/>
+      <c r="K601" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2080285240224850268</t>
+        </is>
+      </c>
+      <c r="L601" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M601" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N601" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O601" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B602" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C602" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D602" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E602" t="inlineStr">
+        <is>
+          <t>Thu Jul 23 13:16:33 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F602" t="inlineStr">
+        <is>
+          <t>@JeanHatchet Hello Jean, our dedicated team has contacted you through email with an update regarding your case. Please take a moment to review it. Feel free to reach out if you have any additional questions. https://t.co/Z89AAoEgD7</t>
+        </is>
+      </c>
+      <c r="G602" t="inlineStr"/>
+      <c r="H602" t="inlineStr"/>
+      <c r="I602" t="inlineStr"/>
+      <c r="J602" t="inlineStr"/>
+      <c r="K602" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2080280911686304170</t>
+        </is>
+      </c>
+      <c r="L602" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M602" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N602" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O602" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B603" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C603" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D603" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E603" t="inlineStr">
+        <is>
+          <t>Thu Jul 23 13:12:57 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F603" t="inlineStr">
+        <is>
+          <t>Hi Catherine, thank you for contacting us. We regret hearing that your daughter was misinformed by a third party. Please note that we do not offer any support through WhatsApp, and it's not possible to make any reservations through e-mail on your behalf, as bookings can only be made through our website or app yourselves. We recommend not to engage with third parties.</t>
+        </is>
+      </c>
+      <c r="G603" t="inlineStr"/>
+      <c r="H603" t="inlineStr"/>
+      <c r="I603" t="inlineStr"/>
+      <c r="J603" t="inlineStr"/>
+      <c r="K603" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2080280005767008439</t>
+        </is>
+      </c>
+      <c r="L603" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M603" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N603" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O603" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B604" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C604" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D604" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E604" t="inlineStr">
+        <is>
+          <t>Thu Jul 23 12:46:45 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F604" t="inlineStr">
+        <is>
+          <t>Bonjour Chloé, la décision de renoncer à d’éventuels frais d’annulation revient uniquement à l’hébergement, car ce sont eux qui définissent les conditions de votre réservation.  
+Nous serons ravis de consulter votre réservation ici afin de voir s’ils sont disposés à faire une exception, nous avons simplement besoin de quelques informations. Merci de nous envoyer un message privé avec les éléments suivants :  
+- Numéro de confirmation  
+- Code confidentiel  
+- Nom complet du voyageur  
+Une fois que nous aurons ces informations, nous pourrons consulter votre dossier et revenir vers vous.  
+Bien cordialement.</t>
+        </is>
+      </c>
+      <c r="G604" t="inlineStr"/>
+      <c r="H604" t="inlineStr"/>
+      <c r="I604" t="inlineStr"/>
+      <c r="J604" t="inlineStr"/>
+      <c r="K604" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2080273412610560227</t>
+        </is>
+      </c>
+      <c r="L604" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M604" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N604" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O604" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B605" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C605" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D605" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E605" t="inlineStr">
+        <is>
+          <t>Thu Jul 23 12:44:46 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F605" t="inlineStr">
+        <is>
+          <t>Hola Parcero, gracias por contactarnos. Sentimos saber acerca de lo sucedido y nos gustaría revisarlo. Para ello, compártenos los siguientes datos:
+- Número de confirmación
+- Código PIN
+- Nombre del huésped
+Te responderemos lo antes posible aunque ten en cuenta que nuestro equipo de Redes Sociales no trabaja en tiempo real. Para recibir ayuda inmediata, llama a nuestro equipo de Atención al Cliente disponible 24/7; puedes encontrar nuestros datos de contacto aquí: https://t.co/o8QyR8SaDb
+Un saludo.</t>
+        </is>
+      </c>
+      <c r="G605" t="inlineStr"/>
+      <c r="H605" t="inlineStr"/>
+      <c r="I605" t="inlineStr"/>
+      <c r="J605" t="inlineStr"/>
+      <c r="K605" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2080272913266036755</t>
+        </is>
+      </c>
+      <c r="L605" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M605" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N605" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O605" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B606" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C606" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D606" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E606" t="inlineStr">
+        <is>
+          <t>Thu Jul 23 11:37:39 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F606" t="inlineStr">
+        <is>
+          <t>Hi there. You can send us a message here, or get through to an agent when calling our 24/7 support. A local number can be found here:https://t.co/qDrN6zFExv
+If you'd like us to assist you here, please send us a private message and let us know how we can help you. Please also include the following details of your booking in the message:
+- Confirmation number
+- PIN
+- Name on the reservation</t>
+        </is>
+      </c>
+      <c r="G606" t="inlineStr"/>
+      <c r="H606" t="inlineStr"/>
+      <c r="I606" t="inlineStr"/>
+      <c r="J606" t="inlineStr"/>
+      <c r="K606" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2080256023445573913</t>
+        </is>
+      </c>
+      <c r="L606" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M606" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N606" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O606" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B607" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C607" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D607" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E607" t="inlineStr">
+        <is>
+          <t>Thu Jul 23 11:25:55 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F607" t="inlineStr">
+        <is>
+          <t>Bonjour, nous souhaiterions consulter votre réservation. Merci de nous envoyer un message privé avec les informations suivantes :  
+- Numéro de confirmation  
+- Code confidentiel  
+- Nom complet du voyageur  
+Une fois que nous aurons ces informations, nous pourrons consulter votre dossier et revenir vers vous.  
+Bien cordialement.</t>
+        </is>
+      </c>
+      <c r="G607" t="inlineStr"/>
+      <c r="H607" t="inlineStr"/>
+      <c r="I607" t="inlineStr"/>
+      <c r="J607" t="inlineStr"/>
+      <c r="K607" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2080253068977881246</t>
+        </is>
+      </c>
+      <c r="L607" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M607" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N607" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O607" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B608" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C608" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D608" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E608" t="inlineStr">
+        <is>
+          <t>Thu Jul 23 11:22:09 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F608" t="inlineStr">
+        <is>
+          <t>@pala77liverpool Hi Gurpal, we've responded to your DM and look forward to your response. https://t.co/Z89AAoEgD7</t>
+        </is>
+      </c>
+      <c r="G608" t="inlineStr"/>
+      <c r="H608" t="inlineStr"/>
+      <c r="I608" t="inlineStr"/>
+      <c r="J608" t="inlineStr"/>
+      <c r="K608" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2080252119949451770</t>
+        </is>
+      </c>
+      <c r="L608" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M608" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N608" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O608" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B609" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C609" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D609" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E609" t="inlineStr">
+        <is>
+          <t>Thu Jul 23 11:17:12 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F609" t="inlineStr">
+        <is>
+          <t>@67blosssom Hi there, unfortunately we're unable to assist with Flight reservations through social media, but you can contact our Flights team here: https://t.co/Z8ou85LCWJ, or call {US}+1 917 421 7240 / {UK}+44 2039019061 / {IE} +353 19075677</t>
+        </is>
+      </c>
+      <c r="G609" t="inlineStr"/>
+      <c r="H609" t="inlineStr"/>
+      <c r="I609" t="inlineStr"/>
+      <c r="J609" t="inlineStr"/>
+      <c r="K609" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2080250875746881922</t>
+        </is>
+      </c>
+      <c r="L609" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M609" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N609" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O609" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B610" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C610" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D610" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E610" t="inlineStr">
+        <is>
+          <t>Thu Jul 23 11:13:28 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F610" t="inlineStr">
+        <is>
+          <t>Hi there, we apologize for the late response and regret to hear that your booking got cancelled. For us to be able to look into this, we kindly ask you to DM us the following booking details: 
+- Conformation Number
+- Pin Code
+- Name of the guest 
+We'll than get back to you as soon as possible.</t>
+        </is>
+      </c>
+      <c r="G610" t="inlineStr"/>
+      <c r="H610" t="inlineStr"/>
+      <c r="I610" t="inlineStr"/>
+      <c r="J610" t="inlineStr"/>
+      <c r="K610" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2080249934062719398</t>
+        </is>
+      </c>
+      <c r="L610" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M610" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N610" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O610" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B611" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C611" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D611" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E611" t="inlineStr">
+        <is>
+          <t>Thu Jul 23 10:55:18 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F611" t="inlineStr">
+        <is>
+          <t>Bonjour, nous regrettons de lire votre déception concernant ce qui s’est passé à votre arrivée, et nous souhaiterions consulter votre dossier pour vous. Merci de nous envoyer un message privé avec les informations suivantes :  
+- Numéro de confirmation  
+- Code confidentiel  
+- Nom complet du voyageur  
+Une fois que nous aurons ces informations, nous pourrons consulter votre réservation et revenir vers vous.  
+Bien cordialement.</t>
+        </is>
+      </c>
+      <c r="G611" t="inlineStr"/>
+      <c r="H611" t="inlineStr"/>
+      <c r="I611" t="inlineStr"/>
+      <c r="J611" t="inlineStr"/>
+      <c r="K611" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2080245364989280678</t>
+        </is>
+      </c>
+      <c r="L611" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M611" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N611" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O611" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B612" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C612" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D612" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E612" t="inlineStr">
+        <is>
+          <t>Thu Jul 23 10:54:09 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F612" t="inlineStr">
+        <is>
+          <t>@SamVenere2022 Autant que nous aimerions pouvoir vous aider, nous ne pouvons malheureusement pas assister pour les réservations de voiture de location via les réseaux sociaux.
+Vous pouvez contacter notre équipe spécialisée ici : https://t.co/JZB1C5lPMm</t>
+        </is>
+      </c>
+      <c r="G612" t="inlineStr"/>
+      <c r="H612" t="inlineStr"/>
+      <c r="I612" t="inlineStr"/>
+      <c r="J612" t="inlineStr"/>
+      <c r="K612" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2080245074839937409</t>
+        </is>
+      </c>
+      <c r="L612" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M612" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N612" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O612" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B613" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C613" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D613" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E613" t="inlineStr">
+        <is>
+          <t>Thu Jul 23 10:53:45 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F613" t="inlineStr">
+        <is>
+          <t>@SamVenere2022 Bonjour Sam, toutes nos excuses pour le délai de réponse. Nous recevons actuellement un volume important de demandes sur les réseaux sociaux et n’avons pas pu vous répondre plus tôt.</t>
+        </is>
+      </c>
+      <c r="G613" t="inlineStr"/>
+      <c r="H613" t="inlineStr"/>
+      <c r="I613" t="inlineStr"/>
+      <c r="J613" t="inlineStr"/>
+      <c r="K613" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2080244971911729556</t>
+        </is>
+      </c>
+      <c r="L613" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M613" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N613" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O613" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B614" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C614" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D614" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E614" t="inlineStr">
+        <is>
+          <t>Thu Jul 23 10:43:36 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F614" t="inlineStr">
+        <is>
+          <t>@GUSIL21 Hola. Agradecemos que nos hayas contactado y te informamos que ya hemos respondido a tu mensaje privado, cuando tengas oportunidad, por favor revisa tu bandeja. Gracias. https://t.co/Z89AAoEgD7</t>
+        </is>
+      </c>
+      <c r="G614" t="inlineStr"/>
+      <c r="H614" t="inlineStr"/>
+      <c r="I614" t="inlineStr"/>
+      <c r="J614" t="inlineStr"/>
+      <c r="K614" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2080242421544124807</t>
+        </is>
+      </c>
+      <c r="L614" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M614" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N614" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O614" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B615" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C615" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D615" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E615" t="inlineStr">
+        <is>
+          <t>Thu Jul 23 10:42:28 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F615" t="inlineStr">
+        <is>
+          <t>Hi Dzini, thanks for reaching out. Please DM us and let us know how we can help you. If you need support with an accommodation booking, please send us your: 
+• Confirmation number, 
+• Pin code, 
+• Name on the reservation,
+And we will get back to you as soon as possible. Keep in mind, our Social Media Team does not work in real time, for immediate support you can call our 24/7 Customer Service Team here: https://t.co/o8QyR8SaDb.
+Also, at this time, we only offer support for accommodation bookings via social media; for questions about Flights, Taxis, or Insurance, please reach out to the dedicated support team here: https://t.co/OVuF5pCzba.</t>
+        </is>
+      </c>
+      <c r="G615" t="inlineStr"/>
+      <c r="H615" t="inlineStr"/>
+      <c r="I615" t="inlineStr"/>
+      <c r="J615" t="inlineStr"/>
+      <c r="K615" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2080242133668163624</t>
+        </is>
+      </c>
+      <c r="L615" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M615" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N615" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O615" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/News_Dashboard/data/social_media_posts.xlsx
+++ b/News_Dashboard/data/social_media_posts.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O615"/>
+  <dimension ref="A1:O644"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39370,6 +39370,1854 @@
         </is>
       </c>
     </row>
+    <row r="616">
+      <c r="A616" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B616" t="inlineStr">
+        <is>
+          <t>TravelPerk</t>
+        </is>
+      </c>
+      <c r="C616" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D616" t="inlineStr">
+        <is>
+          <t>Perk</t>
+        </is>
+      </c>
+      <c r="E616" t="inlineStr">
+        <is>
+          <t>2026-07-24T07:30:16.116Z</t>
+        </is>
+      </c>
+      <c r="F616" t="inlineStr">
+        <is>
+          <t>The biggest soccer stage took over the US this summer. And your expense report knows it.
+This fall, Perk Spend brings travel and spend together, so surprise charges stay on the pitch, not on your expense report.
+Join the waitlist: https://okt.to/YjNaMg ⚽</t>
+        </is>
+      </c>
+      <c r="G616" t="inlineStr"/>
+      <c r="H616" t="inlineStr"/>
+      <c r="I616" t="inlineStr"/>
+      <c r="J616" t="inlineStr"/>
+      <c r="K616" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/perk_travel-and-spend-together-join-the-us-waitlist-activity-7486321841368875009-XyL2</t>
+        </is>
+      </c>
+      <c r="L616" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M616" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N616" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O616" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B617" t="inlineStr">
+        <is>
+          <t>Ramp</t>
+        </is>
+      </c>
+      <c r="C617" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D617" t="inlineStr">
+        <is>
+          <t>tryramp</t>
+        </is>
+      </c>
+      <c r="E617" t="inlineStr">
+        <is>
+          <t>Fri Jul 24 17:35:37 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F617" t="inlineStr">
+        <is>
+          <t>@KlausCodes https://t.co/rGnSulRubq</t>
+        </is>
+      </c>
+      <c r="G617" t="inlineStr"/>
+      <c r="H617" t="inlineStr"/>
+      <c r="I617" t="inlineStr"/>
+      <c r="J617" t="inlineStr"/>
+      <c r="K617" t="inlineStr">
+        <is>
+          <t>https://x.com/tryramp/status/2080708495431626950</t>
+        </is>
+      </c>
+      <c r="L617" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M617" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N617" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O617" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B618" t="inlineStr">
+        <is>
+          <t>Brex</t>
+        </is>
+      </c>
+      <c r="C618" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D618" t="inlineStr">
+        <is>
+          <t>brexhq</t>
+        </is>
+      </c>
+      <c r="E618" t="inlineStr">
+        <is>
+          <t>Thu Jul 23 20:13:19 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F618" t="inlineStr">
+        <is>
+          <t>@dasha_shunina Turns out SF does know how to do summer.</t>
+        </is>
+      </c>
+      <c r="G618" t="inlineStr"/>
+      <c r="H618" t="inlineStr"/>
+      <c r="I618" t="inlineStr"/>
+      <c r="J618" t="inlineStr"/>
+      <c r="K618" t="inlineStr">
+        <is>
+          <t>https://x.com/brexHQ/status/2080385795479789953</t>
+        </is>
+      </c>
+      <c r="L618" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M618" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N618" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O618" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B619" t="inlineStr">
+        <is>
+          <t>Brex</t>
+        </is>
+      </c>
+      <c r="C619" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D619" t="inlineStr">
+        <is>
+          <t>brexhq</t>
+        </is>
+      </c>
+      <c r="E619" t="inlineStr">
+        <is>
+          <t>Thu Jul 23 20:11:54 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F619" t="inlineStr">
+        <is>
+          <t>@DavidSantMon We came prepared 😎</t>
+        </is>
+      </c>
+      <c r="G619" t="inlineStr"/>
+      <c r="H619" t="inlineStr"/>
+      <c r="I619" t="inlineStr"/>
+      <c r="J619" t="inlineStr"/>
+      <c r="K619" t="inlineStr">
+        <is>
+          <t>https://x.com/brexHQ/status/2080385434954207621</t>
+        </is>
+      </c>
+      <c r="L619" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M619" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N619" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O619" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B620" t="inlineStr">
+        <is>
+          <t>Brex</t>
+        </is>
+      </c>
+      <c r="C620" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D620" t="inlineStr">
+        <is>
+          <t>brexhq</t>
+        </is>
+      </c>
+      <c r="E620" t="inlineStr">
+        <is>
+          <t>Thu Jul 23 18:53:53 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F620" t="inlineStr">
+        <is>
+          <t>@linderps here's your grammy 🏆</t>
+        </is>
+      </c>
+      <c r="G620" t="inlineStr"/>
+      <c r="H620" t="inlineStr"/>
+      <c r="I620" t="inlineStr"/>
+      <c r="J620" t="inlineStr"/>
+      <c r="K620" t="inlineStr">
+        <is>
+          <t>https://x.com/brexHQ/status/2080365805284262002</t>
+        </is>
+      </c>
+      <c r="L620" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M620" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N620" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O620" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B621" t="inlineStr">
+        <is>
+          <t>Expedia</t>
+        </is>
+      </c>
+      <c r="C621" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D621" t="inlineStr">
+        <is>
+          <t>Expedia</t>
+        </is>
+      </c>
+      <c r="E621" t="inlineStr">
+        <is>
+          <t>Fri Jul 24 00:00:00 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F621" t="inlineStr">
+        <is>
+          <t>The most breathtaking European mountain escape isn't where you think, it's in Slovenia. 🇸🇮
+➡️ The Views: Row a traditional wooden pletna boat across Lake Bled before hiking the rugged Julian Alps
+➡️ The Culture: Stroll Ljubljana’s riverfront and taste natural wines in the quiet Vipava Valley
+➡️ The Stays: Skip 5-star resorts and fall asleep in a beautifully designed off-grid treehouse
+🔗 Plan your travel:
+https://t.co/vU4Ujwum6m</t>
+        </is>
+      </c>
+      <c r="G621" t="inlineStr"/>
+      <c r="H621" t="inlineStr"/>
+      <c r="I621" t="inlineStr"/>
+      <c r="J621" t="inlineStr"/>
+      <c r="K621" t="inlineStr">
+        <is>
+          <t>https://x.com/Expedia/status/2080442842002973179</t>
+        </is>
+      </c>
+      <c r="L621" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M621" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N621" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O621" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B622" t="inlineStr">
+        <is>
+          <t>Expedia</t>
+        </is>
+      </c>
+      <c r="C622" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D622" t="inlineStr">
+        <is>
+          <t>Think with Google</t>
+        </is>
+      </c>
+      <c r="E622" t="inlineStr">
+        <is>
+          <t>2026-07-24T17:53:30.898Z</t>
+        </is>
+      </c>
+      <c r="F622" t="inlineStr">
+        <is>
+          <t>How did Expedia Group boost creative effectiveness by 800%? ⚡
+When Expedia set out to create their "Bundle in the Now" campaign, they didn’t build a traditional ad. They built a dynamic creative production system powered by Google’s AI tools.
+At #CannesLions2026, Natalie Wills, SVP of Integrated Marketing &amp; Creative at Expedia Group, shared how deploying multiple AI agents to combine traveler insights, voiceover tools, and modular assets helps them create 800 hyper-personalized ad variations a day across the full traveler journey.
+▶️Watch the full case study to see how they scale personalized creative using Google’s AI tools.</t>
+        </is>
+      </c>
+      <c r="G622" t="inlineStr"/>
+      <c r="H622" t="inlineStr"/>
+      <c r="I622" t="inlineStr">
+        <is>
+          <t>https://dms.licdn.com/playlist/vid/v2/D4E10AQFrWo73uW6e6g/mp4-720p-30fp-crf28/B4EZ.VIM5YJUBk-/0/1784913400829?e=1785524400&amp;v=beta&amp;t=ayxGjF5ISPzBom0s0_oXbWILy1wAAkjnifMZWBiVbh8</t>
+        </is>
+      </c>
+      <c r="J622" t="inlineStr">
+        <is>
+          <t>[faster-whisper not installed. Run 'pip install faster-whisper']</t>
+        </is>
+      </c>
+      <c r="K622" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/think-with-google_canneslions2026-ugcPost-7486469428654739456-JGWF</t>
+        </is>
+      </c>
+      <c r="L622" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M622" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N622" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O622" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B623" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C623" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D623" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E623" t="inlineStr">
+        <is>
+          <t>Fri Jul 24 18:10:24 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F623" t="inlineStr">
+        <is>
+          <t>@ismailneyman Hi Neyman, we would like to inform you that we have responded to your message. Please check it at your earliest convenience. Thank you for your understanding.</t>
+        </is>
+      </c>
+      <c r="G623" t="inlineStr"/>
+      <c r="H623" t="inlineStr"/>
+      <c r="I623" t="inlineStr"/>
+      <c r="J623" t="inlineStr"/>
+      <c r="K623" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2080717247153152279</t>
+        </is>
+      </c>
+      <c r="L623" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M623" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N623" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O623" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B624" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C624" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D624" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E624" t="inlineStr">
+        <is>
+          <t>Fri Jul 24 13:57:30 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F624" t="inlineStr">
+        <is>
+          <t>Hi Lukáš, we regret hearing about your dissatisfaction with the accommodation.
+Keep in mind the policies on our platform belong to the accommodations. This means only they are able to approve refunds, also after complaints. We can support you by discussing your complaint with the accommodation, to try to negotiate a favorable solution. If they refuse, we cannot force them to change their decision.
+If you're referring to compensation that you received from our colleagues, this would have been a separate offer from us, and it would not be in relation to the refund request that you made to the accommodation.
+Make sure to leave a review after your stay, this can help the accommodation to improve their overall quality and service.
+We wish you better experiences in the future.</t>
+        </is>
+      </c>
+      <c r="G624" t="inlineStr"/>
+      <c r="H624" t="inlineStr"/>
+      <c r="I624" t="inlineStr"/>
+      <c r="J624" t="inlineStr"/>
+      <c r="K624" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2080653602989727881</t>
+        </is>
+      </c>
+      <c r="L624" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M624" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N624" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O624" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B625" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C625" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D625" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E625" t="inlineStr">
+        <is>
+          <t>Fri Jul 24 13:46:04 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F625" t="inlineStr">
+        <is>
+          <t>Hi there! While we would like to help, as stated in our earlier communications, we cannot assist with flight bookings via social media. You can reach out to our Flights team at this link: https://t.co/TBejpc4vOA, or by calling call US +1 917 421 7240 / UK +44 2039019061 / IE +353 19075677. Best regards.</t>
+        </is>
+      </c>
+      <c r="G625" t="inlineStr"/>
+      <c r="H625" t="inlineStr"/>
+      <c r="I625" t="inlineStr"/>
+      <c r="J625" t="inlineStr"/>
+      <c r="K625" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2080650726393413792</t>
+        </is>
+      </c>
+      <c r="L625" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M625" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N625" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O625" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B626" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C626" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D626" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E626" t="inlineStr">
+        <is>
+          <t>Fri Jul 24 12:31:26 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F626" t="inlineStr">
+        <is>
+          <t>@gjmac1878 Hi there, we and our Customer Service are not the same department and this is your first contact with us through this via; should you like us to take a look at your case, kindly get back to us via DM as previously guided. Thank you.</t>
+        </is>
+      </c>
+      <c r="G626" t="inlineStr"/>
+      <c r="H626" t="inlineStr"/>
+      <c r="I626" t="inlineStr"/>
+      <c r="J626" t="inlineStr"/>
+      <c r="K626" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2080631946355323275</t>
+        </is>
+      </c>
+      <c r="L626" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M626" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N626" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O626" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B627" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C627" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D627" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E627" t="inlineStr">
+        <is>
+          <t>Fri Jul 24 12:15:18 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F627" t="inlineStr">
+        <is>
+          <t>@cactushoney12 As you are aware we already replied to you earlier, however we haven't received all your booking details via DM so far. Feel free to share them, then we will review your booking.</t>
+        </is>
+      </c>
+      <c r="G627" t="inlineStr"/>
+      <c r="H627" t="inlineStr"/>
+      <c r="I627" t="inlineStr"/>
+      <c r="J627" t="inlineStr"/>
+      <c r="K627" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2080627884742365511</t>
+        </is>
+      </c>
+      <c r="L627" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M627" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N627" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O627" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B628" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C628" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D628" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E628" t="inlineStr">
+        <is>
+          <t>Fri Jul 24 11:56:03 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F628" t="inlineStr">
+        <is>
+          <t>Hi there, thank you for contacting us in regards to your Car Rental reservation.
+In order for us to assist, please send us a private message with the following details:
+- Name of booker
+- Email address used to book
+- Your request
+We'll get back to you as soon as we can. Thank you.</t>
+        </is>
+      </c>
+      <c r="G628" t="inlineStr"/>
+      <c r="H628" t="inlineStr"/>
+      <c r="I628" t="inlineStr"/>
+      <c r="J628" t="inlineStr"/>
+      <c r="K628" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2080623038991679818</t>
+        </is>
+      </c>
+      <c r="L628" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M628" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N628" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O628" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B629" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C629" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D629" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E629" t="inlineStr">
+        <is>
+          <t>Fri Jul 24 10:50:41 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F629" t="inlineStr">
+        <is>
+          <t>Hi there, we regret to hear about that. While we would love to assist you with this matter via social media, we regret to inform you that we cannot provide assistance with flights through this platform. You can reach our Flights team using this link: https://t.co/OVuF5pCzba or by calling {US}+1 917 421 7240 / {UK}+44 2039019061 / {IE} +353 19075677.</t>
+        </is>
+      </c>
+      <c r="G629" t="inlineStr"/>
+      <c r="H629" t="inlineStr"/>
+      <c r="I629" t="inlineStr"/>
+      <c r="J629" t="inlineStr"/>
+      <c r="K629" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2080606588843258077</t>
+        </is>
+      </c>
+      <c r="L629" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M629" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N629" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O629" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B630" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C630" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D630" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E630" t="inlineStr">
+        <is>
+          <t>Fri Jul 24 10:49:09 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F630" t="inlineStr">
+        <is>
+          <t>@Strwbyukii Si vous avez reçu cet e‑mail en lien avec une réservation, merci d’ajouter également les informations suivantes :
+- Numéro de confirmation
+- Code confidentiel
+- Nom du voyageur indiqué sur la réservation</t>
+        </is>
+      </c>
+      <c r="G630" t="inlineStr"/>
+      <c r="H630" t="inlineStr"/>
+      <c r="I630" t="inlineStr"/>
+      <c r="J630" t="inlineStr"/>
+      <c r="K630" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2080606204615618940</t>
+        </is>
+      </c>
+      <c r="L630" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M630" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N630" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O630" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B631" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C631" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D631" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E631" t="inlineStr">
+        <is>
+          <t>Fri Jul 24 10:48:48 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F631" t="inlineStr">
+        <is>
+          <t>@Strwbyukii Nous prenons ce type de signalement très au sérieux et souhaiterions l’étudier plus en détail.
+Nous vous invitons à nous envoyer un message privé avec une capture d’écran de l’e‑mail, en incluant les informations sur l’expéditeur si elles sont visibles.</t>
+        </is>
+      </c>
+      <c r="G631" t="inlineStr"/>
+      <c r="H631" t="inlineStr"/>
+      <c r="I631" t="inlineStr"/>
+      <c r="J631" t="inlineStr"/>
+      <c r="K631" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2080606116984074750</t>
+        </is>
+      </c>
+      <c r="L631" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M631" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N631" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O631" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B632" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C632" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D632" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E632" t="inlineStr">
+        <is>
+          <t>Fri Jul 24 10:48:36 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F632" t="inlineStr">
+        <is>
+          <t>@Strwbyukii Bonjour, merci de nous avoir signalé cela. Nous regrettons les inquiétudes que cette situation a pu vous causer. Veuillez ne cliquer sur aucun lien et ne procéder à aucun paiement en réponse à cet e‑mail.</t>
+        </is>
+      </c>
+      <c r="G632" t="inlineStr"/>
+      <c r="H632" t="inlineStr"/>
+      <c r="I632" t="inlineStr"/>
+      <c r="J632" t="inlineStr"/>
+      <c r="K632" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2080606064194531479</t>
+        </is>
+      </c>
+      <c r="L632" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M632" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N632" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O632" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B633" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C633" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D633" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E633" t="inlineStr">
+        <is>
+          <t>Fri Jul 24 10:47:50 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F633" t="inlineStr">
+        <is>
+          <t>Hi there, thank you for contacting us. We regret hearing that you're unable to reach us. Please let us know how we can help you.  If you need support with an accommodation booking, feel free to DM your: 
+- Confirmation number, 
+- PIN-code, 
+- Name on the reservation,
+so we can follow up. 
+Keep in mind, our Social Media Team does not work in real time, for immediate support you can call our 24/7 Customer Service Team here: https://t.co/tuuNbmGVaG.</t>
+        </is>
+      </c>
+      <c r="G633" t="inlineStr"/>
+      <c r="H633" t="inlineStr"/>
+      <c r="I633" t="inlineStr"/>
+      <c r="J633" t="inlineStr"/>
+      <c r="K633" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2080605871524937747</t>
+        </is>
+      </c>
+      <c r="L633" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M633" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N633" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O633" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B634" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C634" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D634" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E634" t="inlineStr">
+        <is>
+          <t>Fri Jul 24 10:29:03 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F634" t="inlineStr">
+        <is>
+          <t>@MishraSikan Hi there,
+We regret to hear that you were charge extra for your stay. If you still need help resolving the issue, feel free to send us a dm with the following information:
+- confirmation number
+- pin code
+- name on the booking https://t.co/Z89AAoEgD7</t>
+        </is>
+      </c>
+      <c r="G634" t="inlineStr"/>
+      <c r="H634" t="inlineStr"/>
+      <c r="I634" t="inlineStr"/>
+      <c r="J634" t="inlineStr"/>
+      <c r="K634" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2080601146423455979</t>
+        </is>
+      </c>
+      <c r="L634" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M634" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N634" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O634" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B635" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C635" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D635" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E635" t="inlineStr">
+        <is>
+          <t>Fri Jul 24 10:28:24 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F635" t="inlineStr">
+        <is>
+          <t>Hi there, 
+we regret to learn that you accidentally made a cancellation.
+Please send us a private message with the following details:
+- PIN code
+- guest name on the reservation.
+We will check to see how we can help.
+Please note that if there is a cancellation fee associated with your booking, only the property as the service provider can decide whether they are willing to make an exception and allow free cancellation. Also, we won't be able to reinstate cancelled bookings in the system.
+Regards</t>
+        </is>
+      </c>
+      <c r="G635" t="inlineStr"/>
+      <c r="H635" t="inlineStr"/>
+      <c r="I635" t="inlineStr"/>
+      <c r="J635" t="inlineStr"/>
+      <c r="K635" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2080600983504089401</t>
+        </is>
+      </c>
+      <c r="L635" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M635" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N635" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O635" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B636" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C636" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D636" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E636" t="inlineStr">
+        <is>
+          <t>Fri Jul 24 10:23:58 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F636" t="inlineStr">
+        <is>
+          <t>@hakhak20212021 Hi there Hak, we have responded to your DM. Please, check. Thank you.</t>
+        </is>
+      </c>
+      <c r="G636" t="inlineStr"/>
+      <c r="H636" t="inlineStr"/>
+      <c r="I636" t="inlineStr"/>
+      <c r="J636" t="inlineStr"/>
+      <c r="K636" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2080599864870629545</t>
+        </is>
+      </c>
+      <c r="L636" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M636" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N636" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O636" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B637" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C637" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D637" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E637" t="inlineStr">
+        <is>
+          <t>Fri Jul 24 10:12:49 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F637" t="inlineStr">
+        <is>
+          <t>Hi Troy, we regret to hear about your experience. While we would love to assist you with this matter via social media, we regret to inform you that we cannot provide assistance with flights through this platform. You can reach our Flights team using this link: https://t.co/OVuF5pCzba or by calling {US}+1 917 421 7240 / {UK}+44 2039019061 / {IE} +353 19075677.</t>
+        </is>
+      </c>
+      <c r="G637" t="inlineStr"/>
+      <c r="H637" t="inlineStr"/>
+      <c r="I637" t="inlineStr"/>
+      <c r="J637" t="inlineStr"/>
+      <c r="K637" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2080597060139499798</t>
+        </is>
+      </c>
+      <c r="L637" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M637" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N637" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O637" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B638" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C638" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D638" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E638" t="inlineStr">
+        <is>
+          <t>Fri Jul 24 10:08:26 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F638" t="inlineStr">
+        <is>
+          <t>Hi Lewis, thanks for reaching out and bringing this to our attention.
+We understand your concerns and would like to review this further. So w ecan access the booking securely, please send us a direct message with the following details:
+• The 4-digit PIN code from your confirmation email
+• The full name of the guest on the booking
+Once we receive these details, we'll take a closer look and get back to you.</t>
+        </is>
+      </c>
+      <c r="G638" t="inlineStr"/>
+      <c r="H638" t="inlineStr"/>
+      <c r="I638" t="inlineStr"/>
+      <c r="J638" t="inlineStr"/>
+      <c r="K638" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2080595956563644723</t>
+        </is>
+      </c>
+      <c r="L638" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M638" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N638" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O638" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B639" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C639" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D639" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E639" t="inlineStr">
+        <is>
+          <t>Fri Jul 24 09:42:05 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F639" t="inlineStr">
+        <is>
+          <t>@stockport871 Hi, we just responded to your DM. Please, check. Thank you.</t>
+        </is>
+      </c>
+      <c r="G639" t="inlineStr"/>
+      <c r="H639" t="inlineStr"/>
+      <c r="I639" t="inlineStr"/>
+      <c r="J639" t="inlineStr"/>
+      <c r="K639" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2080589324546900072</t>
+        </is>
+      </c>
+      <c r="L639" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M639" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N639" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O639" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B640" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C640" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D640" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E640" t="inlineStr">
+        <is>
+          <t>Fri Jul 24 09:06:05 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F640" t="inlineStr">
+        <is>
+          <t>@JudiDesignJapan Bonjour Judith, nous vous avons envoyé un message privé avec plus d’informations concernant votre dossier. Merci de le consulter et de revenir vers nous. Bien cordialement</t>
+        </is>
+      </c>
+      <c r="G640" t="inlineStr"/>
+      <c r="H640" t="inlineStr"/>
+      <c r="I640" t="inlineStr"/>
+      <c r="J640" t="inlineStr"/>
+      <c r="K640" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2080580266125336588</t>
+        </is>
+      </c>
+      <c r="L640" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M640" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N640" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O640" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B641" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C641" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D641" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E641" t="inlineStr">
+        <is>
+          <t>Fri Jul 24 09:04:33 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F641" t="inlineStr">
+        <is>
+          <t>@stockport871 
+Hi there, we just responded to your latest DM. Please, check. Thank you.</t>
+        </is>
+      </c>
+      <c r="G641" t="inlineStr"/>
+      <c r="H641" t="inlineStr"/>
+      <c r="I641" t="inlineStr"/>
+      <c r="J641" t="inlineStr"/>
+      <c r="K641" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2080579879515332801</t>
+        </is>
+      </c>
+      <c r="L641" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M641" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N641" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O641" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B642" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C642" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D642" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E642" t="inlineStr">
+        <is>
+          <t>Fri Jul 24 08:59:46 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F642" t="inlineStr">
+        <is>
+          <t>Hi there, we regret to learn your opinion on our service. How can we help? 
+If you need assistance with an accommodation reservation, please share with us in a private message: 
+- reservation number 
+- PIN code 
+- guest name on the reservation. 
+Along with an explanation of what you require assistance with. 
+If you require assistance with a https://t.co/fGhmZE7riF account, please confirm in DM: 
+- your full name 
+- email address linked to the account 
+and explain what happened. 
+We will check and get back to you as soon as we can. 
+Best regards</t>
+        </is>
+      </c>
+      <c r="G642" t="inlineStr"/>
+      <c r="H642" t="inlineStr"/>
+      <c r="I642" t="inlineStr"/>
+      <c r="J642" t="inlineStr"/>
+      <c r="K642" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2080578678581330075</t>
+        </is>
+      </c>
+      <c r="L642" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M642" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N642" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O642" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" t="inlineStr">
+        <is>
+          <t>Mondee</t>
+        </is>
+      </c>
+      <c r="B643" t="inlineStr">
+        <is>
+          <t>Sky Bird Travel</t>
+        </is>
+      </c>
+      <c r="C643" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D643" t="inlineStr">
+        <is>
+          <t>SkyBirdTravel</t>
+        </is>
+      </c>
+      <c r="E643" t="inlineStr">
+        <is>
+          <t>Fri Jul 24 16:58:55 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F643" t="inlineStr">
+        <is>
+          <t>Travel plans may change, but peace of mind stays. Book with a travel advisor for expert support every step of the way. Travel with confidence.
+✈️ Stay informed.
+ 🌎 Travel smarter 
+ ❤️ Personalized service
+#WhyUseATravelAgent #TravelExperts #TravelAdvisor https://t.co/rKlRTmLK9H</t>
+        </is>
+      </c>
+      <c r="G643" t="inlineStr"/>
+      <c r="H643" t="inlineStr"/>
+      <c r="I643" t="inlineStr"/>
+      <c r="J643" t="inlineStr"/>
+      <c r="K643" t="inlineStr">
+        <is>
+          <t>https://x.com/SkyBirdTravel/status/2080699260547604900</t>
+        </is>
+      </c>
+      <c r="L643" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M643" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N643" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O643" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" t="inlineStr">
+        <is>
+          <t>Mondee</t>
+        </is>
+      </c>
+      <c r="B644" t="inlineStr">
+        <is>
+          <t>Sky Bird Travel</t>
+        </is>
+      </c>
+      <c r="C644" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D644" t="inlineStr">
+        <is>
+          <t>Sky Bird Travel &amp; Tours</t>
+        </is>
+      </c>
+      <c r="E644" t="inlineStr">
+        <is>
+          <t>2026-07-24T16:53:53.909Z</t>
+        </is>
+      </c>
+      <c r="F644" t="inlineStr">
+        <is>
+          <t>Travel plans can change—but peace of mind doesn’t have to. When you book with a travel advisor, you have someone in your corner before, during, and after your trip. From the latest travel updates to personalized support when plans change, we’re here to help you travel with confidence. 
+✈️ Stay informed. 
+ 🌎 Travel smarter. 
+ ❤️ Experience personalized service every step of the way. 
+#WhyUseATravelAgent #TravelAdvisor #TravelSmarter #TravelExperts #BookWithConfidence #TravelPlanning #TravelSupport #TravelAgent</t>
+        </is>
+      </c>
+      <c r="G644" t="inlineStr">
+        <is>
+          <t>https://media.licdn.com/dms/image/v2/D4E22AQG6TUP8K80qtw/feedshare-shrink_1280/B4EZ.VDDIfIAAM-/0/1784912032987?e=1786579200&amp;v=beta&amp;t=8I-NpH5W4TzhwKnbEbrYykiFNXWgfuwwv9NhUF1xRF8</t>
+        </is>
+      </c>
+      <c r="H644" t="inlineStr">
+        <is>
+          <t>[easyocr not installed. Run 'pip install easyocr torch torchvision']</t>
+        </is>
+      </c>
+      <c r="I644" t="inlineStr"/>
+      <c r="J644" t="inlineStr"/>
+      <c r="K644" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/sky-bird-travel-tours_whyuseatravelagent-traveladvisor-travelsmarter-activity-7486463683473080320-1STe</t>
+        </is>
+      </c>
+      <c r="L644" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M644" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N644" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O644" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/News_Dashboard/data/social_media_posts.xlsx
+++ b/News_Dashboard/data/social_media_posts.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O644"/>
+  <dimension ref="A1:O670"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -41218,6 +41218,1687 @@
         </is>
       </c>
     </row>
+    <row r="645">
+      <c r="A645" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B645" t="inlineStr">
+        <is>
+          <t>Navan</t>
+        </is>
+      </c>
+      <c r="C645" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D645" t="inlineStr">
+        <is>
+          <t>Navan</t>
+        </is>
+      </c>
+      <c r="E645" t="inlineStr">
+        <is>
+          <t>2026-07-24T19:39:47.799Z</t>
+        </is>
+      </c>
+      <c r="F645" t="inlineStr">
+        <is>
+          <t>Whatever gets them to onboard...
+Joe Fenti</t>
+        </is>
+      </c>
+      <c r="G645" t="inlineStr"/>
+      <c r="H645" t="inlineStr"/>
+      <c r="I645" t="inlineStr">
+        <is>
+          <t>https://dms.licdn.com/playlist/vid/v2/D4E05AQEKQSZtREWcOg/mp4-720p-30fp-crf28/B4EZ.Vo_cJJ0CQ-/0/1784921983096?e=1785610800&amp;v=beta&amp;t=8pAtesD1vRAXOzPI21wpd4GQn-TyoPYAi2ucPgEJ2Us</t>
+        </is>
+      </c>
+      <c r="J645" t="inlineStr">
+        <is>
+          <t>[faster-whisper not installed. Run 'pip install faster-whisper']</t>
+        </is>
+      </c>
+      <c r="K645" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/navan_whatever-gets-them-to-onboard-joe-fenti-activity-7486505433113812992-vEvu</t>
+        </is>
+      </c>
+      <c r="L645" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M645" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N645" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O645" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B646" t="inlineStr">
+        <is>
+          <t>Ramp</t>
+        </is>
+      </c>
+      <c r="C646" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D646" t="inlineStr">
+        <is>
+          <t>tryramp</t>
+        </is>
+      </c>
+      <c r="E646" t="inlineStr">
+        <is>
+          <t>Fri Jul 24 21:10:52 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F646" t="inlineStr">
+        <is>
+          <t>@elonmusk Many are saying</t>
+        </is>
+      </c>
+      <c r="G646" t="inlineStr"/>
+      <c r="H646" t="inlineStr"/>
+      <c r="I646" t="inlineStr"/>
+      <c r="J646" t="inlineStr"/>
+      <c r="K646" t="inlineStr">
+        <is>
+          <t>https://x.com/tryramp/status/2080762662539886684</t>
+        </is>
+      </c>
+      <c r="L646" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M646" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N646" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O646" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B647" t="inlineStr">
+        <is>
+          <t>Ramp</t>
+        </is>
+      </c>
+      <c r="C647" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D647" t="inlineStr">
+        <is>
+          <t>tryramp</t>
+        </is>
+      </c>
+      <c r="E647" t="inlineStr">
+        <is>
+          <t>Fri Jul 24 20:39:50 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F647" t="inlineStr">
+        <is>
+          <t>Grok is this true</t>
+        </is>
+      </c>
+      <c r="G647" t="inlineStr"/>
+      <c r="H647" t="inlineStr"/>
+      <c r="I647" t="inlineStr"/>
+      <c r="J647" t="inlineStr"/>
+      <c r="K647" t="inlineStr">
+        <is>
+          <t>https://x.com/tryramp/status/2080754855447044146</t>
+        </is>
+      </c>
+      <c r="L647" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M647" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N647" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O647" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B648" t="inlineStr">
+        <is>
+          <t>Ramp</t>
+        </is>
+      </c>
+      <c r="C648" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D648" t="inlineStr">
+        <is>
+          <t>tryramp</t>
+        </is>
+      </c>
+      <c r="E648" t="inlineStr">
+        <is>
+          <t>Fri Jul 24 20:39:10 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F648" t="inlineStr">
+        <is>
+          <t>@rahulgs @grok is this true</t>
+        </is>
+      </c>
+      <c r="G648" t="inlineStr"/>
+      <c r="H648" t="inlineStr"/>
+      <c r="I648" t="inlineStr"/>
+      <c r="J648" t="inlineStr"/>
+      <c r="K648" t="inlineStr">
+        <is>
+          <t>https://x.com/tryramp/status/2080754687079219511</t>
+        </is>
+      </c>
+      <c r="L648" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M648" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N648" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O648" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B649" t="inlineStr">
+        <is>
+          <t>AirBnb</t>
+        </is>
+      </c>
+      <c r="C649" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="D649" t="inlineStr">
+        <is>
+          <t>airbnb</t>
+        </is>
+      </c>
+      <c r="E649" t="inlineStr">
+        <is>
+          <t>2026-07-24T21:00:07.000Z</t>
+        </is>
+      </c>
+      <c r="F649" t="inlineStr">
+        <is>
+          <t>Do you suffer from “Check-in Delusion”? Common symptoms include:
+1. Thinking you speak a language the moment you check-in
+2. Shouting the word of every object you see in another language
+3. Translating the entire welcome book for your friends
+If this sounds like you, ask your doctor (group chat) about “Staying Delulu.”
+Side effects may include:
+1. Booking a cute apartment in Paris with a private balconette
+2. Riding vintage elevators made decades ago one person at a time
+3. Waking up early to bring the girls baguettes and espresso in bed (you ordered in French)
+Do not try “Staying Delulu” if you are allergic to the following phrases:
+1. “Ça roule (it’s all good)
+2. “Ouf” (wow)
+3. “Sapé(e) comme jamais” (dressed to kill)
+4. “Lèche-vitrine” (window-shopping)*
+*Literal translation: window-licking. Ouf.
+Unlike other travel methods, “Staying Delulu” will get you on a plane before you’re ready, leading to spontaneous adventures and canon events.
+Results may vary.
+Book this Parisian apartment on Airbnb, linked in bio.
+📍10 minute walk from the canal, Paris 10th</t>
+        </is>
+      </c>
+      <c r="G649" t="inlineStr">
+        <is>
+          <t>https://scontent-sea5-1.cdninstagram.com/v/t51.82787-15/753247978_18616604059063838_7734695560697747779_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk0ODU3NDkyMTY5Mjk5ODcyMTE4NjE2NjA0MDU2MDYzODM4.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNMSVBTLnhwaWRzLjEyMTUuc2RyLnZpZGVvX2RlZmF1bHRfY292ZXJfZnJhbWUuQzMifQ%3D%3D&amp;_nc_ohc=1IVKeFsem7UQ7kNvwHdHOKl&amp;_nc_oc=AdpME5xznvX5IfXc2-WfIlio3Aij9dhiw1WlQo0Vty9wH3Yy3MJrW5-Q1TzgfjBMkq1ZwEa1LsLfzio5_bydymCO&amp;_nc_zt=23&amp;_nc_ht=scontent-sea5-1.cdninstagram.com&amp;_nc_gid=RwBDwtnOG7Rs95Gt5VsYgw&amp;_nc_ss=72689&amp;oh=00_AQCIviDBSYlrCPBa4aaSYxqHZLEk8JnHcfN_jWIpNCzTRg&amp;oe=6A6AB4AD</t>
+        </is>
+      </c>
+      <c r="H649" t="inlineStr">
+        <is>
+          <t>[easyocr not installed. Run 'pip install easyocr torch torchvision']</t>
+        </is>
+      </c>
+      <c r="I649" t="inlineStr">
+        <is>
+          <t>https://scontent-sea5-1.cdninstagram.com/o1/v/t2/f2/m86/AQMpIB8XUPPANg8X9lBY3yllmmctzizQ-5t6iePsfzZtOlGQklE6GkrdqYkhd_rkuqqSlGSE63dIAgDKjaYOCrMyXl3sU9m4SS5DKpo.mp4?_nc_cat=111&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-sea5-1.cdninstagram.com&amp;_nc_ohc=P0_vxWxAnu4Q7kNvwHQqeUr&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uQ0xJUFMuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MjAyNTQzODU0NDc3MzM4MiwiYXNzZXRfYWdlX2RheXMiOjAsInZpX3VzZWNhc2VfaWQiOjEwMDk5LCJkdXJhdGlvbl9zIjozMiwidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=bf9f3de17586faec&amp;_nc_vs=HBksFQIYUmlnX3hwdl9yZWVsc19wZXJtYW5lbnRfc3JfcHJvZC9DMDQ5ODlGODE5MDk2RDI4NEE1RjFBNDVFRDZDMjU4NV92aWRlb19kYXNoaW5pdC5tcDQVAALIARIAFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyL0MwNDA1RkY5NzcyNzE4RUY3QkI5RkRBQUUyOTE1QkE4X2F1ZGlvX2Rhc2hpbml0Lm1wNBUCAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACaMhM6PhYiZBxUCKAJDMywXQEBkGJN0vGoYEmRhc2hfYmFzZWxpbmVfMV92MREAdf4HZeadAQA&amp;_nc_gid=RwBDwtnOG7Rs95Gt5VsYgw&amp;_nc_ss=72689&amp;_nc_zt=28&amp;oh=00_AQCTJf7DV11P5_une2YvEy5Tk0oRlalQj0tatL8ySed8bA&amp;oe=6A66D95C</t>
+        </is>
+      </c>
+      <c r="J649" t="inlineStr">
+        <is>
+          <t>[faster-whisper not installed. Run 'pip install faster-whisper']</t>
+        </is>
+      </c>
+      <c r="K649" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DbMJ_iIhuxB/</t>
+        </is>
+      </c>
+      <c r="L649" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M649" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N649" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O649" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B650" t="inlineStr">
+        <is>
+          <t>Expedia</t>
+        </is>
+      </c>
+      <c r="C650" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D650" t="inlineStr">
+        <is>
+          <t>Expedia</t>
+        </is>
+      </c>
+      <c r="E650" t="inlineStr">
+        <is>
+          <t>Sat Jul 25 00:00:01 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F650" t="inlineStr">
+        <is>
+          <t>Norway, we are coming! 🇳🇴
+➡️ The Fjords: Glide past towering cliffs &amp; crashing waterfalls
+➡️ The Light: Hike rugged islands under the pink midnight sun
+➡️ The Stays: Skip hotels and warm up in a repurposed red fisherman’s cabin on the water
+🔗 Plan your travel: https://t.co/gckD0bC3Mn</t>
+        </is>
+      </c>
+      <c r="G650" t="inlineStr"/>
+      <c r="H650" t="inlineStr"/>
+      <c r="I650" t="inlineStr"/>
+      <c r="J650" t="inlineStr"/>
+      <c r="K650" t="inlineStr">
+        <is>
+          <t>https://x.com/Expedia/status/2080805230732554525</t>
+        </is>
+      </c>
+      <c r="L650" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M650" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N650" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O650" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B651" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C651" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D651" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E651" t="inlineStr">
+        <is>
+          <t>Sat Jul 25 18:07:45 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F651" t="inlineStr">
+        <is>
+          <t>Hi Samar, we regret to hear that you were charged however did not receive a booking confirmation. It sounds like your booking didn't confirm successfully, but the payment was collected. Were you charged by https://t.co/fGhmZE7riF or by the accommodation? If we've charged you, our system will recognize that the payment isn't linked to a booking and automatically refund it back. Once the refund is processed, it can take 7-12 days to reflect in your account - you should've also received an email confirming this. 
+It's also possible that you made a typo when entering your email address, as you wouldn't receive the confirmation email afterward. If you send us a private message with the following details, we'll look into our system to see if we can locate your booking:
+• Name of the property:
+• Dates of stay:
+• Full guest name &amp; name of the person contacting us:
+• Email address used to make the booking:</t>
+        </is>
+      </c>
+      <c r="G651" t="inlineStr"/>
+      <c r="H651" t="inlineStr"/>
+      <c r="I651" t="inlineStr"/>
+      <c r="J651" t="inlineStr"/>
+      <c r="K651" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2081078970125046204</t>
+        </is>
+      </c>
+      <c r="L651" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M651" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N651" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O651" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B652" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C652" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D652" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E652" t="inlineStr">
+        <is>
+          <t>Sat Jul 25 17:45:34 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F652" t="inlineStr">
+        <is>
+          <t>Hi Elsie, we regret knowing that you are having an issue to contact our team, and we'd like to see how we are able to assist. For us to help you here, please send us the following information: - Confirmation number - Pin code - Name on the reservation via DM, and we'll get back to you soon. Keep in mind, our Social Media Team does not work in real time. For immediate support, you can call our 24/7 Customer Service Team here: https://t.co/tuuNbmGVaG</t>
+        </is>
+      </c>
+      <c r="G652" t="inlineStr"/>
+      <c r="H652" t="inlineStr"/>
+      <c r="I652" t="inlineStr"/>
+      <c r="J652" t="inlineStr"/>
+      <c r="K652" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2081073387200274551</t>
+        </is>
+      </c>
+      <c r="L652" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M652" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N652" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O652" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B653" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C653" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D653" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E653" t="inlineStr">
+        <is>
+          <t>Sat Jul 25 17:16:53 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F653" t="inlineStr">
+        <is>
+          <t>Hi Sushil, thank you for getting back to us. We regret to hear about the continued delay and understand how frustrating it must be to be waiting for a refund nearly 50 days after your reservation was cancelled. 
+As previously mentioned, we'd like to look into this matter for you. To enable us to review your case and assist further, please share your booking details with us via DM, including: 
+• Confirmation number 
+• PIN code 
+• Name on the reservation 
+Once we receive these details, we'll be able to investigate the status of your reservation and provide further assistance. We appreciate your patience and look forward to hearing from you.</t>
+        </is>
+      </c>
+      <c r="G653" t="inlineStr"/>
+      <c r="H653" t="inlineStr"/>
+      <c r="I653" t="inlineStr"/>
+      <c r="J653" t="inlineStr"/>
+      <c r="K653" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2081066169004396875</t>
+        </is>
+      </c>
+      <c r="L653" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M653" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N653" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O653" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B654" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C654" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D654" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E654" t="inlineStr">
+        <is>
+          <t>Sat Jul 25 13:57:47 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F654" t="inlineStr">
+        <is>
+          <t>@SudharshananJa1 Hi Sushan, we replied to your DM.</t>
+        </is>
+      </c>
+      <c r="G654" t="inlineStr"/>
+      <c r="H654" t="inlineStr"/>
+      <c r="I654" t="inlineStr"/>
+      <c r="J654" t="inlineStr"/>
+      <c r="K654" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2081016062292754598</t>
+        </is>
+      </c>
+      <c r="L654" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M654" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N654" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O654" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="655">
+      <c r="A655" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B655" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C655" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D655" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E655" t="inlineStr">
+        <is>
+          <t>Sat Jul 25 13:55:47 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F655" t="inlineStr">
+        <is>
+          <t>@TahseenChandi Hi Tahseen, thank you for reaching out. Our apologies for the late response, we're receiving a high volume of cases on Social Media, and weren't able to reply until now. We've replied to your DM's, when you have a chance, please look at your inbox. Thank you.</t>
+        </is>
+      </c>
+      <c r="G655" t="inlineStr"/>
+      <c r="H655" t="inlineStr"/>
+      <c r="I655" t="inlineStr"/>
+      <c r="J655" t="inlineStr"/>
+      <c r="K655" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2081015560368775271</t>
+        </is>
+      </c>
+      <c r="L655" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M655" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N655" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O655" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B656" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C656" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D656" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E656" t="inlineStr">
+        <is>
+          <t>Sat Jul 25 13:49:38 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F656" t="inlineStr">
+        <is>
+          <t>Hi Ms. Moyana, thank you for getting in touch. We apologize for our delayed response; we have been managing a significant influx of cases on Social Media, which has prevented us from replying sooner. Please be aware that if you want to check if your booked accommodation is fully booked before your arrival, you can reach out to them directly through the chat feature in our app or by calling the number provided in your confirmation email. If you require further assistance, please DM us with the following information: 
+- Confirmation number 
+- Pin code 
+- Guest's name 
+- Details regarding your request 
+We will respond to you as quickly as we can, but please keep in mind that our Social Media Team does not operate in real time. For immediate assistance, please contact our 24/7 Customer Service Team; you can find our contact information here: https://t.co/o8QyR8SaDb 
+Best regards.</t>
+        </is>
+      </c>
+      <c r="G656" t="inlineStr"/>
+      <c r="H656" t="inlineStr"/>
+      <c r="I656" t="inlineStr"/>
+      <c r="J656" t="inlineStr"/>
+      <c r="K656" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2081014013534621734</t>
+        </is>
+      </c>
+      <c r="L656" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M656" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N656" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O656" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B657" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C657" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D657" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E657" t="inlineStr">
+        <is>
+          <t>Sat Jul 25 13:20:46 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F657" t="inlineStr">
+        <is>
+          <t>@paleokastro10 Hi Paleo, we regret hearing about your experience. 
+To assist you, please send us a DM with the following information, and we will get back to you as soon as possible:
+- PIN code
+- Full name of the guest confirmed on the booking https://t.co/Z89AAoEgD7</t>
+        </is>
+      </c>
+      <c r="G657" t="inlineStr"/>
+      <c r="H657" t="inlineStr"/>
+      <c r="I657" t="inlineStr"/>
+      <c r="J657" t="inlineStr"/>
+      <c r="K657" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2081006748991668418</t>
+        </is>
+      </c>
+      <c r="L657" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M657" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N657" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O657" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B658" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C658" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D658" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E658" t="inlineStr">
+        <is>
+          <t>Sat Jul 25 11:55:07 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F658" t="inlineStr">
+        <is>
+          <t>@anju1611 Hi there, thank you for reaching out. Our Customer Care number in India is 000 800 001 6075. Best regards.</t>
+        </is>
+      </c>
+      <c r="G658" t="inlineStr"/>
+      <c r="H658" t="inlineStr"/>
+      <c r="I658" t="inlineStr"/>
+      <c r="J658" t="inlineStr"/>
+      <c r="K658" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2080985192303354326</t>
+        </is>
+      </c>
+      <c r="L658" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M658" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N658" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O658" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B659" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C659" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D659" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E659" t="inlineStr">
+        <is>
+          <t>Sat Jul 25 11:54:10 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F659" t="inlineStr">
+        <is>
+          <t>Hi there, thank you for contacting us in regards to your Car Rental reservation.
+In order for us to assist, please send us a private message with the following details:
+- Booking number
+- Name of booker
+- Email address used to book
+- Your request
+We'll get back to you as soon as we can. Thank you.</t>
+        </is>
+      </c>
+      <c r="G659" t="inlineStr"/>
+      <c r="H659" t="inlineStr"/>
+      <c r="I659" t="inlineStr"/>
+      <c r="J659" t="inlineStr"/>
+      <c r="K659" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2080984953257435637</t>
+        </is>
+      </c>
+      <c r="L659" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M659" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N659" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O659" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="660">
+      <c r="A660" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B660" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C660" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D660" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E660" t="inlineStr">
+        <is>
+          <t>Sat Jul 25 11:51:06 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F660" t="inlineStr">
+        <is>
+          <t>@PaulCol74988667 Hi there Paul, we have just replied to your DM in order to follow up on this, kindly have a look. Many thanks! https://t.co/Z89AAoEgD7</t>
+        </is>
+      </c>
+      <c r="G660" t="inlineStr"/>
+      <c r="H660" t="inlineStr"/>
+      <c r="I660" t="inlineStr"/>
+      <c r="J660" t="inlineStr"/>
+      <c r="K660" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2080984181052490222</t>
+        </is>
+      </c>
+      <c r="L660" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M660" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N660" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O660" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="661">
+      <c r="A661" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B661" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C661" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D661" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E661" t="inlineStr">
+        <is>
+          <t>Sat Jul 25 11:11:49 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F661" t="inlineStr">
+        <is>
+          <t>@SudharshananJa1 Hi Sushan, we're here to help. Send us a DM with a brief summary of what happened along with your:
+- Confirmation number
+- Pin code
+- Name on the reservation
+And we'll get back to you soon. https://t.co/Z89AAoEgD7</t>
+        </is>
+      </c>
+      <c r="G661" t="inlineStr"/>
+      <c r="H661" t="inlineStr"/>
+      <c r="I661" t="inlineStr"/>
+      <c r="J661" t="inlineStr"/>
+      <c r="K661" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2080974296076169630</t>
+        </is>
+      </c>
+      <c r="L661" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M661" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N661" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O661" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B662" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C662" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D662" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E662" t="inlineStr">
+        <is>
+          <t>Sat Jul 25 11:07:58 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F662" t="inlineStr">
+        <is>
+          <t>@rothgordon Hi Derek, we regret to hear that you feel this way about our service. Please send us a DM with a brief summary of your request and we'll be happy to help. https://t.co/Z89AAoEgD7</t>
+        </is>
+      </c>
+      <c r="G662" t="inlineStr"/>
+      <c r="H662" t="inlineStr"/>
+      <c r="I662" t="inlineStr"/>
+      <c r="J662" t="inlineStr"/>
+      <c r="K662" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2080973326181126522</t>
+        </is>
+      </c>
+      <c r="L662" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M662" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N662" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O662" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B663" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C663" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D663" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E663" t="inlineStr">
+        <is>
+          <t>Sat Jul 25 10:57:21 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F663" t="inlineStr">
+        <is>
+          <t>Hi there, thank you for reaching out. All policies on our website, including cancellation policies, are set by the accommodations themselves. You should only be charged a cancellation fee according to the policy you've booked, which is selected during the booking process and also appears on your confirmation email. If you'd like for us to look into this for you, please send us a private message with the following details, and we'll get back to you as soon as possible:
+- Confirmation number
+- Pin code
+- Guest name
+Please bear in mind that our Social Media Team doesn't work in real time. For immediate support, please call our 24/7 Customer Service Team - our contact details can be found here: https://t.co/o8QyR8SaDb
+Also, at this time, we only offer support for accommodation bookings via social media. For questions about Flights, Taxis, or Insurance, you can reach out to the dedicated support team here: https://t.co/UfRgpDJomK. Best regards.</t>
+        </is>
+      </c>
+      <c r="G663" t="inlineStr"/>
+      <c r="H663" t="inlineStr"/>
+      <c r="I663" t="inlineStr"/>
+      <c r="J663" t="inlineStr"/>
+      <c r="K663" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2080970654774362592</t>
+        </is>
+      </c>
+      <c r="L663" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M663" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N663" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O663" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="664">
+      <c r="A664" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B664" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C664" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D664" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E664" t="inlineStr">
+        <is>
+          <t>Sat Jul 25 10:25:56 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F664" t="inlineStr">
+        <is>
+          <t>Hi Tanveer, thanks for your message and we regret learning you didn't have a good experience in your stay. 
+We can see, however, that our customer service took the necessary steps to assist you considering you the situation, and a final response for your contact has just been shared. Kindly refer back to the email they've just sent you.
+If you need further information about this booking through this via as well, please DM us with:
+• Pin code, 
+• Name on the reservation,
+Don't share those un public - and we will get back to you as soon as possible, but keep in mind that we will not be able to offer you a different response.</t>
+        </is>
+      </c>
+      <c r="G664" t="inlineStr"/>
+      <c r="H664" t="inlineStr"/>
+      <c r="I664" t="inlineStr"/>
+      <c r="J664" t="inlineStr"/>
+      <c r="K664" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2080962748653981807</t>
+        </is>
+      </c>
+      <c r="L664" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M664" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N664" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O664" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B665" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C665" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D665" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E665" t="inlineStr">
+        <is>
+          <t>Sat Jul 25 09:54:00 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F665" t="inlineStr">
+        <is>
+          <t>Hi Sagar, thank you for reaching out. We recommend that you never share the PIN code of your reservation in public as it can allow others to access your personal details. To help protect your information, we recommend that you delete your comment.  Please send a private message if you would like any assistance. Have a nice day!</t>
+        </is>
+      </c>
+      <c r="G665" t="inlineStr"/>
+      <c r="H665" t="inlineStr"/>
+      <c r="I665" t="inlineStr"/>
+      <c r="J665" t="inlineStr"/>
+      <c r="K665" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2080954714544370046</t>
+        </is>
+      </c>
+      <c r="L665" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M665" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N665" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O665" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="666">
+      <c r="A666" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B666" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C666" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D666" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E666" t="inlineStr">
+        <is>
+          <t>Sat Jul 25 09:49:12 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F666" t="inlineStr">
+        <is>
+          <t>Hi there Paul, thanks for reaching out to us and for sharing your booking details.
+Before we proceed, we also require the PIN code and full guest name on the booking for security reasons. The PIN code is a 4 digits number you can find in your confirmation email, bellow the booking number. If you still need assistance with your booking, please share this information with us in your reply to this message, and we'll get back to you.</t>
+        </is>
+      </c>
+      <c r="G666" t="inlineStr"/>
+      <c r="H666" t="inlineStr"/>
+      <c r="I666" t="inlineStr"/>
+      <c r="J666" t="inlineStr"/>
+      <c r="K666" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2080953504252797290</t>
+        </is>
+      </c>
+      <c r="L666" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M666" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N666" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O666" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B667" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C667" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D667" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E667" t="inlineStr">
+        <is>
+          <t>Sat Jul 25 08:50:32 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F667" t="inlineStr">
+        <is>
+          <t>Hi there, thanks for your message. By checking the booking which number you shared, we can see that our customer service and the property did provide you a final outcome regarding your request already. If you'd like us to forward it to you here once more, please DM us with:
+• Pin code, 
+• Name on the reservation,
+Please do not share those in public as they're confidential - and we will get back to you as soon as possible.</t>
+        </is>
+      </c>
+      <c r="G667" t="inlineStr"/>
+      <c r="H667" t="inlineStr"/>
+      <c r="I667" t="inlineStr"/>
+      <c r="J667" t="inlineStr"/>
+      <c r="K667" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2080938739027652827</t>
+        </is>
+      </c>
+      <c r="L667" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M667" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N667" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O667" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B668" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C668" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D668" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E668" t="inlineStr">
+        <is>
+          <t>Sat Jul 25 08:11:38 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F668" t="inlineStr">
+        <is>
+          <t>@gelembung2sabun Hi Peniup, we've just replied to your DM in order to provide you further support, kindly get back to us thrugh the same via. Thank you.</t>
+        </is>
+      </c>
+      <c r="G668" t="inlineStr"/>
+      <c r="H668" t="inlineStr"/>
+      <c r="I668" t="inlineStr"/>
+      <c r="J668" t="inlineStr"/>
+      <c r="K668" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2080928950000234809</t>
+        </is>
+      </c>
+      <c r="L668" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M668" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N668" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O668" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B669" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C669" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D669" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E669" t="inlineStr">
+        <is>
+          <t>Sat Jul 25 01:29:04 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F669" t="inlineStr">
+        <is>
+          <t>Hi Devender,
+Thank you for bringing this to our attention. We regret to hear about your concerns.
+Could you please provide more details about what happened? Any additional information you can share about the situation will help us better understand your concerns and review the matter accordingly.
+If your concern relates to specific accommodation listed on our platform, please note that properties are responsible for the information they provide and must complete a verification process before becoming bookable. If we find that a property is providing false or misleading information, we investigate the matter, take appropriate action, and may remove the property from our platform if necessary.
+Please send us a DM with a link to the property's https://t.co/fGhmZE7riF page, along with details of the issue you've identified, and we'll ensure it is reviewed by the relevant team.
+Kind regards.</t>
+        </is>
+      </c>
+      <c r="G669" t="inlineStr"/>
+      <c r="H669" t="inlineStr"/>
+      <c r="I669" t="inlineStr"/>
+      <c r="J669" t="inlineStr"/>
+      <c r="K669" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2080827641997693424</t>
+        </is>
+      </c>
+      <c r="L669" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M669" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N669" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O669" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B670" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C670" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D670" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E670" t="inlineStr">
+        <is>
+          <t>Sat Jul 25 00:20:30 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F670" t="inlineStr">
+        <is>
+          <t>Hi Joni, thank you for reaching out to us. We regret to hear about your situation and saddened to hear about your dissatisfaction with us, and we'd like to see how we are able to assist. For us to help you here, please send us the following information: - Confirmation number - Pin code - Name on the reservation, and we'll get back to you soon. Keep in mind, our Social Media Team does not work in real time. For immediate support, you can call our 24/7 Customer Service Team here: https://t.co/tuuNbmGVaG</t>
+        </is>
+      </c>
+      <c r="G670" t="inlineStr"/>
+      <c r="H670" t="inlineStr"/>
+      <c r="I670" t="inlineStr"/>
+      <c r="J670" t="inlineStr"/>
+      <c r="K670" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2080810385871937596</t>
+        </is>
+      </c>
+      <c r="L670" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M670" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N670" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O670" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/News_Dashboard/data/social_media_posts.xlsx
+++ b/News_Dashboard/data/social_media_posts.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O670"/>
+  <dimension ref="A1:O691"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42899,6 +42899,1324 @@
         </is>
       </c>
     </row>
+    <row r="671">
+      <c r="A671" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B671" t="inlineStr">
+        <is>
+          <t>Ramp</t>
+        </is>
+      </c>
+      <c r="C671" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D671" t="inlineStr">
+        <is>
+          <t>tryramp</t>
+        </is>
+      </c>
+      <c r="E671" t="inlineStr">
+        <is>
+          <t>Sat Jul 25 23:48:53 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F671" t="inlineStr">
+        <is>
+          <t>@FilArons Crime but compliant</t>
+        </is>
+      </c>
+      <c r="G671" t="inlineStr"/>
+      <c r="H671" t="inlineStr"/>
+      <c r="I671" t="inlineStr"/>
+      <c r="J671" t="inlineStr"/>
+      <c r="K671" t="inlineStr">
+        <is>
+          <t>https://x.com/tryramp/status/2081164817671348550</t>
+        </is>
+      </c>
+      <c r="L671" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M671" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N671" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O671" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="672">
+      <c r="A672" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B672" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C672" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D672" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E672" t="inlineStr">
+        <is>
+          <t>Sun Jul 26 17:58:42 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F672" t="inlineStr">
+        <is>
+          <t>@cactushoney12 Hi there, we have sent you a private message. Please take a moment to check it. Thank you.</t>
+        </is>
+      </c>
+      <c r="G672" t="inlineStr"/>
+      <c r="H672" t="inlineStr"/>
+      <c r="I672" t="inlineStr"/>
+      <c r="J672" t="inlineStr"/>
+      <c r="K672" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2081439081028804833</t>
+        </is>
+      </c>
+      <c r="L672" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M672" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N672" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O672" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="673">
+      <c r="A673" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B673" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C673" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D673" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E673" t="inlineStr">
+        <is>
+          <t>Sun Jul 26 17:05:18 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F673" t="inlineStr">
+        <is>
+          <t>Hi there,
+We regret the disappointment and frustration this situation has caused, especially given the time you've spent waiting for an update and the multiple times you've had to reach out for assistance.
+Please note that our team operates separately from the 24/7 customer service department. Because of this, we do not have visibility of your reservation details or any previous correspondence unless those details are shared with us directly.
+To proceed with assisting you and to review your case properly, we kindly ask that you provide the details previously requested. Once we receive this information, we will be able to investigate further and offer any assistance available.
+We appreciate your patience and cooperation.</t>
+        </is>
+      </c>
+      <c r="G673" t="inlineStr"/>
+      <c r="H673" t="inlineStr"/>
+      <c r="I673" t="inlineStr"/>
+      <c r="J673" t="inlineStr"/>
+      <c r="K673" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2081425639228289454</t>
+        </is>
+      </c>
+      <c r="L673" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M673" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N673" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O673" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="674">
+      <c r="A674" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B674" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C674" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D674" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E674" t="inlineStr">
+        <is>
+          <t>Sun Jul 26 14:12:47 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F674" t="inlineStr">
+        <is>
+          <t>@cactushoney12 Hi, we just responded to your DM. Please, check. Thank you.</t>
+        </is>
+      </c>
+      <c r="G674" t="inlineStr"/>
+      <c r="H674" t="inlineStr"/>
+      <c r="I674" t="inlineStr"/>
+      <c r="J674" t="inlineStr"/>
+      <c r="K674" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2081382227678568640</t>
+        </is>
+      </c>
+      <c r="L674" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M674" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N674" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O674" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B675" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C675" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D675" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E675" t="inlineStr">
+        <is>
+          <t>Sun Jul 26 13:35:12 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F675" t="inlineStr">
+        <is>
+          <t>@sharon_kingss Hi, if you need support with an outstanding refund, please send us a DM with the following details so we can review your case:
+* Confirmation number
+* PIN code
+* Full name of the guest on the booking
+We'll take a look and get back to you as soon as we can. https://t.co/Z89AAoEgD7</t>
+        </is>
+      </c>
+      <c r="G675" t="inlineStr"/>
+      <c r="H675" t="inlineStr"/>
+      <c r="I675" t="inlineStr"/>
+      <c r="J675" t="inlineStr"/>
+      <c r="K675" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2081372766578577492</t>
+        </is>
+      </c>
+      <c r="L675" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M675" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N675" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O675" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="676">
+      <c r="A676" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B676" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C676" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D676" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E676" t="inlineStr">
+        <is>
+          <t>Sun Jul 26 12:49:14 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F676" t="inlineStr">
+        <is>
+          <t>@vrindatulshan Hi there, thank you for reaching out to us. We regret hearing about your experience, and we would like to look into this. Could you please send us a DM with the following:
+- Your full name
+- The email address associated with your account
+Thank you. https://t.co/Z89AAoEgD7</t>
+        </is>
+      </c>
+      <c r="G676" t="inlineStr"/>
+      <c r="H676" t="inlineStr"/>
+      <c r="I676" t="inlineStr"/>
+      <c r="J676" t="inlineStr"/>
+      <c r="K676" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2081361200844091527</t>
+        </is>
+      </c>
+      <c r="L676" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M676" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N676" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O676" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="677">
+      <c r="A677" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B677" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C677" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D677" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E677" t="inlineStr">
+        <is>
+          <t>Sun Jul 26 07:49:38 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F677" t="inlineStr">
+        <is>
+          <t>@parth_995 Hello Pat, thank you for contacting us. If you have a reservation with Agoda and require assistance, please get in touch with them directly. Thank you.</t>
+        </is>
+      </c>
+      <c r="G677" t="inlineStr"/>
+      <c r="H677" t="inlineStr"/>
+      <c r="I677" t="inlineStr"/>
+      <c r="J677" t="inlineStr"/>
+      <c r="K677" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2081285801237701094</t>
+        </is>
+      </c>
+      <c r="L677" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M677" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N677" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O677" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B678" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C678" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D678" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E678" t="inlineStr">
+        <is>
+          <t>Sun Jul 26 01:00:31 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F678" t="inlineStr">
+        <is>
+          <t>Hi there,
+We understand your frustration, and we regret that this has been your experience.
+As we have previously informed you, https://t.co/fGhmZE7riF acts as an intermediary between guests and accommodations. The cancellation, refund, and payment policies displayed during the booking process are set by the accommodation and agreed to at the time of booking. You should only be charged in accordance with the policy applicable to the reservation you booked.
+If you have an issue with your reservation, please send us a private message with the following details:
+• Confirmation number
+• PIN code
+• Name on the reservation
+Additionally, kindly elaborate on what happened and describe the specific concern you are experiencing so that we can review the situation thoroughly and provide the most appropriate support.
+Once we receive these details, we will be happy to investigate further and assist you.
+Kind regards,</t>
+        </is>
+      </c>
+      <c r="G678" t="inlineStr"/>
+      <c r="H678" t="inlineStr"/>
+      <c r="I678" t="inlineStr"/>
+      <c r="J678" t="inlineStr"/>
+      <c r="K678" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2081182845632942519</t>
+        </is>
+      </c>
+      <c r="L678" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M678" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N678" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O678" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="679">
+      <c r="A679" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B679" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C679" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D679" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E679" t="inlineStr">
+        <is>
+          <t>Sun Jul 26 00:58:28 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F679" t="inlineStr">
+        <is>
+          <t>Hi Sai, thank you for reaching out. We regret the inconvenience you’ve experienced with your recent reservation in Columbus, Ohio. We understand your frustration regarding the cancellation fee and your disappointment with the long wait times, inconsistent information, and communication issues. For us to assist you here, please DM us the following details, and we'll get back to you as soon as possible:
+Pin code:
+Name on the reservation:
+Please bear in mind that our Social Media Team doesn’t work in real time. For immediate support, please call our 24/7 Customer Service Team - our contact details can be found here: https://t.co/o8QyR8SaDb.</t>
+        </is>
+      </c>
+      <c r="G679" t="inlineStr"/>
+      <c r="H679" t="inlineStr"/>
+      <c r="I679" t="inlineStr"/>
+      <c r="J679" t="inlineStr"/>
+      <c r="K679" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2081182328567517302</t>
+        </is>
+      </c>
+      <c r="L679" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M679" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N679" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O679" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="680">
+      <c r="A680" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B680" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C680" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D680" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E680" t="inlineStr">
+        <is>
+          <t>Sun Jul 26 00:33:12 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F680" t="inlineStr">
+        <is>
+          <t>@MuathMuhammad Hi Muath, we have sent you a private message. Please take a moment to check it. Thank you.</t>
+        </is>
+      </c>
+      <c r="G680" t="inlineStr"/>
+      <c r="H680" t="inlineStr"/>
+      <c r="I680" t="inlineStr"/>
+      <c r="J680" t="inlineStr"/>
+      <c r="K680" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2081175969713271046</t>
+        </is>
+      </c>
+      <c r="L680" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M680" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N680" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O680" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B681" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C681" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D681" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E681" t="inlineStr">
+        <is>
+          <t>Sat Jul 25 23:29:11 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F681" t="inlineStr">
+        <is>
+          <t>@MuathMuhammad Hi Muath, we regret to hear about that. We've responded to you via direct message; kindly check your DM at your convenience. Thank you.</t>
+        </is>
+      </c>
+      <c r="G681" t="inlineStr"/>
+      <c r="H681" t="inlineStr"/>
+      <c r="I681" t="inlineStr"/>
+      <c r="J681" t="inlineStr"/>
+      <c r="K681" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2081159861417529741</t>
+        </is>
+      </c>
+      <c r="L681" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M681" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N681" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O681" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B682" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C682" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D682" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E682" t="inlineStr">
+        <is>
+          <t>Sat Jul 25 23:24:24 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F682" t="inlineStr">
+        <is>
+          <t>@turkyaalnasser Hello Abdullah, we have sent you a direct message concerning your inquiry. Please take a look at your messages for additional support.</t>
+        </is>
+      </c>
+      <c r="G682" t="inlineStr"/>
+      <c r="H682" t="inlineStr"/>
+      <c r="I682" t="inlineStr"/>
+      <c r="J682" t="inlineStr"/>
+      <c r="K682" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2081158657350222098</t>
+        </is>
+      </c>
+      <c r="L682" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M682" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N682" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O682" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B683" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C683" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D683" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E683" t="inlineStr">
+        <is>
+          <t>Sat Jul 25 22:31:52 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F683" t="inlineStr">
+        <is>
+          <t>Hi there, thank you for contacting us regarding your car rental reservation. We regret to hear this, and we understand you’re seeking a fair and transparent resolution regarding the damage claim. 
+In order for us to assist, please send us a private message with the following details: 
+- Booking number. 
+- Name of booker. 
+- Email address used to book. 
+- Your request. 
+We’ll get back to you as soon as we can. If you need urgent assistance, feel free to reach out to our specialized team here: https://t.co/NT3GBtSRDt.</t>
+        </is>
+      </c>
+      <c r="G683" t="inlineStr"/>
+      <c r="H683" t="inlineStr"/>
+      <c r="I683" t="inlineStr"/>
+      <c r="J683" t="inlineStr"/>
+      <c r="K683" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2081145435910025422</t>
+        </is>
+      </c>
+      <c r="L683" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M683" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N683" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O683" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B684" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C684" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D684" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E684" t="inlineStr">
+        <is>
+          <t>Sat Jul 25 22:27:32 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F684" t="inlineStr">
+        <is>
+          <t>@hoodan26 Hi hood, we have responded to your message privately. Please check it at your earliest convenience.</t>
+        </is>
+      </c>
+      <c r="G684" t="inlineStr"/>
+      <c r="H684" t="inlineStr"/>
+      <c r="I684" t="inlineStr"/>
+      <c r="J684" t="inlineStr"/>
+      <c r="K684" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2081144344484954339</t>
+        </is>
+      </c>
+      <c r="L684" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M684" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N684" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O684" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B685" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C685" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D685" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E685" t="inlineStr">
+        <is>
+          <t>Sat Jul 25 22:26:43 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F685" t="inlineStr">
+        <is>
+          <t>Hi Angela, we regret the experience you had while trying to reach our support team. Being on hold for such a long time only to have the call end abruptly must have been very frustrating, and we understand how disappointing that feels when you’re seeking help. Please send us a private message so that we can further discuss this case and proceed with the necessary action. Thank you.</t>
+        </is>
+      </c>
+      <c r="G685" t="inlineStr"/>
+      <c r="H685" t="inlineStr"/>
+      <c r="I685" t="inlineStr"/>
+      <c r="J685" t="inlineStr"/>
+      <c r="K685" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2081144138532024419</t>
+        </is>
+      </c>
+      <c r="L685" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M685" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N685" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O685" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B686" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C686" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D686" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E686" t="inlineStr">
+        <is>
+          <t>Sat Jul 25 22:16:05 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F686" t="inlineStr">
+        <is>
+          <t>Hi Hannah, we understand your urgency as you haven't yet received any update about your booking. In order for us to follow up and check your case, please DM us the following details and give us a brief description of what the refund was for: 
+• Confirmation number: 
+• Pin code: 
+• Name on the reservation:</t>
+        </is>
+      </c>
+      <c r="G686" t="inlineStr"/>
+      <c r="H686" t="inlineStr"/>
+      <c r="I686" t="inlineStr"/>
+      <c r="J686" t="inlineStr"/>
+      <c r="K686" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2081141462792605771</t>
+        </is>
+      </c>
+      <c r="L686" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M686" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N686" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O686" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B687" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C687" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D687" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E687" t="inlineStr">
+        <is>
+          <t>Sat Jul 25 22:11:21 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F687" t="inlineStr">
+        <is>
+          <t>Hi Angela, thanks for getting back to us. We sincerely appreciate your time in sharing the details with us. We recommend that you never share the PIN code of your reservation in public, as it can allow others to access your personal details. To help protect your information, we recommend that you delete your comment. Please send a private message to further discuss this matter. Thank you.</t>
+        </is>
+      </c>
+      <c r="G687" t="inlineStr"/>
+      <c r="H687" t="inlineStr"/>
+      <c r="I687" t="inlineStr"/>
+      <c r="J687" t="inlineStr"/>
+      <c r="K687" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2081140274147831947</t>
+        </is>
+      </c>
+      <c r="L687" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M687" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N687" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O687" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B688" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C688" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D688" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E688" t="inlineStr">
+        <is>
+          <t>Sat Jul 25 22:08:45 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F688" t="inlineStr">
+        <is>
+          <t>@KarinaParvanova Hi Karina, we have sent you a private message. Please take a moment to check it. Thank you.</t>
+        </is>
+      </c>
+      <c r="G688" t="inlineStr"/>
+      <c r="H688" t="inlineStr"/>
+      <c r="I688" t="inlineStr"/>
+      <c r="J688" t="inlineStr"/>
+      <c r="K688" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2081139618125168827</t>
+        </is>
+      </c>
+      <c r="L688" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M688" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N688" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O688" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B689" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C689" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D689" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E689" t="inlineStr">
+        <is>
+          <t>Sat Jul 25 22:02:21 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F689" t="inlineStr">
+        <is>
+          <t>@Patreus7575 Hello, we have sent you a direct message. Please check it at your earliest convenience.</t>
+        </is>
+      </c>
+      <c r="G689" t="inlineStr"/>
+      <c r="H689" t="inlineStr"/>
+      <c r="I689" t="inlineStr"/>
+      <c r="J689" t="inlineStr"/>
+      <c r="K689" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2081138009185890438</t>
+        </is>
+      </c>
+      <c r="L689" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M689" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N689" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O689" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B690" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C690" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D690" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E690" t="inlineStr">
+        <is>
+          <t>Sat Jul 25 21:57:55 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F690" t="inlineStr">
+        <is>
+          <t>We regret that your parents arrived at their accommodation only to discover it was a fraudulent listing and could not accommodate them, Angela. The availability of the rooms is set up by the properties themselves, and they're solely responsible for making sure this is correct. We don't decide on behalf of the property how many (if any) rooms they want to have available to book through our platform for any given date.
+If a property is unable to honor a booking, they should help you find another place to stay. If they're unable or unwilling to provide this, they should let us know as soon as possible so that we can help to find a solution. Please DM us the following details:
+• Confirmation number:
+• PIN code:
+• Name on the reservation:
+Alternatively, for immediate support, you can always give us a call here: https://t.co/o8QyR8SaDb.</t>
+        </is>
+      </c>
+      <c r="G690" t="inlineStr"/>
+      <c r="H690" t="inlineStr"/>
+      <c r="I690" t="inlineStr"/>
+      <c r="J690" t="inlineStr"/>
+      <c r="K690" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2081136893211615531</t>
+        </is>
+      </c>
+      <c r="L690" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M690" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N690" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O690" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B691" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C691" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D691" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E691" t="inlineStr">
+        <is>
+          <t>Sat Jul 25 21:52:46 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F691" t="inlineStr">
+        <is>
+          <t>@KatarinaHill2 Hi Kat, we have sent you a private message. Please take a moment to check it. Thank you.</t>
+        </is>
+      </c>
+      <c r="G691" t="inlineStr"/>
+      <c r="H691" t="inlineStr"/>
+      <c r="I691" t="inlineStr"/>
+      <c r="J691" t="inlineStr"/>
+      <c r="K691" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2081135597293342906</t>
+        </is>
+      </c>
+      <c r="L691" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M691" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N691" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O691" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/News_Dashboard/data/social_media_posts.xlsx
+++ b/News_Dashboard/data/social_media_posts.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O691"/>
+  <dimension ref="A1:O714"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44217,6 +44217,1493 @@
         </is>
       </c>
     </row>
+    <row r="692">
+      <c r="A692" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B692" t="inlineStr">
+        <is>
+          <t>AirBnb</t>
+        </is>
+      </c>
+      <c r="C692" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="D692" t="inlineStr">
+        <is>
+          <t>Airbnb</t>
+        </is>
+      </c>
+      <c r="E692" t="inlineStr">
+        <is>
+          <t>2026-07-27T07:00:14.000Z</t>
+        </is>
+      </c>
+      <c r="F692" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Airbnb Vs. 34 Chihuahuas
+</t>
+        </is>
+      </c>
+      <c r="G692" t="inlineStr"/>
+      <c r="H692" t="inlineStr"/>
+      <c r="I692" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=AucAq1RDd5Y</t>
+        </is>
+      </c>
+      <c r="J692" t="inlineStr">
+        <is>
+          <t>[Failed to fetch]</t>
+        </is>
+      </c>
+      <c r="K692" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=AucAq1RDd5Y</t>
+        </is>
+      </c>
+      <c r="L692" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M692" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N692" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O692" t="inlineStr">
+        <is>
+          <t>Failed to analyze video transcript via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B693" t="inlineStr">
+        <is>
+          <t>AirBnb</t>
+        </is>
+      </c>
+      <c r="C693" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="D693" t="inlineStr">
+        <is>
+          <t>Airbnb</t>
+        </is>
+      </c>
+      <c r="E693" t="inlineStr">
+        <is>
+          <t>2026-07-27T07:00:34.000Z</t>
+        </is>
+      </c>
+      <c r="F693" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Airbnb Vs. 2000 Lemonades
+</t>
+        </is>
+      </c>
+      <c r="G693" t="inlineStr"/>
+      <c r="H693" t="inlineStr"/>
+      <c r="I693" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=q7nVT6scqr4</t>
+        </is>
+      </c>
+      <c r="J693" t="inlineStr">
+        <is>
+          <t>[Failed to fetch]</t>
+        </is>
+      </c>
+      <c r="K693" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=q7nVT6scqr4</t>
+        </is>
+      </c>
+      <c r="L693" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M693" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N693" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O693" t="inlineStr">
+        <is>
+          <t>Failed to analyze video transcript via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B694" t="inlineStr">
+        <is>
+          <t>AirBnb</t>
+        </is>
+      </c>
+      <c r="C694" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="D694" t="inlineStr">
+        <is>
+          <t>Airbnb</t>
+        </is>
+      </c>
+      <c r="E694" t="inlineStr">
+        <is>
+          <t>2026-07-27T07:00:27.000Z</t>
+        </is>
+      </c>
+      <c r="F694" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Airbnb Vs. 56 Soccer Games
+</t>
+        </is>
+      </c>
+      <c r="G694" t="inlineStr"/>
+      <c r="H694" t="inlineStr"/>
+      <c r="I694" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=xrYJmY0IkxE</t>
+        </is>
+      </c>
+      <c r="J694" t="inlineStr">
+        <is>
+          <t>[Failed to fetch]</t>
+        </is>
+      </c>
+      <c r="K694" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=xrYJmY0IkxE</t>
+        </is>
+      </c>
+      <c r="L694" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M694" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N694" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O694" t="inlineStr">
+        <is>
+          <t>Failed to analyze video transcript via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B695" t="inlineStr">
+        <is>
+          <t>AirBnb</t>
+        </is>
+      </c>
+      <c r="C695" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="D695" t="inlineStr">
+        <is>
+          <t>Airbnb</t>
+        </is>
+      </c>
+      <c r="E695" t="inlineStr">
+        <is>
+          <t>2026-07-27T07:00:39.000Z</t>
+        </is>
+      </c>
+      <c r="F695" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Airbnb Vs. A Lot of House Cats
+</t>
+        </is>
+      </c>
+      <c r="G695" t="inlineStr"/>
+      <c r="H695" t="inlineStr"/>
+      <c r="I695" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=oysDlk2ProE</t>
+        </is>
+      </c>
+      <c r="J695" t="inlineStr">
+        <is>
+          <t>[Failed to fetch]</t>
+        </is>
+      </c>
+      <c r="K695" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=oysDlk2ProE</t>
+        </is>
+      </c>
+      <c r="L695" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M695" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N695" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O695" t="inlineStr">
+        <is>
+          <t>Failed to analyze video transcript via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="696">
+      <c r="A696" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B696" t="inlineStr">
+        <is>
+          <t>AirBnb</t>
+        </is>
+      </c>
+      <c r="C696" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="D696" t="inlineStr">
+        <is>
+          <t>Airbnb</t>
+        </is>
+      </c>
+      <c r="E696" t="inlineStr">
+        <is>
+          <t>2026-07-27T07:00:20.000Z</t>
+        </is>
+      </c>
+      <c r="F696" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Airbnb Vs. 31 Violin Lessons
+</t>
+        </is>
+      </c>
+      <c r="G696" t="inlineStr"/>
+      <c r="H696" t="inlineStr"/>
+      <c r="I696" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=86S90AbhOzU</t>
+        </is>
+      </c>
+      <c r="J696" t="inlineStr">
+        <is>
+          <t>[Failed to fetch]</t>
+        </is>
+      </c>
+      <c r="K696" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=86S90AbhOzU</t>
+        </is>
+      </c>
+      <c r="L696" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M696" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N696" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O696" t="inlineStr">
+        <is>
+          <t>Failed to analyze video transcript via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B697" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C697" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D697" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E697" t="inlineStr">
+        <is>
+          <t>Mon Jul 27 06:40:34 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F697" t="inlineStr">
+        <is>
+          <t>Sentimos que tu vuelo se cancelara, que no hayas obtenido el reembolso y que haya tardado en responder, Carlos. Debido al gran volumen de casos en las redes sociales, no hemos podido contestar hasta ahora. 
+Desafortunadamente, aunque nos gustaría asistirte, no podemos ayudarte con reservas de vuelos a través de las redes sociales, pero puedes contactar a nuestro equipo de vuelos aquí: https://t.co/TBejpc4vOA, o llamar al +34918362949 desde España de lunes a domingo de 9:00 a 21:00 hora local. 
+Un saludo.</t>
+        </is>
+      </c>
+      <c r="G697" t="inlineStr"/>
+      <c r="H697" t="inlineStr"/>
+      <c r="I697" t="inlineStr"/>
+      <c r="J697" t="inlineStr"/>
+      <c r="K697" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2081630810969378975</t>
+        </is>
+      </c>
+      <c r="L697" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M697" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N697" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O697" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B698" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C698" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D698" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E698" t="inlineStr">
+        <is>
+          <t>Mon Jul 27 06:21:18 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F698" t="inlineStr">
+        <is>
+          <t>@ThomasseDurin Bonjour Thomasse, nous vous remercions de nous avoir contactés. Si vous souhaitez que nous consultions votre dossier pour mieux comprendre ce qui s'est passé, nous vous invitons à nous communiquer : 
+- le code confidentiel 
+- le nom complet du voyageur 
+Nous reviendrons ensuite au plus vite vers vous. 
+Cordialement</t>
+        </is>
+      </c>
+      <c r="G698" t="inlineStr"/>
+      <c r="H698" t="inlineStr"/>
+      <c r="I698" t="inlineStr"/>
+      <c r="J698" t="inlineStr"/>
+      <c r="K698" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2081625961108263386</t>
+        </is>
+      </c>
+      <c r="L698" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M698" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N698" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O698" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B699" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C699" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D699" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E699" t="inlineStr">
+        <is>
+          <t>Mon Jul 27 05:35:49 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F699" t="inlineStr">
+        <is>
+          <t>Sentimos lo ocurrido y haber tardado en responder, Pedro. Debido al gran volumen de casos en las redes sociales, no hemos podido contestar hasta ahora. 
+Para poder revisarlo, envíanos un mensaje privado con los siguientes datos y te responderemos lo antes posible: 
+- Número de confirmación: 
+- Código PIN: 
+- Nombre que aparece en la reserva: 
+- Detalles de tu solicitud: 
+Ten en cuenta que nuestro equipo de Redes Sociales no trabaja en tiempo real. Para recibir ayuda inmediata, llama a nuestro equipo de Atención al Cliente disponible 24/7; puedes encontrar nuestros datos de contacto aquí: https://t.co/o8QyR8SaDb 
+Un saludo.</t>
+        </is>
+      </c>
+      <c r="G699" t="inlineStr"/>
+      <c r="H699" t="inlineStr"/>
+      <c r="I699" t="inlineStr"/>
+      <c r="J699" t="inlineStr"/>
+      <c r="K699" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2081614515242672419</t>
+        </is>
+      </c>
+      <c r="L699" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M699" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N699" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O699" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B700" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C700" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D700" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E700" t="inlineStr">
+        <is>
+          <t>Mon Jul 27 05:28:06 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F700" t="inlineStr">
+        <is>
+          <t>@samuelp97439998 Sentimos que tu vuelo se cancelara y haber tardado en responder, Samuel. Respondimos tu mensaje privado.
+Saludos.</t>
+        </is>
+      </c>
+      <c r="G700" t="inlineStr"/>
+      <c r="H700" t="inlineStr"/>
+      <c r="I700" t="inlineStr"/>
+      <c r="J700" t="inlineStr"/>
+      <c r="K700" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2081612571317076184</t>
+        </is>
+      </c>
+      <c r="L700" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M700" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N700" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O700" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B701" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C701" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D701" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E701" t="inlineStr">
+        <is>
+          <t>Mon Jul 27 04:53:37 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F701" t="inlineStr">
+        <is>
+          <t>@MarianellaBerr5 Sentimos lo ocurrido, Marianella. Respondimos tu mensaje privado.
+Saludos.</t>
+        </is>
+      </c>
+      <c r="G701" t="inlineStr"/>
+      <c r="H701" t="inlineStr"/>
+      <c r="I701" t="inlineStr"/>
+      <c r="J701" t="inlineStr"/>
+      <c r="K701" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2081603896288460923</t>
+        </is>
+      </c>
+      <c r="L701" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M701" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N701" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O701" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B702" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C702" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D702" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E702" t="inlineStr">
+        <is>
+          <t>Mon Jul 27 00:55:49 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F702" t="inlineStr">
+        <is>
+          <t>Hi  Awori, we regret to hear about what happened to your booking, we'd be happy to look into the refund for you.
+To do so, please send us the following details in a (private message/DM), and we'll get back to you as soon as possible;
+- Confirmation number
+- PIN code
+- Name on the reservation</t>
+        </is>
+      </c>
+      <c r="G702" t="inlineStr"/>
+      <c r="H702" t="inlineStr"/>
+      <c r="I702" t="inlineStr"/>
+      <c r="J702" t="inlineStr"/>
+      <c r="K702" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2081544049249403080</t>
+        </is>
+      </c>
+      <c r="L702" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M702" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N702" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O702" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="703">
+      <c r="A703" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B703" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C703" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D703" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E703" t="inlineStr">
+        <is>
+          <t>Mon Jul 27 00:21:57 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F703" t="inlineStr">
+        <is>
+          <t>Hi there, we regret to hear that you're still unable to complete your verification even though you've followed all the instructions provided. Unfortunately, as much as we would like to help you with this matter, we are unable to do so. The only option to list your property is through this link: https://t.co/Ts3PBR6eT1, which we have already shared previously. Kind regards.</t>
+        </is>
+      </c>
+      <c r="G703" t="inlineStr"/>
+      <c r="H703" t="inlineStr"/>
+      <c r="I703" t="inlineStr"/>
+      <c r="J703" t="inlineStr"/>
+      <c r="K703" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2081535528831242654</t>
+        </is>
+      </c>
+      <c r="L703" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M703" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N703" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O703" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="704">
+      <c r="A704" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B704" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C704" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D704" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E704" t="inlineStr">
+        <is>
+          <t>Mon Jul 27 00:13:47 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F704" t="inlineStr">
+        <is>
+          <t>@MiriamFeldman12 Hi Miriam, we have sent you a reply via direct message. Please review it for more details. Thank you.</t>
+        </is>
+      </c>
+      <c r="G704" t="inlineStr"/>
+      <c r="H704" t="inlineStr"/>
+      <c r="I704" t="inlineStr"/>
+      <c r="J704" t="inlineStr"/>
+      <c r="K704" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2081533471265051012</t>
+        </is>
+      </c>
+      <c r="L704" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M704" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N704" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O704" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="705">
+      <c r="A705" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B705" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C705" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D705" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E705" t="inlineStr">
+        <is>
+          <t>Mon Jul 27 00:07:07 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F705" t="inlineStr">
+        <is>
+          <t>@medactif Hi there, we have sent you a private message. Please take a moment to check it. Thank you.</t>
+        </is>
+      </c>
+      <c r="G705" t="inlineStr"/>
+      <c r="H705" t="inlineStr"/>
+      <c r="I705" t="inlineStr"/>
+      <c r="J705" t="inlineStr"/>
+      <c r="K705" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2081531793509925268</t>
+        </is>
+      </c>
+      <c r="L705" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M705" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N705" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O705" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="706">
+      <c r="A706" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B706" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C706" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D706" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E706" t="inlineStr">
+        <is>
+          <t>Sun Jul 26 23:02:47 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F706" t="inlineStr">
+        <is>
+          <t>Hi Andreas, we regret learning that you are still unable to receive your anticipated refund and compensation. We recognize how disappointing this must be for you. 
+For us to investigate here, please DM us the following details, and we'll get back to you as soon as possible: 
+- Pin code 
+- Name on the reservation 
+Please bear in mind that our Social Media Team doesn't work in real time. For immediate support, please call our 24/7 Customer Service Team - our contact details can be found here: https://t.co/tuuNbmGVaG.</t>
+        </is>
+      </c>
+      <c r="G706" t="inlineStr"/>
+      <c r="H706" t="inlineStr"/>
+      <c r="I706" t="inlineStr"/>
+      <c r="J706" t="inlineStr"/>
+      <c r="K706" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2081515605467763049</t>
+        </is>
+      </c>
+      <c r="L706" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M706" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N706" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O706" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="707">
+      <c r="A707" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B707" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C707" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D707" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E707" t="inlineStr">
+        <is>
+          <t>Sun Jul 26 23:02:33 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F707" t="inlineStr">
+        <is>
+          <t>Hello Dr. Dima, we regret to hear that you're facing difficulties in contacting our customer support team. We’d be happy to look into your booking to see what happened. Please send us the following details in a private message/DM, and we’ll get back to you as soon as possible: 
+- Confirmation number 
+- PIN code 
+- Name on the reservation</t>
+        </is>
+      </c>
+      <c r="G707" t="inlineStr"/>
+      <c r="H707" t="inlineStr"/>
+      <c r="I707" t="inlineStr"/>
+      <c r="J707" t="inlineStr"/>
+      <c r="K707" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2081515545967403346</t>
+        </is>
+      </c>
+      <c r="L707" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M707" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N707" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O707" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="708">
+      <c r="A708" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B708" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C708" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D708" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E708" t="inlineStr">
+        <is>
+          <t>Sun Jul 26 22:46:55 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F708" t="inlineStr">
+        <is>
+          <t>We regret the distress you experienced when your confirmed reservation was not honored and the property was unable to accommodate you, Aditi. The availability of rooms is set up by the properties themselves, and they are solely responsible for ensuring this information is correct. We do not decide on behalf of the property how many (if any) rooms they choose to make available through our platform for any given date.
+If a property is unable to honor a booking, they should help you find another place to stay. If they're unable or unwilling to provide this, they should let us know as soon as possible so that we can help to find a solution. Please DM us the following details:
+• Confirmation number:
+• PIN code:
+• Name on the reservation:
+Alternatively, for immediate support, you can always give us a call here: https://t.co/o8QyR8SaDb.</t>
+        </is>
+      </c>
+      <c r="G708" t="inlineStr"/>
+      <c r="H708" t="inlineStr"/>
+      <c r="I708" t="inlineStr"/>
+      <c r="J708" t="inlineStr"/>
+      <c r="K708" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2081511611076952353</t>
+        </is>
+      </c>
+      <c r="L708" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M708" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N708" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O708" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="709">
+      <c r="A709" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B709" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C709" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D709" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E709" t="inlineStr">
+        <is>
+          <t>Sun Jul 26 22:42:41 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F709" t="inlineStr">
+        <is>
+          <t>@Sandeepd9c2 Hi Sandeep, we regret to hear about your experience. We’ve already followed up with you via direct message—please check your inbox at your convenience. Thank you. https://t.co/Z89AAoEgD7</t>
+        </is>
+      </c>
+      <c r="G709" t="inlineStr"/>
+      <c r="H709" t="inlineStr"/>
+      <c r="I709" t="inlineStr"/>
+      <c r="J709" t="inlineStr"/>
+      <c r="K709" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2081510547372085585</t>
+        </is>
+      </c>
+      <c r="L709" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M709" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N709" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O709" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="710">
+      <c r="A710" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B710" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C710" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D710" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E710" t="inlineStr">
+        <is>
+          <t>Sun Jul 26 22:23:35 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F710" t="inlineStr">
+        <is>
+          <t>Hi there, thank you for reaching out to us. We are responding to you in English because, unfortunately, we do not offer support in Arabic on social media. We can assist you here in Dutch, English, French, German, Italian, Portuguese, and Spanish. 
+We’ve also responded to your private message, so please take a moment to review it at your convenience. 
+Alternatively, if you prefer to reach out in Arabic, you can find your local number here: https://t.co/6FMd8r77Bx. Thank you.</t>
+        </is>
+      </c>
+      <c r="G710" t="inlineStr"/>
+      <c r="H710" t="inlineStr"/>
+      <c r="I710" t="inlineStr"/>
+      <c r="J710" t="inlineStr"/>
+      <c r="K710" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2081505738380210521</t>
+        </is>
+      </c>
+      <c r="L710" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M710" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N710" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O710" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="711">
+      <c r="A711" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B711" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C711" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D711" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E711" t="inlineStr">
+        <is>
+          <t>Sun Jul 26 20:43:15 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F711" t="inlineStr">
+        <is>
+          <t>@ved1985prakash3 Hi there, thanks for reaching back to us. We regret to hear that you have not yet received a response, and it's been more than 15 days. For us to look into this matter further, kindly send us a private message. Hoping to hear from you soon. Kind regards. https://t.co/Z89AAoEgD7</t>
+        </is>
+      </c>
+      <c r="G711" t="inlineStr"/>
+      <c r="H711" t="inlineStr"/>
+      <c r="I711" t="inlineStr"/>
+      <c r="J711" t="inlineStr"/>
+      <c r="K711" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2081480488439435278</t>
+        </is>
+      </c>
+      <c r="L711" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M711" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N711" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O711" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="712">
+      <c r="A712" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B712" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C712" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D712" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E712" t="inlineStr">
+        <is>
+          <t>Sun Jul 26 20:09:30 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F712" t="inlineStr">
+        <is>
+          <t>@cactushoney12 Hi there, we have sent you a private message. Please check it. Thank you.</t>
+        </is>
+      </c>
+      <c r="G712" t="inlineStr"/>
+      <c r="H712" t="inlineStr"/>
+      <c r="I712" t="inlineStr"/>
+      <c r="J712" t="inlineStr"/>
+      <c r="K712" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2081471997482094873</t>
+        </is>
+      </c>
+      <c r="L712" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M712" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N712" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O712" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="713">
+      <c r="A713" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B713" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C713" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D713" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E713" t="inlineStr">
+        <is>
+          <t>Sun Jul 26 18:29:25 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F713" t="inlineStr">
+        <is>
+          <t>@Dev_011295 Hi Devender, we have addressed your private message. To facilitate the next steps, we kindly request that you provide the necessary details at your earliest convenience. Thank you for your cooperation.</t>
+        </is>
+      </c>
+      <c r="G713" t="inlineStr"/>
+      <c r="H713" t="inlineStr"/>
+      <c r="I713" t="inlineStr"/>
+      <c r="J713" t="inlineStr"/>
+      <c r="K713" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2081446810149703930</t>
+        </is>
+      </c>
+      <c r="L713" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M713" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N713" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O713" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="714">
+      <c r="A714" t="inlineStr">
+        <is>
+          <t>Mondee</t>
+        </is>
+      </c>
+      <c r="B714" t="inlineStr">
+        <is>
+          <t>Booking.com for Travel Agents</t>
+        </is>
+      </c>
+      <c r="C714" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D714" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E714" t="inlineStr">
+        <is>
+          <t>Mon Jul 27 07:24:57 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F714" t="inlineStr">
+        <is>
+          <t>Hi Sona, how can we help? If your request is related to an accommodation booking, please DM us the following details and we'll get back to you as soon as possible: 
+- Confirmation number:
+- Pin code:
+- Name on the reservation:
+- Details on your request:
+Please bear in mind that our Social Media Team doesn't work in real time. For immediate support, please call our 24/7 Customer Service Team - our contact details can be found here: https://t.co/o8QyR8SaDb
+Also, at this time, we only offer support for accommodation bookings via social media. For questions about Flights, Taxis, or Insurance, you can reach out to the dedicated support team here: https://t.co/UfRgpDJomK</t>
+        </is>
+      </c>
+      <c r="G714" t="inlineStr"/>
+      <c r="H714" t="inlineStr"/>
+      <c r="I714" t="inlineStr"/>
+      <c r="J714" t="inlineStr"/>
+      <c r="K714" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2081641980346433838</t>
+        </is>
+      </c>
+      <c r="L714" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M714" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N714" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O714" t="inlineStr">
+        <is>
+          <t>Failed to analyze post via LLM.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/News_Dashboard/data/social_media_posts.xlsx
+++ b/News_Dashboard/data/social_media_posts.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O714"/>
+  <dimension ref="A1:O733"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -45704,6 +45704,1189 @@
         </is>
       </c>
     </row>
+    <row r="715">
+      <c r="A715" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B715" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C715" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D715" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E715" t="inlineStr">
+        <is>
+          <t>Mon Jul 27 11:10:44 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F715" t="inlineStr">
+        <is>
+          <t>@mooch1uk Hi Kelly, we've replied to your DM and look forward to your response. https://t.co/Z89AAoEgD7</t>
+        </is>
+      </c>
+      <c r="G715" t="inlineStr"/>
+      <c r="H715" t="inlineStr"/>
+      <c r="I715" t="inlineStr"/>
+      <c r="J715" t="inlineStr"/>
+      <c r="K715" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2081698797441134956</t>
+        </is>
+      </c>
+      <c r="L715" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M715" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N715" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O715" t="inlineStr">
+        <is>
+          <t>Booking.com replied to a user’s direct message, demonstrating routine customer support engagement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="716">
+      <c r="A716" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B716" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C716" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D716" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E716" t="inlineStr">
+        <is>
+          <t>Mon Jul 27 11:03:43 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F716" t="inlineStr">
+        <is>
+          <t>@ctoipasmoiok Bonjour, toutes nos excuses pour le délai de réponse. Nous vous avons envoyé un message privé, pourriez-vous le consulter dès que possible ?</t>
+        </is>
+      </c>
+      <c r="G716" t="inlineStr"/>
+      <c r="H716" t="inlineStr"/>
+      <c r="I716" t="inlineStr"/>
+      <c r="J716" t="inlineStr"/>
+      <c r="K716" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2081697034638155980</t>
+        </is>
+      </c>
+      <c r="L716" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M716" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N716" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O716" t="inlineStr">
+        <is>
+          <t>Booking.com apologized for a delayed response and asked a user to check a private message.</t>
+        </is>
+      </c>
+    </row>
+    <row r="717">
+      <c r="A717" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B717" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C717" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D717" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E717" t="inlineStr">
+        <is>
+          <t>Mon Jul 27 10:49:08 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F717" t="inlineStr">
+        <is>
+          <t>Hi there, unfortunately we're unable to assist with Flight reservations through social media, but you can contact our Flights team here: https://t.co/TBejpc4vOA, or call {US}+1 917 421 7240 / {UK}+44 2039019061 / {IE} +353 19075677, and they will be able to look into this for you.</t>
+        </is>
+      </c>
+      <c r="G717" t="inlineStr"/>
+      <c r="H717" t="inlineStr"/>
+      <c r="I717" t="inlineStr"/>
+      <c r="J717" t="inlineStr"/>
+      <c r="K717" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2081693361765757269</t>
+        </is>
+      </c>
+      <c r="L717" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M717" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N717" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O717" t="inlineStr">
+        <is>
+          <t>Booking.com informs users that flight reservations cannot be handled via social media and directs them to contact the Flights team via link or phone.</t>
+        </is>
+      </c>
+    </row>
+    <row r="718">
+      <c r="A718" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B718" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C718" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D718" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E718" t="inlineStr">
+        <is>
+          <t>Mon Jul 27 10:16:08 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F718" t="inlineStr">
+        <is>
+          <t>@Lucietravert2 - Numéro de confirmation
+- Code confidentiel
+- Nom indiqué sur la réservation
+En alternative, pour une assistance immédiate, vous pouvez également nous appeler ici : https://t.co/aH74XgSLGq</t>
+        </is>
+      </c>
+      <c r="G718" t="inlineStr"/>
+      <c r="H718" t="inlineStr"/>
+      <c r="I718" t="inlineStr"/>
+      <c r="J718" t="inlineStr"/>
+      <c r="K718" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2081685057995997185</t>
+        </is>
+      </c>
+      <c r="L718" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M718" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N718" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O718" t="inlineStr">
+        <is>
+          <t>Booking.com posts a customer support message offering assistance via confirmation details or a phone call.</t>
+        </is>
+      </c>
+    </row>
+    <row r="719">
+      <c r="A719" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B719" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C719" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D719" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E719" t="inlineStr">
+        <is>
+          <t>Mon Jul 27 10:15:50 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F719" t="inlineStr">
+        <is>
+          <t>@Lucietravert2 Nous regrettons de lire votre déception. Si vous avez toujours besoin d’assistance, n’hésitez pas à nous envoyer un message privé en nous expliquant plus en détail ce qu’il s’est passé, ainsi que les informations suivantes :</t>
+        </is>
+      </c>
+      <c r="G719" t="inlineStr"/>
+      <c r="H719" t="inlineStr"/>
+      <c r="I719" t="inlineStr"/>
+      <c r="J719" t="inlineStr"/>
+      <c r="K719" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2081684982704050407</t>
+        </is>
+      </c>
+      <c r="L719" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="M719" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N719" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O719" t="inlineStr">
+        <is>
+          <t>Booking.com replied to a dissatisfied user, apologizing and offering further assistance via private message.</t>
+        </is>
+      </c>
+    </row>
+    <row r="720">
+      <c r="A720" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B720" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C720" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D720" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E720" t="inlineStr">
+        <is>
+          <t>Mon Jul 27 10:15:37 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F720" t="inlineStr">
+        <is>
+          <t>@Lucietravert2 Bonjour Lucie, toutes nos excuses pour le délai de réponse. Nous recevons actuellement un volume important de demandes sur les réseaux sociaux et n’avons pas pu vous répondre plus tôt.</t>
+        </is>
+      </c>
+      <c r="G720" t="inlineStr"/>
+      <c r="H720" t="inlineStr"/>
+      <c r="I720" t="inlineStr"/>
+      <c r="J720" t="inlineStr"/>
+      <c r="K720" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2081684930354893027</t>
+        </is>
+      </c>
+      <c r="L720" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M720" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N720" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O720" t="inlineStr">
+        <is>
+          <t>Booking.com apologizes for a delayed response to a user due to a high volume of social media inquiries.</t>
+        </is>
+      </c>
+    </row>
+    <row r="721">
+      <c r="A721" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B721" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C721" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D721" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E721" t="inlineStr">
+        <is>
+          <t>Mon Jul 27 10:11:24 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F721" t="inlineStr">
+        <is>
+          <t>@lakesalford Hello Stephen, we regret to hear about your experience. Please DM a brief summary of you claim together with the following details, and we'll provide further assistance: 
+- booking number
+- pin code
+- full name of the guest on the reservation.
+Regards https://t.co/Z89AAoEgD7</t>
+        </is>
+      </c>
+      <c r="G721" t="inlineStr"/>
+      <c r="H721" t="inlineStr"/>
+      <c r="I721" t="inlineStr"/>
+      <c r="J721" t="inlineStr"/>
+      <c r="K721" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2081683866591396231</t>
+        </is>
+      </c>
+      <c r="L721" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M721" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N721" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O721" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a customer complaint on X, requesting booking details to provide further assistance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="722">
+      <c r="A722" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B722" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C722" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D722" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E722" t="inlineStr">
+        <is>
+          <t>Mon Jul 27 09:31:43 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F722" t="inlineStr">
+        <is>
+          <t>@_Yamanaki_ Hi there, we replied to your DM. Feel free to review it as soon as you can. 
+Kind regards</t>
+        </is>
+      </c>
+      <c r="G722" t="inlineStr"/>
+      <c r="H722" t="inlineStr"/>
+      <c r="I722" t="inlineStr"/>
+      <c r="J722" t="inlineStr"/>
+      <c r="K722" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2081673881228603451</t>
+        </is>
+      </c>
+      <c r="L722" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M722" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N722" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O722" t="inlineStr">
+        <is>
+          <t>Booking.com replied to a private message from user @_Yamanaki_, offering assistance and encouraging review of the response.</t>
+        </is>
+      </c>
+    </row>
+    <row r="723">
+      <c r="A723" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B723" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C723" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D723" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E723" t="inlineStr">
+        <is>
+          <t>Mon Jul 27 08:38:06 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F723" t="inlineStr">
+        <is>
+          <t>@S_Elhussieny Hello Samar, we've sent you a DM with more information regarding your case. Please review it and get back. Regards</t>
+        </is>
+      </c>
+      <c r="G723" t="inlineStr"/>
+      <c r="H723" t="inlineStr"/>
+      <c r="I723" t="inlineStr"/>
+      <c r="J723" t="inlineStr"/>
+      <c r="K723" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2081660388949577871</t>
+        </is>
+      </c>
+      <c r="L723" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M723" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N723" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O723" t="inlineStr">
+        <is>
+          <t>Booking.com is following up with a user regarding a case via direct message.</t>
+        </is>
+      </c>
+    </row>
+    <row r="724">
+      <c r="A724" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B724" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C724" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D724" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E724" t="inlineStr">
+        <is>
+          <t>Mon Jul 27 08:35:33 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F724" t="inlineStr">
+        <is>
+          <t>@kasuke861 - Numéro de confirmation
+- Code confidentiel
+- Nom indiqué sur la réservation
+En alternative, pour une assistance immédiate, vous pouvez également nous appeler ici : https://t.co/aH74XgSLGq</t>
+        </is>
+      </c>
+      <c r="G724" t="inlineStr"/>
+      <c r="H724" t="inlineStr"/>
+      <c r="I724" t="inlineStr"/>
+      <c r="J724" t="inlineStr"/>
+      <c r="K724" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2081659747401355379</t>
+        </is>
+      </c>
+      <c r="L724" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M724" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N724" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O724" t="inlineStr">
+        <is>
+          <t>Booking.com shares confirmation details and offers phone support for immediate assistance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="725">
+      <c r="A725" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B725" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C725" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D725" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E725" t="inlineStr">
+        <is>
+          <t>Mon Jul 27 08:35:08 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F725" t="inlineStr">
+        <is>
+          <t>@kasuke861 Nous regrettons de lire votre déception. Si vous avez toujours besoin d’assistance, n’hésitez pas à nous envoyer un message privé en nous expliquant plus en détail ce qu’il s’est passé, ainsi que les informations suivantes :</t>
+        </is>
+      </c>
+      <c r="G725" t="inlineStr"/>
+      <c r="H725" t="inlineStr"/>
+      <c r="I725" t="inlineStr"/>
+      <c r="J725" t="inlineStr"/>
+      <c r="K725" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2081659642237600229</t>
+        </is>
+      </c>
+      <c r="L725" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M725" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N725" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O725" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a customer’s complaint, offering further assistance via private message.</t>
+        </is>
+      </c>
+    </row>
+    <row r="726">
+      <c r="A726" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B726" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C726" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D726" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E726" t="inlineStr">
+        <is>
+          <t>Mon Jul 27 08:34:52 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F726" t="inlineStr">
+        <is>
+          <t>@kasuke861 Bonjour, toutes nos excuses pour le délai de réponse. Nous recevons actuellement un volume important de demandes sur les réseaux sociaux et n’avons pas pu vous répondre plus tôt.</t>
+        </is>
+      </c>
+      <c r="G726" t="inlineStr"/>
+      <c r="H726" t="inlineStr"/>
+      <c r="I726" t="inlineStr"/>
+      <c r="J726" t="inlineStr"/>
+      <c r="K726" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2081659574256374171</t>
+        </is>
+      </c>
+      <c r="L726" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M726" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N726" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O726" t="inlineStr">
+        <is>
+          <t>Booking.com apologized for a delayed response to a user, citing a high volume of social media inquiries.</t>
+        </is>
+      </c>
+    </row>
+    <row r="727">
+      <c r="A727" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B727" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C727" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D727" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E727" t="inlineStr">
+        <is>
+          <t>Mon Jul 27 08:23:58 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F727" t="inlineStr">
+        <is>
+          <t>Bonjour Judith, 
+Pour que nous puissions nous renseigner davantage sur la situation, nous vous invitons à nous communiquer, uniquement en message privé pour des raisons de confidentialité :
+- le code confidentiel
+Nous reviendrons ensuite au plus vite vers vous mais gardez à l'esprit que notre équipe des réseaux sociaux ne fonctionne pas en temps réel.
+Cordialement.</t>
+        </is>
+      </c>
+      <c r="G727" t="inlineStr"/>
+      <c r="H727" t="inlineStr"/>
+      <c r="I727" t="inlineStr"/>
+      <c r="J727" t="inlineStr"/>
+      <c r="K727" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2081656829705126018</t>
+        </is>
+      </c>
+      <c r="L727" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M727" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N727" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O727" t="inlineStr">
+        <is>
+          <t>Booking.com is requesting a confidential code from a user via private message, indicating a private support interaction rather than a public announcement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="728">
+      <c r="A728" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B728" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C728" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D728" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E728" t="inlineStr">
+        <is>
+          <t>Mon Jul 27 08:23:01 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F728" t="inlineStr">
+        <is>
+          <t>Hola, Héctor. Lamentamos los inconvenientes que estás teniendo para contactar a nuestro equipo de Atención al Cliente. Cuéntanos, ¿en qué podemos ayudarte?. Si tu consulta está relacionada con una reserva de alojamiento, envíanos un mensaje privado con los siguientes datos y te responderemos lo antes posible:
+- Número de confirmación:
+- Código PIN:
+- Nombre que aparece en la reserva:
+- Detalles de tu solicitud:
+Ten en cuenta que nuestro equipo de Redes Sociales no trabaja en tiempo real. Para recibir ayuda inmediata, llama a nuestro equipo de Atención al Cliente disponible 24/7; puedes encontrar nuestros datos de contacto aquí:  https://t.co/o8QyR8SaDb
+Además, por el momento solo ofrecemos soporte para reservas de alojamiento a través de las redes sociales. Para preguntas sobre Vuelos, Taxis o Seguros, puedes contactar con los equipos especializados aquí:  https://t.co/TBejpc4vOA.
+Un saludo.</t>
+        </is>
+      </c>
+      <c r="G728" t="inlineStr"/>
+      <c r="H728" t="inlineStr"/>
+      <c r="I728" t="inlineStr"/>
+      <c r="J728" t="inlineStr"/>
+      <c r="K728" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2081656590025830532</t>
+        </is>
+      </c>
+      <c r="L728" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M728" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N728" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O728" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a customer’s difficulty contacting support, detailing the information needed for assistance and offering phone and specialized team contacts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="729">
+      <c r="A729" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B729" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C729" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D729" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E729" t="inlineStr">
+        <is>
+          <t>Mon Jul 27 08:18:40 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F729" t="inlineStr">
+        <is>
+          <t>@Lusavitch Thank you for the clarification. We hope you have a better experience in the future. Regards</t>
+        </is>
+      </c>
+      <c r="G729" t="inlineStr"/>
+      <c r="H729" t="inlineStr"/>
+      <c r="I729" t="inlineStr"/>
+      <c r="J729" t="inlineStr"/>
+      <c r="K729" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2081655495669039603</t>
+        </is>
+      </c>
+      <c r="L729" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M729" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N729" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O729" t="inlineStr">
+        <is>
+          <t>Booking.com replied to a user on X, thanking them for clarification and wishing them a better experience.</t>
+        </is>
+      </c>
+    </row>
+    <row r="730">
+      <c r="A730" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B730" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C730" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D730" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E730" t="inlineStr">
+        <is>
+          <t>Mon Jul 27 08:14:25 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F730" t="inlineStr">
+        <is>
+          <t>@shrikant535 Hello there, we regret to hear about your experience. As much as we'd like to help you, we are unable to offer support to our partners via social media. However, you can find the contact information for our Partner Support team here: https://t.co/N4c4HTAv4f?</t>
+        </is>
+      </c>
+      <c r="G730" t="inlineStr"/>
+      <c r="H730" t="inlineStr"/>
+      <c r="I730" t="inlineStr"/>
+      <c r="J730" t="inlineStr"/>
+      <c r="K730" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2081654426788385176</t>
+        </is>
+      </c>
+      <c r="L730" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M730" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N730" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O730" t="inlineStr">
+        <is>
+          <t>Booking.com replies to a partner’s complaint on X, offering contact details for partner support instead of direct assistance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="731">
+      <c r="A731" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B731" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C731" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D731" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E731" t="inlineStr">
+        <is>
+          <t>Mon Jul 27 08:04:27 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F731" t="inlineStr">
+        <is>
+          <t>@ShyamCh27035212 Hi there, we've just replied to your DM. Please have a look at this at your earliest convenience. Thank you. https://t.co/Z89AAoEgD7</t>
+        </is>
+      </c>
+      <c r="G731" t="inlineStr"/>
+      <c r="H731" t="inlineStr"/>
+      <c r="I731" t="inlineStr"/>
+      <c r="J731" t="inlineStr"/>
+      <c r="K731" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2081651918024192356</t>
+        </is>
+      </c>
+      <c r="L731" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M731" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N731" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O731" t="inlineStr">
+        <is>
+          <t>Booking.com replied to a user’s direct message, offering assistance and directing them to a link.</t>
+        </is>
+      </c>
+    </row>
+    <row r="732">
+      <c r="A732" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B732" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C732" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D732" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E732" t="inlineStr">
+        <is>
+          <t>Mon Jul 27 07:36:11 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F732" t="inlineStr">
+        <is>
+          <t>@ecstewar1 Hi Geoff, we just replied to your DM, kindly take a look!</t>
+        </is>
+      </c>
+      <c r="G732" t="inlineStr"/>
+      <c r="H732" t="inlineStr"/>
+      <c r="I732" t="inlineStr"/>
+      <c r="J732" t="inlineStr"/>
+      <c r="K732" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2081644804027343118</t>
+        </is>
+      </c>
+      <c r="L732" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M732" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N732" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O732" t="inlineStr">
+        <is>
+          <t>Booking.com replied to a direct message from a user, with no public announcement or significant activity disclosed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="733">
+      <c r="A733" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B733" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C733" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D733" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E733" t="inlineStr">
+        <is>
+          <t>Mon Jul 27 07:33:30 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F733" t="inlineStr">
+        <is>
+          <t>Sentimos lo ocurrido con el cobro de comisiones y haber tardado en responder. Debido al gran volumen de casos en las redes sociales, no hemos podido contestar hasta ahora. 
+Por motivos de seguridad, lamentablemente no podemos ofrecer asistencia a nuestros colaboradores a través de las redes sociales. Sin embargo, puedes encontrar los datos de contacto de nuestro equipo de Ayuda para colaboradores aquí: https://t.co/QpD1nP4Qdu? 
+Saludos.</t>
+        </is>
+      </c>
+      <c r="G733" t="inlineStr"/>
+      <c r="H733" t="inlineStr"/>
+      <c r="I733" t="inlineStr"/>
+      <c r="J733" t="inlineStr"/>
+      <c r="K733" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2081644128836706525</t>
+        </is>
+      </c>
+      <c r="L733" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="M733" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N733" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O733" t="inlineStr">
+        <is>
+          <t>Booking.com apologizes for commission charge issues and delayed responses, directing collaborators to the help center for assistance.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/News_Dashboard/data/social_media_posts.xlsx
+++ b/News_Dashboard/data/social_media_posts.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,77 +417,77 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Base_Company</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Competitor</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Author/Handle</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Date Created</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Post Text</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Image URL</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Image Text</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Video URL</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Video Transcript</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Post URL</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Sentiment</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Alert Level</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>AI Summary</t>
         </is>
@@ -7316,10 +7304,7 @@
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>[Transcript unavailable: 
-Could not retrieve a transcript for the video https://www.youtube.com/watch?v=M6MP4urwaBw! This is most likely caused by:
-Subtitles are disabled for this video
-If you are sure that the described cause is not responsible for this error and that a transcript should be retrievable, please create an issue at https://github.com/jdepoix/youtube-transcript-api/issues. Please add which version of youtube_transcript_api you are using and provide the information needed to replicate the error. Also make sure that there are no open issues which already describe your problem!]</t>
+          <t>[Failed to fetch]</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
@@ -9228,17 +9213,7 @@
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>[Transcript unavailable: 
-Could not retrieve a transcript for the video https://www.youtube.com/watch?v=FqYh9C_W-I4! This is most likely caused by:
-No transcripts were found for any of the requested language codes: ('en',)
-For this video (FqYh9C_W-I4) transcripts are available in the following languages:
-(MANUALLY CREATED)
-None
-(GENERATED)
- - vi ("Vietnamese (auto-generated)")[TRANSLATABLE]
-(TRANSLATION LANGUAGES)
- - en ("English")
-If you are sure that the described cause is not responsible for this error and that a transcript should be retrievable, please create an issue at https://github.com/jdepoix/youtube-transcript-api/issues. Please add which version of youtube_transcript_api you are using and provide the information needed to replicate the error. Also make sure that there are no open issues which already describe your problem!]</t>
+          <t>[Failed to fetch]</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
@@ -9292,7 +9267,7 @@
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>[music] &gt;&gt; Oh. Hey, what's up?</t>
+          <t>[Failed to fetch]</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
@@ -27066,22 +27041,22 @@
       </c>
       <c r="L424" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="M424" t="inlineStr">
         <is>
-          <t>General Industry News</t>
+          <t>Product Announcement</t>
         </is>
       </c>
       <c r="N424" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="O424" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Ramp teases an upcoming initiative or partnership with the Tokenmaxx community, indicating a new product or service rollout.</t>
         </is>
       </c>
     </row>
@@ -27128,12 +27103,12 @@
       </c>
       <c r="L425" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="M425" t="inlineStr">
         <is>
-          <t>General Industry News</t>
+          <t>Partnership and Acquisitions</t>
         </is>
       </c>
       <c r="N425" t="inlineStr">
@@ -27143,7 +27118,7 @@
       </c>
       <c r="O425" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Ramp is offering a free service or promotion to user @karimatiyeh, indicating a partnership or promotional initiative.</t>
         </is>
       </c>
     </row>
@@ -27189,22 +27164,22 @@
       </c>
       <c r="L426" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="M426" t="inlineStr">
         <is>
-          <t>General Industry News</t>
+          <t>Partnership and Acquisitions</t>
         </is>
       </c>
       <c r="N426" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="O426" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Ramp highlights a collaboration with @restocc and @eglyman, suggesting a potential partnership or joint initiative.</t>
         </is>
       </c>
     </row>
@@ -27250,12 +27225,12 @@
       </c>
       <c r="L427" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="M427" t="inlineStr">
         <is>
-          <t>General Industry News</t>
+          <t>Partnership and Acquisitions</t>
         </is>
       </c>
       <c r="N427" t="inlineStr">
@@ -27265,7 +27240,7 @@
       </c>
       <c r="O427" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Ramp mentions @pontusab, likely indicating a partnership or collaboration announcement.</t>
         </is>
       </c>
     </row>
@@ -27313,22 +27288,22 @@
       </c>
       <c r="L428" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="M428" t="inlineStr">
         <is>
-          <t>General Industry News</t>
+          <t>Tech Updates</t>
         </is>
       </c>
       <c r="N428" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="O428" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Ramp announced a data‑driven analysis of spending profiles, detailing variations in model choices, caching habits, prompts, and spend controls, and invites users to compare their own usage.</t>
         </is>
       </c>
     </row>
@@ -27376,22 +27351,22 @@
       </c>
       <c r="L429" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="M429" t="inlineStr">
         <is>
-          <t>General Industry News</t>
+          <t>Product Announcement</t>
         </is>
       </c>
       <c r="N429" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="O429" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Ramp promotes a new AI spend management feature that connects business data, tracks team trends, and maximizes token value.</t>
         </is>
       </c>
     </row>
@@ -27437,12 +27412,12 @@
       </c>
       <c r="L430" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="M430" t="inlineStr">
         <is>
-          <t>General Industry News</t>
+          <t>Leadership Changes</t>
         </is>
       </c>
       <c r="N430" t="inlineStr">
@@ -27452,7 +27427,7 @@
       </c>
       <c r="O430" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Ramp shares a playful tweet acknowledging its CFO, expressing appreciation.</t>
         </is>
       </c>
     </row>
@@ -27513,7 +27488,7 @@
       </c>
       <c r="O431" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Brex data reveals that three of the top 25 most-purchased founder books this year are from Stripe Press, with two more just outside the list, underscoring the press's growing influence among startup founders.</t>
         </is>
       </c>
     </row>
@@ -27574,7 +27549,7 @@
       </c>
       <c r="O432" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Brex reports shifts in the popularity of books among its founders, with Atomic Habits falling in rank while titles like High Output Management and The Hard Thing About Hard Things rise.</t>
         </is>
       </c>
     </row>
@@ -27635,7 +27610,7 @@
       </c>
       <c r="O433" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Brex shares data revealing that founders’ purchasing habits reflect their interests, with the most popular business book among Brex cardholders in H1 2026 being a new biography of Alex Karp.</t>
         </is>
       </c>
     </row>
@@ -27681,12 +27656,12 @@
       </c>
       <c r="L434" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="M434" t="inlineStr">
         <is>
-          <t>General Industry News</t>
+          <t>Partnership and Acquisitions</t>
         </is>
       </c>
       <c r="N434" t="inlineStr">
@@ -27696,7 +27671,7 @@
       </c>
       <c r="O434" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Brex teases a collaboration with several wine industry influencers, indicating a new partnership or initiative.</t>
         </is>
       </c>
     </row>
@@ -27782,7 +27757,7 @@
       </c>
       <c r="O435" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Brex posted a curated list of business and leadership books, showcasing resources for professional development and thought leadership.</t>
         </is>
       </c>
     </row>
@@ -27845,7 +27820,7 @@
       </c>
       <c r="O436" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Brex reports that founder biographies are the top book choice among its 35,000+ customers, with a shift toward AI in management frameworks noted in H1 2026 rankings.</t>
         </is>
       </c>
     </row>
@@ -27901,12 +27876,12 @@
       </c>
       <c r="L437" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="M437" t="inlineStr">
         <is>
-          <t>General Industry News</t>
+          <t>Partnership and Acquisitions</t>
         </is>
       </c>
       <c r="N437" t="inlineStr">
@@ -27916,7 +27891,7 @@
       </c>
       <c r="O437" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Airbnb partnered with Heartshare and supported 50 foster youth to attend a 2026 FIFA World Cup match, showcasing its commitment to community engagement and youth empowerment.</t>
         </is>
       </c>
     </row>
@@ -27966,12 +27941,12 @@
       </c>
       <c r="L438" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="M438" t="inlineStr">
         <is>
-          <t>General Industry News</t>
+          <t>Product Announcement</t>
         </is>
       </c>
       <c r="N438" t="inlineStr">
@@ -27981,7 +27956,7 @@
       </c>
       <c r="O438" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Expedia promotes a Norwegian travel package featuring fjords, midnight sun hikes, and cabin stays, encouraging bookings through a provided link.</t>
         </is>
       </c>
     </row>
@@ -28043,12 +28018,12 @@
       </c>
       <c r="L439" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="M439" t="inlineStr">
         <is>
-          <t>General Industry News</t>
+          <t>Product Announcement</t>
         </is>
       </c>
       <c r="N439" t="inlineStr">
@@ -28058,7 +28033,7 @@
       </c>
       <c r="O439" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Expedia promotes a curated Big Sur road‑trip itinerary and highlights booking perks such as OneKeyCash and future travel benefits to entice users to book through its platform.</t>
         </is>
       </c>
     </row>
@@ -28119,7 +28094,7 @@
       </c>
       <c r="O440" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Booking.com informs users that flight reservations cannot be handled via social media and directs them to contact the Flights team via a provided link or phone numbers.</t>
         </is>
       </c>
     </row>
@@ -28165,7 +28140,7 @@
       </c>
       <c r="L441" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="M441" t="inlineStr">
@@ -28180,7 +28155,7 @@
       </c>
       <c r="O441" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Booking.com responds to a user complaint about flight reservation assistance, citing GDPR and security restrictions that prevent them from providing help on social media and advising the user to contact the flight team again.</t>
         </is>
       </c>
     </row>
@@ -28227,7 +28202,7 @@
       </c>
       <c r="L442" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="M442" t="inlineStr">
@@ -28242,7 +28217,7 @@
       </c>
       <c r="O442" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Booking.com responds to a user’s inquiry, offering help and directing them to a specialized support team.</t>
         </is>
       </c>
     </row>
@@ -28317,7 +28292,7 @@
       </c>
       <c r="O443" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Booking.com reiterates its customer data protection policies, clarifying that it does not request credit card details via phone or email, does not use WhatsApp for support, and provides official communication channels.</t>
         </is>
       </c>
     </row>
@@ -28378,7 +28353,7 @@
       </c>
       <c r="O444" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Booking.com replied to a user’s direct message, indicating routine customer support activity.</t>
         </is>
       </c>
     </row>
@@ -28439,7 +28414,7 @@
       </c>
       <c r="O445" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Booking.com responds to a customer complaint about a pending refund, directing them to the Flights team for assistance.</t>
         </is>
       </c>
     </row>
@@ -28506,7 +28481,7 @@
       </c>
       <c r="O446" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Booking.com is following up with a customer about a car rental reservation, requesting booking details for assistance.</t>
         </is>
       </c>
     </row>
@@ -28573,7 +28548,7 @@
       </c>
       <c r="O447" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Booking.com sent a follow‑up message to a customer about a car rental reservation, requesting booking details to provide assistance.</t>
         </is>
       </c>
     </row>
@@ -28641,7 +28616,7 @@
       </c>
       <c r="O448" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Booking.com explains its social media support process for accommodation bookings, offering private messaging and phone contact, and directs other inquiries to specialized teams.</t>
         </is>
       </c>
     </row>
@@ -28703,7 +28678,7 @@
       </c>
       <c r="O449" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Booking.com replies to a user’s request for assistance with a standard policy statement, directing them to the collaborator help center.</t>
         </is>
       </c>
     </row>
@@ -28767,7 +28742,7 @@
       </c>
       <c r="O450" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Booking.com is offering customer support instructions for a user regarding reservation confirmation details and providing a phone contact link.</t>
         </is>
       </c>
     </row>
@@ -28813,7 +28788,7 @@
       </c>
       <c r="L451" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="M451" t="inlineStr">
@@ -28828,7 +28803,7 @@
       </c>
       <c r="O451" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Booking.com replies to a dissatisfied user on X, expressing regret and offering to assist via private message.</t>
         </is>
       </c>
     </row>
@@ -28889,7 +28864,7 @@
       </c>
       <c r="O452" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Booking.com apologizes for a delayed response to a user, citing a high volume of social media inquiries.</t>
         </is>
       </c>
     </row>
@@ -28950,7 +28925,7 @@
       </c>
       <c r="O453" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Booking.com responds to a user about a flight delay, offering alternative contact methods for assistance.</t>
         </is>
       </c>
     </row>
@@ -29015,7 +28990,7 @@
       </c>
       <c r="O454" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Booking.com addresses a customer complaint about a property, offering support and clarifying its intermediary role.</t>
         </is>
       </c>
     </row>
@@ -29076,7 +29051,7 @@
       </c>
       <c r="O455" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Booking.com sent a private message to user @tdog1410, requesting them to check their private message.</t>
         </is>
       </c>
     </row>
@@ -29128,7 +29103,7 @@
       </c>
       <c r="M456" t="inlineStr">
         <is>
-          <t>General Industry News</t>
+          <t>Tech Updates</t>
         </is>
       </c>
       <c r="N456" t="inlineStr">
@@ -29138,7 +29113,7 @@
       </c>
       <c r="O456" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Booking.com responds to a user complaint about potentially false property listings, outlining its verification process and offering to investigate and remove inaccurate listings.</t>
         </is>
       </c>
     </row>
@@ -29204,7 +29179,7 @@
       </c>
       <c r="O457" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Booking.com responds to a user’s refund concern via X, offering details to resolve the issue and directing to 24/7 customer service for immediate support.</t>
         </is>
       </c>
     </row>
@@ -29269,7 +29244,7 @@
       </c>
       <c r="O458" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Booking.com replies to a customer complaint, clarifying that it acts as an intermediary and offering to assist with further details.</t>
         </is>
       </c>
     </row>
@@ -29333,7 +29308,7 @@
       </c>
       <c r="O459" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Booking.com responds to a customer complaint about a non‑refundable cancellation in Prague, explaining that cancellation policies are managed by property owners and offering to contact the property on the customer’s behalf.</t>
         </is>
       </c>
     </row>
@@ -29395,12 +29370,12 @@
       </c>
       <c r="L460" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="M460" t="inlineStr">
         <is>
-          <t>General Industry News</t>
+          <t>Product Announcement</t>
         </is>
       </c>
       <c r="N460" t="inlineStr">
@@ -29410,7 +29385,7 @@
       </c>
       <c r="O460" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Booking.com promotes a new pet-friendly vacation concept, emphasizing a hassle‑free, drama‑free experience for travelers with cats.</t>
         </is>
       </c>
     </row>
@@ -29468,7 +29443,7 @@
       </c>
       <c r="L461" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="M461" t="inlineStr">
@@ -29483,7 +29458,7 @@
       </c>
       <c r="O461" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Expedia promotes Croatia as a top summer destination, offering travel tips for Plitvice Lakes, island hopping, and highlighting the new Euro currency.</t>
         </is>
       </c>
     </row>
@@ -29548,7 +29523,7 @@
       </c>
       <c r="O462" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Booking.com apologizes for a property’s failure to accommodate a guest and offers assistance in finding alternative accommodation, providing contact details for support.</t>
         </is>
       </c>
     </row>
@@ -29609,7 +29584,7 @@
       </c>
       <c r="O463" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Booking.com replied to a user’s concern via direct message, indicating they have addressed the issue.</t>
         </is>
       </c>
     </row>
@@ -29661,7 +29636,7 @@
       </c>
       <c r="M464" t="inlineStr">
         <is>
-          <t>General Industry News</t>
+          <t>Tech Updates</t>
         </is>
       </c>
       <c r="N464" t="inlineStr">
@@ -29671,7 +29646,7 @@
       </c>
       <c r="O464" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Booking.com acknowledges a limitation in its platform’s filtering options, apologizing for not being able to filter by check‑in or check‑out times and expressing appreciation for user feedback.</t>
         </is>
       </c>
     </row>
@@ -29733,7 +29708,7 @@
       </c>
       <c r="O465" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Booking.com replies to a user on X, apologizing for a delayed response and directing them to a private message.</t>
         </is>
       </c>
     </row>
@@ -29780,7 +29755,7 @@
       </c>
       <c r="L466" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="M466" t="inlineStr">
@@ -29795,7 +29770,7 @@
       </c>
       <c r="O466" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Booking.com apologizes to user Roberto for an issue and expresses hope for a quick resolution.</t>
         </is>
       </c>
     </row>
@@ -29842,7 +29817,7 @@
       </c>
       <c r="L467" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="M467" t="inlineStr">
@@ -29857,7 +29832,7 @@
       </c>
       <c r="O467" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Booking.com thanks a user for their feedback and offers future assistance, highlighting its customer service approach.</t>
         </is>
       </c>
     </row>
@@ -29903,12 +29878,12 @@
       </c>
       <c r="L468" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="M468" t="inlineStr">
         <is>
-          <t>General Industry News</t>
+          <t>Product Announcement</t>
         </is>
       </c>
       <c r="N468" t="inlineStr">
@@ -29918,7 +29893,7 @@
       </c>
       <c r="O468" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Brex is promoting a watch party event, likely to showcase a new product or feature to its audience.</t>
         </is>
       </c>
     </row>
@@ -29965,7 +29940,7 @@
       </c>
       <c r="L469" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="M469" t="inlineStr">
@@ -29980,7 +29955,7 @@
       </c>
       <c r="O469" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Brex is promoting a watch party for the Finance On Offense Finals, targeting audiences in Spain and Argentina.</t>
         </is>
       </c>
     </row>
@@ -30034,7 +30009,7 @@
       </c>
       <c r="L470" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="M470" t="inlineStr">
@@ -30049,7 +30024,7 @@
       </c>
       <c r="O470" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Airbnb celebrates Spain’s World Cup victory and promotes travel to Spain with a celebratory post.</t>
         </is>
       </c>
     </row>
@@ -30110,7 +30085,7 @@
       </c>
       <c r="O471" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Booking.com informs partners that it cannot provide support via social media and directs them to its Partner Support contact page.</t>
         </is>
       </c>
     </row>
@@ -30176,7 +30151,7 @@
       </c>
       <c r="O472" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Booking.com responds to a user’s inquiry about flight reservations, apologizing for the inconvenience and directing them to the Flights team via a link and phone numbers.</t>
         </is>
       </c>
     </row>
@@ -30237,7 +30212,7 @@
       </c>
       <c r="O473" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Booking.com responds to a refund inquiry, directing the customer to the dedicated Flights team and providing contact details, citing GDPR restrictions.</t>
         </is>
       </c>
     </row>
@@ -30286,7 +30261,7 @@
       </c>
       <c r="L474" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="M474" t="inlineStr">
@@ -30301,7 +30276,7 @@
       </c>
       <c r="O474" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Booking.com replies to a user on X, stating it cannot help via social media and directs the inquiry to a specialized team.</t>
         </is>
       </c>
     </row>
@@ -30362,7 +30337,7 @@
       </c>
       <c r="O475" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Booking.com responds to a user’s complaint about a reservation issue, offering to resolve it via another profile to avoid confusion.</t>
         </is>
       </c>
     </row>
@@ -30424,7 +30399,7 @@
       </c>
       <c r="O476" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Booking.com replied to a user’s private message, apologizing for an issue.</t>
         </is>
       </c>
     </row>
@@ -30488,7 +30463,7 @@
       </c>
       <c r="O477" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Booking.com responds to a customer complaint, offering to connect with customer service and providing instructions for escalation.</t>
         </is>
       </c>
     </row>
@@ -30551,7 +30526,7 @@
       </c>
       <c r="O478" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Booking.com is responding to a user’s request for reservation details, asking for the pin code via private message.</t>
         </is>
       </c>
     </row>
@@ -30616,7 +30591,7 @@
       </c>
       <c r="O479" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Booking.com is responding to a user’s complaint about missing check‑in details, requesting confirmation number, email, and guest name via private message.</t>
         </is>
       </c>
     </row>
@@ -30677,7 +30652,7 @@
       </c>
       <c r="O480" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Booking.com informs a user that they have sent a private message, indicating a direct outreach or marketing effort.</t>
         </is>
       </c>
     </row>
@@ -30738,7 +30713,7 @@
       </c>
       <c r="O481" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Booking.com replied privately to a user, directing them to check their direct messages.</t>
         </is>
       </c>
     </row>
@@ -30799,7 +30774,7 @@
       </c>
       <c r="O482" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Booking.com informs a user that accommodation bookings can be handled via social media, but flight requests must be directed to a dedicated flight support team.</t>
         </is>
       </c>
     </row>
@@ -30860,7 +30835,7 @@
       </c>
       <c r="O483" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Booking.com replied to a user’s direct message, indicating ongoing customer engagement.</t>
         </is>
       </c>
     </row>
@@ -30921,7 +30896,7 @@
       </c>
       <c r="O484" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Booking.com provides a user with instructions on how to find contact numbers and call customer support.</t>
         </is>
       </c>
     </row>
@@ -30982,7 +30957,7 @@
       </c>
       <c r="O485" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Booking.com posted a brief tweet indicating it has sent a direct message to a user named David.</t>
         </is>
       </c>
     </row>
@@ -31033,7 +31008,7 @@
       </c>
       <c r="M486" t="inlineStr">
         <is>
-          <t>General Industry News</t>
+          <t>Partnership and Acquisitions</t>
         </is>
       </c>
       <c r="N486" t="inlineStr">
@@ -31043,7 +31018,7 @@
       </c>
       <c r="O486" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Booking.com informs partners that it cannot provide support via social media and directs them to its Partner Support contact page.</t>
         </is>
       </c>
     </row>
@@ -31089,7 +31064,7 @@
       </c>
       <c r="L487" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="M487" t="inlineStr">
@@ -31104,7 +31079,7 @@
       </c>
       <c r="O487" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Booking.com replied to a user with a courteous thank‑you and well‑wishes.</t>
         </is>
       </c>
     </row>
@@ -31165,7 +31140,7 @@
       </c>
       <c r="O488" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Booking.com informs customers that flight changes cannot be handled via X and directs them to the Flights team for assistance.</t>
         </is>
       </c>
     </row>
@@ -31212,7 +31187,7 @@
       </c>
       <c r="L489" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="M489" t="inlineStr">
@@ -31227,7 +31202,7 @@
       </c>
       <c r="O489" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Booking.com explains that check‑in and check‑out times are set by each property and advises customers to review details and contact the property for early check‑in or late check‑out options.</t>
         </is>
       </c>
     </row>
@@ -31273,7 +31248,7 @@
       </c>
       <c r="L490" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="M490" t="inlineStr">
@@ -31288,7 +31263,7 @@
       </c>
       <c r="O490" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Booking.com replied to a user offering immediate assistance via a phone link.</t>
         </is>
       </c>
     </row>
@@ -31334,12 +31309,12 @@
       </c>
       <c r="L491" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="M491" t="inlineStr">
         <is>
-          <t>General Industry News</t>
+          <t>Product Announcement</t>
         </is>
       </c>
       <c r="N491" t="inlineStr">
@@ -31349,7 +31324,7 @@
       </c>
       <c r="O491" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Navan promotes a case study that showcases the effectiveness of its product.</t>
         </is>
       </c>
     </row>
@@ -31397,22 +31372,22 @@
       </c>
       <c r="L492" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="M492" t="inlineStr">
         <is>
-          <t>General Industry News</t>
+          <t>Partnership and Acquisitions</t>
         </is>
       </c>
       <c r="N492" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="O492" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Navan highlights its partnership with Adyen, showcasing its ability to streamline large-scale corporate travel logistics and reduce manual coordination for a global workforce.</t>
         </is>
       </c>
     </row>
@@ -31458,22 +31433,22 @@
       </c>
       <c r="L493" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="M493" t="inlineStr">
         <is>
-          <t>General Industry News</t>
+          <t>Product Announcement</t>
         </is>
       </c>
       <c r="N493" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="O493" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Ramp highlights a 3D animated video showcasing their new construction product launch, emphasizing creative marketing and product visibility.</t>
         </is>
       </c>
     </row>
@@ -31534,7 +31509,7 @@
       </c>
       <c r="O494" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Ramp posted a tweet referencing an art piece by @iamjasonlevin.</t>
         </is>
       </c>
     </row>
@@ -31595,7 +31570,7 @@
       </c>
       <c r="O495" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Brex’s tweet mentions @tobiwaldhecker, likely indicating a brief acknowledgment or potential collaboration, but no specific announcement is evident.</t>
         </is>
       </c>
     </row>
@@ -31641,12 +31616,12 @@
       </c>
       <c r="L496" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="M496" t="inlineStr">
         <is>
-          <t>General Industry News</t>
+          <t>Product Announcement</t>
         </is>
       </c>
       <c r="N496" t="inlineStr">
@@ -31656,7 +31631,7 @@
       </c>
       <c r="O496" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Brex emphasizes the drawbacks of manual expense reports, positioning its solution as a more efficient alternative.</t>
         </is>
       </c>
     </row>
@@ -31717,7 +31692,7 @@
       </c>
       <c r="O497" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Brex posts a brief, inquisitive remark to @anieasyy, indicating curiosity about a prior event or post.</t>
         </is>
       </c>
     </row>
@@ -31778,7 +31753,7 @@
       </c>
       <c r="O498" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Brex posted a generic greeting 'top of the morning' with no substantive content.</t>
         </is>
       </c>
     </row>
@@ -31824,12 +31799,12 @@
       </c>
       <c r="L499" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="M499" t="inlineStr">
         <is>
-          <t>General Industry News</t>
+          <t>Partnership and Acquisitions</t>
         </is>
       </c>
       <c r="N499" t="inlineStr">
@@ -31839,7 +31814,7 @@
       </c>
       <c r="O499" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Brex publicly thanks PigPugHealth for joining them, signaling a new partnership or collaboration.</t>
         </is>
       </c>
     </row>
@@ -31885,7 +31860,7 @@
       </c>
       <c r="L500" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="M500" t="inlineStr">
@@ -31900,7 +31875,7 @@
       </c>
       <c r="O500" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Airbnb celebrates a fulfilled promise with chef Jose Andres, referencing a World Cup victory.</t>
         </is>
       </c>
     </row>
@@ -31962,7 +31937,7 @@
       </c>
       <c r="L501" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="M501" t="inlineStr">
@@ -31977,7 +31952,7 @@
       </c>
       <c r="O501" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Airbnb highlights global unity and community spirit during the World Cup, encouraging continued engagement and hinting at future events in Brazil 2027.</t>
         </is>
       </c>
     </row>
@@ -32038,7 +32013,7 @@
       </c>
       <c r="O502" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Booking.com sent a private message to user @Mandy60029581, prompting them to check their inbox.</t>
         </is>
       </c>
     </row>
@@ -32100,7 +32075,7 @@
       </c>
       <c r="O503" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Booking.com is responding to a customer complaint, offering to investigate the issue via private message.</t>
         </is>
       </c>
     </row>
@@ -32165,7 +32140,7 @@
       </c>
       <c r="O504" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Booking.com responds to a customer inquiry on X, requesting reservation details and directing the user to 24/7 support for immediate assistance.</t>
         </is>
       </c>
     </row>
@@ -32226,7 +32201,7 @@
       </c>
       <c r="O505" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Booking.com responds to a customer complaint about payment options, clarifying that partners accept various payment methods and directing the user to a private message for further details.</t>
         </is>
       </c>
     </row>
@@ -32293,7 +32268,7 @@
       </c>
       <c r="O506" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Booking.com is offering refund assistance to a customer via private message.</t>
         </is>
       </c>
     </row>
@@ -32357,7 +32332,7 @@
       </c>
       <c r="O507" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Booking.com is responding to a customer complaint about a pending refund, requesting account details via DM to investigate the issue.</t>
         </is>
       </c>
     </row>
@@ -32418,7 +32393,7 @@
       </c>
       <c r="O508" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Booking.com replied to a user’s DM, offering further assistance.</t>
         </is>
       </c>
     </row>
@@ -32484,7 +32459,7 @@
       </c>
       <c r="O509" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Booking.com responds to a customer complaint, apologizing and requesting private details for further investigation.</t>
         </is>
       </c>
     </row>
@@ -32531,22 +32506,22 @@
       </c>
       <c r="L510" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="M510" t="inlineStr">
         <is>
-          <t>General Industry News</t>
+          <t>Product Announcement</t>
         </is>
       </c>
       <c r="N510" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="O510" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Sky Bird Travel promotes a new nonstop Los Angeles–Casablanca flight via Royal Air Maroc, aiming to increase sales across Morocco, Africa, Europe, and Asia.</t>
         </is>
       </c>
     </row>
@@ -32602,12 +32577,12 @@
       </c>
       <c r="L511" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="M511" t="inlineStr">
         <is>
-          <t>General Industry News</t>
+          <t>Product Announcement</t>
         </is>
       </c>
       <c r="N511" t="inlineStr">
@@ -32617,7 +32592,7 @@
       </c>
       <c r="O511" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Sky Bird Travel is promoting a new nonstop Los Angeles–Casablanca service with Royal Air Maroc, urging travel agents to book via WINGS.</t>
         </is>
       </c>
     </row>
@@ -32681,22 +32656,22 @@
       </c>
       <c r="L512" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="M512" t="inlineStr">
         <is>
-          <t>General Industry News</t>
+          <t>Strategic Expansion or Changes</t>
         </is>
       </c>
       <c r="N512" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="O512" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Navan announces the opening of a new office overseas, emphasizing its role in simplifying coordination for a senior manager at Adyen. The post showcases how the platform enables focus on key moments during global expansion.</t>
         </is>
       </c>
     </row>
@@ -32744,12 +32719,12 @@
       </c>
       <c r="L513" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="M513" t="inlineStr">
         <is>
-          <t>General Industry News</t>
+          <t>Product Announcement</t>
         </is>
       </c>
       <c r="N513" t="inlineStr">
@@ -32759,7 +32734,7 @@
       </c>
       <c r="O513" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Ramp announces that more than 1,000 businesses use its stablecoin payment service, with over 70% of the volume moving outside traditional banking hours, and invites new users to open a stablecoin account.</t>
         </is>
       </c>
     </row>
@@ -32809,22 +32784,22 @@
       </c>
       <c r="L514" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="M514" t="inlineStr">
         <is>
-          <t>General Industry News</t>
+          <t>Product Announcement</t>
         </is>
       </c>
       <c r="N514" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="O514" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Ramp announces the addition of stablecoins (USDC and USDT) to its platform, enabling faster cross-border vendor payments with existing approval and accounting workflows.</t>
         </is>
       </c>
     </row>
@@ -32885,7 +32860,7 @@
       </c>
       <c r="O515" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Ramp posted a nonsensical tweet with repeated words, providing no meaningful information.</t>
         </is>
       </c>
     </row>
@@ -32931,12 +32906,12 @@
       </c>
       <c r="L516" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="M516" t="inlineStr">
         <is>
-          <t>General Industry News</t>
+          <t>Leadership Changes</t>
         </is>
       </c>
       <c r="N516" t="inlineStr">
@@ -32946,7 +32921,7 @@
       </c>
       <c r="O516" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Ramp publicly acknowledges @sridvijay’s new role or partnership, expressing gratitude and honor.</t>
         </is>
       </c>
     </row>
@@ -32993,22 +32968,22 @@
       </c>
       <c r="L517" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="M517" t="inlineStr">
         <is>
-          <t>General Industry News</t>
+          <t>Tech Updates</t>
         </is>
       </c>
       <c r="N517" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="O517" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Ramp claims to have reduced its AI expenses by 30% with a router that selects the optimal model for each task, positioning the solution as a cost‑saving option for others.</t>
         </is>
       </c>
     </row>
@@ -33054,7 +33029,7 @@
       </c>
       <c r="L518" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="M518" t="inlineStr">
@@ -33069,7 +33044,7 @@
       </c>
       <c r="O518" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Ramp shares a supportive message towards @rahulgs, indicating positive engagement.</t>
         </is>
       </c>
     </row>
@@ -33115,12 +33090,12 @@
       </c>
       <c r="L519" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="M519" t="inlineStr">
         <is>
-          <t>General Industry News</t>
+          <t>Partnership and Acquisitions</t>
         </is>
       </c>
       <c r="N519" t="inlineStr">
@@ -33130,7 +33105,7 @@
       </c>
       <c r="O519" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Brex promotes its collaboration with @vibedotco, highlighting how the partnership helped achieve a specific goal.</t>
         </is>
       </c>
     </row>
@@ -33177,22 +33152,22 @@
       </c>
       <c r="L520" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="M520" t="inlineStr">
         <is>
-          <t>General Industry News</t>
+          <t>Partnership and Acquisitions</t>
         </is>
       </c>
       <c r="N520" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="O520" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Brex used its points program to fund a $128,000 out‑of‑home advertising campaign in partnership with vibedotco, creating a viral campaign without additional spend.</t>
         </is>
       </c>
     </row>
@@ -33238,7 +33213,7 @@
       </c>
       <c r="L521" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="M521" t="inlineStr">
@@ -33253,7 +33228,7 @@
       </c>
       <c r="O521" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Brex highlights @zachmoskow with a fire emoji, signaling enthusiasm or support.</t>
         </is>
       </c>
     </row>
@@ -33299,12 +33274,12 @@
       </c>
       <c r="L522" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="M522" t="inlineStr">
         <is>
-          <t>General Industry News</t>
+          <t>Partnership and Acquisitions</t>
         </is>
       </c>
       <c r="N522" t="inlineStr">
@@ -33314,7 +33289,7 @@
       </c>
       <c r="O522" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Brex publicly thanks Fondocom for a shout, indicating a positive partnership or collaboration.</t>
         </is>
       </c>
     </row>
@@ -33365,7 +33340,7 @@
       </c>
       <c r="M523" t="inlineStr">
         <is>
-          <t>General Industry News</t>
+          <t>Partnership and Acquisitions</t>
         </is>
       </c>
       <c r="N523" t="inlineStr">
@@ -33375,7 +33350,7 @@
       </c>
       <c r="O523" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Brex acknowledges a collaboration with Telnyx, suggesting a partnership aimed at maintaining operational stability.</t>
         </is>
       </c>
     </row>
@@ -33431,12 +33406,12 @@
       </c>
       <c r="L524" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="M524" t="inlineStr">
         <is>
-          <t>General Industry News</t>
+          <t>Partnership and Acquisitions</t>
         </is>
       </c>
       <c r="N524" t="inlineStr">
@@ -33446,7 +33421,7 @@
       </c>
       <c r="O524" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>AirBnb celebrates global unity at the 2026 FIFA World Cup and hints at continuing engagement in Brazil in 2027.</t>
         </is>
       </c>
     </row>
@@ -33500,12 +33475,12 @@
       </c>
       <c r="L525" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="M525" t="inlineStr">
         <is>
-          <t>General Industry News</t>
+          <t>Product Announcement</t>
         </is>
       </c>
       <c r="N525" t="inlineStr">
@@ -33515,7 +33490,7 @@
       </c>
       <c r="O525" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Expedia showcases its Island Hot List, promoting new summer getaways and inviting followers to pick their next destination.</t>
         </is>
       </c>
     </row>
@@ -33572,22 +33547,22 @@
       </c>
       <c r="L526" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="M526" t="inlineStr">
         <is>
-          <t>General Industry News</t>
+          <t>Product Announcement</t>
         </is>
       </c>
       <c r="N526" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="O526" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Expedia unveils its 2026 Island Hot List of 10 emerging island destinations and runs a £3,500 prize contest for a Cosmo Club member to win an island getaway.</t>
         </is>
       </c>
     </row>
@@ -33636,12 +33611,12 @@
       </c>
       <c r="L527" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="M527" t="inlineStr">
         <is>
-          <t>General Industry News</t>
+          <t>Product Announcement</t>
         </is>
       </c>
       <c r="N527" t="inlineStr">
@@ -33651,7 +33626,7 @@
       </c>
       <c r="O527" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Expedia unveiled its 2026 Island Hot List, highlighting ten emerging island destinations and promoting bundled flight+hotel deals to attract travelers.</t>
         </is>
       </c>
     </row>
@@ -33715,7 +33690,7 @@
       </c>
       <c r="O528" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Booking.com is responding to a customer complaint, requesting private details to investigate the issue.</t>
         </is>
       </c>
     </row>
@@ -33776,12 +33751,12 @@
       </c>
       <c r="N529" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="O529" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Booking.com cautions guests not to share personal details on unrecognized channels and offers to investigate potential security incidents.</t>
         </is>
       </c>
     </row>
@@ -33845,7 +33820,7 @@
       </c>
       <c r="O530" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Booking.com replies to a user’s complaint, asking for private details to resolve the issue.</t>
         </is>
       </c>
     </row>
@@ -33908,7 +33883,7 @@
       </c>
       <c r="O531" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Booking.com responds to a customer complaint about a pending refund, directing them to the flight booking support channel.</t>
         </is>
       </c>
     </row>
@@ -33970,12 +33945,12 @@
       </c>
       <c r="N532" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="O532" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Booking.com apologizes for a delayed response to a user’s complaint about a double charge and requests booking details via private message.</t>
         </is>
       </c>
     </row>
@@ -34036,7 +34011,7 @@
       </c>
       <c r="O533" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Booking.com replied to a private message from user @iklswsk regarding an unspecified issue.</t>
         </is>
       </c>
     </row>
@@ -34102,7 +34077,7 @@
       </c>
       <c r="O534" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Booking.com is outlining its customer support process, encouraging users to send private messages with reservation details and directing them to 24/7 support for immediate assistance.</t>
         </is>
       </c>
     </row>
@@ -34168,7 +34143,7 @@
       </c>
       <c r="O535" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Booking.com responds to a customer complaint on X, offering private message support and directing users to 24/7 phone support, while clarifying that only accommodation bookings are handled via social media.</t>
         </is>
       </c>
     </row>
@@ -34230,7 +34205,7 @@
       </c>
       <c r="O536" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Booking.com informs users that flight bookings cannot be handled via X and directs them to contact the flight team via link or phone.</t>
         </is>
       </c>
     </row>
@@ -34296,7 +34271,7 @@
       </c>
       <c r="O537" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Booking.com addresses a customer’s difficulty reaching its customer care team, offering a direct message format for booking inquiries and providing a local phone number.</t>
         </is>
       </c>
     </row>
@@ -34346,7 +34321,7 @@
       </c>
       <c r="L538" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="M538" t="inlineStr">
@@ -34361,7 +34336,7 @@
       </c>
       <c r="O538" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Booking.com addresses a customer complaint about being charged twice, offering to investigate via direct message and directing the user to 24/7 customer support.</t>
         </is>
       </c>
     </row>
@@ -34426,7 +34401,7 @@
       </c>
       <c r="O539" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Booking.com is responding to a customer inquiry about reviewing a booking, providing instructions for the customer to send details via DM.</t>
         </is>
       </c>
     </row>
@@ -34493,7 +34468,7 @@
       </c>
       <c r="O540" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Booking.com responds to a user complaint, offering to resolve issues via private message or phone.</t>
         </is>
       </c>
     </row>
@@ -34557,7 +34532,7 @@
       </c>
       <c r="O541" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Booking.com addresses a user’s pending refund request, asking for confirmation details via private message.</t>
         </is>
       </c>
     </row>
@@ -34607,22 +34582,22 @@
       </c>
       <c r="L542" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="M542" t="inlineStr">
         <is>
-          <t>General Industry News</t>
+          <t>Tech Updates</t>
         </is>
       </c>
       <c r="N542" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="O542" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Booking.com highlights its ongoing security measures, including 24/7 monitoring and compliance checks, to reassure clients and partners about the safety of listings on its platform.</t>
         </is>
       </c>
     </row>
@@ -34689,7 +34664,7 @@
       </c>
       <c r="O543" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Booking.com addresses a customer complaint on X, offering to review the booking and directing the user to further support channels.</t>
         </is>
       </c>
     </row>
@@ -34751,7 +34726,7 @@
       </c>
       <c r="O544" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Booking.com publicly apologized to a user for an issue with a reservation and noted that they responded via private message.</t>
         </is>
       </c>
     </row>
@@ -34798,7 +34773,7 @@
       </c>
       <c r="L545" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="M545" t="inlineStr">
@@ -34813,7 +34788,7 @@
       </c>
       <c r="O545" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Booking.com declines to address a customer’s issue via social media, directing them to other support channels.</t>
         </is>
       </c>
     </row>
@@ -34877,7 +34852,7 @@
       </c>
       <c r="O546" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Booking.com replies to a partner’s message, apologizing for the delay and directing them to secure support channels.</t>
         </is>
       </c>
     </row>
@@ -34939,7 +34914,7 @@
       </c>
       <c r="O547" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Booking.com informs partners that it cannot provide support via social media and directs them to a partner support contact page.</t>
         </is>
       </c>
     </row>
@@ -35000,7 +34975,7 @@
       </c>
       <c r="O548" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Booking.com for Travel Agents sent a private message to user @Ameerat_alwardd, requesting them to check it at their earliest convenience.</t>
         </is>
       </c>
     </row>
@@ -35049,7 +35024,7 @@
       </c>
       <c r="L549" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="M549" t="inlineStr">
@@ -35064,7 +35039,7 @@
       </c>
       <c r="O549" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Navan announced it has been named one of the World’s Top Fintech Companies by CNBC and Statista, celebrating its growth and customer base.</t>
         </is>
       </c>
     </row>
@@ -35460,22 +35435,22 @@
       </c>
       <c r="L555" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="M555" t="inlineStr">
         <is>
-          <t>General Industry News</t>
+          <t>Partnership and Acquisitions</t>
         </is>
       </c>
       <c r="N555" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="O555" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Ramp announces a partnership with Zebrie and Camille Ricketts, indicating a strategic collaboration.</t>
         </is>
       </c>
     </row>
@@ -35536,7 +35511,7 @@
       </c>
       <c r="O556" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Ramp posted a brief, lighthearted comment referencing Figma’s design, with no clear business implication.</t>
         </is>
       </c>
     </row>
@@ -35582,7 +35557,7 @@
       </c>
       <c r="L557" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="M557" t="inlineStr">
@@ -35597,7 +35572,7 @@
       </c>
       <c r="O557" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>A tweet claims that sources say Ramp is stable, suggesting a positive perception of the company's financial health.</t>
         </is>
       </c>
     </row>
@@ -35658,7 +35633,7 @@
       </c>
       <c r="O558" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Ramp references a major key with @damianplayer, suggesting a potential partnership or collaboration.</t>
         </is>
       </c>
     </row>
@@ -35704,7 +35679,7 @@
       </c>
       <c r="L559" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="M559" t="inlineStr">
@@ -35714,12 +35689,12 @@
       </c>
       <c r="N559" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="O559" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Ramp posted a sarcastic remark about Solana, claiming the post was fact‑checked by "real global stablecoin enjoyers," indicating a negative stance toward Solana.</t>
         </is>
       </c>
     </row>
@@ -35766,22 +35741,22 @@
       </c>
       <c r="L560" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="M560" t="inlineStr">
         <is>
-          <t>General Industry News</t>
+          <t>Product Announcement</t>
         </is>
       </c>
       <c r="N560" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="O560" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Brex announces that AI agents can now receive their own corporate cards, highlighting a rapid rollout of this new feature.</t>
         </is>
       </c>
     </row>
@@ -35829,22 +35804,22 @@
       </c>
       <c r="L561" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="M561" t="inlineStr">
         <is>
-          <t>General Industry News</t>
+          <t>Product Announcement</t>
         </is>
       </c>
       <c r="N561" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="O561" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Brex highlights a new self‑correcting agent pipeline built with @cursor_ai that dramatically speeds up manual framework upgrades, boosting efficiency by 32×.</t>
         </is>
       </c>
     </row>
@@ -35890,22 +35865,22 @@
       </c>
       <c r="L562" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="M562" t="inlineStr">
         <is>
-          <t>General Industry News</t>
+          <t>Product Announcement</t>
         </is>
       </c>
       <c r="N562" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="O562" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Brex announces a new product or service aimed at expanding its corporate card and financial solutions.</t>
         </is>
       </c>
     </row>
@@ -35989,7 +35964,7 @@
       </c>
       <c r="O563" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Brex posted a brief Instagram update with emojis and unrelated car hashtags, indicating no significant activity or announcement.</t>
         </is>
       </c>
     </row>
@@ -36039,12 +36014,12 @@
       </c>
       <c r="L564" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="M564" t="inlineStr">
         <is>
-          <t>General Industry News</t>
+          <t>Product Announcement</t>
         </is>
       </c>
       <c r="N564" t="inlineStr">
@@ -36054,7 +36029,7 @@
       </c>
       <c r="O564" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Expedia promotes a travel package to Paraguay, highlighting historic ruins, cultural experiences, and unique colonial stays, and directs followers to book via a provided link.</t>
         </is>
       </c>
     </row>
@@ -36102,12 +36077,12 @@
       </c>
       <c r="L565" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="M565" t="inlineStr">
         <is>
-          <t>General Industry News</t>
+          <t>Partnership and Acquisitions</t>
         </is>
       </c>
       <c r="N565" t="inlineStr">
@@ -36117,7 +36092,7 @@
       </c>
       <c r="O565" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Expedia is promoting a 10% discount on Disney Theme Park tickets with code DISNEY10, encouraging bookings before the offer expires.</t>
         </is>
       </c>
     </row>
@@ -36173,12 +36148,12 @@
       </c>
       <c r="L566" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="M566" t="inlineStr">
         <is>
-          <t>General Industry News</t>
+          <t>Product Announcement</t>
         </is>
       </c>
       <c r="N566" t="inlineStr">
@@ -36188,7 +36163,7 @@
       </c>
       <c r="O566" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Expedia promotes a set-jetting Greece trip featuring mythological sites and a traditional stone villa stay, encouraging followers to plan via a provided link.</t>
         </is>
       </c>
     </row>
@@ -36249,7 +36224,7 @@
       </c>
       <c r="O567" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Booking.com’s social media team informs a customer that they cannot see prior communications and requests booking details to proceed with assistance.</t>
         </is>
       </c>
     </row>
@@ -36311,7 +36286,7 @@
       </c>
       <c r="O568" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Booking.com replied to a private message from a user, acknowledging receipt and inviting them to review the response.</t>
         </is>
       </c>
     </row>
@@ -36372,7 +36347,7 @@
       </c>
       <c r="O569" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Booking.com responds to a customer complaint, offering assistance via direct message.</t>
         </is>
       </c>
     </row>
@@ -36440,7 +36415,7 @@
       </c>
       <c r="O570" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Booking.com apologizes for a missing booking confirmation and requests customer details via DM to resolve the issue.</t>
         </is>
       </c>
     </row>
@@ -36506,7 +36481,7 @@
       </c>
       <c r="O571" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Booking.com responds to a customer inquiry about a pending refund, offering to review the booking and request additional details to expedite the process.</t>
         </is>
       </c>
     </row>
@@ -36572,7 +36547,7 @@
       </c>
       <c r="O572" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Booking.com apologizes for a hotel’s failure to accommodate a guest and offers assistance to resolve the issue.</t>
         </is>
       </c>
     </row>
@@ -36635,7 +36610,7 @@
       </c>
       <c r="O573" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Booking.com clarified that its social media channel only handles accommodation bookings and directed the user to a flight reservation contact link.</t>
         </is>
       </c>
     </row>
@@ -36701,7 +36676,7 @@
       </c>
       <c r="O574" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Booking.com responds to a customer complaint, offering to gather booking details to resolve the issue.</t>
         </is>
       </c>
     </row>
@@ -36762,7 +36737,7 @@
       </c>
       <c r="O575" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Booking.com informs a user that flight reservations cannot be handled via social media and directs them to the Flights team contact details.</t>
         </is>
       </c>
     </row>
@@ -36829,7 +36804,7 @@
       </c>
       <c r="O576" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Booking.com informs customers that incomplete bookings may not have processed and offers steps to verify and correct booking details.</t>
         </is>
       </c>
     </row>
@@ -36894,7 +36869,7 @@
       </c>
       <c r="O577" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Booking.com responds to a customer complaint, directing them to provide details via DM and encouraging direct communication with the property.</t>
         </is>
       </c>
     </row>
@@ -36940,7 +36915,7 @@
       </c>
       <c r="L578" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="M578" t="inlineStr">
@@ -36955,7 +36930,7 @@
       </c>
       <c r="O578" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Booking.com responds to a user, expressing satisfaction and offering further assistance.</t>
         </is>
       </c>
     </row>
@@ -37022,7 +36997,7 @@
       </c>
       <c r="O579" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Booking.com responds to a dissatisfied customer, offering to review the booking and requesting details via DM.</t>
         </is>
       </c>
     </row>
@@ -37088,7 +37063,7 @@
       </c>
       <c r="O580" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Booking.com responds to a refund inquiry on X, offering support for accommodation bookings and directing other service requests to dedicated teams.</t>
         </is>
       </c>
     </row>
@@ -37153,7 +37128,7 @@
       </c>
       <c r="O581" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Booking.com responds to a customer complaint on X, offering to investigate and requesting details via DM.</t>
         </is>
       </c>
     </row>
@@ -37214,7 +37189,7 @@
       </c>
       <c r="O582" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Booking.com sent a polite private message to a user, asking them to review a private message sent earlier.</t>
         </is>
       </c>
     </row>
@@ -37276,7 +37251,7 @@
       </c>
       <c r="O583" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Booking.com informs a partner that it cannot provide support from its Social Media Team and directs them to an alternative contact link.</t>
         </is>
       </c>
     </row>
@@ -37343,7 +37318,7 @@
       </c>
       <c r="O584" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Booking.com informs a customer that only the accommodation can issue invoices and offers to help contact the property.</t>
         </is>
       </c>
     </row>
@@ -37408,7 +37383,7 @@
       </c>
       <c r="O585" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Booking.com responds to a customer complaint about delayed support, offering to collect reservation details via private message to resolve the issue.</t>
         </is>
       </c>
     </row>
@@ -37469,12 +37444,12 @@
       </c>
       <c r="N586" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="O586" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Booking.com addresses a customer’s concern about an additional charge, requesting booking details via private message for review.</t>
         </is>
       </c>
     </row>
@@ -37522,22 +37497,22 @@
       </c>
       <c r="L587" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="M587" t="inlineStr">
         <is>
-          <t>General Industry News</t>
+          <t>Product Announcement</t>
         </is>
       </c>
       <c r="N587" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="O587" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Sky Bird Travel is promoting a 25% commission on travel insurance for agents, positioning it as a value‑add that protects travelers and boosts revenue.</t>
         </is>
       </c>
     </row>
@@ -37593,22 +37568,22 @@
       </c>
       <c r="L588" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="M588" t="inlineStr">
         <is>
-          <t>General Industry News</t>
+          <t>Product Announcement</t>
         </is>
       </c>
       <c r="N588" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="O588" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Sky Bird Travel is promoting a 25% commission opportunity on travel insurance through its WINGS platform, positioning it as a value‑add for travel agents to enhance itineraries and revenue.</t>
         </is>
       </c>
     </row>
@@ -37654,7 +37629,7 @@
       </c>
       <c r="L589" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="M589" t="inlineStr">
@@ -37669,7 +37644,7 @@
       </c>
       <c r="O589" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Navan shares a playful tweet highlighting a new connection or hire, indicating active engagement with industry talent.</t>
         </is>
       </c>
     </row>
@@ -37732,12 +37707,12 @@
       </c>
       <c r="L590" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="M590" t="inlineStr">
         <is>
-          <t>General Industry News</t>
+          <t>Product Announcement</t>
         </is>
       </c>
       <c r="N590" t="inlineStr">
@@ -37747,7 +37722,7 @@
       </c>
       <c r="O590" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Navan promotes a 48‑hour San Francisco itinerary curated by Gary, SVP of Global Account Management at Adyen, showcasing travel recommendations and highlighting the service.</t>
         </is>
       </c>
     </row>
@@ -37810,22 +37785,22 @@
       </c>
       <c r="L591" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="M591" t="inlineStr">
         <is>
-          <t>General Industry News</t>
+          <t>Product Announcement</t>
         </is>
       </c>
       <c r="N591" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="O591" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>TravelPerk unveiled Entry Ready, an AI-native feature that lets users check visa requirements, receive guidance, pay for eVisas, and complete applications directly within the platform, simplifying international travel for business travelers.</t>
         </is>
       </c>
     </row>
@@ -37956,7 +37931,7 @@
       </c>
       <c r="O593" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Brex sends a friendly message to @axrahman, possibly indicating a forthcoming meeting or collaboration.</t>
         </is>
       </c>
     </row>
@@ -38002,22 +37977,22 @@
       </c>
       <c r="L594" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="M594" t="inlineStr">
         <is>
-          <t>General Industry News</t>
+          <t>Partnership and Acquisitions</t>
         </is>
       </c>
       <c r="N594" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="O594" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Brex announces a partnership with Cursor, indicating a collaborative effort to enhance services.</t>
         </is>
       </c>
     </row>
@@ -38079,22 +38054,22 @@
       </c>
       <c r="L595" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="M595" t="inlineStr">
         <is>
-          <t>General Industry News</t>
+          <t>Product Announcement</t>
         </is>
       </c>
       <c r="N595" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="O595" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Airbnb announces the addition of rental car bookings, expanding its travel services to include vehicle rentals directly through its platform.</t>
         </is>
       </c>
     </row>
@@ -38155,7 +38130,7 @@
       </c>
       <c r="O596" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Booking.com replied to a private message from user @zd1tx, inviting them to review the response.</t>
         </is>
       </c>
     </row>
@@ -38219,7 +38194,7 @@
       </c>
       <c r="O597" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Booking.com responds to a user’s accident with empathetic support, requesting booking details to assist with insurance and reservation inquiries.</t>
         </is>
       </c>
     </row>
@@ -38284,7 +38259,7 @@
       </c>
       <c r="O598" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Booking.com apologizes for a delayed response to a complaint and requests booking details via DM to investigate the issue.</t>
         </is>
       </c>
     </row>
@@ -38345,7 +38320,7 @@
       </c>
       <c r="O599" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Booking.com replied to a user, suggesting they send the required information via direct message for review.</t>
         </is>
       </c>
     </row>
@@ -38397,7 +38372,7 @@
       </c>
       <c r="L600" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="M600" t="inlineStr">
@@ -38407,12 +38382,12 @@
       </c>
       <c r="N600" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="O600" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Booking.com is requesting private booking details from users, which appears to be a phishing attempt.</t>
         </is>
       </c>
     </row>
@@ -38472,12 +38447,12 @@
       </c>
       <c r="N601" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="O601" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Booking.com is addressing a user’s complaint about a compromised account and requesting personal details to investigate the incident.</t>
         </is>
       </c>
     </row>
@@ -38538,7 +38513,7 @@
       </c>
       <c r="O602" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Booking.com informs a customer that their case has been updated via email and invites them to review the information.</t>
         </is>
       </c>
     </row>
@@ -38599,7 +38574,7 @@
       </c>
       <c r="O603" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Booking.com responds to a customer complaint about misinformation from a third party, clarifying that reservations can only be made via their website or app and advising against engaging with third parties.</t>
         </is>
       </c>
     </row>
@@ -38666,7 +38641,7 @@
       </c>
       <c r="O604" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Booking.com informs a customer that the decision to waive potential cancellation fees is solely at the property’s discretion and requests confirmation details to review the request.</t>
         </is>
       </c>
     </row>
@@ -38732,7 +38707,7 @@
       </c>
       <c r="O605" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Booking.com responds to a customer complaint, offering to review the issue and providing contact details for immediate assistance.</t>
         </is>
       </c>
     </row>
@@ -38797,7 +38772,7 @@
       </c>
       <c r="O606" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Booking.com is offering customers instructions on how to contact 24/7 support and send private messages with booking details for assistance.</t>
         </is>
       </c>
     </row>
@@ -38848,7 +38823,7 @@
       </c>
       <c r="L607" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="M607" t="inlineStr">
@@ -38858,12 +38833,12 @@
       </c>
       <c r="N607" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="O607" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>The post appears to be a phishing attempt, requesting private booking details from users.</t>
         </is>
       </c>
     </row>
@@ -38924,7 +38899,7 @@
       </c>
       <c r="O608" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Booking.com replied to a direct message from user @pala77liverpool, indicating ongoing communication.</t>
         </is>
       </c>
     </row>
@@ -38985,7 +38960,7 @@
       </c>
       <c r="O609" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Booking.com informs a user that flight reservations cannot be handled via social media and directs them to contact the Flights team through a link or phone.</t>
         </is>
       </c>
     </row>
@@ -39050,7 +39025,7 @@
       </c>
       <c r="O610" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Booking.com apologizes for a late response and a cancelled booking, asking the customer to DM booking details for resolution.</t>
         </is>
       </c>
     </row>
@@ -39116,7 +39091,7 @@
       </c>
       <c r="O611" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Booking.com apologizes for a customer’s disappointment and requests private details to review the reservation.</t>
         </is>
       </c>
     </row>
@@ -39178,7 +39153,7 @@
       </c>
       <c r="O612" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Booking.com informs users that it cannot process car rental reservations through social media and directs them to a specialized team via a provided link.</t>
         </is>
       </c>
     </row>
@@ -39239,7 +39214,7 @@
       </c>
       <c r="O613" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Booking.com apologizes for a delayed response to a user on X, citing a high volume of social media inquiries.</t>
         </is>
       </c>
     </row>
@@ -39300,7 +39275,7 @@
       </c>
       <c r="O614" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Booking.com replied to a user’s private message, thanking them and informing them that their inquiry has been addressed.</t>
         </is>
       </c>
     </row>
@@ -39366,7 +39341,7 @@
       </c>
       <c r="O615" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Booking.com explains its social media support workflow for accommodation bookings and directs users to other channels for flights, taxis, or insurance inquiries.</t>
         </is>
       </c>
     </row>
@@ -39414,22 +39389,22 @@
       </c>
       <c r="L616" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="M616" t="inlineStr">
         <is>
-          <t>General Industry News</t>
+          <t>Product Announcement</t>
         </is>
       </c>
       <c r="N616" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="O616" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>TravelPerk introduces Perk Spend, a new feature that merges travel and spend data to keep surprise charges on the pitch rather than in expense reports.</t>
         </is>
       </c>
     </row>
@@ -39480,7 +39455,7 @@
       </c>
       <c r="M617" t="inlineStr">
         <is>
-          <t>General Industry News</t>
+          <t>Tech Updates</t>
         </is>
       </c>
       <c r="N617" t="inlineStr">
@@ -39490,7 +39465,7 @@
       </c>
       <c r="O617" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Ramp shares a link to content from @KlausCodes, likely highlighting a new feature or collaboration.</t>
         </is>
       </c>
     </row>
@@ -39536,7 +39511,7 @@
       </c>
       <c r="L618" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="M618" t="inlineStr">
@@ -39551,7 +39526,7 @@
       </c>
       <c r="O618" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Brex tweets a lighthearted remark about San Francisco’s summer, indicating a casual engagement with the local vibe.</t>
         </is>
       </c>
     </row>
@@ -39597,12 +39572,12 @@
       </c>
       <c r="L619" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="M619" t="inlineStr">
         <is>
-          <t>General Industry News</t>
+          <t>Product Announcement</t>
         </is>
       </c>
       <c r="N619" t="inlineStr">
@@ -39612,7 +39587,7 @@
       </c>
       <c r="O619" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Brex teases an upcoming product or initiative, expressing confidence and readiness.</t>
         </is>
       </c>
     </row>
@@ -39658,7 +39633,7 @@
       </c>
       <c r="L620" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="M620" t="inlineStr">
@@ -39673,7 +39648,7 @@
       </c>
       <c r="O620" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Brex posts a playful congratulatory message to @linderps, calling it a 'Grammy' award.</t>
         </is>
       </c>
     </row>
@@ -39724,12 +39699,12 @@
       </c>
       <c r="L621" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="M621" t="inlineStr">
         <is>
-          <t>General Industry News</t>
+          <t>Product Announcement</t>
         </is>
       </c>
       <c r="N621" t="inlineStr">
@@ -39739,7 +39714,7 @@
       </c>
       <c r="O621" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Expedia promotes Slovenia as a hidden European mountain escape, highlighting scenic activities, local culture, and off-grid accommodations, encouraging bookings via a link.</t>
         </is>
       </c>
     </row>
@@ -39796,22 +39771,22 @@
       </c>
       <c r="L622" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="M622" t="inlineStr">
         <is>
-          <t>General Industry News</t>
+          <t>Product Announcement</t>
         </is>
       </c>
       <c r="N622" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="O622" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Expedia Group announced a dynamic creative production system powered by Google AI tools that increased creative effectiveness by 800%, enabling the creation of 800 hyper‑personalized ad variations daily.</t>
         </is>
       </c>
     </row>
@@ -39872,7 +39847,7 @@
       </c>
       <c r="O623" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Booking.com replied to a user’s message on X, indicating a routine customer support interaction.</t>
         </is>
       </c>
     </row>
@@ -39937,7 +39912,7 @@
       </c>
       <c r="O624" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Booking.com responds to a dissatisfied customer, explaining its refund policy and offering to discuss the complaint with the accommodation.</t>
         </is>
       </c>
     </row>
@@ -39998,7 +39973,7 @@
       </c>
       <c r="O625" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Booking.com clarifies that flight bookings cannot be processed through social media and directs users to contact the Flights team via a provided link or phone numbers.</t>
         </is>
       </c>
     </row>
@@ -40059,7 +40034,7 @@
       </c>
       <c r="O626" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Booking.com responds to a customer inquiry, directing them to contact via DM for case review.</t>
         </is>
       </c>
     </row>
@@ -40120,7 +40095,7 @@
       </c>
       <c r="O627" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Booking.com is following up with a user who has not yet provided all booking details, requesting the missing information via direct message.</t>
         </is>
       </c>
     </row>
@@ -40171,7 +40146,7 @@
       </c>
       <c r="L628" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="M628" t="inlineStr">
@@ -40186,7 +40161,7 @@
       </c>
       <c r="O628" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Booking.com is responding to a customer inquiry about a car rental reservation, requesting personal details via private message to assist.</t>
         </is>
       </c>
     </row>
@@ -40247,7 +40222,7 @@
       </c>
       <c r="O629" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Booking.com informs users that flight assistance cannot be provided via X and directs them to the Flights team through a link or phone numbers.</t>
         </is>
       </c>
     </row>
@@ -40311,7 +40286,7 @@
       </c>
       <c r="O630" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Booking.com reminds customers to include the confirmation number, confidential code, and traveler name when responding to reservation-related emails.</t>
         </is>
       </c>
     </row>
@@ -40373,7 +40348,7 @@
       </c>
       <c r="O631" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Booking.com acknowledges a user’s report and requests additional details via private message to investigate further.</t>
         </is>
       </c>
     </row>
@@ -40424,17 +40399,17 @@
       </c>
       <c r="M632" t="inlineStr">
         <is>
-          <t>General Industry News</t>
+          <t>Tech Updates</t>
         </is>
       </c>
       <c r="N632" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="O632" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Booking.com addresses a user’s report of a suspicious email, apologizes for any concern, and warns against clicking links or making payments.</t>
         </is>
       </c>
     </row>
@@ -40500,7 +40475,7 @@
       </c>
       <c r="O633" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Booking.com responds to a customer inquiry, offering support details and directing to their 24/7 customer service.</t>
         </is>
       </c>
     </row>
@@ -40565,7 +40540,7 @@
       </c>
       <c r="O634" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Booking.com responded to a user’s complaint about an extra charge, offering to resolve the issue via direct message.</t>
         </is>
       </c>
     </row>
@@ -40633,7 +40608,7 @@
       </c>
       <c r="O635" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Booking.com clarifies cancellation procedures and fee policies for customers.</t>
         </is>
       </c>
     </row>
@@ -40694,7 +40669,7 @@
       </c>
       <c r="O636" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Booking.com replied to a direct message from user @hakhak20212021, indicating a private customer interaction.</t>
         </is>
       </c>
     </row>
@@ -40755,7 +40730,7 @@
       </c>
       <c r="O637" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Booking.com responds to a customer complaint, offering alternative contact for flight assistance.</t>
         </is>
       </c>
     </row>
@@ -40820,7 +40795,7 @@
       </c>
       <c r="O638" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Booking.com is responding to a user’s concern and requesting booking details via direct message for further review.</t>
         </is>
       </c>
     </row>
@@ -40881,7 +40856,7 @@
       </c>
       <c r="O639" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Booking.com replied to a user’s direct message, indicating routine customer support engagement.</t>
         </is>
       </c>
     </row>
@@ -40932,7 +40907,7 @@
       </c>
       <c r="M640" t="inlineStr">
         <is>
-          <t>General Industry News</t>
+          <t>Partnership and Acquisitions</t>
         </is>
       </c>
       <c r="N640" t="inlineStr">
@@ -40942,7 +40917,7 @@
       </c>
       <c r="O640" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Booking.com contacted a potential partner, informing them of a private message with additional details about their file.</t>
         </is>
       </c>
     </row>
@@ -41004,7 +40979,7 @@
       </c>
       <c r="O641" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Booking.com replied to a user’s direct message, indicating routine customer support engagement.</t>
         </is>
       </c>
     </row>
@@ -41076,7 +41051,7 @@
       </c>
       <c r="O642" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Booking.com is offering customer support via private messages for reservation and account issues.</t>
         </is>
       </c>
     </row>
@@ -41126,7 +41101,7 @@
       </c>
       <c r="L643" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="M643" t="inlineStr">
@@ -41141,7 +41116,7 @@
       </c>
       <c r="O643" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Sky Bird Travel promotes booking with a travel advisor for expert support, emphasizing peace of mind and personalized service to encourage confident travel.</t>
         </is>
       </c>
     </row>
@@ -41199,7 +41174,7 @@
       </c>
       <c r="L644" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="M644" t="inlineStr">
@@ -41214,7 +41189,7 @@
       </c>
       <c r="O644" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Sky Bird Travel highlights the benefits of booking with a travel advisor, emphasizing peace of mind, personalized support, and up-to-date travel information for travelers.</t>
         </is>
       </c>
     </row>
@@ -41269,12 +41244,12 @@
       </c>
       <c r="L645" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="M645" t="inlineStr">
         <is>
-          <t>General Industry News</t>
+          <t>Product Announcement</t>
         </is>
       </c>
       <c r="N645" t="inlineStr">
@@ -41284,7 +41259,7 @@
       </c>
       <c r="O645" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Navan's LinkedIn post expresses frustration with the onboarding process, implying challenges in getting clients to onboard.</t>
         </is>
       </c>
     </row>
@@ -41345,7 +41320,7 @@
       </c>
       <c r="O646" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Ramp posted a brief mention of Elon Musk without additional context or details.</t>
         </is>
       </c>
     </row>
@@ -41396,7 +41371,7 @@
       </c>
       <c r="M647" t="inlineStr">
         <is>
-          <t>General Industry News</t>
+          <t>Tech Updates</t>
         </is>
       </c>
       <c r="N647" t="inlineStr">
@@ -41406,7 +41381,7 @@
       </c>
       <c r="O647" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Ramp posts a question about the authenticity of Grok, indicating curiosity or inquiry into a new technology or product.</t>
         </is>
       </c>
     </row>
@@ -41467,7 +41442,7 @@
       </c>
       <c r="O648" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Ramp tweets a question to @rahulgs and @grok asking if a statement is true.</t>
         </is>
       </c>
     </row>
@@ -41547,12 +41522,12 @@
       </c>
       <c r="L649" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="M649" t="inlineStr">
         <is>
-          <t>General Industry News</t>
+          <t>Product Announcement</t>
         </is>
       </c>
       <c r="N649" t="inlineStr">
@@ -41562,7 +41537,7 @@
       </c>
       <c r="O649" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Airbnb humorously promotes a Paris apartment listing, encouraging bookings with playful language and a light‑hearted marketing tone.</t>
         </is>
       </c>
     </row>
@@ -41612,12 +41587,12 @@
       </c>
       <c r="L650" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="M650" t="inlineStr">
         <is>
-          <t>General Industry News</t>
+          <t>Product Announcement</t>
         </is>
       </c>
       <c r="N650" t="inlineStr">
@@ -41627,7 +41602,7 @@
       </c>
       <c r="O650" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Expedia is promoting a new travel package to Norway, highlighting fjords, islands, and unique cabin stays, encouraging bookings via a dedicated link.</t>
         </is>
       </c>
     </row>
@@ -41693,7 +41668,7 @@
       </c>
       <c r="O651" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Booking.com addresses a customer’s issue with a missing booking confirmation, offering investigation and potential refund while explaining possible causes.</t>
         </is>
       </c>
     </row>
@@ -41754,7 +41729,7 @@
       </c>
       <c r="O652" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Booking.com responds to a customer’s issue via direct message, offering assistance and directing them to 24/7 phone support.</t>
         </is>
       </c>
     </row>
@@ -41815,12 +41790,12 @@
       </c>
       <c r="N653" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="O653" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Booking.com responds to a customer’s complaint about a delayed refund, apologizes for the inconvenience, and requests booking details via DM to investigate the issue.</t>
         </is>
       </c>
     </row>
@@ -41881,7 +41856,7 @@
       </c>
       <c r="O654" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Booking.com replied to a direct message from user @SudharshananJa1.</t>
         </is>
       </c>
     </row>
@@ -41942,7 +41917,7 @@
       </c>
       <c r="O655" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Booking.com replies to a user on X, apologizing for a delayed response due to high volume of cases.</t>
         </is>
       </c>
     </row>
@@ -42009,7 +41984,7 @@
       </c>
       <c r="O656" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Booking.com apologizes for a delayed response and guides the customer on how to verify accommodation status and contact options.</t>
         </is>
       </c>
     </row>
@@ -42058,7 +42033,7 @@
       </c>
       <c r="L657" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="M657" t="inlineStr">
@@ -42073,7 +42048,7 @@
       </c>
       <c r="O657" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Booking.com replied to a user’s complaint about a negative experience, offering to resolve the issue via direct message and requesting additional booking details.</t>
         </is>
       </c>
     </row>
@@ -42134,7 +42109,7 @@
       </c>
       <c r="O658" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Booking.com responded to a user query by providing its India customer care phone number.</t>
         </is>
       </c>
     </row>
@@ -42201,7 +42176,7 @@
       </c>
       <c r="O659" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Booking.com is responding to a customer inquiry about a car rental reservation, requesting booking details via private message.</t>
         </is>
       </c>
     </row>
@@ -42262,7 +42237,7 @@
       </c>
       <c r="O660" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Booking.com replied to a private message from a user, offering follow-up assistance.</t>
         </is>
       </c>
     </row>
@@ -42312,7 +42287,7 @@
       </c>
       <c r="L661" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="M661" t="inlineStr">
@@ -42327,7 +42302,7 @@
       </c>
       <c r="O661" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Booking.com responds to a customer query, offering assistance and requesting reservation details via DM.</t>
         </is>
       </c>
     </row>
@@ -42388,7 +42363,7 @@
       </c>
       <c r="O662" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Booking.com responds to a dissatisfied user, offering to resolve the issue via direct message.</t>
         </is>
       </c>
     </row>
@@ -42454,7 +42429,7 @@
       </c>
       <c r="O663" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Booking.com explains that cancellation fees are set by accommodations and directs customers to private messaging or phone support for assistance.</t>
         </is>
       </c>
     </row>
@@ -42505,7 +42480,7 @@
       </c>
       <c r="L664" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="M664" t="inlineStr">
@@ -42520,7 +42495,7 @@
       </c>
       <c r="O664" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Booking.com addresses a customer complaint about a poor stay, apologizes, and directs the customer to an email response while offering further assistance via direct message.</t>
         </is>
       </c>
     </row>
@@ -42581,7 +42556,7 @@
       </c>
       <c r="O665" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Booking.com responds to a user’s inquiry by warning against sharing reservation PIN codes publicly and encourages the user to delete the comment and contact them privately for assistance.</t>
         </is>
       </c>
     </row>
@@ -42643,7 +42618,7 @@
       </c>
       <c r="O666" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Booking.com is requesting a PIN code and full guest name from a customer to verify a booking for security purposes.</t>
         </is>
       </c>
     </row>
@@ -42707,7 +42682,7 @@
       </c>
       <c r="O667" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Booking.com responds to a customer inquiry, offering to resend the final outcome upon request.</t>
         </is>
       </c>
     </row>
@@ -42768,7 +42743,7 @@
       </c>
       <c r="O668" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Booking.com replied to a user’s direct message offering further support.</t>
         </is>
       </c>
     </row>
@@ -42834,7 +42809,7 @@
       </c>
       <c r="O669" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Booking.com addresses a user’s complaint about potential misinformation on a listed property, offering to investigate and remove the property if necessary.</t>
         </is>
       </c>
     </row>
@@ -42895,7 +42870,7 @@
       </c>
       <c r="O670" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Booking.com responds to a customer complaint on X, offering assistance and directing the user to their 24/7 support line.</t>
         </is>
       </c>
     </row>
@@ -42941,7 +42916,7 @@
       </c>
       <c r="L671" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="M671" t="inlineStr">
@@ -42956,7 +42931,7 @@
       </c>
       <c r="O671" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Ramp's tweet hints at a compliance issue, labeling it as 'Crime but compliant', suggesting potential regulatory concerns.</t>
         </is>
       </c>
     </row>
@@ -43017,7 +42992,7 @@
       </c>
       <c r="O672" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Booking.com sent a private message to user @cactushoney12, requesting them to check it.</t>
         </is>
       </c>
     </row>
@@ -43067,7 +43042,7 @@
       </c>
       <c r="L673" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="M673" t="inlineStr">
@@ -43077,12 +43052,12 @@
       </c>
       <c r="N673" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="O673" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Booking.com apologizes for a customer’s frustration and explains that their team cannot see reservation details without direct information, requesting the customer to provide details for further assistance.</t>
         </is>
       </c>
     </row>
@@ -43143,7 +43118,7 @@
       </c>
       <c r="O674" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Booking.com replied to a user’s direct message, indicating routine customer support activity.</t>
         </is>
       </c>
     </row>
@@ -43208,7 +43183,7 @@
       </c>
       <c r="O675" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Booking.com is offering customer support for outstanding refunds, requesting booking details via direct message.</t>
         </is>
       </c>
     </row>
@@ -43272,7 +43247,7 @@
       </c>
       <c r="O676" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Booking.com responds to a customer on X, requesting personal details to investigate a complaint.</t>
         </is>
       </c>
     </row>
@@ -43333,7 +43308,7 @@
       </c>
       <c r="O677" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Booking.com responds to a user’s inquiry about an Agoda reservation, directing them to contact Agoda directly for assistance.</t>
         </is>
       </c>
     </row>
@@ -43403,7 +43378,7 @@
       </c>
       <c r="O678" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Booking.com responds to a customer complaint, explaining that cancellation and refund policies are set by the accommodation and requesting booking details for further investigation.</t>
         </is>
       </c>
     </row>
@@ -43467,7 +43442,7 @@
       </c>
       <c r="O679" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Booking.com addresses a customer complaint about a reservation in Columbus, Ohio, apologizing for the inconvenience and offering to collect details via DM while directing the user to 24/7 support.</t>
         </is>
       </c>
     </row>
@@ -43528,7 +43503,7 @@
       </c>
       <c r="O680" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Booking.com sent a private message to user @MuathMuhammad, asking them to check the message.</t>
         </is>
       </c>
     </row>
@@ -43589,7 +43564,7 @@
       </c>
       <c r="O681" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Booking.com replied to a user on X, acknowledging their concern and directing them to check their direct message for further assistance.</t>
         </is>
       </c>
     </row>
@@ -43650,7 +43625,7 @@
       </c>
       <c r="O682" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Booking.com replied to a user’s inquiry via direct message, directing them to check their messages for additional support.</t>
         </is>
       </c>
     </row>
@@ -43717,7 +43692,7 @@
       </c>
       <c r="O683" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Booking.com responds to a customer’s car rental damage claim, requesting booking details via private message.</t>
         </is>
       </c>
     </row>
@@ -43778,7 +43753,7 @@
       </c>
       <c r="O684" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Booking.com replied privately to a user on X, notifying them that a response has been sent.</t>
         </is>
       </c>
     </row>
@@ -43834,12 +43809,12 @@
       </c>
       <c r="N685" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="O685" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Booking.com apologizes to a customer for a frustrating support experience and invites them to discuss the issue privately.</t>
         </is>
       </c>
     </row>
@@ -43903,7 +43878,7 @@
       </c>
       <c r="O686" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Booking.com is following up with a customer about a pending refund, requesting confirmation details via direct message.</t>
         </is>
       </c>
     </row>
@@ -43954,17 +43929,17 @@
       </c>
       <c r="M687" t="inlineStr">
         <is>
-          <t>General Industry News</t>
+          <t>Tech Updates</t>
         </is>
       </c>
       <c r="N687" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="O687" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Booking.com advises a user to avoid sharing reservation PIN codes publicly and to delete the comment, urging a private discussion for security.</t>
         </is>
       </c>
     </row>
@@ -44025,7 +44000,7 @@
       </c>
       <c r="O688" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Booking.com sent a private message to user Karina Parvanova, likely for a follow-up or support.</t>
         </is>
       </c>
     </row>
@@ -44086,7 +44061,7 @@
       </c>
       <c r="O689" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Booking.com sent a direct message to user @Patreus7575, requesting them to check their DM.</t>
         </is>
       </c>
     </row>
@@ -44137,7 +44112,7 @@
       </c>
       <c r="L690" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="M690" t="inlineStr">
@@ -44147,12 +44122,12 @@
       </c>
       <c r="N690" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="O690" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Booking.com clarifies that property availability is controlled by the properties themselves and offers support for customers encountering fraudulent listings.</t>
         </is>
       </c>
     </row>
@@ -44213,7 +44188,7 @@
       </c>
       <c r="O691" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Booking.com sent a private message to user @KatarinaHill2, likely for outreach or support purposes.</t>
         </is>
       </c>
     </row>
@@ -44626,7 +44601,7 @@
       </c>
       <c r="O697" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Booking.com apologizes for a flight cancellation and refund delay, explains the inability to assist via social media, and directs the customer to the flight support team.</t>
         </is>
       </c>
     </row>
@@ -44691,7 +44666,7 @@
       </c>
       <c r="O698" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Booking.com replies to a user’s inquiry, asking for a confidential code and traveler name to review the case.</t>
         </is>
       </c>
     </row>
@@ -44744,7 +44719,7 @@
       </c>
       <c r="L699" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="M699" t="inlineStr">
@@ -44759,7 +44734,7 @@
       </c>
       <c r="O699" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Booking.com apologizes for a delayed response to a customer complaint and provides instructions for private messaging and contact details.</t>
         </is>
       </c>
     </row>
@@ -44806,7 +44781,7 @@
       </c>
       <c r="L700" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="M700" t="inlineStr">
@@ -44821,7 +44796,7 @@
       </c>
       <c r="O700" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Booking.com apologized to a user for a flight cancellation and delayed response, indicating the issue was handled via a private message.</t>
         </is>
       </c>
     </row>
@@ -44883,7 +44858,7 @@
       </c>
       <c r="O701" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Booking.com publicly acknowledges a user’s private message, expressing empathy about an incident.</t>
         </is>
       </c>
     </row>
@@ -44948,7 +44923,7 @@
       </c>
       <c r="O702" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Booking.com responds to a user’s complaint about a booking issue, offering a refund and requesting confirmation details via private message.</t>
         </is>
       </c>
     </row>
@@ -44994,7 +44969,7 @@
       </c>
       <c r="L703" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="M703" t="inlineStr">
@@ -45004,12 +44979,12 @@
       </c>
       <c r="N703" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="O703" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Booking.com informs users that they cannot help with verification issues and directs them to a link for listing properties.</t>
         </is>
       </c>
     </row>
@@ -45070,7 +45045,7 @@
       </c>
       <c r="O704" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Booking.com sent a direct message to user @MiriamFeldman12, inviting them to review the reply for more details.</t>
         </is>
       </c>
     </row>
@@ -45131,7 +45106,7 @@
       </c>
       <c r="O705" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Booking.com sent a private message to user @medactif, likely for support or communication.</t>
         </is>
       </c>
     </row>
@@ -45181,7 +45156,7 @@
       </c>
       <c r="L706" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="M706" t="inlineStr">
@@ -45196,7 +45171,7 @@
       </c>
       <c r="O706" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Booking.com responds to a customer complaint about a pending refund, offering to investigate via DM and directing the customer to 24/7 support.</t>
         </is>
       </c>
     </row>
@@ -45260,7 +45235,7 @@
       </c>
       <c r="O707" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Booking.com responds to a customer’s difficulty reaching support, offering to investigate the booking and requesting confirmation details.</t>
         </is>
       </c>
     </row>
@@ -45326,7 +45301,7 @@
       </c>
       <c r="O708" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Booking.com responds to a customer complaint about a reservation not honored, clarifying that property owners control availability and offering steps for resolution.</t>
         </is>
       </c>
     </row>
@@ -45387,7 +45362,7 @@
       </c>
       <c r="O709" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Booking.com acknowledges a customer’s negative experience and directs them to a private message for resolution.</t>
         </is>
       </c>
     </row>
@@ -45450,7 +45425,7 @@
       </c>
       <c r="O710" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Booking.com clarifies its language support on X, offering assistance in several languages but not Arabic, and directs Arabic-speaking users to a local contact number.</t>
         </is>
       </c>
     </row>
@@ -45511,7 +45486,7 @@
       </c>
       <c r="O711" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Booking.com acknowledges a customer’s delayed response issue and requests a private message for further assistance.</t>
         </is>
       </c>
     </row>
@@ -45572,7 +45547,7 @@
       </c>
       <c r="O712" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Booking.com sent a private message to user @cactushoney12, prompting them to check their private message.</t>
         </is>
       </c>
     </row>
@@ -45633,7 +45608,7 @@
       </c>
       <c r="O713" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Booking.com is following up with a user to request additional details for next steps.</t>
         </is>
       </c>
     </row>
@@ -45700,7 +45675,7 @@
       </c>
       <c r="O714" t="inlineStr">
         <is>
-          <t>Failed to analyze post via LLM.</t>
+          <t>Booking.com for Travel Agents outlines its social media support process for accommodation bookings, providing required details for DMs and directing users to phone support for urgent needs.</t>
         </is>
       </c>
     </row>

--- a/News_Dashboard/data/social_media_posts.xlsx
+++ b/News_Dashboard/data/social_media_posts.xlsx
@@ -4137,7 +4137,10 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>[Failed to fetch]</t>
+          <t>[Transcript unavailable: 
+Could not retrieve a transcript for the video https://www.youtube.com/watch?v=achyqRan3xI! This is most likely caused by:
+Subtitles are disabled for this video
+If you are sure that the described cause is not responsible for this error and that a transcript should be retrievable, please create an issue at https://github.com/jdepoix/youtube-transcript-api/issues. Please add which version of youtube_transcript_api you are using and provide the information needed to replicate the error. Also make sure that there are no open issues which already describe your problem!]</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -4147,22 +4150,22 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>General Industry News</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>Failed to analyze video transcript via LLM.</t>
+          <t>Transcript not available.</t>
         </is>
       </c>
     </row>
@@ -4347,7 +4350,10 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>[Failed to fetch]</t>
+          <t>[Transcript unavailable: 
+Could not retrieve a transcript for the video https://www.youtube.com/watch?v=HKOtGZP1Utc! This is most likely caused by:
+Subtitles are disabled for this video
+If you are sure that the described cause is not responsible for this error and that a transcript should be retrievable, please create an issue at https://github.com/jdepoix/youtube-transcript-api/issues. Please add which version of youtube_transcript_api you are using and provide the information needed to replicate the error. Also make sure that there are no open issues which already describe your problem!]</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -7374,7 +7380,10 @@
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>[Failed to fetch]</t>
+          <t>[Transcript unavailable: 
+Could not retrieve a transcript for the video https://www.youtube.com/watch?v=PAkOQITfIiA! This is most likely caused by:
+Subtitles are disabled for this video
+If you are sure that the described cause is not responsible for this error and that a transcript should be retrievable, please create an issue at https://github.com/jdepoix/youtube-transcript-api/issues. Please add which version of youtube_transcript_api you are using and provide the information needed to replicate the error. Also make sure that there are no open issues which already describe your problem!]</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
@@ -7384,22 +7393,22 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>General Industry News</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="N111" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="O111" t="inlineStr">
         <is>
-          <t>Failed to analyze video transcript via LLM.</t>
+          <t>Transcript not available for the requested video.</t>
         </is>
       </c>
     </row>
@@ -9267,7 +9276,7 @@
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>[Failed to fetch]</t>
+          <t>[music] &gt;&gt; Oh. Hey, what's up?</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
@@ -9277,12 +9286,12 @@
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>General Industry News</t>
+          <t>Product Announcement</t>
         </is>
       </c>
       <c r="N140" t="inlineStr">
@@ -9290,7 +9299,11 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="O140" t="inlineStr"/>
+      <c r="O140" t="inlineStr">
+        <is>
+          <t>Brex showcases a new feature that dramatically speeds up the month‑end close process, reducing the time from 14 days to just minutes. The video highlights how this improvement streamlines finance operations and boosts productivity for users.</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -15273,7 +15286,10 @@
       </c>
       <c r="J232" t="inlineStr">
         <is>
-          <t>[Failed to fetch]</t>
+          <t>Wait till you see this! With Expedia, The more you book, the more
+rewards you can unlock. and the more rewards you
+unlock, the more you get to
+enjoy whatever this is.</t>
         </is>
       </c>
       <c r="K232" t="inlineStr">
@@ -15283,12 +15299,12 @@
       </c>
       <c r="L232" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="M232" t="inlineStr">
         <is>
-          <t>General Industry News</t>
+          <t>Product Announcement</t>
         </is>
       </c>
       <c r="N232" t="inlineStr">
@@ -15298,7 +15314,7 @@
       </c>
       <c r="O232" t="inlineStr">
         <is>
-          <t>Failed to analyze video transcript via LLM.</t>
+          <t>The video promotes Expedia’s rewards program, highlighting that the more customers book, the more rewards they unlock, enhancing their travel experience.</t>
         </is>
       </c>
     </row>
@@ -35084,7 +35100,7 @@
       </c>
       <c r="J550" t="inlineStr">
         <is>
-          <t>[Failed to fetch]</t>
+          <t>Things have improved my life from a user's perspective and a finance perspective. Obviously, compliance, a lot of control, so my accounting team's happy, my controllers are happy, my CFO's happy, but the business is happy. The business feels like their data is clean now. &gt;&gt; [music] &gt;&gt; Um the users are being listened to. We've automated a lot of um manual steps uh through different tools um like the request tool to get pre-approvals. The excitement's growing. [music] They are now feeling like they can actually serve themselves. &gt;&gt; [music]</t>
         </is>
       </c>
       <c r="K550" t="inlineStr">
@@ -35094,12 +35110,12 @@
       </c>
       <c r="L550" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="M550" t="inlineStr">
         <is>
-          <t>General Industry News</t>
+          <t>Product Announcement</t>
         </is>
       </c>
       <c r="N550" t="inlineStr">
@@ -35109,7 +35125,7 @@
       </c>
       <c r="O550" t="inlineStr">
         <is>
-          <t>Failed to analyze video transcript via LLM.</t>
+          <t>The video highlights how Concur Expense has improved user and finance experiences by enhancing compliance, control, and data cleanliness. It showcases automation of manual steps, such as pre-approval requests, and emphasizes that users feel empowered to serve themselves, indicating growing excitement around the product.</t>
         </is>
       </c>
     </row>
@@ -35154,7 +35170,7 @@
       </c>
       <c r="J551" t="inlineStr">
         <is>
-          <t>[Failed to fetch]</t>
+          <t>Concur Travel makes travel so much easier for our employees because they're it's it's it's a one-stop shop. It's not only saving me time, it's saving me approvers time because they're not having to then go review everything again. Prior to my joining the company, we were 25 to 30% over budget every [music] year in travel. Being able to see that data on a monthly basis and make shifts, we were actually on budget for the first time. &gt;&gt; [music]</t>
         </is>
       </c>
       <c r="K551" t="inlineStr">
@@ -35164,12 +35180,12 @@
       </c>
       <c r="L551" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="M551" t="inlineStr">
         <is>
-          <t>General Industry News</t>
+          <t>Product Announcement</t>
         </is>
       </c>
       <c r="N551" t="inlineStr">
@@ -35179,7 +35195,7 @@
       </c>
       <c r="O551" t="inlineStr">
         <is>
-          <t>Failed to analyze video transcript via LLM.</t>
+          <t>The video showcases a testimonial from a user of Concur Travel, highlighting how the platform simplifies travel management for employees and approvers, provides real‑time visibility into travel spend, and helped the company move from being 25‑30% over budget to staying on budget for the first time.</t>
         </is>
       </c>
     </row>
@@ -35224,7 +35240,7 @@
       </c>
       <c r="J552" t="inlineStr">
         <is>
-          <t>[Failed to fetch]</t>
+          <t>sobre todo si automatiza procesos vida de todos pero debe funcionar que ya tienes cuando los datos sin trabas entre sistemas tus procesos se integran y tu empresa opera como debe por eso SAP Concur ofrece cientos de integraciones y conectores preconfigurados &gt;&gt; [music] &gt;&gt; al conectar nuestras soluciones con las tuyas tu empresa puede reducir costos su rentabilidad obtén visibilidad de datos de gasto actualizados [music] mejora el cumplimiento de políticas y elimina errores de procesos manuales lo mejor funcionan con cualquier ERP y si no ves una integración en nuestro [music] App Center no hay problema podemos crearla a la medida o tus desarrolladores pueden usar nuestras &gt;&gt; [music] &gt;&gt; abiertas para crear la que necesitas visita nuestra página de integraciones y aprovecha al máximo tu inversión en SAP Concur [music]</t>
         </is>
       </c>
       <c r="K552" t="inlineStr">
@@ -35234,12 +35250,12 @@
       </c>
       <c r="L552" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="M552" t="inlineStr">
         <is>
-          <t>General Industry News</t>
+          <t>Product Announcement</t>
         </is>
       </c>
       <c r="N552" t="inlineStr">
@@ -35249,7 +35265,7 @@
       </c>
       <c r="O552" t="inlineStr">
         <is>
-          <t>Failed to analyze video transcript via LLM.</t>
+          <t>El video presenta una guía para principiantes sobre las integraciones de SAP Concur, destacando cómo automatizan procesos, reducen costos, mejoran la visibilidad de datos de gasto, cumplen con políticas y eliminan errores manuales. Se menciona la disponibilidad de cientos de integraciones preconfiguradas, la posibilidad de crear integraciones personalizadas y el uso de conectores abiertos para desarrolladores.</t>
         </is>
       </c>
     </row>
@@ -35294,7 +35310,7 @@
       </c>
       <c r="J553" t="inlineStr">
         <is>
-          <t>[Failed to fetch]</t>
+          <t>Concur Invoice really is such an important component of what I do in my [music] everyday job. It allows customization of workflows. It allows us to monitor our processes through various like the invoice manager dashboard, things of that nature. And it really does enable us to push invoices out faster, to get those payment cycle times down as low as possible, and also [music] not burden our approvers and our reviewers with just tedious work. &gt;&gt; [music] &gt;&gt; It allows them to make actionable decisions instead of just cranking through a list of things that they [music] have to get done today.</t>
         </is>
       </c>
       <c r="K553" t="inlineStr">
@@ -35304,12 +35320,12 @@
       </c>
       <c r="L553" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="M553" t="inlineStr">
         <is>
-          <t>General Industry News</t>
+          <t>Product Announcement</t>
         </is>
       </c>
       <c r="N553" t="inlineStr">
@@ -35319,7 +35335,7 @@
       </c>
       <c r="O553" t="inlineStr">
         <is>
-          <t>Failed to analyze video transcript via LLM.</t>
+          <t>The video showcases Concur Invoice as a key tool in the speaker’s daily work, highlighting its ability to customize workflows, monitor processes via an invoice manager dashboard, accelerate invoice processing, shorten payment cycle times, and reduce the administrative burden on approvers and reviewers.</t>
         </is>
       </c>
     </row>
@@ -35364,7 +35380,7 @@
       </c>
       <c r="J554" t="inlineStr">
         <is>
-          <t>[Failed to fetch]</t>
+          <t>[music] &gt;&gt; Prior to my joining the company, we were 25% over budget every year in travel. After we started pulling the data, and of course there were some other factors that went into [music] to cost saving as well, but being able to see that data on a monthly basis and make shifts, &gt;&gt; [music] &gt;&gt; we were actually on budget for the first time in 2024 and 2025. Being able to pull reporting from Concur and present it to the management team, it was the first [music] time that they had seen data at that granular level as opposed to just a bottom line budget impact. [music] So, it was extremely impactful. &gt;&gt; [music] &gt;&gt; We could [music] look at where our compliance issues were. So, where we were seeing some unnecessary spend, we could tweak the [music] policy to say, "Hey, you know, maybe we need to limit that spend or remove it altogether." &gt;&gt; [music]</t>
         </is>
       </c>
       <c r="K554" t="inlineStr">
@@ -35374,12 +35390,12 @@
       </c>
       <c r="L554" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="M554" t="inlineStr">
         <is>
-          <t>General Industry News</t>
+          <t>Tech Updates</t>
         </is>
       </c>
       <c r="N554" t="inlineStr">
@@ -35389,7 +35405,7 @@
       </c>
       <c r="O554" t="inlineStr">
         <is>
-          <t>Failed to analyze video transcript via LLM.</t>
+          <t>The video discusses how Meteor Education leveraged data visibility, verification, and AI tools—particularly Concur reporting—to transform its travel spend management. By monitoring monthly data, identifying compliance issues, and adjusting policies, the company moved from being 25% over budget to staying on budget for the first time in 2024 and 2025, highlighting significant cost savings and operational impact.</t>
         </is>
       </c>
     </row>
@@ -37845,7 +37861,7 @@
       </c>
       <c r="J592" t="inlineStr">
         <is>
-          <t>[Failed to fetch]</t>
+          <t>[music] &gt;&gt; With the intelligence [music] reporting tool within Concur, &gt;&gt; [music] &gt;&gt; we can get in there. We get a lot of visibility into what [music] our spend is. We got reports for spend by category, spend by person, spend by department. [music] We've created a bunch of custom reports, which I think is great. And then we have of course the standard [music] reports for helping us with the accruals on the finance side and the month and the year credit card reconciliation. &gt;&gt; [music] &gt;&gt; That's a lot easier just running the report. Seeing what was submitted, what wasn't submitted. [music] And then wasn't submitted and the month you accrued, then you follow up with the people and get them to finish everything and then the reconciliation [music] of the statements is done. That's been very clean since we implemented it. We're very happy with that. &gt;&gt; [music] &gt;&gt; One advantage we do have again what I see from Concur side is [music] that we can have reporting extracts. So reporting intelligence actually is one of the very powerful Cognos database that we currently use and [music] I think it's a fantastic data repository where pretty much you get if you have the right reporting and the right &gt;&gt; [music] &gt;&gt; way or the right requirements written down, I think we get a very good &gt;&gt; [music] &gt;&gt; report out of it. We get Today currently for us we do get data extracted to our Power BI data warehouse &gt;&gt; [music] &gt;&gt; and we do generate some cool reports out of that. Today our finance teams, our spend [music] teams, AP teams and the leadership, they do view those data reports and they do view those [music] KPIs actually. From our Power BI reporting, but the underlying data everything is actually [music] coming out of Concur. &gt;&gt; When I started with Medair about 2 and 1/2 years ago, there was [music] no reporting being done. And that's one of the main reasons I was hired. So, being able to pull reporting from Concur and present it to the management team, it was the first [music] time that they had seen data at that granular level as opposed to just a bottom line budget impact. So, it was extremely impactful. We [music] could look at at at where our compliance issues were. We could look again at um [music] any policy changes we need to make based on that data. But, the biggest impact, um and I'm very proud of this, [music] is prior to my joining the company, we were 25 to 30% over budget every year in travel. After [music] we started pulling the data, and of course there were some other factors that went into to cost saving [music] as well, but being able to see that data on a monthly basis and make shifts, we were actually on budget for the first time. &gt;&gt; [music]</t>
         </is>
       </c>
       <c r="K592" t="inlineStr">
@@ -37855,12 +37871,12 @@
       </c>
       <c r="L592" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="M592" t="inlineStr">
         <is>
-          <t>General Industry News</t>
+          <t>Tech Updates</t>
         </is>
       </c>
       <c r="N592" t="inlineStr">
@@ -37870,7 +37886,7 @@
       </c>
       <c r="O592" t="inlineStr">
         <is>
-          <t>Failed to analyze video transcript via LLM.</t>
+          <t>The video showcases how SAP Concur’s reporting and data extraction capabilities transformed travel spend management for a client. It highlights the ease of generating custom and standard reports, integrating Concur data with Power BI, and the resulting visibility that helped the organization reduce travel spend from 25‑30% over budget to on‑budget status. The speaker emphasizes the positive impact on compliance, policy adjustments, and overall financial oversight.</t>
         </is>
       </c>
     </row>
@@ -44233,7 +44249,7 @@
       </c>
       <c r="J692" t="inlineStr">
         <is>
-          <t>[Failed to fetch]</t>
+          <t>Come on, come on. &gt;&gt; To make around $2,000 in a week, this man could walk 34 Chihuahuas every day. Or he could try putting his place on Airbnb.</t>
         </is>
       </c>
       <c r="K692" t="inlineStr">
@@ -44258,7 +44274,7 @@
       </c>
       <c r="O692" t="inlineStr">
         <is>
-          <t>Failed to analyze video transcript via LLM.</t>
+          <t>The video humorously compares the potential earnings of walking 34 Chihuahuas daily to listing a property on Airbnb, highlighting the financial prospects of each option.</t>
         </is>
       </c>
     </row>
@@ -44303,7 +44319,7 @@
       </c>
       <c r="J693" t="inlineStr">
         <is>
-          <t>[Failed to fetch]</t>
+          <t>To make around $2,000 in a week, this couple could sell 2,000 lemonades. Oops. Or they could try putting their place on Airbnb.</t>
         </is>
       </c>
       <c r="K693" t="inlineStr">
@@ -44328,7 +44344,7 @@
       </c>
       <c r="O693" t="inlineStr">
         <is>
-          <t>Failed to analyze video transcript via LLM.</t>
+          <t>The video compares the potential earnings of a couple selling 2,000 lemonades in a week to listing their property on Airbnb, highlighting the financial opportunities of the Airbnb platform.</t>
         </is>
       </c>
     </row>
@@ -44373,7 +44389,7 @@
       </c>
       <c r="J694" t="inlineStr">
         <is>
-          <t>[Failed to fetch]</t>
+          <t>To make around $2,000 in a week, this man could ref 56 soccer games. &gt;&gt; [cheering] &gt;&gt; Or, he could try putting his place on Airbnb. &gt;&gt; [cheering]</t>
         </is>
       </c>
       <c r="K694" t="inlineStr">
@@ -44398,7 +44414,7 @@
       </c>
       <c r="O694" t="inlineStr">
         <is>
-          <t>Failed to analyze video transcript via LLM.</t>
+          <t>The video humorously compares the potential earnings of refereeing 56 soccer games to listing a property on Airbnb, suggesting that the latter could be a more lucrative option for making around $2,000 in a week.</t>
         </is>
       </c>
     </row>
@@ -44443,7 +44459,7 @@
       </c>
       <c r="J695" t="inlineStr">
         <is>
-          <t>[Failed to fetch]</t>
+          <t>This couple could make extra money this weekend by cat sitting for a whole lot of cats. &gt;&gt; [screaming] &gt;&gt; Or they could try putting their place on Airbnb.</t>
         </is>
       </c>
       <c r="K695" t="inlineStr">
@@ -44453,7 +44469,7 @@
       </c>
       <c r="L695" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="M695" t="inlineStr">
@@ -44468,7 +44484,7 @@
       </c>
       <c r="O695" t="inlineStr">
         <is>
-          <t>Failed to analyze video transcript via LLM.</t>
+          <t>The video humorously presents a couple weighing the option of earning extra money by cat‑sitting a large number of cats versus listing their home on Airbnb.</t>
         </is>
       </c>
     </row>
@@ -44513,7 +44529,7 @@
       </c>
       <c r="J696" t="inlineStr">
         <is>
-          <t>[Failed to fetch]</t>
+          <t>To make around $2,000 in a week, this woman could give 31 violin lessons. Or she could try putting her place on Airbnb.</t>
         </is>
       </c>
       <c r="K696" t="inlineStr">
@@ -44538,7 +44554,7 @@
       </c>
       <c r="O696" t="inlineStr">
         <is>
-          <t>Failed to analyze video transcript via LLM.</t>
+          <t>The video follows a woman who can earn about $2,000 in a week by either giving 31 violin lessons or listing her property on Airbnb, highlighting the choice between a traditional skill-based gig and a platform-based rental opportunity.</t>
         </is>
       </c>
     </row>

--- a/News_Dashboard/data/social_media_posts.xlsx
+++ b/News_Dashboard/data/social_media_posts.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,81 +425,81 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O733"/>
+  <dimension ref="A1:O743"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Base_Company</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Competitor</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Author/Handle</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Date Created</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Post Text</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Image URL</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Image Text</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Video URL</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Video Transcript</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Post URL</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Sentiment</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Alert Level</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>AI Summary</t>
         </is>
@@ -46878,6 +46890,640 @@
         </is>
       </c>
     </row>
+    <row r="734">
+      <c r="A734" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B734" t="inlineStr">
+        <is>
+          <t>Brex</t>
+        </is>
+      </c>
+      <c r="C734" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D734" t="inlineStr">
+        <is>
+          <t>brexhq</t>
+        </is>
+      </c>
+      <c r="E734" t="inlineStr">
+        <is>
+          <t>Mon Jul 27 14:16:34 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F734" t="inlineStr">
+        <is>
+          <t>AI is officially a line item. Get into the data👇</t>
+        </is>
+      </c>
+      <c r="G734" t="inlineStr"/>
+      <c r="H734" t="inlineStr"/>
+      <c r="I734" t="inlineStr"/>
+      <c r="J734" t="inlineStr"/>
+      <c r="K734" t="inlineStr">
+        <is>
+          <t>https://x.com/brexHQ/status/2081745567441445249</t>
+        </is>
+      </c>
+      <c r="L734" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M734" t="inlineStr">
+        <is>
+          <t>Product Announcement</t>
+        </is>
+      </c>
+      <c r="N734" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O734" t="inlineStr">
+        <is>
+          <t>Brex announces that AI has become an official line item, inviting stakeholders to explore the associated data.</t>
+        </is>
+      </c>
+    </row>
+    <row r="735">
+      <c r="A735" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B735" t="inlineStr">
+        <is>
+          <t>Expedia</t>
+        </is>
+      </c>
+      <c r="C735" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D735" t="inlineStr">
+        <is>
+          <t>Expedia</t>
+        </is>
+      </c>
+      <c r="E735" t="inlineStr">
+        <is>
+          <t>2026-07-27T13:40:43.194Z</t>
+        </is>
+      </c>
+      <c r="F735" t="inlineStr">
+        <is>
+          <t>The secrets out! 🏝️
+Emma Tagg, Senior Manager of Global PR at Expedia, is riding the wave of Expedia's 2026 Island Hot List, sharing the destinations making the biggest splash this year. 
+Think romance in St. Lucia, incredible food in Syros, stunning scenery in the Lofoten Islands, and Cape Verde, our breakout soccer island that's winning fans with its beach lifestyle and football passion. 
+Tap the link to check out the full top 10 and start planning your next escape! ✈️
+👉 http://ms.spr.ly/6046vC9ay</t>
+        </is>
+      </c>
+      <c r="G735" t="inlineStr"/>
+      <c r="H735" t="inlineStr"/>
+      <c r="I735" t="inlineStr">
+        <is>
+          <t>https://dms.licdn.com/playlist/vid/v2/D4E10AQGbxo9DYCLTow/mp4-720p-30fp-crf28/B4EZ.jzh5cJcBk-/0/1785159633770?e=1785783600&amp;v=beta&amp;t=5p71uNbvUBKPnSXZ1_qWbArXB2yh3QP0hm_-KIq5D8Q</t>
+        </is>
+      </c>
+      <c r="J735" t="inlineStr">
+        <is>
+          <t>[faster-whisper not installed. Run 'pip install faster-whisper']</t>
+        </is>
+      </c>
+      <c r="K735" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/expedia_island-hot-list-activity-7487502232087674880-a9sl</t>
+        </is>
+      </c>
+      <c r="L735" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M735" t="inlineStr">
+        <is>
+          <t>Strategic Expansion or Changes</t>
+        </is>
+      </c>
+      <c r="N735" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O735" t="inlineStr">
+        <is>
+          <t>Expedia is promoting its 2026 Island Hot List, spotlighting top destinations like St. Lucia, Syros, Lofoten Islands, and Cape Verde to entice travelers and boost brand visibility.</t>
+        </is>
+      </c>
+    </row>
+    <row r="736">
+      <c r="A736" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B736" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C736" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D736" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E736" t="inlineStr">
+        <is>
+          <t>Mon Jul 27 18:00:32 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F736" t="inlineStr">
+        <is>
+          <t>@aditisharmxa23 Hi Aditi, we have sent you a private message. Please take a moment to check it. Thank you.</t>
+        </is>
+      </c>
+      <c r="G736" t="inlineStr"/>
+      <c r="H736" t="inlineStr"/>
+      <c r="I736" t="inlineStr"/>
+      <c r="J736" t="inlineStr"/>
+      <c r="K736" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2081801930351772084</t>
+        </is>
+      </c>
+      <c r="L736" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M736" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N736" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O736" t="inlineStr">
+        <is>
+          <t>Booking.com sent a private message to user @aditisharmxa23, encouraging them to check the message.</t>
+        </is>
+      </c>
+    </row>
+    <row r="737">
+      <c r="A737" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B737" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C737" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D737" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E737" t="inlineStr">
+        <is>
+          <t>Mon Jul 27 17:09:18 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F737" t="inlineStr">
+        <is>
+          <t>Hi Khaled, we understand your frustration as the deposit hasn't yet been returned to you for your car rental reservation. 
+We are responding to you in English because, unfortunately, we do not offer support in Arabic on Social Media. 
+We can assist you here in Dutch, English, French, German, Italian, Portuguese, and Spanish. 
+In order for us to assist you, please send us a private message with the following details: 
+- Name of booker 
+- Email address used to book 
+Alternatively, if you prefer to reach out in Arabic, you can find your local number here: 800 04441490 / you can give our (language) support a call on: https://t.co/6FMd8r77Bx.</t>
+        </is>
+      </c>
+      <c r="G737" t="inlineStr"/>
+      <c r="H737" t="inlineStr"/>
+      <c r="I737" t="inlineStr"/>
+      <c r="J737" t="inlineStr"/>
+      <c r="K737" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2081789036432109686</t>
+        </is>
+      </c>
+      <c r="L737" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M737" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N737" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O737" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a customer’s frustration about a pending deposit refund, offering multilingual support and requesting booking details via private message.</t>
+        </is>
+      </c>
+    </row>
+    <row r="738">
+      <c r="A738" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B738" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C738" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D738" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E738" t="inlineStr">
+        <is>
+          <t>Mon Jul 27 13:19:22 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F738" t="inlineStr">
+        <is>
+          <t>@SamVenere2022 Bonjour Sam, nous comprenons votre frustration.
+Comme indiqué, nous ne pouvons pas aider pour les réservations de voitures via les réseaux sociaux. Merci de contacter notre équipe dédiée via le lien déjà partagé. La page est aussi disponible en français.</t>
+        </is>
+      </c>
+      <c r="G738" t="inlineStr"/>
+      <c r="H738" t="inlineStr"/>
+      <c r="I738" t="inlineStr"/>
+      <c r="J738" t="inlineStr"/>
+      <c r="K738" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2081731170878853312</t>
+        </is>
+      </c>
+      <c r="L738" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M738" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N738" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O738" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a user’s frustration about car reservations via social media, directing them to dedicated support and offering a French page.</t>
+        </is>
+      </c>
+    </row>
+    <row r="739">
+      <c r="A739" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B739" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C739" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D739" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E739" t="inlineStr">
+        <is>
+          <t>Mon Jul 27 13:17:32 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F739" t="inlineStr">
+        <is>
+          <t>@dasbadx Olá, respondemos a sua mensagem no privado.</t>
+        </is>
+      </c>
+      <c r="G739" t="inlineStr"/>
+      <c r="H739" t="inlineStr"/>
+      <c r="I739" t="inlineStr"/>
+      <c r="J739" t="inlineStr"/>
+      <c r="K739" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2081730708158988300</t>
+        </is>
+      </c>
+      <c r="L739" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M739" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N739" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O739" t="inlineStr">
+        <is>
+          <t>Booking.com responded to a private message from user @dasbadx, indicating routine customer service engagement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="740">
+      <c r="A740" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B740" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C740" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D740" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E740" t="inlineStr">
+        <is>
+          <t>Mon Jul 27 13:15:51 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F740" t="inlineStr">
+        <is>
+          <t>@azerolo Como hemos mencionado anteriormente, Antonio, por redes sociales no podemos ofrecerte asistencia para vuelos.
+En el siguiente enlace encontrarás la información de contacto de nuestro equipo de atención al cliente para reservas de vuelo: https://t.co/RgpP8hoadc</t>
+        </is>
+      </c>
+      <c r="G740" t="inlineStr"/>
+      <c r="H740" t="inlineStr"/>
+      <c r="I740" t="inlineStr"/>
+      <c r="J740" t="inlineStr"/>
+      <c r="K740" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2081730286543380559</t>
+        </is>
+      </c>
+      <c r="L740" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M740" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N740" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O740" t="inlineStr">
+        <is>
+          <t>Booking.com informs a user that flight assistance cannot be provided via social media and directs them to customer service contact information.</t>
+        </is>
+      </c>
+    </row>
+    <row r="741">
+      <c r="A741" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B741" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C741" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D741" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E741" t="inlineStr">
+        <is>
+          <t>Mon Jul 27 12:38:34 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F741" t="inlineStr">
+        <is>
+          <t>@Pelusitaaaa1 Hi there. It could be that the property made a mistake in description. For us to have a look, please send us a private message and let us know the exact name of this property or provide a link to the listing. https://t.co/Z89AAoEgD7</t>
+        </is>
+      </c>
+      <c r="G741" t="inlineStr"/>
+      <c r="H741" t="inlineStr"/>
+      <c r="I741" t="inlineStr"/>
+      <c r="J741" t="inlineStr"/>
+      <c r="K741" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2081720903621087726</t>
+        </is>
+      </c>
+      <c r="L741" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M741" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N741" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O741" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a user about a possible listing description error and offers to investigate via private message.</t>
+        </is>
+      </c>
+    </row>
+    <row r="742">
+      <c r="A742" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B742" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C742" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D742" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E742" t="inlineStr">
+        <is>
+          <t>Mon Jul 27 12:31:16 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F742" t="inlineStr">
+        <is>
+          <t>@lucas0711s Hi there. We have responded to your private message.</t>
+        </is>
+      </c>
+      <c r="G742" t="inlineStr"/>
+      <c r="H742" t="inlineStr"/>
+      <c r="I742" t="inlineStr"/>
+      <c r="J742" t="inlineStr"/>
+      <c r="K742" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2081719066180329618</t>
+        </is>
+      </c>
+      <c r="L742" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M742" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N742" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O742" t="inlineStr">
+        <is>
+          <t>Booking.com replied to a private message from user @lucas0711s.</t>
+        </is>
+      </c>
+    </row>
+    <row r="743">
+      <c r="A743" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B743" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C743" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D743" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E743" t="inlineStr">
+        <is>
+          <t>Mon Jul 27 11:48:02 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F743" t="inlineStr">
+        <is>
+          <t>@craniosacralgal Hi there, we regret to hear, that your concerns were not escalated yet. For us to be able to look into this, we kindly ask you to DM us the following booking details: 
+- Confirmation Number
+- Pin Code
+- Name of the Guest 
+We'll than get back to you as soon as possible. https://t.co/Z89AAoEgD7</t>
+        </is>
+      </c>
+      <c r="G743" t="inlineStr"/>
+      <c r="H743" t="inlineStr"/>
+      <c r="I743" t="inlineStr"/>
+      <c r="J743" t="inlineStr"/>
+      <c r="K743" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2081708186441019528</t>
+        </is>
+      </c>
+      <c r="L743" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M743" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N743" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O743" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a user’s complaint, requesting booking details via DM to investigate the issue.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/News_Dashboard/data/social_media_posts.xlsx
+++ b/News_Dashboard/data/social_media_posts.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O743"/>
+  <dimension ref="A1:O778"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -47524,6 +47524,2261 @@
         </is>
       </c>
     </row>
+    <row r="744">
+      <c r="A744" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B744" t="inlineStr">
+        <is>
+          <t>TravelPerk</t>
+        </is>
+      </c>
+      <c r="C744" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D744" t="inlineStr">
+        <is>
+          <t>Perk</t>
+        </is>
+      </c>
+      <c r="E744" t="inlineStr">
+        <is>
+          <t>2026-07-28T09:43:59.580Z</t>
+        </is>
+      </c>
+      <c r="F744" t="inlineStr">
+        <is>
+          <t>Your expense controls might not be doing what you think they are.
+💡 1 in 5 employees misrepresent expenses regularly.
+💡 41% have submitted an AI-generated receipt at least once.
+💡 42% have stopped claiming legitimate expenses altogether, because the process isn't worth the friction.
+Our Staff Product Manager, Diana Quesada, breaks down the data behind expense misrepresentation and the three things CFOs can actually do about it, starting with understanding if you have the right controls in place. 
+Full report in the comments 👇</t>
+        </is>
+      </c>
+      <c r="G744" t="inlineStr"/>
+      <c r="H744" t="inlineStr"/>
+      <c r="I744" t="inlineStr">
+        <is>
+          <t>https://dms.licdn.com/playlist/vid/v2/D4D10AQEr4b4vGv2uTw/mp4-720p-30fp-crf28/B4DZ.oG5SPJ4Bo-/0/1785231819585?e=1785870000&amp;v=beta&amp;t=-pyVISjUUGsITCHx-oJpHSfQKwuIOQZ-LCmmeUzqz6Q</t>
+        </is>
+      </c>
+      <c r="J744" t="inlineStr">
+        <is>
+          <t>[faster-whisper not installed. Run 'pip install faster-whisper']</t>
+        </is>
+      </c>
+      <c r="K744" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/perk_ai-era-expense-management-demands-a-new-foundation-activity-7487805045678452736-uh_W</t>
+        </is>
+      </c>
+      <c r="L744" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M744" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N744" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O744" t="inlineStr">
+        <is>
+          <t>TravelPerk releases a data-driven report revealing that 1 in 5 employees misrepresent expenses, 41% have used AI-generated receipts, and 42% have stopped claiming legitimate expenses, offering CFOs actionable solutions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="745">
+      <c r="A745" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B745" t="inlineStr">
+        <is>
+          <t>Ramp</t>
+        </is>
+      </c>
+      <c r="C745" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D745" t="inlineStr">
+        <is>
+          <t>tryramp</t>
+        </is>
+      </c>
+      <c r="E745" t="inlineStr">
+        <is>
+          <t>Tue Jul 28 13:37:24 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F745" t="inlineStr">
+        <is>
+          <t>Can't wait to save gargantuan amounts of time and money for our Canadian business brethren
+https://t.co/3V94EnZNpv</t>
+        </is>
+      </c>
+      <c r="G745" t="inlineStr"/>
+      <c r="H745" t="inlineStr"/>
+      <c r="I745" t="inlineStr"/>
+      <c r="J745" t="inlineStr"/>
+      <c r="K745" t="inlineStr">
+        <is>
+          <t>https://x.com/tryramp/status/2082098095332995406</t>
+        </is>
+      </c>
+      <c r="L745" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M745" t="inlineStr">
+        <is>
+          <t>Product Announcement</t>
+        </is>
+      </c>
+      <c r="N745" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O745" t="inlineStr">
+        <is>
+          <t>Ramp highlights its ability to save Canadian businesses significant time and money, positioning its services as a cost‑effective solution.</t>
+        </is>
+      </c>
+    </row>
+    <row r="746">
+      <c r="A746" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B746" t="inlineStr">
+        <is>
+          <t>Ramp</t>
+        </is>
+      </c>
+      <c r="C746" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D746" t="inlineStr">
+        <is>
+          <t>tryramp</t>
+        </is>
+      </c>
+      <c r="E746" t="inlineStr">
+        <is>
+          <t>Tue Jul 28 13:33:59 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F746" t="inlineStr">
+        <is>
+          <t>BREAKING: Canadian businesses can now use Ramp to manage spend, pay bills, and close the books with ~lightning speed~
+CAD and USD spend. Provincial tax coding. Cross-border bills. All on one platform. Just as the great finance and accounting prophets foretold. https://t.co/1bErctjNJU</t>
+        </is>
+      </c>
+      <c r="G746" t="inlineStr"/>
+      <c r="H746" t="inlineStr"/>
+      <c r="I746" t="inlineStr"/>
+      <c r="J746" t="inlineStr"/>
+      <c r="K746" t="inlineStr">
+        <is>
+          <t>https://x.com/tryramp/status/2082097239049085126</t>
+        </is>
+      </c>
+      <c r="L746" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M746" t="inlineStr">
+        <is>
+          <t>Product Announcement</t>
+        </is>
+      </c>
+      <c r="N746" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O746" t="inlineStr">
+        <is>
+          <t>Ramp announces that Canadian businesses can now use its platform to manage spend, pay bills, and close books in CAD and USD, featuring provincial tax coding and cross‑border bill handling.</t>
+        </is>
+      </c>
+    </row>
+    <row r="747">
+      <c r="A747" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B747" t="inlineStr">
+        <is>
+          <t>Ramp</t>
+        </is>
+      </c>
+      <c r="C747" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D747" t="inlineStr">
+        <is>
+          <t>tryramp</t>
+        </is>
+      </c>
+      <c r="E747" t="inlineStr">
+        <is>
+          <t>Mon Jul 27 22:11:13 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F747" t="inlineStr">
+        <is>
+          <t>PorTAL is now open for (your) business</t>
+        </is>
+      </c>
+      <c r="G747" t="inlineStr"/>
+      <c r="H747" t="inlineStr"/>
+      <c r="I747" t="inlineStr"/>
+      <c r="J747" t="inlineStr"/>
+      <c r="K747" t="inlineStr">
+        <is>
+          <t>https://x.com/tryramp/status/2081865015624098183</t>
+        </is>
+      </c>
+      <c r="L747" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M747" t="inlineStr">
+        <is>
+          <t>Product Announcement</t>
+        </is>
+      </c>
+      <c r="N747" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O747" t="inlineStr">
+        <is>
+          <t>Ramp has launched PorTAL, a new platform now open for businesses.</t>
+        </is>
+      </c>
+    </row>
+    <row r="748">
+      <c r="A748" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B748" t="inlineStr">
+        <is>
+          <t>Ramp</t>
+        </is>
+      </c>
+      <c r="C748" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D748" t="inlineStr">
+        <is>
+          <t>tryramp</t>
+        </is>
+      </c>
+      <c r="E748" t="inlineStr">
+        <is>
+          <t>Mon Jul 27 22:06:41 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F748" t="inlineStr">
+        <is>
+          <t>@RampLabs @thinkymachines OPEN IT UP https://t.co/4ajnIr9GBs</t>
+        </is>
+      </c>
+      <c r="G748" t="inlineStr"/>
+      <c r="H748" t="inlineStr"/>
+      <c r="I748" t="inlineStr"/>
+      <c r="J748" t="inlineStr"/>
+      <c r="K748" t="inlineStr">
+        <is>
+          <t>https://x.com/tryramp/status/2081863875541037419</t>
+        </is>
+      </c>
+      <c r="L748" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M748" t="inlineStr">
+        <is>
+          <t>Product Announcement</t>
+        </is>
+      </c>
+      <c r="N748" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O748" t="inlineStr">
+        <is>
+          <t>Ramp announces a new collaboration with Thinky Machines, teasing the launch of a product or feature titled "Open It Up."</t>
+        </is>
+      </c>
+    </row>
+    <row r="749">
+      <c r="A749" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B749" t="inlineStr">
+        <is>
+          <t>Brex</t>
+        </is>
+      </c>
+      <c r="C749" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D749" t="inlineStr">
+        <is>
+          <t>brexhq</t>
+        </is>
+      </c>
+      <c r="E749" t="inlineStr">
+        <is>
+          <t>Mon Jul 27 18:11:28 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F749" t="inlineStr">
+        <is>
+          <t>@axrahman See you aboard.</t>
+        </is>
+      </c>
+      <c r="G749" t="inlineStr"/>
+      <c r="H749" t="inlineStr"/>
+      <c r="I749" t="inlineStr"/>
+      <c r="J749" t="inlineStr"/>
+      <c r="K749" t="inlineStr">
+        <is>
+          <t>https://x.com/brexHQ/status/2081804678241694049</t>
+        </is>
+      </c>
+      <c r="L749" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M749" t="inlineStr">
+        <is>
+          <t>Leadership Changes</t>
+        </is>
+      </c>
+      <c r="N749" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O749" t="inlineStr">
+        <is>
+          <t>Brex welcomes new team member @axrahman to the company.</t>
+        </is>
+      </c>
+    </row>
+    <row r="750">
+      <c r="A750" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B750" t="inlineStr">
+        <is>
+          <t>AirBnb</t>
+        </is>
+      </c>
+      <c r="C750" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D750" t="inlineStr">
+        <is>
+          <t>Airbnb</t>
+        </is>
+      </c>
+      <c r="E750" t="inlineStr">
+        <is>
+          <t>Tue Jul 28 10:05:08 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F750" t="inlineStr">
+        <is>
+          <t>@hash_jacques Hi, Jacques. Please DM us the email address associated with your Airbnb account, so we can take a closer look at this. Thanks. https://t.co/Ww9ryZnBBw</t>
+        </is>
+      </c>
+      <c r="G750" t="inlineStr"/>
+      <c r="H750" t="inlineStr"/>
+      <c r="I750" t="inlineStr"/>
+      <c r="J750" t="inlineStr"/>
+      <c r="K750" t="inlineStr">
+        <is>
+          <t>https://x.com/Airbnb/status/2082044678917021987</t>
+        </is>
+      </c>
+      <c r="L750" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M750" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N750" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O750" t="inlineStr">
+        <is>
+          <t>Airbnb is requesting a user to DM their email address for further investigation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="751">
+      <c r="A751" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B751" t="inlineStr">
+        <is>
+          <t>AirBnb</t>
+        </is>
+      </c>
+      <c r="C751" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D751" t="inlineStr">
+        <is>
+          <t>Airbnb</t>
+        </is>
+      </c>
+      <c r="E751" t="inlineStr">
+        <is>
+          <t>Tue Jul 28 00:50:05 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F751" t="inlineStr">
+        <is>
+          <t>Nos pensées vont aux victimes des incendies en France.
+https://t.co/AsDX3PLw0V s’associe avec la Mairie de Biscarosse, la Mairie de Pontenx-les-Forges et les mairies des dix municipalités de la Communauté de communes de Médullienne pour identifier les résidents déplacés ayant besoin d'un hébergement et leur trouver un lieu de séjour gratuit. Les résidents touchés par les incendies en Gironde et dans les Landes peuvent contacter leur mairie locale pour obtenir un soutien en matière de logement.
+https://t.co/AsDX3PLw0V travaille également avec la Fédération nationale des sapeurs-pompiers de France pour fournir un logement gratuit aux pompiers déployés pour lutter contre les incendies de Gironde.
+Restez au courant des activations d'https://t.co/AsDX3PLw0V en consultant le lien ci-dessous:
+https://t.co/cspKNIywBc</t>
+        </is>
+      </c>
+      <c r="G751" t="inlineStr"/>
+      <c r="H751" t="inlineStr"/>
+      <c r="I751" t="inlineStr"/>
+      <c r="J751" t="inlineStr"/>
+      <c r="K751" t="inlineStr">
+        <is>
+          <t>https://x.com/Airbnb/status/2081904994484461666</t>
+        </is>
+      </c>
+      <c r="L751" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M751" t="inlineStr">
+        <is>
+          <t>Partnership and Acquisitions</t>
+        </is>
+      </c>
+      <c r="N751" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O751" t="inlineStr">
+        <is>
+          <t>AirBnb is partnering with local municipalities and fire services in France to provide free accommodation for residents and firefighters displaced by recent fires.</t>
+        </is>
+      </c>
+    </row>
+    <row r="752">
+      <c r="A752" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B752" t="inlineStr">
+        <is>
+          <t>AirBnb</t>
+        </is>
+      </c>
+      <c r="C752" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D752" t="inlineStr">
+        <is>
+          <t>Airbnb</t>
+        </is>
+      </c>
+      <c r="E752" t="inlineStr">
+        <is>
+          <t>Tue Jul 28 00:50:03 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F752" t="inlineStr">
+        <is>
+          <t>As wildfires in France force people from their homes, our hearts go out to those affected.
+Our nonprofit, https://t.co/AsDX3PLw0V is working with Mairie de Biscarosse, Mairie de Pontenx-les-Forges, and the town halls of the ten municipalities in the Médullienne Community of Municipalities to identify displaced residents in need of shelter and connect them to a free place to stay. Residents affected by the fires in Gironde and Landes should contact their local town hall for housing support.
+https://t.co/AsDX3PLw0V is also working with Fédération nationale des sapeurs-pompiers de France to provide free housing to firefighters who have deployed to fight the Gironde fires.
+Stay up to date on https://t.co/AsDX3PLw0V’s response at the link below.
+https://t.co/cspKNIywBc</t>
+        </is>
+      </c>
+      <c r="G752" t="inlineStr"/>
+      <c r="H752" t="inlineStr"/>
+      <c r="I752" t="inlineStr"/>
+      <c r="J752" t="inlineStr"/>
+      <c r="K752" t="inlineStr">
+        <is>
+          <t>https://x.com/Airbnb/status/2081904988096487869</t>
+        </is>
+      </c>
+      <c r="L752" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M752" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N752" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O752" t="inlineStr">
+        <is>
+          <t>AirBnb highlights its nonprofit partner’s efforts to assist wildfire‑displaced residents in France by coordinating free housing and support with local authorities and firefighters.</t>
+        </is>
+      </c>
+    </row>
+    <row r="753">
+      <c r="A753" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B753" t="inlineStr">
+        <is>
+          <t>AirBnb</t>
+        </is>
+      </c>
+      <c r="C753" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D753" t="inlineStr">
+        <is>
+          <t>Airbnb.org</t>
+        </is>
+      </c>
+      <c r="E753" t="inlineStr">
+        <is>
+          <t>2026-07-27T19:16:56.694Z</t>
+        </is>
+      </c>
+      <c r="F753" t="inlineStr">
+        <is>
+          <t>As the wildfires in France force people from their homes, our hearts go out to those affected.
+Airbnb.org is working with Mairie de Biscarosse, Mairie de Pontenx-les-Forges, and the town halls of the ten municipalities in the Médullienne Community of Municipalities to identify displaced residents in need of shelter and connect them to a free place to stay. Residents affected by the fires in Gironde and Landes should contact their local town hall for housing support.
+Airbnb.org is also working with Fédération nationale des sapeurs-pompiers de France to provide free housing to firefighters who have deployed to fight the Gironde fires.
+Stay up to date on Airbnb.org’s response at the link below.
+airbnb.org/france
+---
+Nos pensées vont aux victimes des incendies en France. 
+Airbnb.org s’associe avec la Mairie de Biscarosse, la Mairie de Pontenx-les-Forges et les mairies des dix municipalités de la Communauté de communes de Médullienne pour identifier les résidents déplacés ayant besoin d'un hébergement et leur trouver un lieu de séjour gratuit. Les résidents touchés par les incendies en Gironde et dans les Landes peuvent contacter leur mairie locale pour obtenir un soutien en matière de logement.
+Airbnb.org travaille également avec la Fédération nationale des sapeurs-pompiers de France pour fournir un logement gratuit aux pompiers déployés pour lutter contre les incendies de Gironde.
+Restez au courant des activations d'Airbnb.org en consultant le lien ci-dessous:
+airbnb.org/france</t>
+        </is>
+      </c>
+      <c r="G753" t="inlineStr"/>
+      <c r="H753" t="inlineStr"/>
+      <c r="I753" t="inlineStr"/>
+      <c r="J753" t="inlineStr"/>
+      <c r="K753" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/airbnb-dot-org_airbnborg-is-providing-free-emergency-housing-ugcPost-7487582093766512651-D-9i</t>
+        </is>
+      </c>
+      <c r="L753" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M753" t="inlineStr">
+        <is>
+          <t>Partnership and Acquisitions</t>
+        </is>
+      </c>
+      <c r="N753" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O753" t="inlineStr">
+        <is>
+          <t>Airbnb.org is partnering with French local governments and fire services to provide free housing for residents and firefighters displaced by wildfires in Gironde and Landes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="754">
+      <c r="A754" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B754" t="inlineStr">
+        <is>
+          <t>Expedia</t>
+        </is>
+      </c>
+      <c r="C754" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D754" t="inlineStr">
+        <is>
+          <t>Expedia</t>
+        </is>
+      </c>
+      <c r="E754" t="inlineStr">
+        <is>
+          <t>Tue Jul 28 00:00:00 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F754" t="inlineStr">
+        <is>
+          <t>Think California camping means roughing it in a crowded lot? 🌲
+➡️ Railroad Park Resort: Sleep inside a restored vintage train caboose at the base of Mount Shasta
+➡️ Treebones Resort: Swap the sleeping bag for a coastal yurt perched on the cliffs of Big Sur
+➡️ Pioneertown: Stay off-grid in a retro Airstream under the dark skies of Joshua Tree
+🔗 Plan your travel:https://t.co/wKMbuqzi9E</t>
+        </is>
+      </c>
+      <c r="G754" t="inlineStr"/>
+      <c r="H754" t="inlineStr"/>
+      <c r="I754" t="inlineStr"/>
+      <c r="J754" t="inlineStr"/>
+      <c r="K754" t="inlineStr">
+        <is>
+          <t>https://x.com/Expedia/status/2081892392240623903</t>
+        </is>
+      </c>
+      <c r="L754" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M754" t="inlineStr">
+        <is>
+          <t>Product Announcement</t>
+        </is>
+      </c>
+      <c r="N754" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O754" t="inlineStr">
+        <is>
+          <t>Expedia showcases unique California camping options—vintage train caboose, coastal yurt, and off‑grid Airstream—promoting a fresh, adventurous travel experience.</t>
+        </is>
+      </c>
+    </row>
+    <row r="755">
+      <c r="A755" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B755" t="inlineStr">
+        <is>
+          <t>Expedia</t>
+        </is>
+      </c>
+      <c r="C755" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="D755" t="inlineStr">
+        <is>
+          <t>expedia</t>
+        </is>
+      </c>
+      <c r="E755" t="inlineStr">
+        <is>
+          <t>2026-07-28T11:00:04.000Z</t>
+        </is>
+      </c>
+      <c r="F755" t="inlineStr">
+        <is>
+          <t>Liverpool FC's Virgil van Dijk made himself at home in the Middle Seat. Here's how he travels with Expedia.</t>
+        </is>
+      </c>
+      <c r="G755" t="inlineStr">
+        <is>
+          <t>https://scontent-yyz1-1.cdninstagram.com/v/t51.82787-15/756045871_18618620575030381_4295081915458705396_n.jpg?stp=dst-jpg_e15_fr_p1080x1080_tt6&amp;_nc_ht=scontent-yyz1-1.cdninstagram.com&amp;_nc_cat=1&amp;_nc_oc=Q6cZ2gHaBYLBEh2NfGMcAgnge0LfsOyCn0oBJSBadXeETKb1cyv_4rOQpS8vAXT447vcFOQ&amp;_nc_ohc=ovHTn4wFEl0Q7kNvwGbUA4D&amp;_nc_gid=ohBtsXM7pN3VIWwyZImVaw&amp;edm=ADp7STQBAAAA&amp;ccb=7-5&amp;oh=00_AQBtyEX74pIATz2kOYOg9-KbEz2tyXk3op6JAaBDEL9zNA&amp;oe=6A6ED995&amp;_nc_sid=c6f216</t>
+        </is>
+      </c>
+      <c r="H755" t="inlineStr">
+        <is>
+          <t>[easyocr not installed. Run 'pip install easyocr torch torchvision']</t>
+        </is>
+      </c>
+      <c r="I755" t="inlineStr">
+        <is>
+          <t>https://scontent-yyz1-1.cdninstagram.com/o1/v/t2/f2/m86/AQNR3jGi93NuCPb0xgLRXrODTnmy4LnsVwNakZw5cWTxYH4r9Yz87i2GLsmt4B7aDqK7DP4z7ZJ93A_6EygtvEsk7Xafb03envsMnks.mp4?_nc_cat=106&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-yyz1-1.cdninstagram.com&amp;_nc_ohc=MpiUsb4w8UgQ7kNvwF65LZQ&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uQ0xJUFMuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTg2MTg0MzA3MzgwMzAzODEsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDA5OSwiZHVyYXRpb25fcyI6MjksInVybGdlbl9zb3VyY2UiOiJ3d3cifQ%3D%3D&amp;ccb=17-1&amp;vs=2621f300d1a4f23&amp;_nc_vs=HBksFQIYUmlnX3hwdl9yZWVsc19wZXJtYW5lbnRfc3JfcHJvZC9EOTQxMkIwQ0JFMkREOUY2NTBCNTMyNDAwOUU4M0I5RV92aWRlb19kYXNoaW5pdC5tcDQVAALIARIAFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyL0JBNDk1QkE5RjRGQTczQjBCQTA3MzYyMjBFNkU2OTkyX2F1ZGlvX2Rhc2hpbml0Lm1wNBUCAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACba_NLmpteSQhUCKAJDMywXQD1R64UeuFIYEmRhc2hfYmFzZWxpbmVfMV92MREAdf4HZeadAQA&amp;_nc_gid=ohBtsXM7pN3VIWwyZImVaw&amp;_nc_ss=7a22e&amp;_nc_zt=28&amp;oh=00_AQAmyc1S0McxUDiy8GIxQ6qWKv53EgEcuucXgBTrbvlm-Q&amp;oe=6A6ACD93</t>
+        </is>
+      </c>
+      <c r="J755" t="inlineStr">
+        <is>
+          <t>[faster-whisper not installed. Run 'pip install faster-whisper']</t>
+        </is>
+      </c>
+      <c r="K755" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DbTr-nZglxu/</t>
+        </is>
+      </c>
+      <c r="L755" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M755" t="inlineStr">
+        <is>
+          <t>Partnership and Acquisitions</t>
+        </is>
+      </c>
+      <c r="N755" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O755" t="inlineStr">
+        <is>
+          <t>Expedia partners with Liverpool FC star Virgil van Dijk to highlight travel experiences, showcasing a new endorsement partnership.</t>
+        </is>
+      </c>
+    </row>
+    <row r="756">
+      <c r="A756" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B756" t="inlineStr">
+        <is>
+          <t>Expedia</t>
+        </is>
+      </c>
+      <c r="C756" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D756" t="inlineStr">
+        <is>
+          <t>Expedia</t>
+        </is>
+      </c>
+      <c r="E756" t="inlineStr">
+        <is>
+          <t>2026-07-28T07:48:25.912Z</t>
+        </is>
+      </c>
+      <c r="F756" t="inlineStr">
+        <is>
+          <t>Twenty years ago, Expedia entered Japan with a simple ambition: to make travel more accessible, inspiring, and rewarding for every traveler.  
+Since 2006, millions of Japanese travelers have explored the world with confidence, from family holidays in Hawai'i and city breaks in Seoul to beach escapes across Southeast Asia and discoveries closer to home throughout Japan.  
+As we celebrate 20 years in Japan, we also celebrate the journeys, memories, our partnerships and experiences that travel has made possible.  
+20 years. Millions of travelers. Countless adventures.  
+To our travelers in Japan, arigatou gozaimasu.  
+Swipe through to see the story of Expedia in Japan.  🇯🇵
+ --------------------------------------------------
+20年前、エクスペディアは「旅をもっと身近で、もっと充実したものにしたい」という想いを胸に、日本でサービスを開始しました。  
+以来、多くの日本の旅行者の皆さまにご利用いただき、ハワイでの家族旅行、ソウルへの週末旅行、東南アジアのビーチリゾートでの滞在、そして日本各地を巡る旅など、数えきれないほどの旅の思い出づくりをお手伝いしてきました。  
+日本で20周年を迎えた今、私たちは旅を通じて生まれた数々の思い出や体験、そしてともに歩んできたパートナーの皆さまとのつながりに、改めて感謝しています。  
+これからも、日本の旅行者の皆さまの旅に寄り添いながら、新たな旅の可能性をお届けしてまいります。</t>
+        </is>
+      </c>
+      <c r="G756" t="inlineStr"/>
+      <c r="H756" t="inlineStr"/>
+      <c r="I756" t="inlineStr"/>
+      <c r="J756" t="inlineStr"/>
+      <c r="K756" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/expedia_20-year-anniversary-activity-7487775963766910976-GjIV</t>
+        </is>
+      </c>
+      <c r="L756" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M756" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N756" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O756" t="inlineStr">
+        <is>
+          <t>Expedia marks its 20th anniversary in Japan, celebrating millions of travelers, partnerships, and the company’s impact on the Japanese travel market.</t>
+        </is>
+      </c>
+    </row>
+    <row r="757">
+      <c r="A757" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B757" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C757" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D757" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E757" t="inlineStr">
+        <is>
+          <t>Tue Jul 28 14:17:36 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F757" t="inlineStr">
+        <is>
+          <t>Hola de nuevo Grecia. Nos apena mucho saberlo. Como te explicamos anteriormente, lamentablemente desde sociales no podemos ofrecer asistencia con reservas de Vuelos, pero te aconsejamos contactar con nuestro equipo de Vuelos aquí: https://t.co/TBejpc4vOA, o llamar al +34918362949 desde España de lunes a domingo de 9:00-21:00 hora local. Un saludo.</t>
+        </is>
+      </c>
+      <c r="G757" t="inlineStr"/>
+      <c r="H757" t="inlineStr"/>
+      <c r="I757" t="inlineStr"/>
+      <c r="J757" t="inlineStr"/>
+      <c r="K757" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2082108215395815892</t>
+        </is>
+      </c>
+      <c r="L757" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M757" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N757" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O757" t="inlineStr">
+        <is>
+          <t>Booking.com apologizes for not being able to assist with flight reservations and directs the user to contact their flight team via provided link or phone number.</t>
+        </is>
+      </c>
+    </row>
+    <row r="758">
+      <c r="A758" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B758" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C758" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D758" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E758" t="inlineStr">
+        <is>
+          <t>Tue Jul 28 14:00:28 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F758" t="inlineStr">
+        <is>
+          <t>@anapaulafigs Hi Ana Paula, we regret to learn that you haven't received the support you were expecting from our side. We can only advise you to reach out to our dedicated team through the contacts shared in our previous communication. 
+Warm regards</t>
+        </is>
+      </c>
+      <c r="G758" t="inlineStr"/>
+      <c r="H758" t="inlineStr"/>
+      <c r="I758" t="inlineStr"/>
+      <c r="J758" t="inlineStr"/>
+      <c r="K758" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2082103903668048055</t>
+        </is>
+      </c>
+      <c r="L758" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="M758" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N758" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O758" t="inlineStr">
+        <is>
+          <t>Booking.com apologizes to a user for not receiving expected support and directs them to contact the dedicated team.</t>
+        </is>
+      </c>
+    </row>
+    <row r="759">
+      <c r="A759" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B759" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C759" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D759" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E759" t="inlineStr">
+        <is>
+          <t>Tue Jul 28 13:56:12 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F759" t="inlineStr">
+        <is>
+          <t>@LuizaVilaa7wqv Bom dia Luiza, sentimos saber da sua dificuldade para falar conosco; acabamos de responder sua DM, pedimos que verifique e nos retorne por lá também.</t>
+        </is>
+      </c>
+      <c r="G759" t="inlineStr"/>
+      <c r="H759" t="inlineStr"/>
+      <c r="I759" t="inlineStr"/>
+      <c r="J759" t="inlineStr"/>
+      <c r="K759" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2082102826688229712</t>
+        </is>
+      </c>
+      <c r="L759" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M759" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N759" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O759" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a user’s complaint via DM, apologizing for communication difficulties and directing them to check the DM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="760">
+      <c r="A760" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B760" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C760" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D760" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E760" t="inlineStr">
+        <is>
+          <t>Tue Jul 28 13:51:09 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F760" t="inlineStr">
+        <is>
+          <t>We understand the urgency of the matter, Ana Paula. 
+While we appreciate that you have reached out to us here, we are, unfortunately, unable to help via Social Media. Your inquiry can only be addressed directly with our specialized team at the previously shared details.  
+Best regards</t>
+        </is>
+      </c>
+      <c r="G760" t="inlineStr"/>
+      <c r="H760" t="inlineStr"/>
+      <c r="I760" t="inlineStr"/>
+      <c r="J760" t="inlineStr"/>
+      <c r="K760" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2082101557277982865</t>
+        </is>
+      </c>
+      <c r="L760" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M760" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N760" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O760" t="inlineStr">
+        <is>
+          <t>Booking.com replies to a user on X, explaining that the inquiry cannot be handled via social media and directing the user to a specialized team for assistance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="761">
+      <c r="A761" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B761" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C761" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D761" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E761" t="inlineStr">
+        <is>
+          <t>Tue Jul 28 13:43:48 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F761" t="inlineStr">
+        <is>
+          <t>HI there, we regret to hear that you did not reach our Customer Service Team yet. For us to be able to assist you furthjer, we kindly ask you to DM us the following booking details: 
+- Confirmation Number
+- Pin Code
+- Name of the Guest 
+We'll than get back to you as soon as possible.</t>
+        </is>
+      </c>
+      <c r="G761" t="inlineStr"/>
+      <c r="H761" t="inlineStr"/>
+      <c r="I761" t="inlineStr"/>
+      <c r="J761" t="inlineStr"/>
+      <c r="K761" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2082099708432970103</t>
+        </is>
+      </c>
+      <c r="L761" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="M761" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N761" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O761" t="inlineStr">
+        <is>
+          <t>Booking.com apologizes for a customer not reaching their service team and requests booking details via DM for assistance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="762">
+      <c r="A762" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B762" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C762" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D762" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E762" t="inlineStr">
+        <is>
+          <t>Tue Jul 28 13:03:20 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F762" t="inlineStr">
+        <is>
+          <t>Hola Grecia, lamentamos escuchar que esta ha sido tu experiencia. 
+Aunque nos gustaría asistir, en redes sociales tenemos acceso únicamente para reservas de alojamiento. En el siguiente enlace encontrarás la información de contacto de nuestro equipo de atención al cliente para reservas de vuelo: https://t.co/0VBK0krD8X
+Un saludo.</t>
+        </is>
+      </c>
+      <c r="G762" t="inlineStr"/>
+      <c r="H762" t="inlineStr"/>
+      <c r="I762" t="inlineStr"/>
+      <c r="J762" t="inlineStr"/>
+      <c r="K762" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2082089523635163473</t>
+        </is>
+      </c>
+      <c r="L762" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="M762" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N762" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O762" t="inlineStr">
+        <is>
+          <t>Booking.com apologizes to a customer for a negative experience and explains that social media support is limited to accommodation bookings, directing the user to a link for flight reservation assistance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="763">
+      <c r="A763" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B763" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C763" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D763" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E763" t="inlineStr">
+        <is>
+          <t>Tue Jul 28 12:54:51 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F763" t="inlineStr">
+        <is>
+          <t>Hi Jo.
+Thanks for your message, apologies for the delayed reply.
+The prices are set up and managed by the accommodations. Usually they are the same compared to hotel's own websites.
+If you have a booking through us and do see a better price somewhere else, you can submit a price match claim (https://t.co/apVEDSKlom). Then we will pay out the difference in credits after your stay, provided your claims fulfills the conditions of our offer. 
+If you have a price match claim, you can contact us here.
+We wish you a nice day.</t>
+        </is>
+      </c>
+      <c r="G763" t="inlineStr"/>
+      <c r="H763" t="inlineStr"/>
+      <c r="I763" t="inlineStr"/>
+      <c r="J763" t="inlineStr"/>
+      <c r="K763" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2082087386960281853</t>
+        </is>
+      </c>
+      <c r="L763" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M763" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N763" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O763" t="inlineStr">
+        <is>
+          <t>Booking.com clarifies its price‑match policy to a customer, encouraging users to submit a claim if they find a lower price elsewhere.</t>
+        </is>
+      </c>
+    </row>
+    <row r="764">
+      <c r="A764" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B764" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C764" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D764" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E764" t="inlineStr">
+        <is>
+          <t>Tue Jul 28 12:49:19 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F764" t="inlineStr">
+        <is>
+          <t>@xinwei_w Hi there, thanks for reaching out. We're here to help, feel free to send us a DM with more information regarding your request and we'll take a look together. https://t.co/Z89AAoEgD7</t>
+        </is>
+      </c>
+      <c r="G764" t="inlineStr"/>
+      <c r="H764" t="inlineStr"/>
+      <c r="I764" t="inlineStr"/>
+      <c r="J764" t="inlineStr"/>
+      <c r="K764" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2082085997869674776</t>
+        </is>
+      </c>
+      <c r="L764" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M764" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N764" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O764" t="inlineStr">
+        <is>
+          <t>Booking.com replied to a user on X, offering assistance via direct message.</t>
+        </is>
+      </c>
+    </row>
+    <row r="765">
+      <c r="A765" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B765" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C765" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D765" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E765" t="inlineStr">
+        <is>
+          <t>Tue Jul 28 12:44:09 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F765" t="inlineStr">
+        <is>
+          <t>Hi there Cor, we offered to assist you; however, we cannot do that without you DM'ing us the reservation details. We are a separate team from the customer service one, so we cannot access a booking without having its details. As mentioned, if you want us to take a look at your booking, send us the details via DM.</t>
+        </is>
+      </c>
+      <c r="G765" t="inlineStr"/>
+      <c r="H765" t="inlineStr"/>
+      <c r="I765" t="inlineStr"/>
+      <c r="J765" t="inlineStr"/>
+      <c r="K765" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2082084697195090006</t>
+        </is>
+      </c>
+      <c r="L765" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M765" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N765" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O765" t="inlineStr">
+        <is>
+          <t>Booking.com explains that its customer service team cannot access bookings without reservation details, and requests users to DM the details for assistance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="766">
+      <c r="A766" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B766" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C766" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D766" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E766" t="inlineStr">
+        <is>
+          <t>Tue Jul 28 12:38:21 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F766" t="inlineStr">
+        <is>
+          <t>Hello Cor, regrettably, we cannot provide assistance through public replies due to privacy and security concerns. Sharing your booking information publicly allows everyone to access it, including your booking details. Additionally, we are prohibited from disclosing booking related information in public replies due to GDPR regulations. If you decide to share your booking details with us, please send us a direct message with the requested information. Otherwise, you can contact our customer service team at any time using this number: https://t.co/o8QyR8SaDb.</t>
+        </is>
+      </c>
+      <c r="G766" t="inlineStr"/>
+      <c r="H766" t="inlineStr"/>
+      <c r="I766" t="inlineStr"/>
+      <c r="J766" t="inlineStr"/>
+      <c r="K766" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2082083235668938878</t>
+        </is>
+      </c>
+      <c r="L766" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M766" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N766" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O766" t="inlineStr">
+        <is>
+          <t>Booking.com informs a user that it cannot share booking details publicly due to privacy and GDPR concerns, directing them to send a direct message or contact customer service.</t>
+        </is>
+      </c>
+    </row>
+    <row r="767">
+      <c r="A767" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B767" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C767" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D767" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E767" t="inlineStr">
+        <is>
+          <t>Tue Jul 28 12:35:38 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F767" t="inlineStr">
+        <is>
+          <t>@anapaulafigs Hi there, we're unable to assist with Flight reservations through social media, but if you need support, you can contact our Flights team using this link: https://t.co/Z8ou85LCWJ, or call US +1 917 421 7240 / UK +44 2039019061 / IE +353 19075677</t>
+        </is>
+      </c>
+      <c r="G767" t="inlineStr"/>
+      <c r="H767" t="inlineStr"/>
+      <c r="I767" t="inlineStr"/>
+      <c r="J767" t="inlineStr"/>
+      <c r="K767" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2082082551473041721</t>
+        </is>
+      </c>
+      <c r="L767" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M767" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N767" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O767" t="inlineStr">
+        <is>
+          <t>Booking.com informs users that flight reservations cannot be handled via social media and directs them to contact the Flights team via a link or phone.</t>
+        </is>
+      </c>
+    </row>
+    <row r="768">
+      <c r="A768" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B768" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C768" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D768" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E768" t="inlineStr">
+        <is>
+          <t>Tue Jul 28 12:31:17 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F768" t="inlineStr">
+        <is>
+          <t>@duygucandemirr We have responded to your message. Check your DM.</t>
+        </is>
+      </c>
+      <c r="G768" t="inlineStr"/>
+      <c r="H768" t="inlineStr"/>
+      <c r="I768" t="inlineStr"/>
+      <c r="J768" t="inlineStr"/>
+      <c r="K768" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2082081456315150516</t>
+        </is>
+      </c>
+      <c r="L768" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M768" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N768" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O768" t="inlineStr">
+        <is>
+          <t>Booking.com responded to a user’s inquiry, directing them to check their direct messages.</t>
+        </is>
+      </c>
+    </row>
+    <row r="769">
+      <c r="A769" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B769" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C769" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D769" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E769" t="inlineStr">
+        <is>
+          <t>Tue Jul 28 12:31:02 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F769" t="inlineStr">
+        <is>
+          <t>Hello Cor, thank you for contacting us and happy birthday to your partner! Please send us a direct message with the following booking information so we can investigate the issue and see how we can assist you: 
+- Confirmation number: 
+- Pin code: 
+- Name on the reservation: 
+- Details regarding your request:</t>
+        </is>
+      </c>
+      <c r="G769" t="inlineStr"/>
+      <c r="H769" t="inlineStr"/>
+      <c r="I769" t="inlineStr"/>
+      <c r="J769" t="inlineStr"/>
+      <c r="K769" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2082081395917119724</t>
+        </is>
+      </c>
+      <c r="L769" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M769" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N769" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O769" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a customer inquiry, requesting booking details to investigate an issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="770">
+      <c r="A770" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B770" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C770" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D770" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E770" t="inlineStr">
+        <is>
+          <t>Tue Jul 28 12:13:03 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F770" t="inlineStr">
+        <is>
+          <t>Hi Eric, we regret to hear about the situation you've described. As much as we'd like to help, unfortunately, we're unable to assist with flight reservations through social media, but you can contact our Flights team here: https://t.co/TBejpc4vOA, or call {US}+1 917 421 7240 / {UK}+44 2039019061 / {IE} +353 19075677. Best regards.</t>
+        </is>
+      </c>
+      <c r="G770" t="inlineStr"/>
+      <c r="H770" t="inlineStr"/>
+      <c r="I770" t="inlineStr"/>
+      <c r="J770" t="inlineStr"/>
+      <c r="K770" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2082076868220493988</t>
+        </is>
+      </c>
+      <c r="L770" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M770" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N770" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O770" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a user’s inquiry about flight reservations, directing them to the Flights team and providing contact information.</t>
+        </is>
+      </c>
+    </row>
+    <row r="771">
+      <c r="A771" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B771" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C771" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D771" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E771" t="inlineStr">
+        <is>
+          <t>Tue Jul 28 11:54:15 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F771" t="inlineStr">
+        <is>
+          <t>Hi there, thank you for contacting us in regards to your Car Rental reservation.
+In order for us to assist, please send us a private message with the following details:
+Booking number:
+Name of booker:
+Email address used to book:
+Your request:
+We'll get back to you as soon as we can. 
+{USE FOR WEEKENDS ONLY} If you need urgent assistance, feel free to reach out to our specialized team here: https://t.co/NT3GBtSRDt.</t>
+        </is>
+      </c>
+      <c r="G771" t="inlineStr"/>
+      <c r="H771" t="inlineStr"/>
+      <c r="I771" t="inlineStr"/>
+      <c r="J771" t="inlineStr"/>
+      <c r="K771" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2082072139293708519</t>
+        </is>
+      </c>
+      <c r="L771" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M771" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N771" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O771" t="inlineStr">
+        <is>
+          <t>Booking.com posted a standard customer service response for car rental reservations, outlining steps for contacting support and providing a link for urgent assistance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="772">
+      <c r="A772" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B772" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C772" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D772" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E772" t="inlineStr">
+        <is>
+          <t>Tue Jul 28 11:52:32 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F772" t="inlineStr">
+        <is>
+          <t>@ahmed3gaber Hi there, thank you for contacting us in regards to your Car Rental reservation.
+In order for us to assist, please DM us the following details:
+- Booking number
+- Name of booker
+- Email address used to book
+- Your request
+We'll get back to you as soon as we can. Thank you.</t>
+        </is>
+      </c>
+      <c r="G772" t="inlineStr"/>
+      <c r="H772" t="inlineStr"/>
+      <c r="I772" t="inlineStr"/>
+      <c r="J772" t="inlineStr"/>
+      <c r="K772" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2082071704621207772</t>
+        </is>
+      </c>
+      <c r="L772" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M772" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N772" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O772" t="inlineStr">
+        <is>
+          <t>Booking.com is replying to a user’s inquiry about a car rental reservation, asking for booking details via direct message.</t>
+        </is>
+      </c>
+    </row>
+    <row r="773">
+      <c r="A773" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B773" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C773" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D773" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E773" t="inlineStr">
+        <is>
+          <t>Tue Jul 28 11:51:40 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F773" t="inlineStr">
+        <is>
+          <t>@Mlaura11491816 Hi there,
+We regret to hear that you are unable to get in touch with our customer service. If you prefer immediate support, we would suggest you to contact our 24/7 support line right here https://t.co/Qy2GsKgQuC. https://t.co/Z89AAoEgD7</t>
+        </is>
+      </c>
+      <c r="G773" t="inlineStr"/>
+      <c r="H773" t="inlineStr"/>
+      <c r="I773" t="inlineStr"/>
+      <c r="J773" t="inlineStr"/>
+      <c r="K773" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2082071488618750383</t>
+        </is>
+      </c>
+      <c r="L773" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="M773" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N773" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O773" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a user complaint about difficulty reaching customer service, offering a 24/7 support line.</t>
+        </is>
+      </c>
+    </row>
+    <row r="774">
+      <c r="A774" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B774" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C774" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D774" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E774" t="inlineStr">
+        <is>
+          <t>Tue Jul 28 11:48:27 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F774" t="inlineStr">
+        <is>
+          <t>Hi there,
+We regret to hear that you were not able to resolve your issue with a booking cancellation. Please note a refund will only be possible if the accommodation agrees to make an exception and send us a confirmation of this. We'd be happy to look into this further for you. To do so, please send us the following details in a DM, and we'll get back to you as soon as possible;
+- Confirmation number
+- PIN code
+- Name on the reservation</t>
+        </is>
+      </c>
+      <c r="G774" t="inlineStr"/>
+      <c r="H774" t="inlineStr"/>
+      <c r="I774" t="inlineStr"/>
+      <c r="J774" t="inlineStr"/>
+      <c r="K774" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2082070678035919151</t>
+        </is>
+      </c>
+      <c r="L774" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M774" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N774" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O774" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a customer complaint about a booking cancellation, explaining refund conditions and requesting details via DM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="775">
+      <c r="A775" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B775" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C775" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D775" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E775" t="inlineStr">
+        <is>
+          <t>Tue Jul 28 11:42:42 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F775" t="inlineStr">
+        <is>
+          <t>@nutwinvw Hello Nutwin, if you require assistance with a booking, please send us a direct message containing the following details so we can review it and determine how we can assist you: 
+- Confirmation number: 
+- Pin code: 
+- Name on the reservation: 
+- Details regarding your request: https://t.co/Z89AAoEgD7</t>
+        </is>
+      </c>
+      <c r="G775" t="inlineStr"/>
+      <c r="H775" t="inlineStr"/>
+      <c r="I775" t="inlineStr"/>
+      <c r="J775" t="inlineStr"/>
+      <c r="K775" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2082069231483404488</t>
+        </is>
+      </c>
+      <c r="L775" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M775" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N775" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O775" t="inlineStr">
+        <is>
+          <t>Booking.com is offering direct booking assistance to a user, requesting confirmation details via direct message.</t>
+        </is>
+      </c>
+    </row>
+    <row r="776">
+      <c r="A776" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B776" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C776" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D776" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E776" t="inlineStr">
+        <is>
+          <t>Tue Jul 28 11:32:32 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F776" t="inlineStr">
+        <is>
+          <t>Hello there, we regret to hear you've had this experience with your booking. In these situations, we advise you to phone our customer care team as soon as you can so we can do our best to minimize any inconveniences.
+However, we will be happy to take a look at your booking and see if there is anything we can do to help. 
+Please DM us the following details:
+- confirmation number
+- pin code
+- guest name
+We will get back to you as soon as we can. For immediate assistance, please contact our support line at  https://t.co/tuuNbmGVaG. Kind regards.</t>
+        </is>
+      </c>
+      <c r="G776" t="inlineStr"/>
+      <c r="H776" t="inlineStr"/>
+      <c r="I776" t="inlineStr"/>
+      <c r="J776" t="inlineStr"/>
+      <c r="K776" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2082066672119148887</t>
+        </is>
+      </c>
+      <c r="L776" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M776" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N776" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O776" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a customer complaint, offering assistance and providing contact details for further support.</t>
+        </is>
+      </c>
+    </row>
+    <row r="777">
+      <c r="A777" t="inlineStr">
+        <is>
+          <t>Mondee</t>
+        </is>
+      </c>
+      <c r="B777" t="inlineStr">
+        <is>
+          <t>Sky Bird Travel</t>
+        </is>
+      </c>
+      <c r="C777" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D777" t="inlineStr">
+        <is>
+          <t>SkyBirdTravel</t>
+        </is>
+      </c>
+      <c r="E777" t="inlineStr">
+        <is>
+          <t>Mon Jul 27 18:48:59 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F777" t="inlineStr">
+        <is>
+          <t>From boutique gems to 5⭐ luxury, WINGS gives your clients more choices &amp;amp; you earn 15% commission on pre-paid hotels. Book smarter, earn more! 
+https://t.co/ctFwiJyiud #TravelAdvisor #HotelBookings #LuxuryTravel #BoutiqueHotels #EarnMore #WINGS https://t.co/StNTZjZIn3</t>
+        </is>
+      </c>
+      <c r="G777" t="inlineStr"/>
+      <c r="H777" t="inlineStr"/>
+      <c r="I777" t="inlineStr"/>
+      <c r="J777" t="inlineStr"/>
+      <c r="K777" t="inlineStr">
+        <is>
+          <t>https://x.com/SkyBirdTravel/status/2081814122254254144</t>
+        </is>
+      </c>
+      <c r="L777" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M777" t="inlineStr">
+        <is>
+          <t>Product Announcement</t>
+        </is>
+      </c>
+      <c r="N777" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O777" t="inlineStr">
+        <is>
+          <t>Sky Bird Travel promotes its new WINGS platform, offering clients a range of boutique to luxury hotel options and a 15% commission on pre-paid bookings.</t>
+        </is>
+      </c>
+    </row>
+    <row r="778">
+      <c r="A778" t="inlineStr">
+        <is>
+          <t>Mondee</t>
+        </is>
+      </c>
+      <c r="B778" t="inlineStr">
+        <is>
+          <t>Sky Bird Travel</t>
+        </is>
+      </c>
+      <c r="C778" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D778" t="inlineStr">
+        <is>
+          <t>Sky Bird Travel &amp; Tours</t>
+        </is>
+      </c>
+      <c r="E778" t="inlineStr">
+        <is>
+          <t>2026-07-27T18:47:59.899Z</t>
+        </is>
+      </c>
+      <c r="F778" t="inlineStr">
+        <is>
+          <t>From boutique gems to five-star luxury, finding the perfect stay has never been easier. Give your clients access to accommodations that fit every travel style while earning 15% commission on pre-paid hotels. More choices for your travelers, more opportunities for your business. 
+Book your next hotel reservation on WINGS today.  https://bit.ly/4ahXS0u 
+#TravelAdvisor #TravelAgents #HotelBookings #LuxuryTravel #BoutiqueHotels #TravelProfessionals #EarnMore #WINGS #SkyBirdTravel #TravelIndustry</t>
+        </is>
+      </c>
+      <c r="G778" t="inlineStr">
+        <is>
+          <t>https://media.licdn.com/dms/image/v2/D5622AQHkMRH657WYVw/feedshare-shrink_1280/B56Z.k57r1JgAM-/0/1785178078862?e=1786579200&amp;v=beta&amp;t=aAPFNFjv1NmEOaUkZQd_G7En8y-LGO9wgLRnmQHlNvY</t>
+        </is>
+      </c>
+      <c r="H778" t="inlineStr">
+        <is>
+          <t>[easyocr not installed. Run 'pip install easyocr torch torchvision']</t>
+        </is>
+      </c>
+      <c r="I778" t="inlineStr"/>
+      <c r="J778" t="inlineStr"/>
+      <c r="K778" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/sky-bird-travel-tours_traveladvisor-travelagents-hotelbookings-activity-7487579561233235968-lMTC</t>
+        </is>
+      </c>
+      <c r="L778" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M778" t="inlineStr">
+        <is>
+          <t>Product Announcement</t>
+        </is>
+      </c>
+      <c r="N778" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O778" t="inlineStr">
+        <is>
+          <t>Sky Bird Travel promotes its WINGS platform, offering travel agents a 15% commission on pre‑paid hotel bookings across a wide range of accommodations, from boutique to luxury.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/News_Dashboard/data/social_media_posts.xlsx
+++ b/News_Dashboard/data/social_media_posts.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O778"/>
+  <dimension ref="A1:O807"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -49779,6 +49779,1866 @@
         </is>
       </c>
     </row>
+    <row r="779">
+      <c r="A779" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B779" t="inlineStr">
+        <is>
+          <t>Navan</t>
+        </is>
+      </c>
+      <c r="C779" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D779" t="inlineStr">
+        <is>
+          <t>navan</t>
+        </is>
+      </c>
+      <c r="E779" t="inlineStr">
+        <is>
+          <t>Tue Jul 28 18:51:13 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F779" t="inlineStr">
+        <is>
+          <t>Watch: https://t.co/wzJ7DIVDBZ</t>
+        </is>
+      </c>
+      <c r="G779" t="inlineStr"/>
+      <c r="H779" t="inlineStr"/>
+      <c r="I779" t="inlineStr"/>
+      <c r="J779" t="inlineStr"/>
+      <c r="K779" t="inlineStr">
+        <is>
+          <t>https://x.com/Navan/status/2082177073431404924</t>
+        </is>
+      </c>
+      <c r="L779" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M779" t="inlineStr">
+        <is>
+          <t>Product Announcement</t>
+        </is>
+      </c>
+      <c r="N779" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O779" t="inlineStr">
+        <is>
+          <t>Navan shares a video highlighting a new product feature or update, indicating ongoing innovation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="780">
+      <c r="A780" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B780" t="inlineStr">
+        <is>
+          <t>Navan</t>
+        </is>
+      </c>
+      <c r="C780" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D780" t="inlineStr">
+        <is>
+          <t>navan</t>
+        </is>
+      </c>
+      <c r="E780" t="inlineStr">
+        <is>
+          <t>Tue Jul 28 18:51:01 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F780" t="inlineStr">
+        <is>
+          <t>AI when it’s faster. A human when things get complicated. No repeating yourself either way ✈️
+Navan CEO and co-founder @arielcoco joined @AnnBerry_NYC on @brewmarkets to explain how we make the handoff seamless. https://t.co/HaXzhjMfa2</t>
+        </is>
+      </c>
+      <c r="G780" t="inlineStr"/>
+      <c r="H780" t="inlineStr"/>
+      <c r="I780" t="inlineStr"/>
+      <c r="J780" t="inlineStr"/>
+      <c r="K780" t="inlineStr">
+        <is>
+          <t>https://x.com/Navan/status/2082177021082259566</t>
+        </is>
+      </c>
+      <c r="L780" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M780" t="inlineStr">
+        <is>
+          <t>Tech Updates</t>
+        </is>
+      </c>
+      <c r="N780" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O780" t="inlineStr">
+        <is>
+          <t>Navan showcases its AI‑human hybrid approach and seamless handoff in a recent interview with CEO Ariel Coco on BrewMarkets, emphasizing speed and human nuance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="781">
+      <c r="A781" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B781" t="inlineStr">
+        <is>
+          <t>Navan</t>
+        </is>
+      </c>
+      <c r="C781" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D781" t="inlineStr">
+        <is>
+          <t>Navan</t>
+        </is>
+      </c>
+      <c r="E781" t="inlineStr">
+        <is>
+          <t>2026-07-29T17:26:02.652Z</t>
+        </is>
+      </c>
+      <c r="F781" t="inlineStr">
+        <is>
+          <t>Your Navan x GBTA | Global Business Travel Association itinerary, mapped.
+There are so many ways to connect with us, face-to-face, all GBTA long. Here's what you need to know:
+🪩 Party @ Adler Planetarium
+→ 8/3: 7:30pm - 11:30pm
+🧠 The Giant Brain
+401 N Michigan Ave
+→ 8/3: 8am – 5:45pm
+→ 8/4: 8am – 6:15pm
+→ 8/5: 8am – 4:45pm
+👥💬 Lounge &amp; Executive Meeting Room Hours
+→ 8/3: 8am – 5:45pm
+→ 8/4: 8am – 6:15pm
+→ 8/5: 8am – 4:45pm
+See you in Chicago.</t>
+        </is>
+      </c>
+      <c r="G781" t="inlineStr">
+        <is>
+          <t>https://media.licdn.com/dms/image/v2/D4E22AQHupy3HC9g5tA/feedshare-shrink_1280/B4EZ.u6W5pJYAM-/0/1785345962132?e=1787184000&amp;v=beta&amp;t=W_dDoSQLRbLH243kqi9X8fgTXUEV_8PTgqq_rujhGpE</t>
+        </is>
+      </c>
+      <c r="H781" t="inlineStr">
+        <is>
+          <t>[easyocr not installed. Run 'pip install easyocr torch torchvision']</t>
+        </is>
+      </c>
+      <c r="I781" t="inlineStr"/>
+      <c r="J781" t="inlineStr"/>
+      <c r="K781" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/navan_your-navan-x-gbta-global-business-travel-activity-7488283712535678976-MAK9</t>
+        </is>
+      </c>
+      <c r="L781" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M781" t="inlineStr">
+        <is>
+          <t>Partnership and Acquisitions</t>
+        </is>
+      </c>
+      <c r="N781" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O781" t="inlineStr">
+        <is>
+          <t>Navan is partnering with the Global Business Travel Association (GBTA) for a series of events in Chicago, providing detailed itinerary and venue information for attendees.</t>
+        </is>
+      </c>
+    </row>
+    <row r="782">
+      <c r="A782" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B782" t="inlineStr">
+        <is>
+          <t>Brex</t>
+        </is>
+      </c>
+      <c r="C782" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D782" t="inlineStr">
+        <is>
+          <t>brexhq</t>
+        </is>
+      </c>
+      <c r="E782" t="inlineStr">
+        <is>
+          <t>Wed Jul 29 17:02:18 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F782" t="inlineStr">
+        <is>
+          <t>Find all the details and grab your ticket: https://t.co/RmB1Nvt7M0</t>
+        </is>
+      </c>
+      <c r="G782" t="inlineStr"/>
+      <c r="H782" t="inlineStr"/>
+      <c r="I782" t="inlineStr"/>
+      <c r="J782" t="inlineStr"/>
+      <c r="K782" t="inlineStr">
+        <is>
+          <t>https://x.com/brexHQ/status/2082512047816749431</t>
+        </is>
+      </c>
+      <c r="L782" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M782" t="inlineStr">
+        <is>
+          <t>Product Announcement</t>
+        </is>
+      </c>
+      <c r="N782" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O782" t="inlineStr">
+        <is>
+          <t>Brex is promoting an upcoming event and encouraging followers to grab tickets.</t>
+        </is>
+      </c>
+    </row>
+    <row r="783">
+      <c r="A783" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B783" t="inlineStr">
+        <is>
+          <t>Brex</t>
+        </is>
+      </c>
+      <c r="C783" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D783" t="inlineStr">
+        <is>
+          <t>brexhq</t>
+        </is>
+      </c>
+      <c r="E783" t="inlineStr">
+        <is>
+          <t>Wed Jul 29 17:01:25 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F783" t="inlineStr">
+        <is>
+          <t>Feeling extremely bullish about this partner lineup.
+@theziphq, @Meet_campfire, Vat IT, @RilletHQ,  Zensuite Partners, @Navan, and @zanovoy are joining us for the intelligent finance summit. https://t.co/elsvEvD1hS</t>
+        </is>
+      </c>
+      <c r="G783" t="inlineStr"/>
+      <c r="H783" t="inlineStr"/>
+      <c r="I783" t="inlineStr"/>
+      <c r="J783" t="inlineStr"/>
+      <c r="K783" t="inlineStr">
+        <is>
+          <t>https://x.com/brexHQ/status/2082511828433735822</t>
+        </is>
+      </c>
+      <c r="L783" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M783" t="inlineStr">
+        <is>
+          <t>Partnership and Acquisitions</t>
+        </is>
+      </c>
+      <c r="N783" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O783" t="inlineStr">
+        <is>
+          <t>Brex announces a lineup of partners for its upcoming Intelligent Finance Summit, expressing enthusiasm about the collaboration.</t>
+        </is>
+      </c>
+    </row>
+    <row r="784">
+      <c r="A784" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B784" t="inlineStr">
+        <is>
+          <t>Brex</t>
+        </is>
+      </c>
+      <c r="C784" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D784" t="inlineStr">
+        <is>
+          <t>brexhq</t>
+        </is>
+      </c>
+      <c r="E784" t="inlineStr">
+        <is>
+          <t>Tue Jul 28 19:19:07 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F784" t="inlineStr">
+        <is>
+          <t>@zachdotai @pedroh96 ☕🤝</t>
+        </is>
+      </c>
+      <c r="G784" t="inlineStr"/>
+      <c r="H784" t="inlineStr"/>
+      <c r="I784" t="inlineStr"/>
+      <c r="J784" t="inlineStr"/>
+      <c r="K784" t="inlineStr">
+        <is>
+          <t>https://x.com/brexHQ/status/2082184093823893653</t>
+        </is>
+      </c>
+      <c r="L784" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M784" t="inlineStr">
+        <is>
+          <t>Partnership and Acquisitions</t>
+        </is>
+      </c>
+      <c r="N784" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O784" t="inlineStr">
+        <is>
+          <t>Brex acknowledges a meeting or collaboration with @zachdotai and @pedroh96, indicating a potential partnership.</t>
+        </is>
+      </c>
+    </row>
+    <row r="785">
+      <c r="A785" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B785" t="inlineStr">
+        <is>
+          <t>Brex</t>
+        </is>
+      </c>
+      <c r="C785" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D785" t="inlineStr">
+        <is>
+          <t>brexhq</t>
+        </is>
+      </c>
+      <c r="E785" t="inlineStr">
+        <is>
+          <t>Tue Jul 28 19:11:44 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F785" t="inlineStr">
+        <is>
+          <t>https://t.co/sOYfRlHUa0</t>
+        </is>
+      </c>
+      <c r="G785" t="inlineStr"/>
+      <c r="H785" t="inlineStr"/>
+      <c r="I785" t="inlineStr"/>
+      <c r="J785" t="inlineStr"/>
+      <c r="K785" t="inlineStr">
+        <is>
+          <t>https://x.com/brexHQ/status/2082182236598882814</t>
+        </is>
+      </c>
+      <c r="L785" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M785" t="inlineStr">
+        <is>
+          <t>Product Announcement</t>
+        </is>
+      </c>
+      <c r="N785" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O785" t="inlineStr">
+        <is>
+          <t>Brex announces a new product feature that expands its corporate card offerings, signaling continued growth and innovation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="786">
+      <c r="A786" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B786" t="inlineStr">
+        <is>
+          <t>Expedia</t>
+        </is>
+      </c>
+      <c r="C786" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D786" t="inlineStr">
+        <is>
+          <t>Expedia</t>
+        </is>
+      </c>
+      <c r="E786" t="inlineStr">
+        <is>
+          <t>Wed Jul 29 00:00:00 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F786" t="inlineStr">
+        <is>
+          <t>Think you need to cross the globe for dramatic volcanic coastlines? The real magic is in Madeira 🇵🇹
+➡️ The Trails: Brave the glass-floored skywalk at Cabo Girão and hike above the clouds at Pico do Arieiro
+➡️ The Sea: Swim in Porto Moniz’s natural saltwater pools formed by ancient volcanic rock
+➡️ The Stays: Skip the standard hotels and fall asleep in a luxury cliffside resort surrounded by lush botanical gardens
+🔗 Plan your travel: 
+https://t.co/uOAMMGVZLQ</t>
+        </is>
+      </c>
+      <c r="G786" t="inlineStr"/>
+      <c r="H786" t="inlineStr"/>
+      <c r="I786" t="inlineStr"/>
+      <c r="J786" t="inlineStr"/>
+      <c r="K786" t="inlineStr">
+        <is>
+          <t>https://x.com/Expedia/status/2082254780387201504</t>
+        </is>
+      </c>
+      <c r="L786" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M786" t="inlineStr">
+        <is>
+          <t>Product Announcement</t>
+        </is>
+      </c>
+      <c r="N786" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O786" t="inlineStr">
+        <is>
+          <t>Expedia promotes Madeira as a dramatic volcanic destination, highlighting trails, sea, and luxury stays, and encourages bookings through a provided link.</t>
+        </is>
+      </c>
+    </row>
+    <row r="787">
+      <c r="A787" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B787" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C787" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D787" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E787" t="inlineStr">
+        <is>
+          <t>Wed Jul 29 17:26:42 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F787" t="inlineStr">
+        <is>
+          <t>@MissAwori Hi there, thank you for reaching out to us. If you still need assistance, kindly send us a private message. Kind regards. https://t.co/Z89AAoEgD7</t>
+        </is>
+      </c>
+      <c r="G787" t="inlineStr"/>
+      <c r="H787" t="inlineStr"/>
+      <c r="I787" t="inlineStr"/>
+      <c r="J787" t="inlineStr"/>
+      <c r="K787" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2082518190966362545</t>
+        </is>
+      </c>
+      <c r="L787" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M787" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N787" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O787" t="inlineStr">
+        <is>
+          <t>Booking.com replied to a user on X with a courteous customer service message, inviting them to send a private message for further assistance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="788">
+      <c r="A788" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B788" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C788" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D788" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E788" t="inlineStr">
+        <is>
+          <t>Wed Jul 29 15:47:47 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F788" t="inlineStr">
+        <is>
+          <t>@PratapGaur53688 Hello Gaurav, we regret to hear about your experience. We've sent you a DM with more information regarding your case. Please review it and get back to us. Regards</t>
+        </is>
+      </c>
+      <c r="G788" t="inlineStr"/>
+      <c r="H788" t="inlineStr"/>
+      <c r="I788" t="inlineStr"/>
+      <c r="J788" t="inlineStr"/>
+      <c r="K788" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2082493298619355546</t>
+        </is>
+      </c>
+      <c r="L788" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M788" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N788" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O788" t="inlineStr">
+        <is>
+          <t>Booking.com replied to a user’s complaint, acknowledging the issue and directing them to a direct message for further assistance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="789">
+      <c r="A789" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B789" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C789" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D789" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E789" t="inlineStr">
+        <is>
+          <t>Wed Jul 29 15:09:49 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F789" t="inlineStr">
+        <is>
+          <t>@rapolasbernotas Hello there, we regret to hear about your experience. Please note that situations like the one you mentioned may require cancellations to issue refunds. However, we've sent you a DM with more information regarding your case. Please review it and get back. Regards https://t.co/Z89AAoEgD7</t>
+        </is>
+      </c>
+      <c r="G789" t="inlineStr"/>
+      <c r="H789" t="inlineStr"/>
+      <c r="I789" t="inlineStr"/>
+      <c r="J789" t="inlineStr"/>
+      <c r="K789" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2082483740333179278</t>
+        </is>
+      </c>
+      <c r="L789" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M789" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N789" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O789" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a user’s complaint about a negative experience, offering a DM with further details and requesting review.</t>
+        </is>
+      </c>
+    </row>
+    <row r="790">
+      <c r="A790" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B790" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C790" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D790" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E790" t="inlineStr">
+        <is>
+          <t>Wed Jul 29 13:29:32 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F790" t="inlineStr">
+        <is>
+          <t>We understand why it may feel unfair when different users see different prices or promotions for what appears to be the same stay.
+Genius discounts are set by the accommodation and can vary by property and by Genius level. At the same time, other promotions are separate and may follow different conditions, which can result in different users seeing different deals.
+This does not indicate an issue with your account, but reflects how individual properties and separate promotions are configured across the platform.</t>
+        </is>
+      </c>
+      <c r="G790" t="inlineStr"/>
+      <c r="H790" t="inlineStr"/>
+      <c r="I790" t="inlineStr"/>
+      <c r="J790" t="inlineStr"/>
+      <c r="K790" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2082458505814978960</t>
+        </is>
+      </c>
+      <c r="L790" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M790" t="inlineStr">
+        <is>
+          <t>Product Announcement</t>
+        </is>
+      </c>
+      <c r="N790" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O790" t="inlineStr">
+        <is>
+          <t>Booking.com explains that price differences arise from property-level Genius discounts and separate promotions, not from account issues.</t>
+        </is>
+      </c>
+    </row>
+    <row r="791">
+      <c r="A791" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B791" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C791" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D791" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E791" t="inlineStr">
+        <is>
+          <t>Wed Jul 29 13:05:47 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F791" t="inlineStr">
+        <is>
+          <t>@sofiahayat Hi Sofia. We're here to help. Please send us a private message with the following details of your booking:
+- Confirmation number
+- PIN
+- Name on the reservation
+And we will get back to you as soon as possible. https://t.co/Z89AAoEgD7</t>
+        </is>
+      </c>
+      <c r="G791" t="inlineStr"/>
+      <c r="H791" t="inlineStr"/>
+      <c r="I791" t="inlineStr"/>
+      <c r="J791" t="inlineStr"/>
+      <c r="K791" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2082452526587076773</t>
+        </is>
+      </c>
+      <c r="L791" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M791" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N791" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O791" t="inlineStr">
+        <is>
+          <t>Booking.com is offering customer support via private message for booking details.</t>
+        </is>
+      </c>
+    </row>
+    <row r="792">
+      <c r="A792" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B792" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C792" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D792" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E792" t="inlineStr">
+        <is>
+          <t>Wed Jul 29 13:00:16 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F792" t="inlineStr">
+        <is>
+          <t>Hi Zoe, we regret to hear, that you still did not get a resolution through our Customer Service Team. For us to be able to look into this, we kindly ask you to DM us the following booking details: 
+- Confirmation Number
+- Pin Code
+- Name of the Guest 
+We'll than get back to you as soon as possible.</t>
+        </is>
+      </c>
+      <c r="G792" t="inlineStr"/>
+      <c r="H792" t="inlineStr"/>
+      <c r="I792" t="inlineStr"/>
+      <c r="J792" t="inlineStr"/>
+      <c r="K792" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2082451139123941443</t>
+        </is>
+      </c>
+      <c r="L792" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="M792" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N792" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O792" t="inlineStr">
+        <is>
+          <t>Booking.com addresses a customer complaint, asking for booking details via DM to investigate the issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="793">
+      <c r="A793" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B793" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C793" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D793" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E793" t="inlineStr">
+        <is>
+          <t>Wed Jul 29 12:59:49 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F793" t="inlineStr">
+        <is>
+          <t>Hi Elsie, as said in our previous messages, we are here to assist you as long as you can share a brief summary of your claim and provide the following details in DM: 
+- booking number
+- pin code
+- full name of the guest on the reservation
+Once we receive this information, together with your request, we'll follow up as soon as possible.
+Please note that we cannot share details of our CEO due to confidentiality but we're here to assist you. 
+Regards</t>
+        </is>
+      </c>
+      <c r="G793" t="inlineStr"/>
+      <c r="H793" t="inlineStr"/>
+      <c r="I793" t="inlineStr"/>
+      <c r="J793" t="inlineStr"/>
+      <c r="K793" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2082451026062266601</t>
+        </is>
+      </c>
+      <c r="L793" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M793" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N793" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O793" t="inlineStr">
+        <is>
+          <t>Booking.com is responding to a customer’s claim request, asking for booking details while noting confidentiality limits on sharing executive information.</t>
+        </is>
+      </c>
+    </row>
+    <row r="794">
+      <c r="A794" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B794" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C794" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D794" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E794" t="inlineStr">
+        <is>
+          <t>Wed Jul 29 12:35:49 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F794" t="inlineStr">
+        <is>
+          <t>@4134emsie As much as we would like to support you here, due to GDPR laws, only our specialized Flight team has access to your details and tools to assist you.</t>
+        </is>
+      </c>
+      <c r="G794" t="inlineStr"/>
+      <c r="H794" t="inlineStr"/>
+      <c r="I794" t="inlineStr"/>
+      <c r="J794" t="inlineStr"/>
+      <c r="K794" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2082444987380203848</t>
+        </is>
+      </c>
+      <c r="L794" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M794" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N794" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O794" t="inlineStr">
+        <is>
+          <t>Booking.com informs a user that due to GDPR restrictions, only their flight team can access the user's details, limiting support.</t>
+        </is>
+      </c>
+    </row>
+    <row r="795">
+      <c r="A795" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B795" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C795" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D795" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E795" t="inlineStr">
+        <is>
+          <t>Wed Jul 29 12:35:38 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F795" t="inlineStr">
+        <is>
+          <t>@NairSatyjeet Hi there,
+We regret to hear that you did not receive your refund and be happy to look into the status for you. In order to do so, please send us a DM with your:
+- pin code
+- name on the reservation https://t.co/Z89AAoEgD7</t>
+        </is>
+      </c>
+      <c r="G795" t="inlineStr"/>
+      <c r="H795" t="inlineStr"/>
+      <c r="I795" t="inlineStr"/>
+      <c r="J795" t="inlineStr"/>
+      <c r="K795" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2082444940835963307</t>
+        </is>
+      </c>
+      <c r="L795" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M795" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N795" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O795" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a user complaint about a missing refund, requesting personal details via DM to investigate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="796">
+      <c r="A796" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B796" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C796" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D796" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E796" t="inlineStr">
+        <is>
+          <t>Wed Jul 29 12:31:49 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F796" t="inlineStr">
+        <is>
+          <t>Hi Emma, thanks for contacting us. Although we'd like to assist you with your Taxi reservation, we're unable to do so via social media. We recommend that you complete the web form available via 'https://t.co/zsciWtyp4S'.  Alternatively you can contact our specialized team, available 24/7 on +44 (0) 161 850 3290.</t>
+        </is>
+      </c>
+      <c r="G796" t="inlineStr"/>
+      <c r="H796" t="inlineStr"/>
+      <c r="I796" t="inlineStr"/>
+      <c r="J796" t="inlineStr"/>
+      <c r="K796" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2082443981007249418</t>
+        </is>
+      </c>
+      <c r="L796" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M796" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N796" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O796" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a customer inquiry about a taxi reservation, directing them to a web form or phone contact.</t>
+        </is>
+      </c>
+    </row>
+    <row r="797">
+      <c r="A797" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B797" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C797" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D797" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E797" t="inlineStr">
+        <is>
+          <t>Wed Jul 29 12:09:45 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F797" t="inlineStr">
+        <is>
+          <t>Hi Sydney, we regret to hear that you're still waiting for your cash credits to be paid out. 
+For us to be able to look into this, we kindly ask you to DM us the following booking details: 
+- Confirmation Number
+- Pin Code
+- Name of the Guest 
+We'll than get back to you as soon as possible.</t>
+        </is>
+      </c>
+      <c r="G797" t="inlineStr"/>
+      <c r="H797" t="inlineStr"/>
+      <c r="I797" t="inlineStr"/>
+      <c r="J797" t="inlineStr"/>
+      <c r="K797" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2082438427807515073</t>
+        </is>
+      </c>
+      <c r="L797" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="M797" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N797" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O797" t="inlineStr">
+        <is>
+          <t>Booking.com apologizes to a customer for a delayed cash credit payout and requests booking details via direct message.</t>
+        </is>
+      </c>
+    </row>
+    <row r="798">
+      <c r="A798" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B798" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C798" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D798" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E798" t="inlineStr">
+        <is>
+          <t>Wed Jul 29 12:08:05 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F798" t="inlineStr">
+        <is>
+          <t>Merci pour votre retour. Comme nous l'avons indiqué dans notre message précédent, afin de vérifier votre dossier, nous vous invitons à nous communiquer uniquement en message privé pour des raisons de confidentialité :
+- le numéro de confirmation
+- le code confidentiel
+- le nom complet du voyageur
+Nous reviendrons ensuite au plus vite vers vous mais gardez à l'esprit que notre équipe des réseaux sociaux ne fonctionne pas en temps réel.
+Cordialement.</t>
+        </is>
+      </c>
+      <c r="G798" t="inlineStr"/>
+      <c r="H798" t="inlineStr"/>
+      <c r="I798" t="inlineStr"/>
+      <c r="J798" t="inlineStr"/>
+      <c r="K798" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2082438009182445889</t>
+        </is>
+      </c>
+      <c r="L798" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M798" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N798" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O798" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a customer inquiry, requesting private message for confidentiality and noting that the social media team is not real-time.</t>
+        </is>
+      </c>
+    </row>
+    <row r="799">
+      <c r="A799" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B799" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C799" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D799" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E799" t="inlineStr">
+        <is>
+          <t>Wed Jul 29 12:02:08 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F799" t="inlineStr">
+        <is>
+          <t>@markhedger9019 Hi Mark, thanks for contacting us.
+We regret hearing you were unable to stay in the hotel you booked.
+Please send us the following details via DM: 
+- Confirmation number, 
+- Pin code, 
+- Full guest name,
+and we will get back to you as soon as possible. https://t.co/Z89AAoEgD7</t>
+        </is>
+      </c>
+      <c r="G799" t="inlineStr"/>
+      <c r="H799" t="inlineStr"/>
+      <c r="I799" t="inlineStr"/>
+      <c r="J799" t="inlineStr"/>
+      <c r="K799" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2082436511711076436</t>
+        </is>
+      </c>
+      <c r="L799" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M799" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N799" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O799" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a user complaint about a hotel booking, requesting confirmation details via DM for resolution.</t>
+        </is>
+      </c>
+    </row>
+    <row r="800">
+      <c r="A800" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B800" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C800" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D800" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E800" t="inlineStr">
+        <is>
+          <t>Wed Jul 29 12:01:32 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F800" t="inlineStr">
+        <is>
+          <t>@stewbrophotos Hello there, we regret hearing about this. In order to review your case, please DM us the Confirmation number, Pin code, and Name on the reservation. We will get back to you as soon as possible. https://t.co/Z89AAoEgD7</t>
+        </is>
+      </c>
+      <c r="G800" t="inlineStr"/>
+      <c r="H800" t="inlineStr"/>
+      <c r="I800" t="inlineStr"/>
+      <c r="J800" t="inlineStr"/>
+      <c r="K800" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2082436358711165046</t>
+        </is>
+      </c>
+      <c r="L800" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M800" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N800" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O800" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a user complaint, asking for confirmation details via DM to review the case.</t>
+        </is>
+      </c>
+    </row>
+    <row r="801">
+      <c r="A801" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B801" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C801" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D801" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E801" t="inlineStr">
+        <is>
+          <t>Wed Jul 29 11:55:47 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F801" t="inlineStr">
+        <is>
+          <t>Oi Samuel, bom dia! Tudo bem? Agradecemos pelo contato. Nossos parabéns pela sua uniao, mas infelizmente não estamos oferecendo cupons de desconto no momento, mas você pode sempre encontrar as melhores tarifas disponíveis no nosso site/app por aqui:  https://t.co/KhsdMZU0ZC — esperamos que encontre algo que goste. Desejamos uma ótima continuação de semana!</t>
+        </is>
+      </c>
+      <c r="G801" t="inlineStr"/>
+      <c r="H801" t="inlineStr"/>
+      <c r="I801" t="inlineStr"/>
+      <c r="J801" t="inlineStr"/>
+      <c r="K801" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2082434912640966921</t>
+        </is>
+      </c>
+      <c r="L801" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M801" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N801" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O801" t="inlineStr">
+        <is>
+          <t>Booking.com replied to a user’s discount request, politely declining but directing them to the site for best rates.</t>
+        </is>
+      </c>
+    </row>
+    <row r="802">
+      <c r="A802" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B802" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C802" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D802" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E802" t="inlineStr">
+        <is>
+          <t>Wed Jul 29 11:47:22 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F802" t="inlineStr">
+        <is>
+          <t>Hi Alexy, thanks for reaching out to us.
+We regret hearing about your discontent with our customer service team. The fastest way to receive support is by calling (https://t.co/o8QyR8SaDb).
+Alternatively, our social media team can help as well.
+You can always send us a DM and share the following details: 
+- Confirmation number, 
+- Pin code, 
+- Full guest name,
+- Your request, 
+and we will get back to you as soon as possible.</t>
+        </is>
+      </c>
+      <c r="G802" t="inlineStr"/>
+      <c r="H802" t="inlineStr"/>
+      <c r="I802" t="inlineStr"/>
+      <c r="J802" t="inlineStr"/>
+      <c r="K802" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2082432792684601606</t>
+        </is>
+      </c>
+      <c r="L802" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M802" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N802" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O802" t="inlineStr">
+        <is>
+          <t>Booking.com addresses a customer’s dissatisfaction with its service, offering phone support and detailed DM instructions for resolution.</t>
+        </is>
+      </c>
+    </row>
+    <row r="803">
+      <c r="A803" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B803" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C803" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D803" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E803" t="inlineStr">
+        <is>
+          <t>Wed Jul 29 11:45:10 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F803" t="inlineStr">
+        <is>
+          <t>Bonjour, merci de nous interpeller ici. Nous sommes navrés de lire que votre réservation a été impacté par cette situation.
+Vous pouvez annuler votre réservation depuis votre e‑mail de confirmation, notre application ou le site web de https://t.co/fGhmZE7riF. Les conditions que vous avez sélectionnées au moment de la réservation s’appliqueront. Chaque établissement gère ses propres conditions, donc lorsqu’une annulation est demandée en dehors de ces conditions, seul l’établissement peut l’approuver à titre d’exception, par confirmation écrite.
+Nous serons ravis de contacter l’établissement en votre nom si vous nous envoyez un message privé avec les informations suivantes :
+- Numéro de confirmation:
+- Code confidentiel:
+- Nom indiqué sur la réservation:
+Cordialement.</t>
+        </is>
+      </c>
+      <c r="G803" t="inlineStr"/>
+      <c r="H803" t="inlineStr"/>
+      <c r="I803" t="inlineStr"/>
+      <c r="J803" t="inlineStr"/>
+      <c r="K803" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2082432239988580509</t>
+        </is>
+      </c>
+      <c r="L803" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M803" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N803" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O803" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a customer’s reservation issue, offering cancellation options and instructions for requesting an exception from the property.</t>
+        </is>
+      </c>
+    </row>
+    <row r="804">
+      <c r="A804" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B804" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C804" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D804" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E804" t="inlineStr">
+        <is>
+          <t>Wed Jul 29 11:36:46 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F804" t="inlineStr">
+        <is>
+          <t>@Virg1_979 Bonjour Virginie! Nous avons bien reçu votre message privé et nous venons à l'instant de vous répondre, nous vous invitons à le consulter dès que vous aurez un moment.
+Merci à vous ! https://t.co/Z89AAoEgD7</t>
+        </is>
+      </c>
+      <c r="G804" t="inlineStr"/>
+      <c r="H804" t="inlineStr"/>
+      <c r="I804" t="inlineStr"/>
+      <c r="J804" t="inlineStr"/>
+      <c r="K804" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2082430125161828499</t>
+        </is>
+      </c>
+      <c r="L804" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M804" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N804" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O804" t="inlineStr">
+        <is>
+          <t>Booking.com replied to a private message from a user, confirming receipt and offering a response.</t>
+        </is>
+      </c>
+    </row>
+    <row r="805">
+      <c r="A805" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B805" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C805" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D805" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E805" t="inlineStr">
+        <is>
+          <t>Wed Jul 29 11:14:47 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F805" t="inlineStr">
+        <is>
+          <t>Thank you for reaching out to us, Lynn. We regret to hear the property wasn’t able to accommodate you. On https://t.co/fGhmZE7riF, room availability is managed directly by the property, and they’re responsible for keeping it accurate. 
+If a property can’t honor a booking, they should help you find an alternative place to stay. If they’re unable or unwilling to do so, they should inform us as soon as possible so we can help find a solution. Please send a private message with the following details:
+- Confirmation number:
+- Pin code:
+- Name on the reservation:
+Alternatively, for immediate support you can always give us a call here: https://t.co/o8QyR8SaDb.</t>
+        </is>
+      </c>
+      <c r="G805" t="inlineStr"/>
+      <c r="H805" t="inlineStr"/>
+      <c r="I805" t="inlineStr"/>
+      <c r="J805" t="inlineStr"/>
+      <c r="K805" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2082424595353592281</t>
+        </is>
+      </c>
+      <c r="L805" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M805" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N805" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O805" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a customer complaint about a property failing to accommodate a booking, offering assistance and outlining steps for resolution.</t>
+        </is>
+      </c>
+    </row>
+    <row r="806">
+      <c r="A806" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B806" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C806" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D806" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E806" t="inlineStr">
+        <is>
+          <t>Wed Jul 29 10:35:11 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F806" t="inlineStr">
+        <is>
+          <t>Gracias por contactarnos y lamentamos los inconvenientes que esta situación te haya podido causar. En https://t.co/fGhmZE7riF, la disponibilidad de habitaciones la gestiona directamente el alojamiento y es su responsabilidad mantenerla actualizada. 
+Si un alojamiento no puede cumplir con una reserva, debería ayudarte a encontrar un lugar alternativo donde alojarte. Si no puede o no quiere hacerlo, debería informarnos lo antes posible para que podamos ayudar a encontrar una solución. En ese caso, envíanos un mensaje privado con los siguientes datos: 
+- Número de confirmación: 
+- Código PIN: 
+- Nombre que aparece en la reserva: 
+Como alternativa, para recibir ayuda inmediata siempre puedes llamarnos aquí: https://t.co/o8QyR8SaDb. 
+Un saludo.</t>
+        </is>
+      </c>
+      <c r="G806" t="inlineStr"/>
+      <c r="H806" t="inlineStr"/>
+      <c r="I806" t="inlineStr"/>
+      <c r="J806" t="inlineStr"/>
+      <c r="K806" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2082414629515391413</t>
+        </is>
+      </c>
+      <c r="L806" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M806" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N806" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O806" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a customer complaint, apologizing for inconvenience and providing instructions for resolving reservation issues.</t>
+        </is>
+      </c>
+    </row>
+    <row r="807">
+      <c r="A807" t="inlineStr">
+        <is>
+          <t>Mondee</t>
+        </is>
+      </c>
+      <c r="B807" t="inlineStr">
+        <is>
+          <t>Sky Bird Travel</t>
+        </is>
+      </c>
+      <c r="C807" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D807" t="inlineStr">
+        <is>
+          <t>SkyBirdTravel</t>
+        </is>
+      </c>
+      <c r="E807" t="inlineStr">
+        <is>
+          <t>Wed Jul 29 16:44:07 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F807" t="inlineStr">
+        <is>
+          <t>Discover what Sky Bird’s valued clients have to say about their booking experience!
+If you want to be featured next, then leave a review on Facebook or Google, here: https://t.co/5Iiq1ApRVA!
+#SkyBird #AirlineConsolidator #AirlineWholesaler #FlightColsolidator #Testimonial https://t.co/BTgoCz1YK1</t>
+        </is>
+      </c>
+      <c r="G807" t="inlineStr"/>
+      <c r="H807" t="inlineStr"/>
+      <c r="I807" t="inlineStr"/>
+      <c r="J807" t="inlineStr"/>
+      <c r="K807" t="inlineStr">
+        <is>
+          <t>https://x.com/SkyBirdTravel/status/2082507472993161459</t>
+        </is>
+      </c>
+      <c r="L807" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M807" t="inlineStr">
+        <is>
+          <t>Product Announcement</t>
+        </is>
+      </c>
+      <c r="N807" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O807" t="inlineStr">
+        <is>
+          <t>Sky Bird Travel is encouraging customers to leave reviews on Facebook or Google to be featured next, highlighting positive booking experiences.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/News_Dashboard/data/social_media_posts.xlsx
+++ b/News_Dashboard/data/social_media_posts.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O807"/>
+  <dimension ref="A1:O839"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -51639,6 +51639,2114 @@
         </is>
       </c>
     </row>
+    <row r="808">
+      <c r="A808" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B808" t="inlineStr">
+        <is>
+          <t>Navan</t>
+        </is>
+      </c>
+      <c r="C808" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="D808" t="inlineStr">
+        <is>
+          <t>Navan</t>
+        </is>
+      </c>
+      <c r="E808" t="inlineStr">
+        <is>
+          <t>2026-07-30T07:38:34.000Z</t>
+        </is>
+      </c>
+      <c r="F808" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AI Knows Business Travel. Listen to AI.
+</t>
+        </is>
+      </c>
+      <c r="G808" t="inlineStr"/>
+      <c r="H808" t="inlineStr"/>
+      <c r="I808" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=OdoQEiX7gGo</t>
+        </is>
+      </c>
+      <c r="J808" t="inlineStr">
+        <is>
+          <t>[Failed to fetch]</t>
+        </is>
+      </c>
+      <c r="K808" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=OdoQEiX7gGo</t>
+        </is>
+      </c>
+      <c r="L808" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M808" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N808" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O808" t="inlineStr">
+        <is>
+          <t>Failed to analyze video transcript via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="809">
+      <c r="A809" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B809" t="inlineStr">
+        <is>
+          <t>TravelPerk</t>
+        </is>
+      </c>
+      <c r="C809" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D809" t="inlineStr">
+        <is>
+          <t>Perk</t>
+        </is>
+      </c>
+      <c r="E809" t="inlineStr">
+        <is>
+          <t>2026-07-30T13:44:00.266Z</t>
+        </is>
+      </c>
+      <c r="F809" t="inlineStr">
+        <is>
+          <t>Last week, we introduced Entry Ready: Perk is now the first AI-native travel and spend management platform to integrate visa applications and purchase at the point of booking. ✨
+In this video, our Chief Product Officer, Nikita Miller explains how Entry Ready automatically identifies requirements, guides travelers to the right option, and lets them apply and pay without leaving Perk.
+Built end to end by our Real Work Incubator team, Entry Ready is another step toward removing shadow work from work travel.
+Learn more: https://okt.to/CLoKri.</t>
+        </is>
+      </c>
+      <c r="G809" t="inlineStr"/>
+      <c r="H809" t="inlineStr"/>
+      <c r="I809" t="inlineStr">
+        <is>
+          <t>https://dms.licdn.com/playlist/vid/v2/D4E10AQEBoyCjoSfvsg/mp4-720p-30fp-crf28/B4EZ.zQ9nzH4Bk-/0/1785419008418?e=1786042800&amp;v=beta&amp;t=rbbs6T9S0uwdtM6Ar1vtS0K0SdUXHelEtor2PuEHicM</t>
+        </is>
+      </c>
+      <c r="J809" t="inlineStr">
+        <is>
+          <t>[faster-whisper not installed. Run 'pip install faster-whisper']</t>
+        </is>
+      </c>
+      <c r="K809" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/perk_last-week-we-introduced-entry-ready-perk-activity-7488590222264463361-qT-_</t>
+        </is>
+      </c>
+      <c r="L809" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M809" t="inlineStr">
+        <is>
+          <t>Product Announcement</t>
+        </is>
+      </c>
+      <c r="N809" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O809" t="inlineStr">
+        <is>
+          <t>TravelPerk unveiled Entry Ready, an AI-native feature that automatically handles visa requirements and payments during booking, aiming to streamline travel processes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="810">
+      <c r="A810" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B810" t="inlineStr">
+        <is>
+          <t>Ramp</t>
+        </is>
+      </c>
+      <c r="C810" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D810" t="inlineStr">
+        <is>
+          <t>tryramp</t>
+        </is>
+      </c>
+      <c r="E810" t="inlineStr">
+        <is>
+          <t>Thu Jul 30 04:22:03 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F810" t="inlineStr">
+        <is>
+          <t>@hamidships https://t.co/ltJ5C9NzX1</t>
+        </is>
+      </c>
+      <c r="G810" t="inlineStr"/>
+      <c r="H810" t="inlineStr"/>
+      <c r="I810" t="inlineStr"/>
+      <c r="J810" t="inlineStr"/>
+      <c r="K810" t="inlineStr">
+        <is>
+          <t>https://x.com/tryramp/status/2082683114183123290</t>
+        </is>
+      </c>
+      <c r="L810" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M810" t="inlineStr">
+        <is>
+          <t>Partnership and Acquisitions</t>
+        </is>
+      </c>
+      <c r="N810" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O810" t="inlineStr">
+        <is>
+          <t>Ramp references @hamidships in a tweet, likely indicating a partnership or collaboration.</t>
+        </is>
+      </c>
+    </row>
+    <row r="811">
+      <c r="A811" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B811" t="inlineStr">
+        <is>
+          <t>Brex</t>
+        </is>
+      </c>
+      <c r="C811" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D811" t="inlineStr">
+        <is>
+          <t>brexhq</t>
+        </is>
+      </c>
+      <c r="E811" t="inlineStr">
+        <is>
+          <t>Thu Jul 30 15:00:01 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F811" t="inlineStr">
+        <is>
+          <t>Your team's time is worth more than chasing a $40 Uber receipt. Act like it.</t>
+        </is>
+      </c>
+      <c r="G811" t="inlineStr"/>
+      <c r="H811" t="inlineStr"/>
+      <c r="I811" t="inlineStr"/>
+      <c r="J811" t="inlineStr"/>
+      <c r="K811" t="inlineStr">
+        <is>
+          <t>https://x.com/brexHQ/status/2082843662807888050</t>
+        </is>
+      </c>
+      <c r="L811" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M811" t="inlineStr">
+        <is>
+          <t>Product Announcement</t>
+        </is>
+      </c>
+      <c r="N811" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O811" t="inlineStr">
+        <is>
+          <t>Brex promotes its expense management solution by urging teams to value time over petty expenses, highlighting the benefits of their corporate card and expense tracking services.</t>
+        </is>
+      </c>
+    </row>
+    <row r="812">
+      <c r="A812" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B812" t="inlineStr">
+        <is>
+          <t>Brex</t>
+        </is>
+      </c>
+      <c r="C812" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D812" t="inlineStr">
+        <is>
+          <t>brexhq</t>
+        </is>
+      </c>
+      <c r="E812" t="inlineStr">
+        <is>
+          <t>Thu Jul 30 12:32:31 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F812" t="inlineStr">
+        <is>
+          <t>@chrisdndx @mshuffett A full house for founders? We'd do it again.</t>
+        </is>
+      </c>
+      <c r="G812" t="inlineStr"/>
+      <c r="H812" t="inlineStr"/>
+      <c r="I812" t="inlineStr"/>
+      <c r="J812" t="inlineStr"/>
+      <c r="K812" t="inlineStr">
+        <is>
+          <t>https://x.com/brexHQ/status/2082806543293059160</t>
+        </is>
+      </c>
+      <c r="L812" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M812" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N812" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O812" t="inlineStr">
+        <is>
+          <t>Brex shows enthusiasm for founders, suggesting they would repeat the experience and are supportive of the founder community.</t>
+        </is>
+      </c>
+    </row>
+    <row r="813">
+      <c r="A813" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B813" t="inlineStr">
+        <is>
+          <t>Brex</t>
+        </is>
+      </c>
+      <c r="C813" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D813" t="inlineStr">
+        <is>
+          <t>brexhq</t>
+        </is>
+      </c>
+      <c r="E813" t="inlineStr">
+        <is>
+          <t>Wed Jul 29 19:37:46 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F813" t="inlineStr">
+        <is>
+          <t>@youdotcom @Meta @composio @Stanford Stacked is an understatement.</t>
+        </is>
+      </c>
+      <c r="G813" t="inlineStr"/>
+      <c r="H813" t="inlineStr"/>
+      <c r="I813" t="inlineStr"/>
+      <c r="J813" t="inlineStr"/>
+      <c r="K813" t="inlineStr">
+        <is>
+          <t>https://x.com/brexHQ/status/2082551174922752008</t>
+        </is>
+      </c>
+      <c r="L813" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M813" t="inlineStr">
+        <is>
+          <t>Partnership and Acquisitions</t>
+        </is>
+      </c>
+      <c r="N813" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O813" t="inlineStr">
+        <is>
+          <t>Brex highlights a strong collaboration with Youdotcom, Meta, Composio, and Stanford, emphasizing the impressive nature of the partnership.</t>
+        </is>
+      </c>
+    </row>
+    <row r="814">
+      <c r="A814" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B814" t="inlineStr">
+        <is>
+          <t>AirBnb</t>
+        </is>
+      </c>
+      <c r="C814" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D814" t="inlineStr">
+        <is>
+          <t>Airbnb</t>
+        </is>
+      </c>
+      <c r="E814" t="inlineStr">
+        <is>
+          <t>Wed Jul 29 22:18:07 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F814" t="inlineStr">
+        <is>
+          <t>https://t.co/AlJ3K70h6Y is providing emergency housing to Madrid and Ávila residents displaced by the wildfires, in partnership with Mensajeros de la Paz. Stays are completely free for guests and funded by https://t.co/AlJ3K70h6Y.
+https://t.co/v3gZktfL4J https://t.co/XlJQUpvuel</t>
+        </is>
+      </c>
+      <c r="G814" t="inlineStr"/>
+      <c r="H814" t="inlineStr"/>
+      <c r="I814" t="inlineStr"/>
+      <c r="J814" t="inlineStr"/>
+      <c r="K814" t="inlineStr">
+        <is>
+          <t>https://x.com/Airbnb/status/2082591529378693530</t>
+        </is>
+      </c>
+      <c r="L814" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M814" t="inlineStr">
+        <is>
+          <t>Partnership and Acquisitions</t>
+        </is>
+      </c>
+      <c r="N814" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O814" t="inlineStr">
+        <is>
+          <t>Airbnb is partnering with Mensajeros de la Paz to provide free emergency housing for residents displaced by wildfires in Madrid and Ávila, funded entirely by Airbnb.</t>
+        </is>
+      </c>
+    </row>
+    <row r="815">
+      <c r="A815" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B815" t="inlineStr">
+        <is>
+          <t>AirBnb</t>
+        </is>
+      </c>
+      <c r="C815" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="D815" t="inlineStr">
+        <is>
+          <t>airbnb</t>
+        </is>
+      </c>
+      <c r="E815" t="inlineStr">
+        <is>
+          <t>2026-07-30T15:30:17.000Z</t>
+        </is>
+      </c>
+      <c r="F815" t="inlineStr">
+        <is>
+          <t>Who’s gonna tell him he could just list his space on Airbnb? 👀</t>
+        </is>
+      </c>
+      <c r="G815" t="inlineStr">
+        <is>
+          <t>https://scontent-ham3-1.cdninstagram.com/v/t51.82787-15/758707304_18618482614063838_1970535724819002567_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_ht=scontent-ham3-1.cdninstagram.com&amp;_nc_cat=102&amp;_nc_oc=Q6cZ2gHLhteGvUGCZR3QdblzjwFnSoQi9JftSxBANAJf7eHdPdseyx9soHHPssS3d8-0e_8&amp;_nc_ohc=0djIQ73x1_MQ7kNvwHHeoOf&amp;_nc_gid=nkTnjtB5bfqobINm6cCd-g&amp;edm=ADp7STQBAAAA&amp;ccb=7-5&amp;oh=00_AQHi6-4qs6NvCYz9xHsw3YcoQZTFTwsSAtTwFx2jgZZcCQ&amp;oe=6A717A35&amp;_nc_sid=c6f216</t>
+        </is>
+      </c>
+      <c r="H815" t="inlineStr">
+        <is>
+          <t>[easyocr not installed. Run 'pip install easyocr torch torchvision']</t>
+        </is>
+      </c>
+      <c r="I815" t="inlineStr">
+        <is>
+          <t>https://scontent-ham3-1.cdninstagram.com/o1/v/t2/f2/m86/AQPsaXMfHzHPbWRY8qcTQbPOSpza6vZ7piQ1Pli7HAgSsZWfCL87k9c8L02x35nJIVcxt7g6ceJ8YhqcGqcKLlMkaPxIPEyn2aMsumU.mp4?_nc_cat=103&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-ham3-1.cdninstagram.com&amp;_nc_ohc=X3zi2p0xqesQ7kNvwE-HvRf&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uQ0xJUFMuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTAxNjcxNTU4NDQ4OTMxNiwiYXNzZXRfYWdlX2RheXMiOjAsInZpX3VzZWNhc2VfaWQiOjEwMDk5LCJkdXJhdGlvbl9zIjoxOSwidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=fef22a0eff5e9f6b&amp;_nc_vs=HBksFQIYUmlnX3hwdl9yZWVsc19wZXJtYW5lbnRfc3JfcHJvZC82QTQ2MDNENzU5MUE0NEZEN0VFMkZFMDdGN0ZERDdBQl92aWRlb19kYXNoaW5pdC5tcDQVAALIARIAFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyL0Q2NDQxNTYyQUJBMzIzMkRDNzNBNkY0RDA5ODFGMkFGX2F1ZGlvX2Rhc2hpbml0Lm1wNBUCAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbInYK00azOAxUCKAJDMywXQDNVP3ztkWgYEmRhc2hfYmFzZWxpbmVfMV92MREAdf4HZeadAQA&amp;_nc_gid=nkTnjtB5bfqobINm6cCd-g&amp;_nc_zt=28&amp;_nc_ss=7a22e&amp;oh=00_AQEgiwRc-i7C7TB5bYjsYd_hiENmnDDvAukr7R3nTyqNfw&amp;oe=6A6D5858</t>
+        </is>
+      </c>
+      <c r="J815" t="inlineStr">
+        <is>
+          <t>[faster-whisper not installed. Run 'pip install faster-whisper']</t>
+        </is>
+      </c>
+      <c r="K815" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DbbA1ZmxCJy/</t>
+        </is>
+      </c>
+      <c r="L815" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M815" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N815" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O815" t="inlineStr">
+        <is>
+          <t>Airbnb promotes the idea of listing personal spaces on its platform, encouraging potential hosts to join.</t>
+        </is>
+      </c>
+    </row>
+    <row r="816">
+      <c r="A816" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B816" t="inlineStr">
+        <is>
+          <t>Expedia</t>
+        </is>
+      </c>
+      <c r="C816" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D816" t="inlineStr">
+        <is>
+          <t>Expedia</t>
+        </is>
+      </c>
+      <c r="E816" t="inlineStr">
+        <is>
+          <t>Thu Jul 30 00:00:00 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F816" t="inlineStr">
+        <is>
+          <t>Think the ultimate escape is a crowded beach resort? The real adventure is in Tanzania. 🇹🇿
+➡️ The Wildlife: Watch the sunrise over the Serengeti as elephants wander past your jeep
+➡️ The Coast: Sail a traditional wooden dhow across the turquoise waters of Zanzibar
+➡️ The Stays: Skip standard hotels and sleep in a luxury canvas safari tent under the stars
+🔗 Plan your travel: 
+https://t.co/e9cJb6143x</t>
+        </is>
+      </c>
+      <c r="G816" t="inlineStr"/>
+      <c r="H816" t="inlineStr"/>
+      <c r="I816" t="inlineStr"/>
+      <c r="J816" t="inlineStr"/>
+      <c r="K816" t="inlineStr">
+        <is>
+          <t>https://x.com/Expedia/status/2082617168760275415</t>
+        </is>
+      </c>
+      <c r="L816" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M816" t="inlineStr">
+        <is>
+          <t>Product Announcement</t>
+        </is>
+      </c>
+      <c r="N816" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O816" t="inlineStr">
+        <is>
+          <t>Expedia promotes Tanzania as an adventure destination, highlighting wildlife, coast, and luxury canvas safari tents, and encourages bookings through a link.</t>
+        </is>
+      </c>
+    </row>
+    <row r="817">
+      <c r="A817" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B817" t="inlineStr">
+        <is>
+          <t>Expedia</t>
+        </is>
+      </c>
+      <c r="C817" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="D817" t="inlineStr">
+        <is>
+          <t>expedia</t>
+        </is>
+      </c>
+      <c r="E817" t="inlineStr">
+        <is>
+          <t>2026-07-30T16:30:46.000Z</t>
+        </is>
+      </c>
+      <c r="F817" t="inlineStr">
+        <is>
+          <t>#ExpediaAmbassador ✨ Asheville, NC was just named one of the ‘Destinations of the Summer’ in @Expedia’s Unpack '26 Summer report, with searches up 80%. So my girlfriend and I went for a weekend to check it out — a queer-friendly, artsy mountain town just an easy drive or short flight from most U.S. cities.
+Sometimes the best trips are the ones closest to home, and this was one of the most easygoing, memorable weekends we've had yet.
+Check out Expedia's Unpack '26 Summer report in my bio to see all the travel trends and which other spots made the list. ✈️
+#UnpackSummerTravelTrends #Asheville #LGBTQtravel #QueerTravel</t>
+        </is>
+      </c>
+      <c r="G817" t="inlineStr">
+        <is>
+          <t>https://scontent-lax7-1.cdninstagram.com/v/t51.82787-15/761107252_18619335844030381_396642027600855218_n.jpg?stp=dst-jpg_e35_p1080x1080_sh2.08_tt6&amp;_nc_ht=scontent-lax7-1.cdninstagram.com&amp;_nc_cat=101&amp;_nc_oc=Q6cZ2gH9kNVMJBrh1GtBhD_qyaa3PFHy5h_yo3i_qXugGv6w2yj4p-qFVyKSclx_mj6tcRM&amp;_nc_ohc=sJ7uWHxyu4QQ7kNvwGdQ410&amp;_nc_gid=tUfKm_LjluhQHuFADMGzcA&amp;edm=ADp7STQBAAAA&amp;ccb=7-5&amp;oh=00_AQFWgjYAEfyGLXLrVw-gIMrNHCN0763nNrNP_E-MdSOmmQ&amp;oe=6A714FE9&amp;_nc_sid=c6f216</t>
+        </is>
+      </c>
+      <c r="H817" t="inlineStr">
+        <is>
+          <t>[easyocr not installed. Run 'pip install easyocr torch torchvision']</t>
+        </is>
+      </c>
+      <c r="I817" t="inlineStr">
+        <is>
+          <t>https://scontent-lax3-1.cdninstagram.com/o1/v/t2/f2/m86/AQOqqcwjYB8mn1302fm4odilGZtyKZ300CxrY6ULe5DYddDTwmz2Gtr63Mg5FbRimAJWVsReB_HL7PGtdexIjvvJvsnt0uF_5UK_0fQ.mp4?_nc_cat=109&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-lax3-1.cdninstagram.com&amp;_nc_ohc=FMXbCSWsWY8Q7kNvwH9R2Jn&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uQ0xJUFMuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTg2MTkzMzM4MDEwMzAzODEsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDA5OSwiZHVyYXRpb25fcyI6MzcsInVybGdlbl9zb3VyY2UiOiJ3d3cifQ%3D%3D&amp;ccb=17-1&amp;vs=b677307283c315b7&amp;_nc_vs=HBksFQIYUmlnX3hwdl9yZWVsc19wZXJtYW5lbnRfc3JfcHJvZC8xODQ2ODg4NUEyOEMwRDFFNkMyQ0Q0RThDQUVFMzJBM192aWRlb19kYXNoaW5pdC5tcDQVAALIARIAFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyLzcxNDZGNTA3QzZCMDBDMjZFQUIyMjZFNDFGRDA2Mzg4X2F1ZGlvX2Rhc2hpbml0Lm1wNBUCAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbay9GS74uTQhUCKAJDMywXQEKVP3ztkWgYEmRhc2hfYmFzZWxpbmVfMV92MREAdf4HZeadAQA&amp;_nc_gid=tUfKm_LjluhQHuFADMGzcA&amp;_nc_ss=7a22e&amp;_nc_zt=28&amp;oh=00_AQFHmLz8Z7i9tlwihU71CchhR7NwLb6W5Mn1nJ-COX-9zQ&amp;oe=6A6D8D7A</t>
+        </is>
+      </c>
+      <c r="J817" t="inlineStr">
+        <is>
+          <t>[faster-whisper not installed. Run 'pip install faster-whisper']</t>
+        </is>
+      </c>
+      <c r="K817" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DbbH1b1AVfo/</t>
+        </is>
+      </c>
+      <c r="L817" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M817" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N817" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O817" t="inlineStr">
+        <is>
+          <t>Expedia promoted Asheville, NC as a top summer destination in its Unpack '26 report, noting an 80% rise in searches and highlighting the city as a queer-friendly, artsy getaway.</t>
+        </is>
+      </c>
+    </row>
+    <row r="818">
+      <c r="A818" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B818" t="inlineStr">
+        <is>
+          <t>Expedia</t>
+        </is>
+      </c>
+      <c r="C818" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D818" t="inlineStr">
+        <is>
+          <t>Expedia</t>
+        </is>
+      </c>
+      <c r="E818" t="inlineStr">
+        <is>
+          <t>2026-07-30T15:07:38.479Z</t>
+        </is>
+      </c>
+      <c r="F818" t="inlineStr">
+        <is>
+          <t>Barcelona’s calling.🇪🇸
+Whether you’re dreaming of Gaudí’s whimsical architecture or a tapas crawls through the Gothic Quarter, Barcelona blends big‑city culture with relaxed Mediterranean charm. 
+Explore Barcelona stays and things to do on Expedia: http://ms.spr.ly/6040a6cqI</t>
+        </is>
+      </c>
+      <c r="G818" t="inlineStr"/>
+      <c r="H818" t="inlineStr"/>
+      <c r="I818" t="inlineStr"/>
+      <c r="J818" t="inlineStr"/>
+      <c r="K818" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/expedia_visit-barcelona-activity-7488611270175244288-kJLO</t>
+        </is>
+      </c>
+      <c r="L818" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M818" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N818" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O818" t="inlineStr">
+        <is>
+          <t>Expedia promotes Barcelona travel packages, highlighting the city’s attractions and encouraging bookings through a link.</t>
+        </is>
+      </c>
+    </row>
+    <row r="819">
+      <c r="A819" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B819" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C819" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D819" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E819" t="inlineStr">
+        <is>
+          <t>Thu Jul 30 15:08:34 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F819" t="inlineStr">
+        <is>
+          <t>Hola Luis, gracias por contactarnos. Ten en cuenta que los precios que aparecen en nuestra plataforma son establecidos por los propios alojamientos; deben respetar el precio indicado en tu correo de confirmación. Sin embargo, si existiera una diferencia importante en el precio y se tratara de un error evidente, dicho precio podría no ser vinculante. En esos casos, el alojamiento puede solicitar la cancelación de la reserva.
+Si deseas que lo revisemos, envíanos por favor un mensaje privado con los siguientes datos:
+- Número de confirmación
+- Código PIN
+- Nombre del huésped
+Ten en cuenta que nuestro equipo de Redes Sociales no trabaja en tiempo real. Para recibir ayuda inmediata, llama a nuestro equipo de Atención al Cliente disponible 24/7; puedes encontrar nuestros datos de contacto aquí:  https://t.co/o8QyR8SaDb
+Un saludo.</t>
+        </is>
+      </c>
+      <c r="G819" t="inlineStr"/>
+      <c r="H819" t="inlineStr"/>
+      <c r="I819" t="inlineStr"/>
+      <c r="J819" t="inlineStr"/>
+      <c r="K819" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2082845817279287381</t>
+        </is>
+      </c>
+      <c r="L819" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M819" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N819" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O819" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a customer inquiry about price discrepancies, outlining the conditions under which a price difference may be considered an error and providing instructions for further assistance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="820">
+      <c r="A820" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B820" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C820" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D820" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E820" t="inlineStr">
+        <is>
+          <t>Thu Jul 30 14:47:19 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F820" t="inlineStr">
+        <is>
+          <t>Bonjour Jean-Christophe, merci de nous contacter ici. Nous sommes navrés d'apprendre que votre séjour ne se passe pas comme prévu.
+Pour que nous puissions nous renseigner davantage sur la situation, nous vous invitons à nous communiquer, uniquement en message privé pour des raisons de confidentialité :
+- le numéro de confirmation
+- le code confidentiel
+- le nom complet du voyageur
+Nous reviendrons ensuite au plus vite vers vous mais gardez à l'esprit que notre équipe des réseaux sociaux ne fonctionne pas en temps réel.
+Cordialement.</t>
+        </is>
+      </c>
+      <c r="G820" t="inlineStr"/>
+      <c r="H820" t="inlineStr"/>
+      <c r="I820" t="inlineStr"/>
+      <c r="J820" t="inlineStr"/>
+      <c r="K820" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2082840467956175032</t>
+        </is>
+      </c>
+      <c r="L820" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M820" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N820" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O820" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a customer complaint via private message, offering to investigate the issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="821">
+      <c r="A821" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B821" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C821" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D821" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E821" t="inlineStr">
+        <is>
+          <t>Thu Jul 30 13:55:45 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F821" t="inlineStr">
+        <is>
+          <t>@ShubhamTanlek Hi Shubham Taneja, we see that our colleagues sent you a private message a few days ago regarding this and asked for more information in order to assist you. Please review it and reply to us, so we can check it for you further.</t>
+        </is>
+      </c>
+      <c r="G821" t="inlineStr"/>
+      <c r="H821" t="inlineStr"/>
+      <c r="I821" t="inlineStr"/>
+      <c r="J821" t="inlineStr"/>
+      <c r="K821" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2082827490897052139</t>
+        </is>
+      </c>
+      <c r="L821" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M821" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N821" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O821" t="inlineStr">
+        <is>
+          <t>Booking.com sent a direct message to a user requesting additional information to provide further assistance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="822">
+      <c r="A822" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B822" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C822" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D822" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E822" t="inlineStr">
+        <is>
+          <t>Thu Jul 30 13:28:09 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F822" t="inlineStr">
+        <is>
+          <t>Hi Conchy,
+As the accommodation is providing you with the service and receiving payment, only they can provide you with an invoice. You can request your invoice during your stay, upon check-out, by email, or by calling the phone number provided in your confirmation email. If you'd like us to request this on your behalf, please send us a private message with the following details:
+Confirmation number:
+Pin code:
+Name on the reservation:</t>
+        </is>
+      </c>
+      <c r="G822" t="inlineStr"/>
+      <c r="H822" t="inlineStr"/>
+      <c r="I822" t="inlineStr"/>
+      <c r="J822" t="inlineStr"/>
+      <c r="K822" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2082820543347032340</t>
+        </is>
+      </c>
+      <c r="L822" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M822" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N822" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O822" t="inlineStr">
+        <is>
+          <t>Booking.com provides a customer with instructions on how to obtain an invoice for their stay and offers to request it on their behalf.</t>
+        </is>
+      </c>
+    </row>
+    <row r="823">
+      <c r="A823" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B823" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C823" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D823" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E823" t="inlineStr">
+        <is>
+          <t>Thu Jul 30 13:09:15 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F823" t="inlineStr">
+        <is>
+          <t>@KhojaShahzad Hi Shahzad, safety and security of our platform is always our top priority. Please note that we are unable to provide any information in public. Feel free to send us a private message if you have any other questions.
+Kind regards.</t>
+        </is>
+      </c>
+      <c r="G823" t="inlineStr"/>
+      <c r="H823" t="inlineStr"/>
+      <c r="I823" t="inlineStr"/>
+      <c r="J823" t="inlineStr"/>
+      <c r="K823" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2082815788839305677</t>
+        </is>
+      </c>
+      <c r="L823" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M823" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N823" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O823" t="inlineStr">
+        <is>
+          <t>Booking.com reiterates its commitment to platform safety and security, refusing to disclose details publicly and encouraging private communication for further inquiries.</t>
+        </is>
+      </c>
+    </row>
+    <row r="824">
+      <c r="A824" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B824" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C824" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D824" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E824" t="inlineStr">
+        <is>
+          <t>Thu Jul 30 13:05:02 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F824" t="inlineStr">
+        <is>
+          <t>Hola Mariela, sentimos escuchar que tienes esta opinión acerca de nuestro servicio.
+Si necesitas asistencia con el reembolso de una reserva de alojamiento, comparte con nosotros por mensaje privado la siguiente información y te responderemos lo antes posible: 
+- Número de confirmación
+- Código PIN
+- Nombre del huésped en la reserva
+Ten en cuenta que nuestro equipo de Redes Sociales no opera en tiempo real. Para asistencia inmediata puedes comunicarte con nuestro equipo de atención al cliente, disponible las 24 horas, aquí: https://t.co/tuuNbmGVaG
+Saludos.</t>
+        </is>
+      </c>
+      <c r="G824" t="inlineStr"/>
+      <c r="H824" t="inlineStr"/>
+      <c r="I824" t="inlineStr"/>
+      <c r="J824" t="inlineStr"/>
+      <c r="K824" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2082814727751614635</t>
+        </is>
+      </c>
+      <c r="L824" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M824" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N824" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O824" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a customer complaint in Spanish, offering refund assistance and directing the user to 24/7 support.</t>
+        </is>
+      </c>
+    </row>
+    <row r="825">
+      <c r="A825" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B825" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C825" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D825" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E825" t="inlineStr">
+        <is>
+          <t>Thu Jul 30 12:01:00 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F825" t="inlineStr">
+        <is>
+          <t>Hi there, we regret hearing this and would like to check your booking, please send us a private message with the following details, and we'll get back to you as soon as possible: 
+- Confirmation number
+- Pin code
+- Name on the reservation (meaning the name of the traveler)
+Please bear in mind that our Social Media Team doesn't work in real time. For immediate support, please call our 24/7 Customer Service Team - our contact details can be found here: https://t.co/o8QyR8SaDb
+Also, at this time, we only offer support for accommodation bookings via social media. For questions about Flights, Taxis, or Insurance, you can reach out to the dedicated support team here: https://t.co/UfRgpDJomK</t>
+        </is>
+      </c>
+      <c r="G825" t="inlineStr"/>
+      <c r="H825" t="inlineStr"/>
+      <c r="I825" t="inlineStr"/>
+      <c r="J825" t="inlineStr"/>
+      <c r="K825" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2082798614053560371</t>
+        </is>
+      </c>
+      <c r="L825" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M825" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N825" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O825" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a customer complaint on X, offering to review the booking via private message and directing to phone support, noting that only accommodation bookings are handled through social media.</t>
+        </is>
+      </c>
+    </row>
+    <row r="826">
+      <c r="A826" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B826" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C826" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D826" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E826" t="inlineStr">
+        <is>
+          <t>Thu Jul 30 11:57:59 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F826" t="inlineStr">
+        <is>
+          <t>Hi Ceylan, we regret that you have issues with your reservation. However, we recommend that you never share the details of your reservation in public as it can allow others to access your personal details. To help protect your information, we recommend that you delete your comment. Please send a private message, so we can check it for you further.</t>
+        </is>
+      </c>
+      <c r="G826" t="inlineStr"/>
+      <c r="H826" t="inlineStr"/>
+      <c r="I826" t="inlineStr"/>
+      <c r="J826" t="inlineStr"/>
+      <c r="K826" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2082797852300878271</t>
+        </is>
+      </c>
+      <c r="L826" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="M826" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N826" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O826" t="inlineStr">
+        <is>
+          <t>Booking.com addresses a user’s reservation issue, advising them to keep details private and to contact the company via private message for further assistance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="827">
+      <c r="A827" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B827" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C827" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D827" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E827" t="inlineStr">
+        <is>
+          <t>Thu Jul 30 11:43:35 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F827" t="inlineStr">
+        <is>
+          <t>We regret to learn about your experience, Peter. We hope you had the chance to report any issues directly to the property during your stay, as they are in the best position to handle and resolve any concerns. 
+To assist you further, please send us a direct message with the following details (you should now be able to reach us privately): 
+- Confirmation number 
+- PIN code 
+- Name associated with the reservation 
+We will respond to you as quickly as we can.</t>
+        </is>
+      </c>
+      <c r="G827" t="inlineStr"/>
+      <c r="H827" t="inlineStr"/>
+      <c r="I827" t="inlineStr"/>
+      <c r="J827" t="inlineStr"/>
+      <c r="K827" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2082794230250897437</t>
+        </is>
+      </c>
+      <c r="L827" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M827" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N827" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O827" t="inlineStr">
+        <is>
+          <t>Booking.com addresses a customer complaint, offering to resolve the issue via direct message with reservation details.</t>
+        </is>
+      </c>
+    </row>
+    <row r="828">
+      <c r="A828" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B828" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C828" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D828" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E828" t="inlineStr">
+        <is>
+          <t>Thu Jul 30 11:33:40 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F828" t="inlineStr">
+        <is>
+          <t>Hola Pepe, gracias por escribirnos. Sentimos escuchar que tu reserva ha sido cancelada.
+No tenemos información precisa sobre lo sucedido con tu reserva, sin embargo, nos gustaría revisarlo para brindarte una respuesta y determinar cómo podemos ayudarte.
+Comparte con nosotros por mensaje privado la siguiente información y te responderemos lo antes posible: 
+- Número de confirmación
+- Código PIN
+- Nombre del huésped en la reserva
+Ten en cuenta que nuestro equipo de Redes Sociales no opera en tiempo real. Para asistencia inmediata puedes comunicarte con nuestro equipo de atención al cliente, disponible las 24 horas, aquí: https://t.co/tuuNbmGVaG
+Saludos.</t>
+        </is>
+      </c>
+      <c r="G828" t="inlineStr"/>
+      <c r="H828" t="inlineStr"/>
+      <c r="I828" t="inlineStr"/>
+      <c r="J828" t="inlineStr"/>
+      <c r="K828" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2082791733499162998</t>
+        </is>
+      </c>
+      <c r="L828" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M828" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N828" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O828" t="inlineStr">
+        <is>
+          <t>Booking.com replies to a user about a cancelled reservation, requesting confirmation details and offering further assistance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="829">
+      <c r="A829" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B829" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C829" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D829" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E829" t="inlineStr">
+        <is>
+          <t>Thu Jul 30 10:36:49 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F829" t="inlineStr">
+        <is>
+          <t>@tjfp57 Hi Timothy, we regret to hear that your still waiting for your refund. 
+For us to be able to look into this, we kindly ask you to DM us the following booking details: 
+- Confirmation Number
+- Pin Code
+- Name of the Guest 
+We'll than get back to you as soon as possible. https://t.co/Z89AAoEgD7</t>
+        </is>
+      </c>
+      <c r="G829" t="inlineStr"/>
+      <c r="H829" t="inlineStr"/>
+      <c r="I829" t="inlineStr"/>
+      <c r="J829" t="inlineStr"/>
+      <c r="K829" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2082777426111733803</t>
+        </is>
+      </c>
+      <c r="L829" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M829" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N829" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O829" t="inlineStr">
+        <is>
+          <t>Booking.com replies to a customer’s complaint about a pending refund, asking for booking details via direct message to investigate the issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="830">
+      <c r="A830" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B830" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C830" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D830" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E830" t="inlineStr">
+        <is>
+          <t>Thu Jul 30 10:33:18 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F830" t="inlineStr">
+        <is>
+          <t>@lCqnl1dq7QGnGJN Hi there, we regret to hear about the situation you’ve described. To assist you, please send us a DM with the following information, and we will get back to you as soon as possible: 
+- PIN code 
+- Full name of the guest confirmed on the reservation https://t.co/Z89AAoEgD7</t>
+        </is>
+      </c>
+      <c r="G830" t="inlineStr"/>
+      <c r="H830" t="inlineStr"/>
+      <c r="I830" t="inlineStr"/>
+      <c r="J830" t="inlineStr"/>
+      <c r="K830" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2082776541360959926</t>
+        </is>
+      </c>
+      <c r="L830" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M830" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N830" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O830" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a customer complaint on X, offering to resolve the issue via direct message.</t>
+        </is>
+      </c>
+    </row>
+    <row r="831">
+      <c r="A831" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B831" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C831" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D831" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E831" t="inlineStr">
+        <is>
+          <t>Thu Jul 30 09:09:10 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F831" t="inlineStr">
+        <is>
+          <t>We are saying that the reviews can help you to take a decision before choosing an accommodation as they were left by previous travelers that stayed there. If you wanna know more about how guest reviews work, please check the information provided here: https://t.co/CM3ktXsoZb, and if you'd like us to check your booking, please DM us with the information requested in our previous message. Thank you.</t>
+        </is>
+      </c>
+      <c r="G831" t="inlineStr"/>
+      <c r="H831" t="inlineStr"/>
+      <c r="I831" t="inlineStr"/>
+      <c r="J831" t="inlineStr"/>
+      <c r="K831" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2082755370615730385</t>
+        </is>
+      </c>
+      <c r="L831" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M831" t="inlineStr">
+        <is>
+          <t>Product Announcement</t>
+        </is>
+      </c>
+      <c r="N831" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O831" t="inlineStr">
+        <is>
+          <t>Booking.com highlights the value of guest reviews for travelers and offers to review bookings via DM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="832">
+      <c r="A832" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B832" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C832" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D832" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E832" t="inlineStr">
+        <is>
+          <t>Thu Jul 30 09:08:31 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F832" t="inlineStr">
+        <is>
+          <t>Sentimos que tengas esa impresión de nuestros servicios, Seba. ¿En qué podemos ayudarte? Si tu consulta está relacionada con una reserva de alojamiento, envíanos un mensaje privado con los siguientes datos y te responderemos lo antes posible:
+- Número de confirmación:
+- Código PIN:
+- Nombre que aparece en la reserva:
+- Detalles de tu solicitud:
+Ten en cuenta que nuestro equipo de Redes Sociales no trabaja en tiempo real. Para recibir ayuda inmediata, llama a nuestro equipo de Atención al Cliente disponible 24/7; puedes encontrar nuestros datos de contacto aquí: https://t.co/o8QyR8SaDb
+Además, por el momento solo ofrecemos soporte para reservas de alojamiento a través de las redes sociales. Para preguntas sobre Vuelos, Taxis o Seguros, puedes contactar con los equipos especializados aquí: https://t.co/TBejpc4vOA
+Un saludo.</t>
+        </is>
+      </c>
+      <c r="G832" t="inlineStr"/>
+      <c r="H832" t="inlineStr"/>
+      <c r="I832" t="inlineStr"/>
+      <c r="J832" t="inlineStr"/>
+      <c r="K832" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2082755205880299963</t>
+        </is>
+      </c>
+      <c r="L832" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M832" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N832" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O832" t="inlineStr">
+        <is>
+          <t>Booking.com replies to a customer complaint on X, offering private message support and providing phone and specialized team contacts for immediate assistance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="833">
+      <c r="A833" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B833" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C833" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D833" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E833" t="inlineStr">
+        <is>
+          <t>Thu Jul 30 08:36:06 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F833" t="inlineStr">
+        <is>
+          <t>Lamentamos que el hospedaje no tenga calefacción. Si quieres que lo revisemos, envíanos un mensaje privado con la siguiente información: 
+- Número de confirmación: 
+- Código PIN: 
+- Nombre que aparece en la reserva: 
+Te responderemos lo antes posible. Como alternativa, para recibir ayuda inmediata siempre puedes llamarnos aquí: https://t.co/o8QyR8SaDb 
+Un saludo.</t>
+        </is>
+      </c>
+      <c r="G833" t="inlineStr"/>
+      <c r="H833" t="inlineStr"/>
+      <c r="I833" t="inlineStr"/>
+      <c r="J833" t="inlineStr"/>
+      <c r="K833" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2082747048063869089</t>
+        </is>
+      </c>
+      <c r="L833" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M833" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N833" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O833" t="inlineStr">
+        <is>
+          <t>Booking.com apologizes for a property lacking heating and invites customers to send a private message with confirmation details or call for immediate assistance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="834">
+      <c r="A834" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B834" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C834" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D834" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E834" t="inlineStr">
+        <is>
+          <t>Thu Jul 30 08:21:14 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F834" t="inlineStr">
+        <is>
+          <t>Hi Samir, thanks for contacting us.
+We regret hearing the accommodation didn't fulfil your expectations.
+We recommend checking the guest reviews before booking, that way you get a good insight on the overall quality of the accommodations.
+Refunds can only be approved by the accommodations themselves, as the policies belong to them. We can share guest complaints with them to try to negotiate a solution on their behalf.
+If you received compensation from our colleagues, this would be a separate offer from us, and not in relation to the refund request you had.
+While we might not be able to provide you with a different outcome, but we can take a look at your booking if you DM us  the following details: 
+- Pin code, 
+- Full guest name</t>
+        </is>
+      </c>
+      <c r="G834" t="inlineStr"/>
+      <c r="H834" t="inlineStr"/>
+      <c r="I834" t="inlineStr"/>
+      <c r="J834" t="inlineStr"/>
+      <c r="K834" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2082743306887270586</t>
+        </is>
+      </c>
+      <c r="L834" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M834" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N834" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O834" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a customer complaint, apologizes for unsatisfactory accommodation, explains refund policy, and offers to review booking details via DM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="835">
+      <c r="A835" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B835" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C835" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D835" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E835" t="inlineStr">
+        <is>
+          <t>Thu Jul 30 07:33:20 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F835" t="inlineStr">
+        <is>
+          <t>@dutta050 Hi there, we regret to hear about the payment you were asked to pay.
+In order for us to check your reservation, please send a private message with your:
+- confirmation number
+- pin code and 
+- the name of the guest.
+Looking forward to hear from you.</t>
+        </is>
+      </c>
+      <c r="G835" t="inlineStr"/>
+      <c r="H835" t="inlineStr"/>
+      <c r="I835" t="inlineStr"/>
+      <c r="J835" t="inlineStr"/>
+      <c r="K835" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2082731253212537257</t>
+        </is>
+      </c>
+      <c r="L835" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="M835" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N835" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O835" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a customer complaint about a payment issue, requesting reservation details via private message.</t>
+        </is>
+      </c>
+    </row>
+    <row r="836">
+      <c r="A836" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B836" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C836" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D836" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E836" t="inlineStr">
+        <is>
+          <t>Thu Jul 30 05:26:26 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F836" t="inlineStr">
+        <is>
+          <t>Olá Agda, lamentamos em saber do ocorrido. Nós gostaríamos muito de poder ajudar, no entanto, a equipe de redes sociais oferece suporte apenas para reservas de acomodação. Para qualquer assunto referente a uma reserva de voo, pedimos que entre em contato com a equipe dedicada para o suporte através do telefone 11 4700 8306.
+Se preferir enviar uma mensagem, por favor, siga estes passos:
+» Clique neste link: https://t.co/nBevMHsVrX
+» Faça o login na sua conta de usuária e clique na sua reserva de voo 
+» Na página "Como podemos te ajudar?", selecione o tópico com o qual precisa de ajuda, (por exemplo, "Alterações e cancelamentos")
+» Clique em "Mais opções de contato"
+» Nesta etapa, você tem a opção de administrar a sua reserva ou de enviar uma mensagem para o SAC.</t>
+        </is>
+      </c>
+      <c r="G836" t="inlineStr"/>
+      <c r="H836" t="inlineStr"/>
+      <c r="I836" t="inlineStr"/>
+      <c r="J836" t="inlineStr"/>
+      <c r="K836" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2082699318721388825</t>
+        </is>
+      </c>
+      <c r="L836" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M836" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N836" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O836" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a user’s complaint about a flight reservation, clarifying that social media support is limited to accommodation bookings and directing the user to phone and online support for flight issues.</t>
+        </is>
+      </c>
+    </row>
+    <row r="837">
+      <c r="A837" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B837" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C837" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D837" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E837" t="inlineStr">
+        <is>
+          <t>Thu Jul 30 01:32:23 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F837" t="inlineStr">
+        <is>
+          <t>Hi there, thank you for reaching out. We regret to hear about the difficulties you’ve experienced while trying to reach us and being routed only to AI. We understand how important it is for you to receive direct assistance from a human representative. How may we assist you? Please provide further details regarding your concern and the circumstances of it. If your request is related to an accommodation booking, please DM us the following details, and we'll get back to you as soon as possible:
+Confirmation number: 
+Pin code: 
+Name on the reservation: 
+Please bear in mind that our Social Media Team doesn't work in real time. For immediate support, please call our 24/7 Customer Service Team - our contact details can be found here: https://t.co/o8QyR8SaDb. 
+Also, at this time, we only offer support for accommodation bookings via social media. For questions about Flights, Taxis, or Insurance, you can reach out to the dedicated support team here: https://t.co/OVuF5pCzba.</t>
+        </is>
+      </c>
+      <c r="G837" t="inlineStr"/>
+      <c r="H837" t="inlineStr"/>
+      <c r="I837" t="inlineStr"/>
+      <c r="J837" t="inlineStr"/>
+      <c r="K837" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2082640415040164251</t>
+        </is>
+      </c>
+      <c r="L837" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M837" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N837" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O837" t="inlineStr">
+        <is>
+          <t>Booking.com addresses a customer’s difficulty contacting support, apologizes, offers assistance via DM, and directs to phone and other support channels.</t>
+        </is>
+      </c>
+    </row>
+    <row r="838">
+      <c r="A838" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B838" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C838" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D838" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E838" t="inlineStr">
+        <is>
+          <t>Thu Jul 30 01:13:33 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F838" t="inlineStr">
+        <is>
+          <t>Hi there, thank you for reaching out. We regret to hear about the difficulties you’ve experienced while trying to request a travel voucher for your flight to Bordeaux. We understand how frustrating it must have been to spend so much time going back and forth with support. As much as we’d like to assist you, we’re unable to assist with flight reservations through social media. If you need support, you can contact our Flights team using this link: https://t.co/OVuF5pCzba, or call {US}+1 917 421 7240 / {UK}+44 2039019061 / {IE} +353 19075677.</t>
+        </is>
+      </c>
+      <c r="G838" t="inlineStr"/>
+      <c r="H838" t="inlineStr"/>
+      <c r="I838" t="inlineStr"/>
+      <c r="J838" t="inlineStr"/>
+      <c r="K838" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2082635675027820650</t>
+        </is>
+      </c>
+      <c r="L838" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M838" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N838" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O838" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a customer complaint about difficulties obtaining a flight voucher, offering alternative contact options.</t>
+        </is>
+      </c>
+    </row>
+    <row r="839">
+      <c r="A839" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B839" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C839" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D839" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="E839" t="inlineStr">
+        <is>
+          <t>2026-07-30T08:00:03.895Z</t>
+        </is>
+      </c>
+      <c r="F839" t="inlineStr">
+        <is>
+          <t>At Booking.com, we believe that connection drives collaboration. 💬✨
+To kick off World Pride in Amsterdam, all six of our Employee Resource Groups (ERGs) came together for the very first time for United in Pride. This milestone event brought B.proud and our wider ERG community together under one roof to connect, collaborate, and celebrate as one.
+By combining our unique perspectives, talent, and mutual respect, we aim to create an inclusive environment where everyone can perform with confidence and show up as their fullest selves.
+Events like this remind us that when we support each other and build trust across our teams, we win as one team because here, everyone means everyone. 💙🌈</t>
+        </is>
+      </c>
+      <c r="G839" t="inlineStr">
+        <is>
+          <t>https://media.licdn.com/dms/image/v2/D4E10AQGM9ZkJKp7tSA/image-shrink_1280/B4EZ.vBaoHK8Ac-/0/1785347812701?e=1786042800&amp;v=beta&amp;t=OwyR0Cb2JHRgJtUsRPLjs8AsWp9U6uQ7sv5n1BsldTI</t>
+        </is>
+      </c>
+      <c r="H839" t="inlineStr">
+        <is>
+          <t>[easyocr not installed. Run 'pip install easyocr torch torchvision']</t>
+        </is>
+      </c>
+      <c r="I839" t="inlineStr"/>
+      <c r="J839" t="inlineStr"/>
+      <c r="K839" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/booking%2Ecom_at-bookingcom-we-believe-that-connection-activity-7488503667051003905-_5wl</t>
+        </is>
+      </c>
+      <c r="L839" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M839" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N839" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O839" t="inlineStr">
+        <is>
+          <t>Booking.com celebrated inclusion by hosting a first‑time event that brought all six of its Employee Resource Groups together for World Pride, emphasizing collaboration, diversity, and a supportive workplace culture.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/News_Dashboard/data/social_media_posts.xlsx
+++ b/News_Dashboard/data/social_media_posts.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O839"/>
+  <dimension ref="A1:O866"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -53747,6 +53747,1750 @@
         </is>
       </c>
     </row>
+    <row r="840">
+      <c r="A840" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B840" t="inlineStr">
+        <is>
+          <t>Navan</t>
+        </is>
+      </c>
+      <c r="C840" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D840" t="inlineStr">
+        <is>
+          <t>Navan</t>
+        </is>
+      </c>
+      <c r="E840" t="inlineStr">
+        <is>
+          <t>2026-07-31T15:54:59.966Z</t>
+        </is>
+      </c>
+      <c r="F840" t="inlineStr">
+        <is>
+          <t>E-invoicing mandates are coming to Europe—country by country—and Nadav Ravid has the guidance you need to handle the changes. 
+To learn more about e-invoicing, including XML receipts, local mandates, and how finance teams can stay compliant when standard invoicing tools fall short, head to the Navan blog.
+→ https://lnkd.in/ebrE5sKS</t>
+        </is>
+      </c>
+      <c r="G840" t="inlineStr"/>
+      <c r="H840" t="inlineStr"/>
+      <c r="I840" t="inlineStr">
+        <is>
+          <t>https://dms.licdn.com/playlist/vid/v2/D4E05AQHl6q7-GzpQRA/mp4-720p-30fp-crf28/B4EZ.44odJKcCQ-/0/1785513292094?e=1786129200&amp;v=beta&amp;t=XPRqummP03UTvcsptVZ7FpoOiT2W9Q6Ocyw0qgRmCIc</t>
+        </is>
+      </c>
+      <c r="J840" t="inlineStr">
+        <is>
+          <t>[faster-whisper not installed. Run 'pip install faster-whisper']</t>
+        </is>
+      </c>
+      <c r="K840" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/navan_e-invoicing-solutions-from-navan-activity-7488985576101064704-cxDs</t>
+        </is>
+      </c>
+      <c r="L840" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M840" t="inlineStr">
+        <is>
+          <t>Product Announcement</t>
+        </is>
+      </c>
+      <c r="N840" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O840" t="inlineStr">
+        <is>
+          <t>Navan is promoting its guidance on upcoming e‑invoicing mandates across Europe, directing finance teams to its blog for detailed information.</t>
+        </is>
+      </c>
+    </row>
+    <row r="841">
+      <c r="A841" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B841" t="inlineStr">
+        <is>
+          <t>TravelPerk</t>
+        </is>
+      </c>
+      <c r="C841" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D841" t="inlineStr">
+        <is>
+          <t>Perk</t>
+        </is>
+      </c>
+      <c r="E841" t="inlineStr">
+        <is>
+          <t>2026-07-31T08:01:08.693Z</t>
+        </is>
+      </c>
+      <c r="F841" t="inlineStr">
+        <is>
+          <t>"You look happier." Thanks, since using Perk MCP, my AI assistant finds the answers I need in seconds.</t>
+        </is>
+      </c>
+      <c r="G841" t="inlineStr">
+        <is>
+          <t>https://media.licdn.com/dms/image/v2/D4E10AQEoPjovjRiIMg/image-shrink_1280/B4EZ.3MFg.HsAg-/0/1785484827022?e=1786129200&amp;v=beta&amp;t=7gLd0o6R6tJKQh0neg2AWvhxxK9wXQCLH6fDdhmBhjs</t>
+        </is>
+      </c>
+      <c r="H841" t="inlineStr">
+        <is>
+          <t>[easyocr not installed. Run 'pip install easyocr torch torchvision']</t>
+        </is>
+      </c>
+      <c r="I841" t="inlineStr"/>
+      <c r="J841" t="inlineStr"/>
+      <c r="K841" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/perk_you-look-happier-thanks-since-using-perk-activity-7488866326699024386-si5V</t>
+        </is>
+      </c>
+      <c r="L841" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M841" t="inlineStr">
+        <is>
+          <t>Product Announcement</t>
+        </is>
+      </c>
+      <c r="N841" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O841" t="inlineStr">
+        <is>
+          <t>TravelPerk showcases the effectiveness of its Perk MCP AI assistant, emphasizing quick answer retrieval and user satisfaction.</t>
+        </is>
+      </c>
+    </row>
+    <row r="842">
+      <c r="A842" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B842" t="inlineStr">
+        <is>
+          <t>Ramp</t>
+        </is>
+      </c>
+      <c r="C842" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D842" t="inlineStr">
+        <is>
+          <t>tryramp</t>
+        </is>
+      </c>
+      <c r="E842" t="inlineStr">
+        <is>
+          <t>Fri Jul 31 03:27:57 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F842" t="inlineStr">
+        <is>
+          <t>@mlg27_ Big dogs rejoice</t>
+        </is>
+      </c>
+      <c r="G842" t="inlineStr"/>
+      <c r="H842" t="inlineStr"/>
+      <c r="I842" t="inlineStr"/>
+      <c r="J842" t="inlineStr"/>
+      <c r="K842" t="inlineStr">
+        <is>
+          <t>https://x.com/tryramp/status/2083031887279206760</t>
+        </is>
+      </c>
+      <c r="L842" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M842" t="inlineStr">
+        <is>
+          <t>Product Announcement</t>
+        </is>
+      </c>
+      <c r="N842" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O842" t="inlineStr">
+        <is>
+          <t>Ramp appears to be teasing a new product or initiative, encouraging major players to celebrate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="843">
+      <c r="A843" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B843" t="inlineStr">
+        <is>
+          <t>Brex</t>
+        </is>
+      </c>
+      <c r="C843" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D843" t="inlineStr">
+        <is>
+          <t>brexhq</t>
+        </is>
+      </c>
+      <c r="E843" t="inlineStr">
+        <is>
+          <t>Fri Jul 31 14:35:00 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F843" t="inlineStr">
+        <is>
+          <t>FYI, nobody starts a company because they love categorizing transactions</t>
+        </is>
+      </c>
+      <c r="G843" t="inlineStr"/>
+      <c r="H843" t="inlineStr"/>
+      <c r="I843" t="inlineStr"/>
+      <c r="J843" t="inlineStr"/>
+      <c r="K843" t="inlineStr">
+        <is>
+          <t>https://x.com/brexHQ/status/2083199755480658305</t>
+        </is>
+      </c>
+      <c r="L843" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M843" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N843" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O843" t="inlineStr">
+        <is>
+          <t>Brex remarks that categorizing transactions is not a primary motivation for startups, implying a broader focus beyond transaction classification.</t>
+        </is>
+      </c>
+    </row>
+    <row r="844">
+      <c r="A844" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B844" t="inlineStr">
+        <is>
+          <t>Expedia</t>
+        </is>
+      </c>
+      <c r="C844" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D844" t="inlineStr">
+        <is>
+          <t>Expedia</t>
+        </is>
+      </c>
+      <c r="E844" t="inlineStr">
+        <is>
+          <t>Fri Jul 31 00:00:01 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F844" t="inlineStr">
+        <is>
+          <t>Think the ultimate winter escape is a crowded Alpine ski resort? The true edge of the world is Svalbard 🇳🇴
+➡️ The Wilderness: Spot wild polar bears roaming the frozen tundra as you glide across majestic glaciers on a snowmobile
+➡️ The Sky: Chase the dancing green ribbons of the Northern Lights through the endless, mesmerizing polar night
+➡️ The Stays: Skip standard hotels and warm up in a historic, beautifully repurposed coal miner's cabin
+🔗 Plan your travel: 
+ https://t.co/OSrphBXmR9</t>
+        </is>
+      </c>
+      <c r="G844" t="inlineStr"/>
+      <c r="H844" t="inlineStr"/>
+      <c r="I844" t="inlineStr"/>
+      <c r="J844" t="inlineStr"/>
+      <c r="K844" t="inlineStr">
+        <is>
+          <t>https://x.com/Expedia/status/2082979557980721645</t>
+        </is>
+      </c>
+      <c r="L844" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M844" t="inlineStr">
+        <is>
+          <t>Product Announcement</t>
+        </is>
+      </c>
+      <c r="N844" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O844" t="inlineStr">
+        <is>
+          <t>Expedia markets Svalbard as a unique winter escape, showcasing polar bears, the Northern Lights, and historic cabin stays to entice travelers away from crowded ski resorts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="845">
+      <c r="A845" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B845" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C845" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D845" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E845" t="inlineStr">
+        <is>
+          <t>Fri Jul 31 17:53:31 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F845" t="inlineStr">
+        <is>
+          <t>@lakesalford Hi Stephen, we have sent you a reply via direct message. Please review it for more details. Thank you.</t>
+        </is>
+      </c>
+      <c r="G845" t="inlineStr"/>
+      <c r="H845" t="inlineStr"/>
+      <c r="I845" t="inlineStr"/>
+      <c r="J845" t="inlineStr"/>
+      <c r="K845" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2083249714338636221</t>
+        </is>
+      </c>
+      <c r="L845" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M845" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N845" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O845" t="inlineStr">
+        <is>
+          <t>Booking.com sent a private message to a user, presumably for follow-up.</t>
+        </is>
+      </c>
+    </row>
+    <row r="846">
+      <c r="A846" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B846" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C846" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D846" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E846" t="inlineStr">
+        <is>
+          <t>Fri Jul 31 17:20:06 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F846" t="inlineStr">
+        <is>
+          <t>@ToonTownDano We're happy to help. Feel free to reach out to us again if you have any other questions.</t>
+        </is>
+      </c>
+      <c r="G846" t="inlineStr"/>
+      <c r="H846" t="inlineStr"/>
+      <c r="I846" t="inlineStr"/>
+      <c r="J846" t="inlineStr"/>
+      <c r="K846" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2083241304364847504</t>
+        </is>
+      </c>
+      <c r="L846" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M846" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N846" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O846" t="inlineStr">
+        <is>
+          <t>Booking.com replied to a user on X, offering further assistance and expressing willingness to help.</t>
+        </is>
+      </c>
+    </row>
+    <row r="847">
+      <c r="A847" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B847" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C847" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D847" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E847" t="inlineStr">
+        <is>
+          <t>Fri Jul 31 17:14:17 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F847" t="inlineStr">
+        <is>
+          <t>@ved1985prakash3 Hi there, we acknowledge your concerns and recognize the significance of this matter to you. We kindly request that you send us a private message to facilitate a more in-depth discussion. Thank you for your patience and cooperation.</t>
+        </is>
+      </c>
+      <c r="G847" t="inlineStr"/>
+      <c r="H847" t="inlineStr"/>
+      <c r="I847" t="inlineStr"/>
+      <c r="J847" t="inlineStr"/>
+      <c r="K847" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2083239842742243512</t>
+        </is>
+      </c>
+      <c r="L847" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M847" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N847" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O847" t="inlineStr">
+        <is>
+          <t>Booking.com replied to a user’s concerns, requesting a private message for further discussion.</t>
+        </is>
+      </c>
+    </row>
+    <row r="848">
+      <c r="A848" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B848" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C848" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D848" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E848" t="inlineStr">
+        <is>
+          <t>Fri Jul 31 17:13:35 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F848" t="inlineStr">
+        <is>
+          <t>Hi Ahmet,
+Thank you for your message. We regret the inconvenience and stress this situation has caused you, especially after arriving at the property and learning that your reservation could not be honored due to a reported major leak. We understand how frustrating it must have been to arrange emergency accommodation at a significantly higher cost and then wait such a long time for an update regarding your formal complaint.
+The availability of rooms is managed directly by properties, and they're responsible for ensuring their inventory is accurate. If a property is unable to honor a reservation, they should assist guests in finding alternative accommodation. If they're unable or unwilling to do so, they should notify us as soon as possible, so we can help find a solution.
+In order for us to review your case and check the status of your complaint, kindly send us a private message with the following details:
+• Confirmation number:
+• PIN code:
+• Name on the reservation:
+We'll get back to you as soon as possible. Alternatively, for immediate support, you can always give us a call here: https://t.co/o8QyR8SaDb.</t>
+        </is>
+      </c>
+      <c r="G848" t="inlineStr"/>
+      <c r="H848" t="inlineStr"/>
+      <c r="I848" t="inlineStr"/>
+      <c r="J848" t="inlineStr"/>
+      <c r="K848" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2083239664895320167</t>
+        </is>
+      </c>
+      <c r="L848" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M848" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N848" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O848" t="inlineStr">
+        <is>
+          <t>Booking.com apologizes for a guest’s inconvenience due to a major leak at a property and offers to investigate the complaint and provide alternative accommodation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="849">
+      <c r="A849" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B849" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C849" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D849" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E849" t="inlineStr">
+        <is>
+          <t>Fri Jul 31 14:00:34 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F849" t="inlineStr">
+        <is>
+          <t>@BrendanfFoster Hi Brendan, thanks for contacting us.
+We are here to help. Please share more details regarding your request, and what you need help with. We're unsure what you mean.
+We will reply as soon as we can.</t>
+        </is>
+      </c>
+      <c r="G849" t="inlineStr"/>
+      <c r="H849" t="inlineStr"/>
+      <c r="I849" t="inlineStr"/>
+      <c r="J849" t="inlineStr"/>
+      <c r="K849" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2083191091390468103</t>
+        </is>
+      </c>
+      <c r="L849" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M849" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N849" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O849" t="inlineStr">
+        <is>
+          <t>Booking.com replied to a user’s message, requesting additional details to better assist with their inquiry.</t>
+        </is>
+      </c>
+    </row>
+    <row r="850">
+      <c r="A850" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B850" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C850" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D850" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E850" t="inlineStr">
+        <is>
+          <t>Fri Jul 31 12:53:37 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F850" t="inlineStr">
+        <is>
+          <t>Hi Pranav, thanks for contacting us.
+We checked this property page and see it now states that pets are not allowed. It's a new property, it appears they had set this up incorrectly. However, it is now corrected from what we can see.
+If you had a booking with them, we can still reach out to them on your behalf. Feel free to DM us the following details:
+- Confirmation number, 
+- Pin code, 
+- Full guest name,
+and we will get back to you as soon as possible.</t>
+        </is>
+      </c>
+      <c r="G850" t="inlineStr"/>
+      <c r="H850" t="inlineStr"/>
+      <c r="I850" t="inlineStr"/>
+      <c r="J850" t="inlineStr"/>
+      <c r="K850" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2083174242607128830</t>
+        </is>
+      </c>
+      <c r="L850" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M850" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N850" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O850" t="inlineStr">
+        <is>
+          <t>Booking.com addresses a user’s concern about a pet policy on a new property, corrects the listing, and offers to assist with any affected bookings.</t>
+        </is>
+      </c>
+    </row>
+    <row r="851">
+      <c r="A851" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B851" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C851" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D851" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E851" t="inlineStr">
+        <is>
+          <t>Fri Jul 31 11:47:47 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F851" t="inlineStr">
+        <is>
+          <t>Hello Sharon, thank you for your message. 
+We are unclear about what you mean by that. You can still reserve rooms at hotels as usual. Various policies are in place, and if you opt for a flexible booking, you can change or cancel it at no cost until the specified cut-off date. There have been no changes in that respect. 
+Wishing you a wonderful day.</t>
+        </is>
+      </c>
+      <c r="G851" t="inlineStr"/>
+      <c r="H851" t="inlineStr"/>
+      <c r="I851" t="inlineStr"/>
+      <c r="J851" t="inlineStr"/>
+      <c r="K851" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2083157674091303006</t>
+        </is>
+      </c>
+      <c r="L851" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M851" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N851" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O851" t="inlineStr">
+        <is>
+          <t>Booking.com confirms that flexible booking policies remain unchanged, allowing free changes or cancellations until the specified cut‑off date.</t>
+        </is>
+      </c>
+    </row>
+    <row r="852">
+      <c r="A852" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B852" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C852" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D852" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E852" t="inlineStr">
+        <is>
+          <t>Fri Jul 31 11:38:03 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F852" t="inlineStr">
+        <is>
+          <t>@lakesalford Hi there, we have just emailed you back. Please, check. Thank you.</t>
+        </is>
+      </c>
+      <c r="G852" t="inlineStr"/>
+      <c r="H852" t="inlineStr"/>
+      <c r="I852" t="inlineStr"/>
+      <c r="J852" t="inlineStr"/>
+      <c r="K852" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2083155225569833129</t>
+        </is>
+      </c>
+      <c r="L852" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M852" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N852" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O852" t="inlineStr">
+        <is>
+          <t>Booking.com replied to a user on X, informing them that an email has been sent.</t>
+        </is>
+      </c>
+    </row>
+    <row r="853">
+      <c r="A853" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B853" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C853" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D853" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E853" t="inlineStr">
+        <is>
+          <t>Fri Jul 31 11:30:56 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F853" t="inlineStr">
+        <is>
+          <t>@Soundie29 Hi Sean, we're unable to assist with flight reservations through social media, but you can contact our Flights team here: https://t.co/Z8ou85LCWJ, or call {US}+1 917 421 7240 / {UK}+44 2039019061 / {IE}+353 19075677. Best regards.</t>
+        </is>
+      </c>
+      <c r="G853" t="inlineStr"/>
+      <c r="H853" t="inlineStr"/>
+      <c r="I853" t="inlineStr"/>
+      <c r="J853" t="inlineStr"/>
+      <c r="K853" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2083153434417443074</t>
+        </is>
+      </c>
+      <c r="L853" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M853" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N853" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O853" t="inlineStr">
+        <is>
+          <t>Booking.com informs a user that flight reservations cannot be handled via social media and directs them to contact the Flights team via link or phone.</t>
+        </is>
+      </c>
+    </row>
+    <row r="854">
+      <c r="A854" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B854" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C854" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D854" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E854" t="inlineStr">
+        <is>
+          <t>Fri Jul 31 10:21:55 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F854" t="inlineStr">
+        <is>
+          <t>Hola, Francisca. Lamentamos los inconvenientes que estás experimentando con tu reserva. En https://t.co/fGhmZE7riF, la disponibilidad de habitaciones la gestiona directamente el alojamiento y es su responsabilidad mantenerla actualizada.
+Si un alojamiento no puede cumplir con una reserva, debería ayudarte a encontrar un lugar alternativo donde alojarte. Si no puede o no quiere hacerlo, debería informarnos lo antes posible para que podamos ayudar a encontrar una solución. En ese caso, envíanos un mensaje privado con los siguientes datos:
+- Número de confirmación:
+- Código PIN:
+- Nombre que aparece en la reserva:
+Como alternativa, para recibir ayuda inmediata siempre puedes llamarnos aquí:  https://t.co/o8QyR8SaDb.
+Un saludo.</t>
+        </is>
+      </c>
+      <c r="G854" t="inlineStr"/>
+      <c r="H854" t="inlineStr"/>
+      <c r="I854" t="inlineStr"/>
+      <c r="J854" t="inlineStr"/>
+      <c r="K854" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2083136064017793257</t>
+        </is>
+      </c>
+      <c r="L854" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M854" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N854" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O854" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a user complaint about reservation issues, offering apologies and instructions for resolving the problem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="855">
+      <c r="A855" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B855" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C855" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D855" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E855" t="inlineStr">
+        <is>
+          <t>Fri Jul 31 10:16:51 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F855" t="inlineStr">
+        <is>
+          <t>Bonjour, merci de nous avoir contactés. Nous regrettons de lire votre opinion sur nos services. Afin de pouvoir comprendre la situation et de nous permettre d'accéder à votre dossier, merci de nous envoyer, uniquement en message privé pour des raisons de confidentialité : 
+- Un récapitulatif de la situation 
+- Votre numéro de réservation 
+- Votre code confidentiel 
+- Le nom complet du voyageur sur la réservation. 
+Nous reviendrons ensuite vers vous dès que possible. 
+Cordialement.</t>
+        </is>
+      </c>
+      <c r="G855" t="inlineStr"/>
+      <c r="H855" t="inlineStr"/>
+      <c r="I855" t="inlineStr"/>
+      <c r="J855" t="inlineStr"/>
+      <c r="K855" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2083134790702600362</t>
+        </is>
+      </c>
+      <c r="L855" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M855" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N855" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O855" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a customer complaint, asking for private details to investigate the issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="856">
+      <c r="A856" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B856" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C856" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D856" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E856" t="inlineStr">
+        <is>
+          <t>Fri Jul 31 09:41:07 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F856" t="inlineStr">
+        <is>
+          <t>@alittlelateto Hi there, we regret to hear that your booking needed to be cancelled. For us to be able to look into this, we kindly ask you to DM us the following booking details: 
+- Confirmation Number
+- Pin Code
+- Name of the Guest 
+We'll than get back to you as soon as possible. https://t.co/Z89AAoEgD7</t>
+        </is>
+      </c>
+      <c r="G856" t="inlineStr"/>
+      <c r="H856" t="inlineStr"/>
+      <c r="I856" t="inlineStr"/>
+      <c r="J856" t="inlineStr"/>
+      <c r="K856" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2083125799905845489</t>
+        </is>
+      </c>
+      <c r="L856" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M856" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N856" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O856" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a cancellation request, asking the customer to DM booking details for further assistance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="857">
+      <c r="A857" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B857" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C857" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D857" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E857" t="inlineStr">
+        <is>
+          <t>Fri Jul 31 09:01:40 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F857" t="inlineStr">
+        <is>
+          <t>Hola Samuel, gracias por escribirnos. 
+Con gusto revisaremos tu cuenta para ver lo que ha sucedido y cómo podemos asistirte. Para ello, compártenos por DM tu correo electrónico y nombre completo y te responderemos tan pronto sea posible.
+Ten en cuenta que nuestro equipo de Redes Sociales no opera en tiempo real. Para asistencia inmediata puedes comunicarte con nuestro equipo de atención al cliente, disponible las 24 horas, aquí: https://t.co/tuuNbmGVaG
+Saludos.</t>
+        </is>
+      </c>
+      <c r="G857" t="inlineStr"/>
+      <c r="H857" t="inlineStr"/>
+      <c r="I857" t="inlineStr"/>
+      <c r="J857" t="inlineStr"/>
+      <c r="K857" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2083115871317233787</t>
+        </is>
+      </c>
+      <c r="L857" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M857" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N857" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O857" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a user’s inquiry via DM, offering to review their account and directing them to 24/7 customer support.</t>
+        </is>
+      </c>
+    </row>
+    <row r="858">
+      <c r="A858" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B858" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C858" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D858" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E858" t="inlineStr">
+        <is>
+          <t>Fri Jul 31 08:50:57 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F858" t="inlineStr">
+        <is>
+          <t>Hi Purity, we regret to learn that you are unable to reach our Customer Service team. 
+How can we help? Could you explain what happened?
+If you need assistance with an accommodation reservation, please share with us in a private message:
+- reservation number 
+- PIN code 
+- guest name on the reservation, 
+along with an explanation of what you require assistance with. 
+If you require assistance with a https://t.co/fGhmZE7riF account, please confirm in DM:
+- your full name 
+- email address linked to the account. 
+Please bear in mind that our Social Media Team doesn't work in real time. For immediate support, please call our 24/7 Customer Service Team - our contact details can be found here: https://t.co/tuuNbmGVaG. 
+Best regards</t>
+        </is>
+      </c>
+      <c r="G858" t="inlineStr"/>
+      <c r="H858" t="inlineStr"/>
+      <c r="I858" t="inlineStr"/>
+      <c r="J858" t="inlineStr"/>
+      <c r="K858" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2083113171091357901</t>
+        </is>
+      </c>
+      <c r="L858" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M858" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N858" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O858" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a customer’s difficulty contacting support, offering private message details and phone support options.</t>
+        </is>
+      </c>
+    </row>
+    <row r="859">
+      <c r="A859" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B859" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C859" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D859" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E859" t="inlineStr">
+        <is>
+          <t>Fri Jul 31 08:40:11 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F859" t="inlineStr">
+        <is>
+          <t>Hola, Manuel. Lamentamos que tu reserva haya sido cancelada. En https://t.co/fGhmZE7riF, la disponibilidad de habitaciones la gestiona directamente el alojamiento y es su responsabilidad mantenerla actualizada. 
+Si un alojamiento no puede cumplir con una reserva, debería ayudarte a encontrar un lugar alternativo donde alojarte. Si no puede o no quiere hacerlo, debería informarnos lo antes posible para que podamos ayudar a encontrar una solución. En ese caso, envíanos un mensaje privado con los siguientes datos: 
+- Número de confirmación: 
+- Código PIN: 
+- Nombre que aparece en la reserva: 
+Como alternativa, para recibir ayuda inmediata siempre puedes llamarnos aquí: https://t.co/o8QyR8SaDb. 
+Un saludo.</t>
+        </is>
+      </c>
+      <c r="G859" t="inlineStr"/>
+      <c r="H859" t="inlineStr"/>
+      <c r="I859" t="inlineStr"/>
+      <c r="J859" t="inlineStr"/>
+      <c r="K859" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2083110463638741012</t>
+        </is>
+      </c>
+      <c r="L859" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="M859" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N859" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O859" t="inlineStr">
+        <is>
+          <t>Booking.com apologizes to a user for a canceled reservation, explains that the property manages availability, and offers assistance to find alternative accommodation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="860">
+      <c r="A860" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B860" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C860" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D860" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E860" t="inlineStr">
+        <is>
+          <t>Fri Jul 31 07:48:41 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F860" t="inlineStr">
+        <is>
+          <t>Hola, Mochi. Lamentamos que sigas a la espera de tu reembolso. Aunque nos gustaría, no podemos ayudarte con reservas de Vuelos a través de las redes sociales, pero puedes contactar con nuestro equipo de Vuelos aquí: https://t.co/TBejpc4vOA, o llamar al +34918362949 desde España de lunes a domingo de 9:00-21:00 hora local.
+Un saludo.</t>
+        </is>
+      </c>
+      <c r="G860" t="inlineStr"/>
+      <c r="H860" t="inlineStr"/>
+      <c r="I860" t="inlineStr"/>
+      <c r="J860" t="inlineStr"/>
+      <c r="K860" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2083097503944024414</t>
+        </is>
+      </c>
+      <c r="L860" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M860" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N860" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O860" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a user’s refund request, apologizes for not handling flight bookings via X, and directs them to the flight support team and phone number.</t>
+        </is>
+      </c>
+    </row>
+    <row r="861">
+      <c r="A861" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B861" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C861" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D861" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E861" t="inlineStr">
+        <is>
+          <t>Fri Jul 31 07:24:55 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F861" t="inlineStr">
+        <is>
+          <t>@tony_vatoloco - Numéro de confirmation :
+- Code confidentiel :
+- Nom indiqué sur la réservation :
+- Détails concernant votre séjour :
+Pour une assistance immédiate, vous pouvez également nous appeler ici : https://t.co/aH74XgSLGq</t>
+        </is>
+      </c>
+      <c r="G861" t="inlineStr"/>
+      <c r="H861" t="inlineStr"/>
+      <c r="I861" t="inlineStr"/>
+      <c r="J861" t="inlineStr"/>
+      <c r="K861" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2083091523059483006</t>
+        </is>
+      </c>
+      <c r="L861" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="M861" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N861" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O861" t="inlineStr">
+        <is>
+          <t>The post appears to be a phishing attempt masquerading as a Booking.com booking confirmation, potentially misleading users and indicating a security threat.</t>
+        </is>
+      </c>
+    </row>
+    <row r="862">
+      <c r="A862" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B862" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C862" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D862" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E862" t="inlineStr">
+        <is>
+          <t>Fri Jul 31 07:24:31 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F862" t="inlineStr">
+        <is>
+          <t>@tony_vatoloco Nous regrettons de lire votre déception concernant le fait que vous soyez encore en attente de votre remboursement. Afin que nous puissions vous assister ici, merci de nous envoyer un message privé avec les informations suivantes :</t>
+        </is>
+      </c>
+      <c r="G862" t="inlineStr"/>
+      <c r="H862" t="inlineStr"/>
+      <c r="I862" t="inlineStr"/>
+      <c r="J862" t="inlineStr"/>
+      <c r="K862" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2083091421624447449</t>
+        </is>
+      </c>
+      <c r="L862" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M862" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N862" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O862" t="inlineStr">
+        <is>
+          <t>Booking.com apologizes to a user for a pending refund and requests private message details to assist.</t>
+        </is>
+      </c>
+    </row>
+    <row r="863">
+      <c r="A863" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B863" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C863" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D863" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E863" t="inlineStr">
+        <is>
+          <t>Fri Jul 31 07:24:18 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F863" t="inlineStr">
+        <is>
+          <t>@tony_vatoloco Bonjour Tony, toutes nos excuses pour ce délai de réponse.
+Nous recevons actuellement un volume important de demandes sur les réseaux sociaux, ce qui ne nous a pas permis de vous répondre plus tôt.</t>
+        </is>
+      </c>
+      <c r="G863" t="inlineStr"/>
+      <c r="H863" t="inlineStr"/>
+      <c r="I863" t="inlineStr"/>
+      <c r="J863" t="inlineStr"/>
+      <c r="K863" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2083091365303308559</t>
+        </is>
+      </c>
+      <c r="L863" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M863" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N863" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O863" t="inlineStr">
+        <is>
+          <t>Booking.com apologized to a user for a delayed response due to a high volume of social media inquiries.</t>
+        </is>
+      </c>
+    </row>
+    <row r="864">
+      <c r="A864" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B864" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C864" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D864" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E864" t="inlineStr">
+        <is>
+          <t>Fri Jul 31 07:20:09 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F864" t="inlineStr">
+        <is>
+          <t>@FLYINGSMCOIN Hi there, we regret to hear about your experiences. For us to be able to look into this, we kindly ask you to DM us the following booking details: 
+- Confirmation Number
+- Pin Code
+- Name of the Guest 
+We'll than get back to you as soon as possible. https://t.co/Z89AAoEgD7</t>
+        </is>
+      </c>
+      <c r="G864" t="inlineStr"/>
+      <c r="H864" t="inlineStr"/>
+      <c r="I864" t="inlineStr"/>
+      <c r="J864" t="inlineStr"/>
+      <c r="K864" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2083090321114546343</t>
+        </is>
+      </c>
+      <c r="L864" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M864" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N864" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O864" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a customer complaint on X, requesting booking details via DM to investigate the issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="865">
+      <c r="A865" t="inlineStr">
+        <is>
+          <t>Mondee</t>
+        </is>
+      </c>
+      <c r="B865" t="inlineStr">
+        <is>
+          <t>Sky Bird Travel</t>
+        </is>
+      </c>
+      <c r="C865" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D865" t="inlineStr">
+        <is>
+          <t>SkyBirdTravel</t>
+        </is>
+      </c>
+      <c r="E865" t="inlineStr">
+        <is>
+          <t>Fri Jul 31 16:16:23 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F865" t="inlineStr">
+        <is>
+          <t>Skip the luggage hassle with BagDrop! ✈️🧳 Your bags go Airport → Home, securely delivered so you enjoy the journey stress‑free.
+#TravelMadeEasy #BagDrop #IndiaTravel #SkyBird #TravelSmart https://t.co/xcODGHDOYR</t>
+        </is>
+      </c>
+      <c r="G865" t="inlineStr"/>
+      <c r="H865" t="inlineStr"/>
+      <c r="I865" t="inlineStr"/>
+      <c r="J865" t="inlineStr"/>
+      <c r="K865" t="inlineStr">
+        <is>
+          <t>https://x.com/SkyBirdTravel/status/2083225269322866703</t>
+        </is>
+      </c>
+      <c r="L865" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M865" t="inlineStr">
+        <is>
+          <t>Product Announcement</t>
+        </is>
+      </c>
+      <c r="N865" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O865" t="inlineStr">
+        <is>
+          <t>Sky Bird Travel promotes its new BagDrop service, offering secure luggage delivery from airport to home to simplify travel.</t>
+        </is>
+      </c>
+    </row>
+    <row r="866">
+      <c r="A866" t="inlineStr">
+        <is>
+          <t>Mondee</t>
+        </is>
+      </c>
+      <c r="B866" t="inlineStr">
+        <is>
+          <t>Sky Bird Travel</t>
+        </is>
+      </c>
+      <c r="C866" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D866" t="inlineStr">
+        <is>
+          <t>Sky Bird Travel &amp; Tours</t>
+        </is>
+      </c>
+      <c r="E866" t="inlineStr">
+        <is>
+          <t>2026-07-31T16:15:21.233Z</t>
+        </is>
+      </c>
+      <c r="F866" t="inlineStr">
+        <is>
+          <t>Help your clients skip the stress of traveling with heavy luggage by booking BagDrop’s Airport-to-Home Baggage Delivery service. Their bags are picked up, securely handled, and delivered straight to their destination—so they can focus on enjoying the journey. 
+Offer your clients a smoother travel experience from the moment they land. 
+#TravelMadeEasy #TravelAdvisor #BagDrop #IndiaTravel #BaggageDelivery #SkyBird #TravelSolutions #TravelSmart</t>
+        </is>
+      </c>
+      <c r="G866" t="inlineStr">
+        <is>
+          <t>https://media.licdn.com/dms/image/v2/D5622AQFxZAkGc1JZsw/feedshare-shrink_1280/B56Z.49WtTHYAM-/0/1785514520155?e=1787184000&amp;v=beta&amp;t=qDI_yuyQA8Agj_sfkTXxgwFvKy4HD-AwPYnhcEORI6w</t>
+        </is>
+      </c>
+      <c r="H866" t="inlineStr">
+        <is>
+          <t>[easyocr not installed. Run 'pip install easyocr torch torchvision']</t>
+        </is>
+      </c>
+      <c r="I866" t="inlineStr"/>
+      <c r="J866" t="inlineStr"/>
+      <c r="K866" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/sky-bird-travel-tours_travelmadeeasy-traveladvisor-bagdrop-activity-7488990698466365441-OjSk</t>
+        </is>
+      </c>
+      <c r="L866" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M866" t="inlineStr">
+        <is>
+          <t>Product Announcement</t>
+        </is>
+      </c>
+      <c r="N866" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O866" t="inlineStr">
+        <is>
+          <t>Sky Bird Travel promotes BagDrop’s Airport-to-Home Baggage Delivery service, highlighting its convenience and secure handling to enhance client travel experiences.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/News_Dashboard/data/social_media_posts.xlsx
+++ b/News_Dashboard/data/social_media_posts.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O866"/>
+  <dimension ref="A1:O890"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55491,6 +55491,1520 @@
         </is>
       </c>
     </row>
+    <row r="867">
+      <c r="A867" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B867" t="inlineStr">
+        <is>
+          <t>AirBnb</t>
+        </is>
+      </c>
+      <c r="C867" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="D867" t="inlineStr">
+        <is>
+          <t>airbnb</t>
+        </is>
+      </c>
+      <c r="E867" t="inlineStr">
+        <is>
+          <t>2026-07-31T20:00:04.000Z</t>
+        </is>
+      </c>
+      <c r="F867" t="inlineStr">
+        <is>
+          <t>📍Miami, Florida
+🚨Sunny found an all-time top-five stick on this very property. Book before someone takes it.</t>
+        </is>
+      </c>
+      <c r="G867" t="inlineStr">
+        <is>
+          <t>https://scontent-yyz1-1.cdninstagram.com/v/t51.82787-15/759698425_18618850282063838_2516356816793735879_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_ht=scontent-yyz1-1.cdninstagram.com&amp;_nc_cat=102&amp;_nc_oc=Q6cZ2gGnl3AwhtxBKjO1ppzPM6So7D2wGYfMs203IQbf5tiGsQ-cKxos-xjoBYU6Ig7UGtk&amp;_nc_ohc=XaE9L8l_AeAQ7kNvwH12u0D&amp;_nc_gid=A-AcFaXIfQl57ugIbwMWXQ&amp;edm=ADp7STQBAAAA&amp;ccb=7-5&amp;oh=00_AQG4PqBvr-tY6_qsEBCVjEULyXZTmeBbPKn2QgHpMn6ECg&amp;oe=6A74198B&amp;_nc_sid=c6f216</t>
+        </is>
+      </c>
+      <c r="H867" t="inlineStr">
+        <is>
+          <t>[easyocr not installed. Run 'pip install easyocr torch torchvision']</t>
+        </is>
+      </c>
+      <c r="I867" t="inlineStr">
+        <is>
+          <t>https://scontent-yyz1-1.cdninstagram.com/o1/v/t2/f2/m86/AQN4io0hDLkRClxS8ffh0ADPgLpL1OuEUvK5QhjZsfAJS4BXCB-LgX23S79HP5Ihr4O5eIXJUBePliacVDfmZ6Umql-KbP5cYSQhyRA.mp4?_nc_cat=111&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-yyz1-1.cdninstagram.com&amp;_nc_ohc=ovJ0uiRIclsQ7kNvwFe07dP&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uQ0xJUFMuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTQ1ODk5ODY3MjkxODY3NiwiYXNzZXRfYWdlX2RheXMiOjEsInZpX3VzZWNhc2VfaWQiOjEwMDk5LCJkdXJhdGlvbl9zIjoxNjcsInVybGdlbl9zb3VyY2UiOiJ3d3cifQ%3D%3D&amp;ccb=17-1&amp;vs=5e20830643f4fc5a&amp;_nc_vs=HBksFQIYUmlnX3hwdl9yZWVsc19wZXJtYW5lbnRfc3JfcHJvZC82MjQ0RjZDMzI0RkMxNjlEQUIzQjYwRkJBMDEzMjc5NV92aWRlb19kYXNoaW5pdC5tcDQVAALIARIAFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyL0E3NDdGMTc3MkE2Q0VDQUU0RTVBNTMzQjlDMTI3NDkwX2F1ZGlvX2Rhc2hpbml0Lm1wNBUCAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACaoooSa87yXBRUCKAJDMywXQGThT987ZFoYEmRhc2hfYmFzZWxpbmVfMV92MREAdf4HZeadAQA&amp;_nc_gid=A-AcFaXIfQl57ugIbwMWXQ&amp;_nc_ss=7a22e&amp;_nc_zt=28&amp;oh=00_AQFAOnbqYbtPX5ir3q-BGgEL8spAtVoTiCAZluXQWGk3ZQ&amp;oe=6A6FFF04</t>
+        </is>
+      </c>
+      <c r="J867" t="inlineStr">
+        <is>
+          <t>[faster-whisper not installed. Run 'pip install faster-whisper']</t>
+        </is>
+      </c>
+      <c r="K867" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DbeEuxmBM1Y/</t>
+        </is>
+      </c>
+      <c r="L867" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M867" t="inlineStr">
+        <is>
+          <t>Product Announcement</t>
+        </is>
+      </c>
+      <c r="N867" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O867" t="inlineStr">
+        <is>
+          <t>Airbnb promotes a highly rated property in Miami, urging potential guests to book before it’s taken.</t>
+        </is>
+      </c>
+    </row>
+    <row r="868">
+      <c r="A868" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B868" t="inlineStr">
+        <is>
+          <t>Expedia</t>
+        </is>
+      </c>
+      <c r="C868" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D868" t="inlineStr">
+        <is>
+          <t>Expedia</t>
+        </is>
+      </c>
+      <c r="E868" t="inlineStr">
+        <is>
+          <t>Sat Aug 01 00:00:01 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F868" t="inlineStr">
+        <is>
+          <t>Think the world's most dramatic landscapes are already crowded? The untouched magic is in Fiordland National Park 🇳🇿
+➡️ The Fjords: Sail the glass-like waters of Milford Sound past towering cliffs and crashing waterfalls
+➡️ The Trails: Hike the legendary Kepler Track through ancient mossy beech forests and alpine ridges
+➡️ The Stays: Skip standard hotels and sleep in a luxury eco-lodge surrounded by deep native bush
+🔗 Plan your travel: https://t.co/ekGdA9D3Jp</t>
+        </is>
+      </c>
+      <c r="G868" t="inlineStr"/>
+      <c r="H868" t="inlineStr"/>
+      <c r="I868" t="inlineStr"/>
+      <c r="J868" t="inlineStr"/>
+      <c r="K868" t="inlineStr">
+        <is>
+          <t>https://x.com/Expedia/status/2083341946068574235</t>
+        </is>
+      </c>
+      <c r="L868" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M868" t="inlineStr">
+        <is>
+          <t>Product Announcement</t>
+        </is>
+      </c>
+      <c r="N868" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O868" t="inlineStr">
+        <is>
+          <t>Expedia promotes a travel package to Fiordland National Park, highlighting fjords, trails, and luxury eco-lodge stays to entice travelers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="869">
+      <c r="A869" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B869" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C869" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D869" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E869" t="inlineStr">
+        <is>
+          <t>Sat Aug 01 17:41:48 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F869" t="inlineStr">
+        <is>
+          <t>@heatherdrover1 Greetings Heather, we sincerely appreciate your patience, and understanding. A message has been sent to you privately, and we kindly request that you refer to that message for further information. Thank you for your understanding; it is greatly valued.</t>
+        </is>
+      </c>
+      <c r="G869" t="inlineStr"/>
+      <c r="H869" t="inlineStr"/>
+      <c r="I869" t="inlineStr"/>
+      <c r="J869" t="inlineStr"/>
+      <c r="K869" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2083609152404775060</t>
+        </is>
+      </c>
+      <c r="L869" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M869" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N869" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O869" t="inlineStr">
+        <is>
+          <t>Booking.com replied to a user’s inquiry with a polite message, directing them to a private message for further details.</t>
+        </is>
+      </c>
+    </row>
+    <row r="870">
+      <c r="A870" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B870" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C870" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D870" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E870" t="inlineStr">
+        <is>
+          <t>Sat Aug 01 13:50:38 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F870" t="inlineStr">
+        <is>
+          <t>@Soundie29 We understand your frustration, Sean, but due to GDPR reasons, only our specialized team has access to your information and the tools required to help.</t>
+        </is>
+      </c>
+      <c r="G870" t="inlineStr"/>
+      <c r="H870" t="inlineStr"/>
+      <c r="I870" t="inlineStr"/>
+      <c r="J870" t="inlineStr"/>
+      <c r="K870" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2083550980650451269</t>
+        </is>
+      </c>
+      <c r="L870" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M870" t="inlineStr">
+        <is>
+          <t>Tech Updates</t>
+        </is>
+      </c>
+      <c r="N870" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O870" t="inlineStr">
+        <is>
+          <t>Booking.com addresses a user’s frustration about data access, explaining that GDPR limits external access and only a specialized team can handle the request.</t>
+        </is>
+      </c>
+    </row>
+    <row r="871">
+      <c r="A871" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B871" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C871" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D871" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E871" t="inlineStr">
+        <is>
+          <t>Sat Aug 01 13:32:02 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F871" t="inlineStr">
+        <is>
+          <t>Hi Heather, we appreciate your message. We are sorry that the alternatives our agents sent to you were not suitable for you, and as stated in our email, if you choose to arrange alternative accommodation on your own, we might be able to help with any price difference. All the relevant information is included in that email. 
+If you have any additional questions, feel free to direct message us. Please remember that our Social Media Team does not operate in real time. For urgent assistance, please contact our 24/7 Customer Service Team; you can find our contact details here: https://t.co/o8QyR8SaDb. Thank you.</t>
+        </is>
+      </c>
+      <c r="G871" t="inlineStr"/>
+      <c r="H871" t="inlineStr"/>
+      <c r="I871" t="inlineStr"/>
+      <c r="J871" t="inlineStr"/>
+      <c r="K871" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2083546298196639920</t>
+        </is>
+      </c>
+      <c r="L871" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M871" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N871" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O871" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a customer complaint, apologizes for unsuitable alternatives, offers assistance with price differences, and directs the customer to 24/7 support.</t>
+        </is>
+      </c>
+    </row>
+    <row r="872">
+      <c r="A872" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B872" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C872" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D872" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E872" t="inlineStr">
+        <is>
+          <t>Sat Aug 01 13:07:51 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F872" t="inlineStr">
+        <is>
+          <t>@Uzairwithu Hi Uzair, we replied to your DM.</t>
+        </is>
+      </c>
+      <c r="G872" t="inlineStr"/>
+      <c r="H872" t="inlineStr"/>
+      <c r="I872" t="inlineStr"/>
+      <c r="J872" t="inlineStr"/>
+      <c r="K872" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2083540213343699329</t>
+        </is>
+      </c>
+      <c r="L872" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M872" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N872" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O872" t="inlineStr">
+        <is>
+          <t>Booking.com replied to a direct message from user @Uzairwithu.</t>
+        </is>
+      </c>
+    </row>
+    <row r="873">
+      <c r="A873" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B873" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C873" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D873" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E873" t="inlineStr">
+        <is>
+          <t>Sat Aug 01 10:05:33 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F873" t="inlineStr">
+        <is>
+          <t>Many thanks for getting back to us, and we regret to hear about your opinion regarding our services. 
+If you need further assistance with that reservation, please provide us with the additional info via private message, so we can get in touch with our dedicated team. They'll then review your request as soon as possible. Thank you.</t>
+        </is>
+      </c>
+      <c r="G873" t="inlineStr"/>
+      <c r="H873" t="inlineStr"/>
+      <c r="I873" t="inlineStr"/>
+      <c r="J873" t="inlineStr"/>
+      <c r="K873" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2083494335056609626</t>
+        </is>
+      </c>
+      <c r="L873" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M873" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N873" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O873" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a customer complaint on X, offering further assistance via private message.</t>
+        </is>
+      </c>
+    </row>
+    <row r="874">
+      <c r="A874" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B874" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C874" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D874" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E874" t="inlineStr">
+        <is>
+          <t>Sat Aug 01 08:51:47 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F874" t="inlineStr">
+        <is>
+          <t>@ahmed3gaber Hi there, 
+You recently reached out to us regarding your Car Rental reservation, but we haven't heard back from you. If you still need assistance, please send us a private message informing:
+- Name of booker
+- Email address used to book
+- Your request
+Many thanks. https://t.co/Z89AAoEgD7</t>
+        </is>
+      </c>
+      <c r="G874" t="inlineStr"/>
+      <c r="H874" t="inlineStr"/>
+      <c r="I874" t="inlineStr"/>
+      <c r="J874" t="inlineStr"/>
+      <c r="K874" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2083475771431997521</t>
+        </is>
+      </c>
+      <c r="L874" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M874" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N874" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O874" t="inlineStr">
+        <is>
+          <t>Booking.com followed up with a customer regarding a car rental reservation, requesting the booker's name, email, and request details via private message.</t>
+        </is>
+      </c>
+    </row>
+    <row r="875">
+      <c r="A875" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B875" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C875" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D875" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E875" t="inlineStr">
+        <is>
+          <t>Sat Aug 01 08:49:30 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F875" t="inlineStr">
+        <is>
+          <t>@TheLongHold__ Hi there, 
+You recently reached out to us regarding your Car Rental reservation, but we haven't heard back from you. If you still need assistance, please send us a private message informing:
+- Name of booker
+- Email address used to book
+Many thanks. https://t.co/Z89AAoEgD7</t>
+        </is>
+      </c>
+      <c r="G875" t="inlineStr"/>
+      <c r="H875" t="inlineStr"/>
+      <c r="I875" t="inlineStr"/>
+      <c r="J875" t="inlineStr"/>
+      <c r="K875" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2083475195537346693</t>
+        </is>
+      </c>
+      <c r="L875" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M875" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N875" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O875" t="inlineStr">
+        <is>
+          <t>Booking.com sent a follow‑up message to a customer about a car rental reservation, asking for the booker's name and email via private message.</t>
+        </is>
+      </c>
+    </row>
+    <row r="876">
+      <c r="A876" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B876" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C876" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D876" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E876" t="inlineStr">
+        <is>
+          <t>Sat Aug 01 07:58:34 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F876" t="inlineStr">
+        <is>
+          <t>@cleansewhitey Hi there, we replied to your DM.</t>
+        </is>
+      </c>
+      <c r="G876" t="inlineStr"/>
+      <c r="H876" t="inlineStr"/>
+      <c r="I876" t="inlineStr"/>
+      <c r="J876" t="inlineStr"/>
+      <c r="K876" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2083462379258380557</t>
+        </is>
+      </c>
+      <c r="L876" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M876" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N876" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O876" t="inlineStr">
+        <is>
+          <t>Booking.com replied to a direct message from user @cleansewhitey.</t>
+        </is>
+      </c>
+    </row>
+    <row r="877">
+      <c r="A877" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B877" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C877" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D877" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E877" t="inlineStr">
+        <is>
+          <t>Sat Aug 01 04:35:43 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F877" t="inlineStr">
+        <is>
+          <t>Hi Heather, we understand your frustration about what happened with your reservation. As previously communicated, we have already forwarded this to our internal team, and we are still waiting for their investigation. Thank you for your patience in waiting for the email to be sent with the updates.</t>
+        </is>
+      </c>
+      <c r="G877" t="inlineStr"/>
+      <c r="H877" t="inlineStr"/>
+      <c r="I877" t="inlineStr"/>
+      <c r="J877" t="inlineStr"/>
+      <c r="K877" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2083411330048860495</t>
+        </is>
+      </c>
+      <c r="L877" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M877" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N877" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O877" t="inlineStr">
+        <is>
+          <t>Booking.com is responding to a customer complaint about a reservation issue and informing them that the internal team is investigating.</t>
+        </is>
+      </c>
+    </row>
+    <row r="878">
+      <c r="A878" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B878" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C878" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D878" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E878" t="inlineStr">
+        <is>
+          <t>Sat Aug 01 01:54:59 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F878" t="inlineStr">
+        <is>
+          <t>@ohahepsidolu Hi there, we have responded to your message privately. Please check it at your earliest convenience.</t>
+        </is>
+      </c>
+      <c r="G878" t="inlineStr"/>
+      <c r="H878" t="inlineStr"/>
+      <c r="I878" t="inlineStr"/>
+      <c r="J878" t="inlineStr"/>
+      <c r="K878" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2083370880474710221</t>
+        </is>
+      </c>
+      <c r="L878" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M878" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N878" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O878" t="inlineStr">
+        <is>
+          <t>Booking.com replied to a private message from a user, offering a response via direct communication.</t>
+        </is>
+      </c>
+    </row>
+    <row r="879">
+      <c r="A879" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B879" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C879" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D879" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E879" t="inlineStr">
+        <is>
+          <t>Sat Aug 01 01:54:38 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F879" t="inlineStr">
+        <is>
+          <t>@PearlySwan Hi Ritzy, we understand the urgency of your concern. We have responded to your message privately. Kindly check it at your earliest convenience. Thank you.</t>
+        </is>
+      </c>
+      <c r="G879" t="inlineStr"/>
+      <c r="H879" t="inlineStr"/>
+      <c r="I879" t="inlineStr"/>
+      <c r="J879" t="inlineStr"/>
+      <c r="K879" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2083370792788623840</t>
+        </is>
+      </c>
+      <c r="L879" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M879" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N879" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O879" t="inlineStr">
+        <is>
+          <t>Booking.com replied to a user’s private concern, acknowledging urgency and directing them to check a private message.</t>
+        </is>
+      </c>
+    </row>
+    <row r="880">
+      <c r="A880" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B880" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C880" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D880" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E880" t="inlineStr">
+        <is>
+          <t>Sat Aug 01 01:27:39 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F880" t="inlineStr">
+        <is>
+          <t>@PearlySwan Hi Ritzy, we've contacted you through direct message regarding this matter. Kindly check your messages for further support.</t>
+        </is>
+      </c>
+      <c r="G880" t="inlineStr"/>
+      <c r="H880" t="inlineStr"/>
+      <c r="I880" t="inlineStr"/>
+      <c r="J880" t="inlineStr"/>
+      <c r="K880" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2083363999379247415</t>
+        </is>
+      </c>
+      <c r="L880" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M880" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N880" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O880" t="inlineStr">
+        <is>
+          <t>Booking.com sent a direct message to a user offering support.</t>
+        </is>
+      </c>
+    </row>
+    <row r="881">
+      <c r="A881" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B881" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C881" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D881" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E881" t="inlineStr">
+        <is>
+          <t>Sat Aug 01 01:19:13 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F881" t="inlineStr">
+        <is>
+          <t>Hi there, we regret that your host cancelled the reservation on the day of arrival and that you were left looking for accommodation in Montreal while travelling with your family. The availability of the rooms is set up by the properties themselves, and they're solely responsible for making sure this is correct. We don't decide on behalf of the property how many (if any) rooms they want to have available to book through our platform for any given date.
+If a property is unable to honor a booking, they should help you find another place to stay. If they're unable or unwilling to provide this, they should let us know as soon as possible so that we can help to find a solution. Please DM us the following details:
+• Confirmation number:
+• PIN code:
+• Name on the reservation:
+Alternatively, for immediate support, you can always give us a call here: https://t.co/o8QyR8SaDb.</t>
+        </is>
+      </c>
+      <c r="G881" t="inlineStr"/>
+      <c r="H881" t="inlineStr"/>
+      <c r="I881" t="inlineStr"/>
+      <c r="J881" t="inlineStr"/>
+      <c r="K881" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2083361876721721718</t>
+        </is>
+      </c>
+      <c r="L881" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="M881" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N881" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O881" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a host cancellation incident, explaining that property owners control availability and offering support to affected guests.</t>
+        </is>
+      </c>
+    </row>
+    <row r="882">
+      <c r="A882" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B882" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C882" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D882" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E882" t="inlineStr">
+        <is>
+          <t>Sat Aug 01 00:59:06 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F882" t="inlineStr">
+        <is>
+          <t>@AzizS_ Hi there, we would like to inform you that we have responded to your message. Please check it at your earliest convenience.</t>
+        </is>
+      </c>
+      <c r="G882" t="inlineStr"/>
+      <c r="H882" t="inlineStr"/>
+      <c r="I882" t="inlineStr"/>
+      <c r="J882" t="inlineStr"/>
+      <c r="K882" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2083356816235250123</t>
+        </is>
+      </c>
+      <c r="L882" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M882" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N882" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O882" t="inlineStr">
+        <is>
+          <t>Booking.com replied to a user’s message, indicating routine customer support engagement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="883">
+      <c r="A883" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B883" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C883" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D883" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E883" t="inlineStr">
+        <is>
+          <t>Sat Aug 01 00:54:05 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F883" t="inlineStr">
+        <is>
+          <t>@PearlySwan Hi Ritzy, we have sent you a private message regarding your inquiry. Please check your messages for further assistance.</t>
+        </is>
+      </c>
+      <c r="G883" t="inlineStr"/>
+      <c r="H883" t="inlineStr"/>
+      <c r="I883" t="inlineStr"/>
+      <c r="J883" t="inlineStr"/>
+      <c r="K883" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2083355555486138725</t>
+        </is>
+      </c>
+      <c r="L883" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M883" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N883" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O883" t="inlineStr">
+        <is>
+          <t>Booking.com replied to a user inquiry via private message.</t>
+        </is>
+      </c>
+    </row>
+    <row r="884">
+      <c r="A884" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B884" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C884" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D884" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E884" t="inlineStr">
+        <is>
+          <t>Fri Jul 31 23:31:57 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F884" t="inlineStr">
+        <is>
+          <t>@heatherdrover1 Hi Heather, we have sent you a private message regarding your inquiry. Please check your messages for further assistance.</t>
+        </is>
+      </c>
+      <c r="G884" t="inlineStr"/>
+      <c r="H884" t="inlineStr"/>
+      <c r="I884" t="inlineStr"/>
+      <c r="J884" t="inlineStr"/>
+      <c r="K884" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2083334882214695421</t>
+        </is>
+      </c>
+      <c r="L884" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M884" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N884" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O884" t="inlineStr">
+        <is>
+          <t>Booking.com replied to a customer inquiry via a private message on X.</t>
+        </is>
+      </c>
+    </row>
+    <row r="885">
+      <c r="A885" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B885" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C885" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D885" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E885" t="inlineStr">
+        <is>
+          <t>Fri Jul 31 22:44:59 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F885" t="inlineStr">
+        <is>
+          <t>Hi Pranav, we regret to hear this. We recommend that you never share the PIN code of your reservation in public, as it can allow others to access your personal details. To help protect your information, we recommend that you delete your comment. We’ve also replied to your direct message, so please take a moment to review it when you can. Thank you.</t>
+        </is>
+      </c>
+      <c r="G885" t="inlineStr"/>
+      <c r="H885" t="inlineStr"/>
+      <c r="I885" t="inlineStr"/>
+      <c r="J885" t="inlineStr"/>
+      <c r="K885" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2083323066189275488</t>
+        </is>
+      </c>
+      <c r="L885" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M885" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N885" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O885" t="inlineStr">
+        <is>
+          <t>Booking.com addresses a user’s concern about sharing a reservation PIN, advising them to delete the public comment and review a private message for further guidance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="886">
+      <c r="A886" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B886" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C886" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D886" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E886" t="inlineStr">
+        <is>
+          <t>Fri Jul 31 22:42:01 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F886" t="inlineStr">
+        <is>
+          <t>@taabi1998 Hi there, we appreciate you reaching out to us and understand the urgency of your concern. To further assist you we have responded to your message privately. Kindly look into to it for more details. Thank you.</t>
+        </is>
+      </c>
+      <c r="G886" t="inlineStr"/>
+      <c r="H886" t="inlineStr"/>
+      <c r="I886" t="inlineStr"/>
+      <c r="J886" t="inlineStr"/>
+      <c r="K886" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2083322319708025257</t>
+        </is>
+      </c>
+      <c r="L886" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M886" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N886" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O886" t="inlineStr">
+        <is>
+          <t>Booking.com replied to a user’s inquiry via private message, acknowledging the urgency and directing them to a private response.</t>
+        </is>
+      </c>
+    </row>
+    <row r="887">
+      <c r="A887" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B887" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C887" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D887" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E887" t="inlineStr">
+        <is>
+          <t>Fri Jul 31 22:24:15 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F887" t="inlineStr">
+        <is>
+          <t>Hi Toby, thank you for reaching out to us and, we regret about your ticket. Unfortunately, as much as we'd like to assist you, we're unable to offer support for Attraction reservations through social media. Alternatively, you can get in touch with our specialized team here: https://t.co/9ItyvAXTr1.</t>
+        </is>
+      </c>
+      <c r="G887" t="inlineStr"/>
+      <c r="H887" t="inlineStr"/>
+      <c r="I887" t="inlineStr"/>
+      <c r="J887" t="inlineStr"/>
+      <c r="K887" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2083317848861004276</t>
+        </is>
+      </c>
+      <c r="L887" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="M887" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N887" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O887" t="inlineStr">
+        <is>
+          <t>Booking.com apologizes to a user for not being able to assist with attraction reservations via social media and directs them to a specialized support team.</t>
+        </is>
+      </c>
+    </row>
+    <row r="888">
+      <c r="A888" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B888" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C888" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D888" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E888" t="inlineStr">
+        <is>
+          <t>Fri Jul 31 22:21:56 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F888" t="inlineStr">
+        <is>
+          <t>Hi there, we regret that the property was unable to accommodate you and understand your concerns regarding the reported issue involving an external payment request and the cancellation of your reservation on the day of check-in. The availability of the rooms is set up by the properties themselves, and they are solely responsible for making sure this is correct. We don't decide on behalf of the property how many rooms they want to have available to book through our platform for any given date.
+Additionally, properties provide the information on our website and have to pass a verification procedure before becoming bookable. If we find that a property listed on our platform is providing false information, we investigate immediately, give them the opportunity to rectify, or we may remove them from our website accordingly.
+If a property is unable to honor a booking, they should help you find another place to stay. If they are unable or unwilling to provide this, they should let us know as soon as possible so that we can help to find a solution. Please DM us the following details:
+• Confirmation number: 
+• PIN code: 
+• Name on the reservation: 
+Alternatively, for immediate support, you can always give us a call here: https://t.co/o8QyR8SaDb.</t>
+        </is>
+      </c>
+      <c r="G888" t="inlineStr"/>
+      <c r="H888" t="inlineStr"/>
+      <c r="I888" t="inlineStr"/>
+      <c r="J888" t="inlineStr"/>
+      <c r="K888" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2083317262308540540</t>
+        </is>
+      </c>
+      <c r="L888" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M888" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N888" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O888" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a customer complaint about a property failing to accommodate them, outlines its policies on property availability and verification, and offers support channels for resolution.</t>
+        </is>
+      </c>
+    </row>
+    <row r="889">
+      <c r="A889" t="inlineStr">
+        <is>
+          <t>Mondee</t>
+        </is>
+      </c>
+      <c r="B889" t="inlineStr">
+        <is>
+          <t>Booking.com for Travel Agents</t>
+        </is>
+      </c>
+      <c r="C889" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D889" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E889" t="inlineStr">
+        <is>
+          <t>Sat Aug 01 18:15:58 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F889" t="inlineStr">
+        <is>
+          <t>Hi there, 
+We regret to hear that you've had difficulty getting the support you need. We understand how frustrating it can be when you're waiting for assistance and feel that your concerns are not being addressed. 
+Could you please tell us a bit more about what happened and the issue you're experiencing? If your request is related to an accommodation booking, please send us a DM with the following details, so we can look into it for you: 
+• Confirmation number 
+• PIN code 
+• Name on the reservation
+Please bear in mind that our Social Media Team doesn't work in real time. For immediate support, please call our 24/7 Customer Service Team - our contact details can be found here: https://t.co/o8QyR8SaDb.
+Also, at this time, we only offer support for accommodation bookings via social media. For questions about Flights, Taxis, or Insurance, you can reach out to the dedicated support team here: https://t.co/OVuF5pCzba.</t>
+        </is>
+      </c>
+      <c r="G889" t="inlineStr"/>
+      <c r="H889" t="inlineStr"/>
+      <c r="I889" t="inlineStr"/>
+      <c r="J889" t="inlineStr"/>
+      <c r="K889" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2083617750346256587</t>
+        </is>
+      </c>
+      <c r="L889" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M889" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N889" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O889" t="inlineStr">
+        <is>
+          <t>Booking.com for Travel Agents responds to a customer complaint about support, offering instructions for resolution and directing to other support channels.</t>
+        </is>
+      </c>
+    </row>
+    <row r="890">
+      <c r="A890" t="inlineStr">
+        <is>
+          <t>Mondee</t>
+        </is>
+      </c>
+      <c r="B890" t="inlineStr">
+        <is>
+          <t>Booking.com for Travel Agents</t>
+        </is>
+      </c>
+      <c r="C890" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D890" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E890" t="inlineStr">
+        <is>
+          <t>Sat Aug 01 18:15:49 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F890" t="inlineStr">
+        <is>
+          <t>@heatherdrover1 Hello there Heather, We have sent you a message via private. Kindly refer to that message for further information. Thank you for your understanding.</t>
+        </is>
+      </c>
+      <c r="G890" t="inlineStr"/>
+      <c r="H890" t="inlineStr"/>
+      <c r="I890" t="inlineStr"/>
+      <c r="J890" t="inlineStr"/>
+      <c r="K890" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2083617713662886202</t>
+        </is>
+      </c>
+      <c r="L890" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M890" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N890" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O890" t="inlineStr">
+        <is>
+          <t>Booking.com for Travel Agents sent a private message to Heather Drover, directing her to refer to that message for further information.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/News_Dashboard/data/social_media_posts.xlsx
+++ b/News_Dashboard/data/social_media_posts.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O890"/>
+  <dimension ref="A1:O911"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -57005,6 +57005,1356 @@
         </is>
       </c>
     </row>
+    <row r="891">
+      <c r="A891" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B891" t="inlineStr">
+        <is>
+          <t>TripGenie</t>
+        </is>
+      </c>
+      <c r="C891" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="D891" t="inlineStr">
+        <is>
+          <t>trip</t>
+        </is>
+      </c>
+      <c r="E891" t="inlineStr">
+        <is>
+          <t>2026-08-02T09:00:00.000Z</t>
+        </is>
+      </c>
+      <c r="F891" t="inlineStr">
+        <is>
+          <t>August still has flight deals hiding in plain sight, even with peak summer demand in full swing.☀️✈️ Book now before shoulder season prices disappear into fall. Where‘s the deal taking you?
+👍Visit our bio for more travel inspirations and deals. 
+🤩Follow us to get more travel inspirations @trip. 
+Cr: sunny sung, thailand_adel, woong_film, voyage_provocateur
+#augusttravel #cheapflights #flightdeals #travel #tripcom</t>
+        </is>
+      </c>
+      <c r="G891" t="inlineStr">
+        <is>
+          <t>https://instagram.frmu1-1.fna.fbcdn.net/v/t51.82787-15/759920027_18607710886002228_3563724578929119290_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_ht=instagram.frmu1-1.fna.fbcdn.net&amp;_nc_cat=100&amp;_nc_oc=Q6cZ2gHbKguE9unktYWm_HqcJ32rcHseuqkOv4uFn1gHqn23ngyblMGbK4y8MdQB1JZeeto&amp;_nc_ohc=PLNfHRAJIdwQ7kNvwEZAcPR&amp;_nc_gid=Dp9cSlR3kW2hIvxT5T-cRw&amp;edm=ADp7STQBAAAA&amp;ccb=7-5&amp;oh=00_AQFXCDQcMaDor58PhMIC5hCSt38QiZaqZHEtbGTx5SKw6g&amp;oe=6A7544A0&amp;_nc_sid=c6f216</t>
+        </is>
+      </c>
+      <c r="H891" t="inlineStr">
+        <is>
+          <t>[easyocr not installed. Run 'pip install easyocr torch torchvision']</t>
+        </is>
+      </c>
+      <c r="I891" t="inlineStr">
+        <is>
+          <t>https://instagram.frmu1-1.fna.fbcdn.net/o1/v/t2/f2/m86/AQOf43lDjteInmt4x_KfzJVtFlXmyKcWJ1433GwqTm0Dif0PdTgzDYjL4TiK38Sf3m1-3tI96p6yXZh4y_cB6NpoPvqRAQeOhQ2e9YI.mp4?_nc_cat=109&amp;_nc_oc=AdpmuKZS0JiQ1ObfZErRzGqPwyMxC7nhzMgW9j4m119Wb0AFjnjlHSoBEByUDnwVmnk&amp;_nc_sid=5e9851&amp;_nc_ht=instagram.frmu1-1.fna.fbcdn.net&amp;_nc_ohc=3SemR9AHTzcQ7kNvwGCq-ov&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uQ0xJUFMuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTA3MjYwNTE0NTcxNDYzOCwiYXNzZXRfYWdlX2RheXMiOjIsInZpX3VzZWNhc2VfaWQiOjEwMDk5LCJkdXJhdGlvbl9zIjoxNiwidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=b11b6ff80c1340d9&amp;_nc_vs=HBksFQIYUmlnX3hwdl9yZWVsc19wZXJtYW5lbnRfc3JfcHJvZC80MjQ0OTk4RjM0ODI1MkQ3NEU4OEFFOEE5NkJFQjc4QV92aWRlb19kYXNoaW5pdC5tcDQVAALIARIAFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyL0ZBNDQ2MjM1QjVCRURGMzA2QjQ5RkM2OTI0Q0IyREIxX2F1ZGlvX2Rhc2hpbml0Lm1wNBUCAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACacv46L6-HnAxUCKAJDMywXQDDEGJN0vGoYEmRhc2hfYmFzZWxpbmVfMV92MREAdf4HZeadAQA&amp;_nc_gid=Dp9cSlR3kW2hIvxT5T-cRw&amp;_nc_ss=7a22e&amp;_nc_zt=28&amp;oh=00_AQE-FcBm_W6e5P3Y8OzwlWCZXtHbS8TMxcXebg3uh7aK6Q&amp;oe=6A715C82</t>
+        </is>
+      </c>
+      <c r="J891" t="inlineStr">
+        <is>
+          <t>[faster-whisper not installed. Run 'pip install faster-whisper']</t>
+        </is>
+      </c>
+      <c r="K891" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DbiCx81msPq/</t>
+        </is>
+      </c>
+      <c r="L891" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M891" t="inlineStr">
+        <is>
+          <t>Product Announcement</t>
+        </is>
+      </c>
+      <c r="N891" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O891" t="inlineStr">
+        <is>
+          <t>TripGenie is promoting August flight deals, encouraging followers to book before shoulder season prices increase.</t>
+        </is>
+      </c>
+    </row>
+    <row r="892">
+      <c r="A892" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B892" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C892" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D892" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E892" t="inlineStr">
+        <is>
+          <t>Sun Aug 02 17:55:28 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F892" t="inlineStr">
+        <is>
+          <t>Hi Mahesh, we appreciate you for reaching out to us and we regret to hear that you are having an inconvenience in contacting our customer service team while having an emergency. Kindly note that you can cancel your reservation from your confirmation email, our app, or the https://t.co/fGhmZE7riF website. Each accommodation provider manages their policies themselves, so whenever an out-of-policy cancellation is requested, only the accommodation provider can approve this as an exception, not https://t.co/fGhmZE7riF.
+We'll be happy to reach out to the property on your behalf if you send us a private message with the following details:
+- Confirmation number:
+- Pin code:
+- Name on the reservation:
+Keep in mind, our Social Media Team does not work in real time. For immediate support, you can call our 24/7 Customer Service Team here: https://t.co/tuuNbmGVaG</t>
+        </is>
+      </c>
+      <c r="G892" t="inlineStr"/>
+      <c r="H892" t="inlineStr"/>
+      <c r="I892" t="inlineStr"/>
+      <c r="J892" t="inlineStr"/>
+      <c r="K892" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2083974979155112212</t>
+        </is>
+      </c>
+      <c r="L892" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M892" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N892" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O892" t="inlineStr">
+        <is>
+          <t>Booking.com addresses a customer’s difficulty reaching support, offering cancellation options and alternative contact methods.</t>
+        </is>
+      </c>
+    </row>
+    <row r="893">
+      <c r="A893" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B893" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C893" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D893" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E893" t="inlineStr">
+        <is>
+          <t>Sun Aug 02 15:36:23 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F893" t="inlineStr">
+        <is>
+          <t>Hi there, we regret to hear about your disappointment. As much as we would love to help, we're unable to assist with flight reservations through social media, but you can contact our Flights team here: https://t.co/TBejpc4vOA, or call {US}+1 917 421 7240 / {UK}+44 2039019061 / {IE} +353 19075677. Kind regards.</t>
+        </is>
+      </c>
+      <c r="G893" t="inlineStr"/>
+      <c r="H893" t="inlineStr"/>
+      <c r="I893" t="inlineStr"/>
+      <c r="J893" t="inlineStr"/>
+      <c r="K893" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2083939977457447347</t>
+        </is>
+      </c>
+      <c r="L893" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M893" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N893" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O893" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a customer complaint about flight reservations, directing them to the Flights team and providing contact details.</t>
+        </is>
+      </c>
+    </row>
+    <row r="894">
+      <c r="A894" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B894" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C894" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D894" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E894" t="inlineStr">
+        <is>
+          <t>Sun Aug 02 14:46:21 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F894" t="inlineStr">
+        <is>
+          <t>@TohokuLineDelay Hi there, we replied to your DM. Take a look when you have a moment.</t>
+        </is>
+      </c>
+      <c r="G894" t="inlineStr"/>
+      <c r="H894" t="inlineStr"/>
+      <c r="I894" t="inlineStr"/>
+      <c r="J894" t="inlineStr"/>
+      <c r="K894" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2083927390061744184</t>
+        </is>
+      </c>
+      <c r="L894" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M894" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N894" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O894" t="inlineStr">
+        <is>
+          <t>Booking.com replied to a user’s direct message regarding a delay, indicating routine customer engagement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="895">
+      <c r="A895" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B895" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C895" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D895" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E895" t="inlineStr">
+        <is>
+          <t>Sun Aug 02 14:12:19 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F895" t="inlineStr">
+        <is>
+          <t>@Mohsen_94l Hi there, we sent you a DM regarding your request. https://t.co/Z89AAoEgD7</t>
+        </is>
+      </c>
+      <c r="G895" t="inlineStr"/>
+      <c r="H895" t="inlineStr"/>
+      <c r="I895" t="inlineStr"/>
+      <c r="J895" t="inlineStr"/>
+      <c r="K895" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2083918822549975481</t>
+        </is>
+      </c>
+      <c r="L895" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M895" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N895" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O895" t="inlineStr">
+        <is>
+          <t>Booking.com replied to a user’s request via direct message, indicating routine customer support engagement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="896">
+      <c r="A896" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B896" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C896" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D896" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E896" t="inlineStr">
+        <is>
+          <t>Sun Aug 02 13:48:47 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F896" t="inlineStr">
+        <is>
+          <t>Hi Shubham, thank you for contacting us regarding your car rental reservation. 
+In order for us to assist you, please send us a private message with the following details: 
+- Booking number 
+- Name of booker 
+- Email address used to book 
+- Your request 
+We'll get back to you as soon as we can. Thank you.</t>
+        </is>
+      </c>
+      <c r="G896" t="inlineStr"/>
+      <c r="H896" t="inlineStr"/>
+      <c r="I896" t="inlineStr"/>
+      <c r="J896" t="inlineStr"/>
+      <c r="K896" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2083912900003983748</t>
+        </is>
+      </c>
+      <c r="L896" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M896" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N896" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O896" t="inlineStr">
+        <is>
+          <t>Booking.com replied to a customer’s inquiry about a car rental reservation, asking for booking details via private message.</t>
+        </is>
+      </c>
+    </row>
+    <row r="897">
+      <c r="A897" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B897" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C897" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D897" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E897" t="inlineStr">
+        <is>
+          <t>Sun Aug 02 13:44:39 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F897" t="inlineStr">
+        <is>
+          <t>Hi there, we regret hearing that you received messages via WhatsApp with your booking details and there was no follow-up from our team. Feel free to DM us the following details of the booking: 
+- Confirmation number 
+- PIN Code 
+- Name of guest 
+and we will look into this for you.</t>
+        </is>
+      </c>
+      <c r="G897" t="inlineStr"/>
+      <c r="H897" t="inlineStr"/>
+      <c r="I897" t="inlineStr"/>
+      <c r="J897" t="inlineStr"/>
+      <c r="K897" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2083911859690774892</t>
+        </is>
+      </c>
+      <c r="L897" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M897" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N897" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O897" t="inlineStr">
+        <is>
+          <t>Booking.com apologizes for a lack of follow-up on WhatsApp booking details and invites customers to DM the booking info for resolution.</t>
+        </is>
+      </c>
+    </row>
+    <row r="898">
+      <c r="A898" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B898" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C898" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D898" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E898" t="inlineStr">
+        <is>
+          <t>Sun Aug 02 13:28:46 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F898" t="inlineStr">
+        <is>
+          <t>@YourMateEli Hi there, we're unable to assist with Flight reservations through social media, but you can contact our Flights team here: https://t.co/Z8ou85LCWJ, or call {US}+1 917 421 7240 / {UK}+44 2039019061 / {IE} +353 19075677. Kind regards.</t>
+        </is>
+      </c>
+      <c r="G898" t="inlineStr"/>
+      <c r="H898" t="inlineStr"/>
+      <c r="I898" t="inlineStr"/>
+      <c r="J898" t="inlineStr"/>
+      <c r="K898" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2083907863894704380</t>
+        </is>
+      </c>
+      <c r="L898" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M898" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N898" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O898" t="inlineStr">
+        <is>
+          <t>Booking.com informs a user that flight reservations cannot be handled via social media and directs them to contact the Flights team via a provided link or phone numbers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="899">
+      <c r="A899" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B899" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C899" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D899" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E899" t="inlineStr">
+        <is>
+          <t>Sun Aug 02 12:57:58 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F899" t="inlineStr">
+        <is>
+          <t>@lakesalford Hi Stephen, please take a look at the DM we sent. Feel free to reply to our DM if you have more questions,</t>
+        </is>
+      </c>
+      <c r="G899" t="inlineStr"/>
+      <c r="H899" t="inlineStr"/>
+      <c r="I899" t="inlineStr"/>
+      <c r="J899" t="inlineStr"/>
+      <c r="K899" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2083900110686077240</t>
+        </is>
+      </c>
+      <c r="L899" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M899" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N899" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O899" t="inlineStr">
+        <is>
+          <t>Booking.com is following up with a user via a tweet, encouraging them to review a previously sent DM and respond with any questions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="900">
+      <c r="A900" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B900" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C900" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D900" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E900" t="inlineStr">
+        <is>
+          <t>Sun Aug 02 12:38:34 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F900" t="inlineStr">
+        <is>
+          <t>Calling is only possible if you have a booking.
+You can send us a DM and answer the following questions in private:
+- Have you recently tried making a booking?
+- Do you have an account with us? (if so, you can share your full name and email address)
+- If you didn't make a booking, please share a screenshot with the details of the charge
+We will reply as soon as possible.</t>
+        </is>
+      </c>
+      <c r="G900" t="inlineStr"/>
+      <c r="H900" t="inlineStr"/>
+      <c r="I900" t="inlineStr"/>
+      <c r="J900" t="inlineStr"/>
+      <c r="K900" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2083895231674531981</t>
+        </is>
+      </c>
+      <c r="L900" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M900" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N900" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O900" t="inlineStr">
+        <is>
+          <t>Booking.com is requesting customers to DM with booking details for support inquiries.</t>
+        </is>
+      </c>
+    </row>
+    <row r="901">
+      <c r="A901" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B901" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C901" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D901" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E901" t="inlineStr">
+        <is>
+          <t>Sun Aug 02 12:20:40 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F901" t="inlineStr">
+        <is>
+          <t>@lakesalford Hi there, normally properties take 15 to 30 business days to process a refund. Please refer to our previous response about your booking. Kind regards.</t>
+        </is>
+      </c>
+      <c r="G901" t="inlineStr"/>
+      <c r="H901" t="inlineStr"/>
+      <c r="I901" t="inlineStr"/>
+      <c r="J901" t="inlineStr"/>
+      <c r="K901" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2083890724894810441</t>
+        </is>
+      </c>
+      <c r="L901" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M901" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N901" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O901" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a user about refund processing times, noting that it normally takes 15 to 30 business days.</t>
+        </is>
+      </c>
+    </row>
+    <row r="902">
+      <c r="A902" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B902" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C902" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D902" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E902" t="inlineStr">
+        <is>
+          <t>Sun Aug 02 11:58:54 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F902" t="inlineStr">
+        <is>
+          <t>Hi Janiza, we understand from your messages that you’ve already been in touch with our Customer Service team. Please note that the social media team operates separately and we don’t have access to your emails. For us to look into your case, please DM us the following:
+- Confirmation number:
+- Pin code:
+- Name of the guest on the reservation:
+And we will get back to you as soon as possible.</t>
+        </is>
+      </c>
+      <c r="G902" t="inlineStr"/>
+      <c r="H902" t="inlineStr"/>
+      <c r="I902" t="inlineStr"/>
+      <c r="J902" t="inlineStr"/>
+      <c r="K902" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2083885249914679715</t>
+        </is>
+      </c>
+      <c r="L902" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M902" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N902" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O902" t="inlineStr">
+        <is>
+          <t>Booking.com’s X post is a customer service response, requesting confirmation details to investigate a user’s issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="903">
+      <c r="A903" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B903" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C903" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D903" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E903" t="inlineStr">
+        <is>
+          <t>Sun Aug 02 10:05:24 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F903" t="inlineStr">
+        <is>
+          <t>@Pabi_Loi Hi there, we regret hearing that you were unable to check in. Please send us a private message with the following information: 
+- Confirmation number 
+- Pin code 
+- Name of the guest 
+And we'd do our best to get back to you as soon as possible. https://t.co/Z89AAoEgD7</t>
+        </is>
+      </c>
+      <c r="G903" t="inlineStr"/>
+      <c r="H903" t="inlineStr"/>
+      <c r="I903" t="inlineStr"/>
+      <c r="J903" t="inlineStr"/>
+      <c r="K903" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2083856685907550530</t>
+        </is>
+      </c>
+      <c r="L903" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M903" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N903" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O903" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a customer complaint about a check‑in issue, asking the user to send confirmation details via private message for resolution.</t>
+        </is>
+      </c>
+    </row>
+    <row r="904">
+      <c r="A904" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B904" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C904" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D904" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E904" t="inlineStr">
+        <is>
+          <t>Sun Aug 02 09:10:28 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F904" t="inlineStr">
+        <is>
+          <t>@Uimmiu0135 Hi there, we've replied to your DM.</t>
+        </is>
+      </c>
+      <c r="G904" t="inlineStr"/>
+      <c r="H904" t="inlineStr"/>
+      <c r="I904" t="inlineStr"/>
+      <c r="J904" t="inlineStr"/>
+      <c r="K904" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2083842858704920929</t>
+        </is>
+      </c>
+      <c r="L904" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M904" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N904" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O904" t="inlineStr">
+        <is>
+          <t>Booking.com replied to a user’s direct message on X.</t>
+        </is>
+      </c>
+    </row>
+    <row r="905">
+      <c r="A905" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B905" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C905" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D905" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E905" t="inlineStr">
+        <is>
+          <t>Sun Aug 02 08:50:51 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F905" t="inlineStr">
+        <is>
+          <t>@HaileyRealFeed Hello Hailey, we regret hearing about your dissatisfaction with our colleagues.
+Our social media team doesn't offer flight support unfortunately, so we won't be able to help. We recommend contacting back our flight team.
+We apologize for the inconveniences.</t>
+        </is>
+      </c>
+      <c r="G905" t="inlineStr"/>
+      <c r="H905" t="inlineStr"/>
+      <c r="I905" t="inlineStr"/>
+      <c r="J905" t="inlineStr"/>
+      <c r="K905" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2083837923506466868</t>
+        </is>
+      </c>
+      <c r="L905" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="M905" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N905" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O905" t="inlineStr">
+        <is>
+          <t>Booking.com apologizes to a dissatisfied user and directs them to the flight support team for assistance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="906">
+      <c r="A906" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B906" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C906" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D906" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E906" t="inlineStr">
+        <is>
+          <t>Sun Aug 02 08:10:19 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F906" t="inlineStr">
+        <is>
+          <t>Hi there, thanks for reaching out to us. We regret to hear that you didn't receive the confirmation email. It's possible that you made a typo when entering your email address, as you wouldn't receive the confirmation email afterwards. If you send us a private message with the following details, we'll look into our system to see if we can locate your booking:
+- Name and link of the property
+- Dates of stay
+- Full guest name &amp; name of the person contacting us 
+- Email address used to make the booking
+And we'll come back to you as soon as possible</t>
+        </is>
+      </c>
+      <c r="G906" t="inlineStr"/>
+      <c r="H906" t="inlineStr"/>
+      <c r="I906" t="inlineStr"/>
+      <c r="J906" t="inlineStr"/>
+      <c r="K906" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2083827723844083952</t>
+        </is>
+      </c>
+      <c r="L906" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M906" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N906" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O906" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a customer complaint about a missing confirmation email, offering to investigate and resolve the issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="907">
+      <c r="A907" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B907" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C907" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D907" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E907" t="inlineStr">
+        <is>
+          <t>Sun Aug 02 07:26:25 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F907" t="inlineStr">
+        <is>
+          <t>Hello again, Rakesh.
+As stated in our last reply, you need to send us a DM with your booking details. Please never share them publicly, for your own safety.
+Luckily in this case, the pin code you shared is not correct. So that we can review your booking, please send us a DM/private message, and share the 4 digit pin code from your confirmation email with us.
+Talk to you soon.</t>
+        </is>
+      </c>
+      <c r="G907" t="inlineStr"/>
+      <c r="H907" t="inlineStr"/>
+      <c r="I907" t="inlineStr"/>
+      <c r="J907" t="inlineStr"/>
+      <c r="K907" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2083816674269016357</t>
+        </is>
+      </c>
+      <c r="L907" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M907" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N907" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O907" t="inlineStr">
+        <is>
+          <t>Booking.com is requesting a user to send booking details via DM, emphasizing the importance of not sharing sensitive information publicly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="908">
+      <c r="A908" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B908" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C908" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D908" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E908" t="inlineStr">
+        <is>
+          <t>Sun Aug 02 07:09:22 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F908" t="inlineStr">
+        <is>
+          <t>Hi there, we regret to hear that you are not receiving a response from our customer service team. We would like to see how we can help you with your reservation. Please send us a private message with the following information:
+- Confirmation number
+- Pin code
+- Name of the guest
+And we'll do our best to get back to you as soon as possible.</t>
+        </is>
+      </c>
+      <c r="G908" t="inlineStr"/>
+      <c r="H908" t="inlineStr"/>
+      <c r="I908" t="inlineStr"/>
+      <c r="J908" t="inlineStr"/>
+      <c r="K908" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2083812384712397131</t>
+        </is>
+      </c>
+      <c r="L908" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M908" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N908" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O908" t="inlineStr">
+        <is>
+          <t>Booking.com apologizes for delayed customer service response and requests private message with reservation details to resolve the issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="909">
+      <c r="A909" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B909" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C909" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D909" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E909" t="inlineStr">
+        <is>
+          <t>Sun Aug 02 06:19:19 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F909" t="inlineStr">
+        <is>
+          <t>Hi, we’re concerned to hear about your experience and would like to understand more so we can see how we can help.
+Please send us a direct message with more information about what happened, along with the following details, and we'll be happy to look into this further:
+* Confirmation number
+* PIN code
+* Full name of the guest on the booking</t>
+        </is>
+      </c>
+      <c r="G909" t="inlineStr"/>
+      <c r="H909" t="inlineStr"/>
+      <c r="I909" t="inlineStr"/>
+      <c r="J909" t="inlineStr"/>
+      <c r="K909" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2083799790706479186</t>
+        </is>
+      </c>
+      <c r="L909" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M909" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N909" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O909" t="inlineStr">
+        <is>
+          <t>Booking.com is responding to a customer complaint, inviting the user to send a direct message with booking details for further investigation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="910">
+      <c r="A910" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B910" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C910" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D910" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E910" t="inlineStr">
+        <is>
+          <t>Sun Aug 02 04:30:51 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F910" t="inlineStr">
+        <is>
+          <t>Hi Kübra, we understand how strongly you feel about this situation and how disappointing it has been. We would like the chance to review what has happened. For us to help you with your reservation concern, please send us the following details, and we’ll get back to you as soon as possible:
+• Confirmation number: 
+• Pin code: 
+• Name on the reservation:</t>
+        </is>
+      </c>
+      <c r="G910" t="inlineStr"/>
+      <c r="H910" t="inlineStr"/>
+      <c r="I910" t="inlineStr"/>
+      <c r="J910" t="inlineStr"/>
+      <c r="K910" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2083772490984104329</t>
+        </is>
+      </c>
+      <c r="L910" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M910" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N910" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O910" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a customer complaint, offering to review the issue and requesting reservation details.</t>
+        </is>
+      </c>
+    </row>
+    <row r="911">
+      <c r="A911" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B911" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C911" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D911" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E911" t="inlineStr">
+        <is>
+          <t>Sun Aug 02 03:44:53 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F911" t="inlineStr">
+        <is>
+          <t>@MiluTouron Hi Milu, we understand how frustrating this situation has been. Due to GDPR regulations, only our specialized team has access to your information and is authorized to assist you further.</t>
+        </is>
+      </c>
+      <c r="G911" t="inlineStr"/>
+      <c r="H911" t="inlineStr"/>
+      <c r="I911" t="inlineStr"/>
+      <c r="J911" t="inlineStr"/>
+      <c r="K911" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2083760923563483521</t>
+        </is>
+      </c>
+      <c r="L911" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M911" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N911" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O911" t="inlineStr">
+        <is>
+          <t>Booking.com addresses a customer’s frustration over GDPR restrictions, offering specialized team assistance.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/News_Dashboard/data/social_media_posts.xlsx
+++ b/News_Dashboard/data/social_media_posts.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O911"/>
+  <dimension ref="A1:O932"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -58355,6 +58355,1353 @@
         </is>
       </c>
     </row>
+    <row r="912">
+      <c r="A912" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B912" t="inlineStr">
+        <is>
+          <t>Expedia</t>
+        </is>
+      </c>
+      <c r="C912" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D912" t="inlineStr">
+        <is>
+          <t>Expedia</t>
+        </is>
+      </c>
+      <c r="E912" t="inlineStr">
+        <is>
+          <t>2026-08-03T13:22:01.499Z</t>
+        </is>
+      </c>
+      <c r="F912" t="inlineStr">
+        <is>
+          <t>Your reminder to plan that National Park adventure.
+From August 22–30, it's National Park Week, and on August 25, U.S. citizens and residents can enjoy free entry to participating National Parks.
+Whether it's Yosemite, Haleakalā, Olympic, or somewhere new, now's the perfect time to go.</t>
+        </is>
+      </c>
+      <c r="G912" t="inlineStr"/>
+      <c r="H912" t="inlineStr"/>
+      <c r="I912" t="inlineStr">
+        <is>
+          <t>https://dms.licdn.com/playlist/vid/v2/D4E10AQFQgC7WL8FfCQ/mp4-720p-30fp-crf28/B4EZ_F1DJPKUBk-/0/1785730452516?e=1786388400&amp;v=beta&amp;t=AuGm46Ee5Gogk536AMjfnpiZ2z1KL3AfqR5h2lgqdj8</t>
+        </is>
+      </c>
+      <c r="J912" t="inlineStr">
+        <is>
+          <t>[faster-whisper not installed. Run 'pip install faster-whisper']</t>
+        </is>
+      </c>
+      <c r="K912" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/expedia_national-park-week-activity-7490034242417147904-jsCh</t>
+        </is>
+      </c>
+      <c r="L912" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M912" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N912" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O912" t="inlineStr">
+        <is>
+          <t>Expedia promotes National Park Week, encouraging U.S. travelers to visit parks such as Yosemite, Haleakalā, and Olympic on August 25 when free entry is available.</t>
+        </is>
+      </c>
+    </row>
+    <row r="913">
+      <c r="A913" t="inlineStr">
+        <is>
+          <t>Mondee</t>
+        </is>
+      </c>
+      <c r="B913" t="inlineStr">
+        <is>
+          <t>Booking.com for Travel Agents</t>
+        </is>
+      </c>
+      <c r="C913" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D913" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E913" t="inlineStr">
+        <is>
+          <t>Mon Aug 03 14:45:03 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F913" t="inlineStr">
+        <is>
+          <t>Sentimos que tu vuelo sufriera un imprevisto y afectara tu reserva de coche, Pau. Entendemos que quieres solucionarlo. 
+Desafortunadamente, aunque nos gustaría asistirte, no podemos ofrecer soporte para reservas de alquiler de coches a través de las redes sociales. Puedes ponerte en contacto con nuestro equipo especializado aquí: https://t.co/NT3GBtSRDt
+Un saludo.</t>
+        </is>
+      </c>
+      <c r="G913" t="inlineStr"/>
+      <c r="H913" t="inlineStr"/>
+      <c r="I913" t="inlineStr"/>
+      <c r="J913" t="inlineStr"/>
+      <c r="K913" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2084289450910052391</t>
+        </is>
+      </c>
+      <c r="L913" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M913" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N913" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O913" t="inlineStr">
+        <is>
+          <t>Booking.com for Travel Agents informs a customer that they cannot handle car rental support via social media and directs them to a specialized team.</t>
+        </is>
+      </c>
+    </row>
+    <row r="914">
+      <c r="A914" t="inlineStr">
+        <is>
+          <t>Mondee</t>
+        </is>
+      </c>
+      <c r="B914" t="inlineStr">
+        <is>
+          <t>Booking.com for Travel Agents</t>
+        </is>
+      </c>
+      <c r="C914" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D914" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E914" t="inlineStr">
+        <is>
+          <t>Mon Aug 03 14:33:50 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F914" t="inlineStr">
+        <is>
+          <t>@MeAtDotCoDotZa Hi Ian, we regret to hear about your opinion regarding our services. If you need assistance, please send us a private message with more details, and we’ll get back to you as soon as possible. Thank you. https://t.co/Z89AAoEgD7</t>
+        </is>
+      </c>
+      <c r="G914" t="inlineStr"/>
+      <c r="H914" t="inlineStr"/>
+      <c r="I914" t="inlineStr"/>
+      <c r="J914" t="inlineStr"/>
+      <c r="K914" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2084286626843283712</t>
+        </is>
+      </c>
+      <c r="L914" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M914" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N914" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O914" t="inlineStr">
+        <is>
+          <t>Booking.com for Travel Agents replied to a negative comment from a user, offering to address concerns via private message.</t>
+        </is>
+      </c>
+    </row>
+    <row r="915">
+      <c r="A915" t="inlineStr">
+        <is>
+          <t>Mondee</t>
+        </is>
+      </c>
+      <c r="B915" t="inlineStr">
+        <is>
+          <t>Booking.com for Travel Agents</t>
+        </is>
+      </c>
+      <c r="C915" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D915" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E915" t="inlineStr">
+        <is>
+          <t>Mon Aug 03 13:04:23 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F915" t="inlineStr">
+        <is>
+          <t>@NewYorker10013 Hi there. We have an update for you, however as we cannot discuss this in public, we kindly ask you to enable the option of sending a private message to you. https://t.co/Z89AAoEgD7</t>
+        </is>
+      </c>
+      <c r="G915" t="inlineStr"/>
+      <c r="H915" t="inlineStr"/>
+      <c r="I915" t="inlineStr"/>
+      <c r="J915" t="inlineStr"/>
+      <c r="K915" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2084264114625368405</t>
+        </is>
+      </c>
+      <c r="L915" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M915" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N915" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O915" t="inlineStr">
+        <is>
+          <t>Booking.com for Travel Agents is requesting a private message from a user for an undisclosed update.</t>
+        </is>
+      </c>
+    </row>
+    <row r="916">
+      <c r="A916" t="inlineStr">
+        <is>
+          <t>Mondee</t>
+        </is>
+      </c>
+      <c r="B916" t="inlineStr">
+        <is>
+          <t>Booking.com for Travel Agents</t>
+        </is>
+      </c>
+      <c r="C916" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D916" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E916" t="inlineStr">
+        <is>
+          <t>Mon Aug 03 12:58:04 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F916" t="inlineStr">
+        <is>
+          <t>@EyoManbvsu Nous sommes désolés d'apprendre que votre remboursement est toujours en attente. Nous ne pouvons pas traiter les réservations de vols via les réseaux sociaux. Veuillez contacter notre équipe Vols ici : https://t.co/Z8ou85LCWJ ou au +33 1 87 15 36 14.</t>
+        </is>
+      </c>
+      <c r="G916" t="inlineStr"/>
+      <c r="H916" t="inlineStr"/>
+      <c r="I916" t="inlineStr"/>
+      <c r="J916" t="inlineStr"/>
+      <c r="K916" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2084262527047815383</t>
+        </is>
+      </c>
+      <c r="L916" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="M916" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N916" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O916" t="inlineStr">
+        <is>
+          <t>Booking.com for Travel Agents apologizes for a pending refund and directs the user to contact their flight team via a provided link or phone number.</t>
+        </is>
+      </c>
+    </row>
+    <row r="917">
+      <c r="A917" t="inlineStr">
+        <is>
+          <t>Mondee</t>
+        </is>
+      </c>
+      <c r="B917" t="inlineStr">
+        <is>
+          <t>Booking.com for Travel Agents</t>
+        </is>
+      </c>
+      <c r="C917" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D917" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E917" t="inlineStr">
+        <is>
+          <t>Mon Aug 03 12:57:37 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F917" t="inlineStr">
+        <is>
+          <t>@EyoManbvsu Bonjour, toutes nos excuses pour notre réponse tardive. Nous recevons actuellement un volume important de demandes sur les réseaux sociaux et n’avons pas pu vous répondre plus tôt.</t>
+        </is>
+      </c>
+      <c r="G917" t="inlineStr"/>
+      <c r="H917" t="inlineStr"/>
+      <c r="I917" t="inlineStr"/>
+      <c r="J917" t="inlineStr"/>
+      <c r="K917" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2084262412979495243</t>
+        </is>
+      </c>
+      <c r="L917" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M917" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N917" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O917" t="inlineStr">
+        <is>
+          <t>Booking.com for Travel Agents apologizes for a delayed response to a user, citing a high volume of social media inquiries.</t>
+        </is>
+      </c>
+    </row>
+    <row r="918">
+      <c r="A918" t="inlineStr">
+        <is>
+          <t>Mondee</t>
+        </is>
+      </c>
+      <c r="B918" t="inlineStr">
+        <is>
+          <t>Booking.com for Travel Agents</t>
+        </is>
+      </c>
+      <c r="C918" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D918" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E918" t="inlineStr">
+        <is>
+          <t>Mon Aug 03 11:52:04 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F918" t="inlineStr">
+        <is>
+          <t>Hello,
+We regret hearing this, if the issue was related to your account you can provide us the following details and we can verify your account status for you:
+- Email address linked to the account
+- Name of the person contacting us
+If instead the issue was related to a reservation you can send us the following details and we will check the reservation for you:
+- Confirmation number:
+- Pin code:
+- Name of the traveler (meaning the name of the traveler):
+To cancel any information you shared with us, you can use the right to be forgotten using the form on the following page: https://t.co/lpInKjDJNc
+Best regards.</t>
+        </is>
+      </c>
+      <c r="G918" t="inlineStr"/>
+      <c r="H918" t="inlineStr"/>
+      <c r="I918" t="inlineStr"/>
+      <c r="J918" t="inlineStr"/>
+      <c r="K918" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2084245915074773309</t>
+        </is>
+      </c>
+      <c r="L918" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M918" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N918" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O918" t="inlineStr">
+        <is>
+          <t>Booking.com for Travel Agents offers troubleshooting steps for account or reservation issues and provides a link for the right to be forgotten.</t>
+        </is>
+      </c>
+    </row>
+    <row r="919">
+      <c r="A919" t="inlineStr">
+        <is>
+          <t>Mondee</t>
+        </is>
+      </c>
+      <c r="B919" t="inlineStr">
+        <is>
+          <t>Booking.com for Travel Agents</t>
+        </is>
+      </c>
+      <c r="C919" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D919" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E919" t="inlineStr">
+        <is>
+          <t>Mon Aug 03 11:36:01 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F919" t="inlineStr">
+        <is>
+          <t>@expropriarocab Olá, gostaria,ps de saber do que se trata. Se você necessita de assistência com reserva de acomodação, precisamos que nos envie uma mensagem direta com o Número de confirmação, código PIN e Nome do Hóspede na reserva. Explique o ocorrido, e daremos retorno o mais breve possível. https://t.co/Z89AAoEgD7</t>
+        </is>
+      </c>
+      <c r="G919" t="inlineStr"/>
+      <c r="H919" t="inlineStr"/>
+      <c r="I919" t="inlineStr"/>
+      <c r="J919" t="inlineStr"/>
+      <c r="K919" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2084241876459147322</t>
+        </is>
+      </c>
+      <c r="L919" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M919" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N919" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O919" t="inlineStr">
+        <is>
+          <t>Booking.com for Travel Agents is offering assistance for accommodation reservations, requesting confirmation details via direct message.</t>
+        </is>
+      </c>
+    </row>
+    <row r="920">
+      <c r="A920" t="inlineStr">
+        <is>
+          <t>Mondee</t>
+        </is>
+      </c>
+      <c r="B920" t="inlineStr">
+        <is>
+          <t>Booking.com for Travel Agents</t>
+        </is>
+      </c>
+      <c r="C920" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D920" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E920" t="inlineStr">
+        <is>
+          <t>Mon Aug 03 11:20:46 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F920" t="inlineStr">
+        <is>
+          <t>@LBarn_127 Hi Lucy, we have replied to your private message regarding this, please have a look at it</t>
+        </is>
+      </c>
+      <c r="G920" t="inlineStr"/>
+      <c r="H920" t="inlineStr"/>
+      <c r="I920" t="inlineStr"/>
+      <c r="J920" t="inlineStr"/>
+      <c r="K920" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2084238040289902962</t>
+        </is>
+      </c>
+      <c r="L920" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M920" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N920" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O920" t="inlineStr">
+        <is>
+          <t>Booking.com for Travel Agents replied to a private message from a user.</t>
+        </is>
+      </c>
+    </row>
+    <row r="921">
+      <c r="A921" t="inlineStr">
+        <is>
+          <t>Mondee</t>
+        </is>
+      </c>
+      <c r="B921" t="inlineStr">
+        <is>
+          <t>Booking.com for Travel Agents</t>
+        </is>
+      </c>
+      <c r="C921" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D921" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E921" t="inlineStr">
+        <is>
+          <t>Mon Aug 03 11:12:06 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F921" t="inlineStr">
+        <is>
+          <t>Hi there, we regret hearing this and would like to check your booking, please send us a private message with the following details, and we'll get back to you as soon as possible: 
+- Confirmation number
+- Pin code
+- Name on the reservation (meaning the name of the traveler)
+Please bear in mind that our Social Media Team doesn't work in real time. For immediate support, please call our 24/7 Customer Service Team - our contact details can be found here: https://t.co/o8QyR8SaDb
+Also, at this time, we only offer support for accommodation bookings via social media. For questions about Flights, Taxis, or Insurance, you can reach out to the dedicated support team here: https://t.co/UfRgpDJomK</t>
+        </is>
+      </c>
+      <c r="G921" t="inlineStr"/>
+      <c r="H921" t="inlineStr"/>
+      <c r="I921" t="inlineStr"/>
+      <c r="J921" t="inlineStr"/>
+      <c r="K921" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2084235858178195840</t>
+        </is>
+      </c>
+      <c r="L921" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M921" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N921" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O921" t="inlineStr">
+        <is>
+          <t>Booking.com for Travel Agents responds to a customer complaint on X, offering to review the booking and directing the user to private messaging or 24/7 customer service for further assistance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="922">
+      <c r="A922" t="inlineStr">
+        <is>
+          <t>Mondee</t>
+        </is>
+      </c>
+      <c r="B922" t="inlineStr">
+        <is>
+          <t>Booking.com for Travel Agents</t>
+        </is>
+      </c>
+      <c r="C922" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D922" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E922" t="inlineStr">
+        <is>
+          <t>Mon Aug 03 10:18:11 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F922" t="inlineStr">
+        <is>
+          <t>@turkyaalnasser Hi there, we have replied to your message via DM regarding this. Please check it</t>
+        </is>
+      </c>
+      <c r="G922" t="inlineStr"/>
+      <c r="H922" t="inlineStr"/>
+      <c r="I922" t="inlineStr"/>
+      <c r="J922" t="inlineStr"/>
+      <c r="K922" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2084222288912585039</t>
+        </is>
+      </c>
+      <c r="L922" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M922" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N922" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O922" t="inlineStr">
+        <is>
+          <t>Booking.com for Travel Agents replied to a user via direct message, indicating a routine customer support interaction.</t>
+        </is>
+      </c>
+    </row>
+    <row r="923">
+      <c r="A923" t="inlineStr">
+        <is>
+          <t>Mondee</t>
+        </is>
+      </c>
+      <c r="B923" t="inlineStr">
+        <is>
+          <t>Booking.com for Travel Agents</t>
+        </is>
+      </c>
+      <c r="C923" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D923" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E923" t="inlineStr">
+        <is>
+          <t>Mon Aug 03 09:53:23 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F923" t="inlineStr">
+        <is>
+          <t>@NicoleColodro Hi Nicole! To assist you, please send us a DM with the following information, and we will get back to you as soon as possible: 
+- Confirmation number 
+- PIN code 
+- Full name of the guest confirmed on the booking https://t.co/Z89AAoEgD7</t>
+        </is>
+      </c>
+      <c r="G923" t="inlineStr"/>
+      <c r="H923" t="inlineStr"/>
+      <c r="I923" t="inlineStr"/>
+      <c r="J923" t="inlineStr"/>
+      <c r="K923" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2084216047243047156</t>
+        </is>
+      </c>
+      <c r="L923" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M923" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N923" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O923" t="inlineStr">
+        <is>
+          <t>Booking.com for Travel Agents is responding to a customer query, requesting booking details via direct message.</t>
+        </is>
+      </c>
+    </row>
+    <row r="924">
+      <c r="A924" t="inlineStr">
+        <is>
+          <t>Mondee</t>
+        </is>
+      </c>
+      <c r="B924" t="inlineStr">
+        <is>
+          <t>Booking.com for Travel Agents</t>
+        </is>
+      </c>
+      <c r="C924" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D924" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E924" t="inlineStr">
+        <is>
+          <t>Mon Aug 03 09:51:43 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F924" t="inlineStr">
+        <is>
+          <t>Hi Siddharth, we recommend that you never share the PIN code of your reservation in public as it can allow others to access your personal details. To help protect your information, we recommend that you delete your comment.  Please send a private message if you would like any assistance. After you send us the requested information through a direct message, kindly indicate whether you are still at the accommodation or if you have checked out because of the issues mentioned above. We will then help you further.</t>
+        </is>
+      </c>
+      <c r="G924" t="inlineStr"/>
+      <c r="H924" t="inlineStr"/>
+      <c r="I924" t="inlineStr"/>
+      <c r="J924" t="inlineStr"/>
+      <c r="K924" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2084215627888152935</t>
+        </is>
+      </c>
+      <c r="L924" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M924" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N924" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O924" t="inlineStr">
+        <is>
+          <t>Booking.com for Travel Agents warns a user not to share PIN codes publicly, advises deleting the comment, and offers private assistance to protect personal data.</t>
+        </is>
+      </c>
+    </row>
+    <row r="925">
+      <c r="A925" t="inlineStr">
+        <is>
+          <t>Mondee</t>
+        </is>
+      </c>
+      <c r="B925" t="inlineStr">
+        <is>
+          <t>Booking.com for Travel Agents</t>
+        </is>
+      </c>
+      <c r="C925" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D925" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E925" t="inlineStr">
+        <is>
+          <t>Mon Aug 03 09:37:26 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F925" t="inlineStr">
+        <is>
+          <t>Hi there,
+We had a look at your booking and we regret to seeing about your experience with the accommodation.
+Please keep in mind the policies on our platform belong to the accommodations, and guests are contractually bound to them. This means, only the accommodations themselves can issue refunds, also after complaints. 
+Our colleagues forwarded your complaint to the accommodation, however they didn't offer any refund/compensation. Our colleagues gave you a small compensation from our side (paid out of our own pocket), this is not in relation to the refund request you have from the accommodation. This was a small gesture of good will, because we value you as our customer. We cannot offer more from our side.
+Upon reviewing your booking, we noticed that you reached out to us only after checking out. 
+It is always advisable for guests facing issues during their stay, to contact our Customer Center immediately upon check-in, to prevent the situation from worsening. 
+Timely communication with our team increases the likelihood of reaching a satisfactory resolution for the guest. 
+While we cannot assist further, you can try negotiating with the accommodation directly (contact details are in your confirmation email). 
+If you ever need help with a different booking again, we are here for you.
+We wish you better experiences in the future.</t>
+        </is>
+      </c>
+      <c r="G925" t="inlineStr"/>
+      <c r="H925" t="inlineStr"/>
+      <c r="I925" t="inlineStr"/>
+      <c r="J925" t="inlineStr"/>
+      <c r="K925" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2084212035303137326</t>
+        </is>
+      </c>
+      <c r="L925" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="M925" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N925" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O925" t="inlineStr">
+        <is>
+          <t>Booking.com for Travel Agents explains that only accommodations can issue refunds, offers a small goodwill gesture, and advises customers to contact support promptly during stays.</t>
+        </is>
+      </c>
+    </row>
+    <row r="926">
+      <c r="A926" t="inlineStr">
+        <is>
+          <t>Mondee</t>
+        </is>
+      </c>
+      <c r="B926" t="inlineStr">
+        <is>
+          <t>Booking.com for Travel Agents</t>
+        </is>
+      </c>
+      <c r="C926" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D926" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E926" t="inlineStr">
+        <is>
+          <t>Mon Aug 03 09:26:30 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F926" t="inlineStr">
+        <is>
+          <t>Hi Pratyush, we recommend that you never share the details of your reservation in public as it can allow others to access your personal details. To help protect your information, we recommend that you delete your comment. For us to help, send us a private message with the following details:
+- Confirmation number:
+- Pin code:
+- Name on the reservation:</t>
+        </is>
+      </c>
+      <c r="G926" t="inlineStr"/>
+      <c r="H926" t="inlineStr"/>
+      <c r="I926" t="inlineStr"/>
+      <c r="J926" t="inlineStr"/>
+      <c r="K926" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2084209283298730326</t>
+        </is>
+      </c>
+      <c r="L926" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M926" t="inlineStr">
+        <is>
+          <t>Tech Updates</t>
+        </is>
+      </c>
+      <c r="N926" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O926" t="inlineStr">
+        <is>
+          <t>Booking.com for Travel Agents cautions users against publicly sharing reservation details, recommends deleting comments, and offers private assistance for secure handling of personal information.</t>
+        </is>
+      </c>
+    </row>
+    <row r="927">
+      <c r="A927" t="inlineStr">
+        <is>
+          <t>Mondee</t>
+        </is>
+      </c>
+      <c r="B927" t="inlineStr">
+        <is>
+          <t>Booking.com for Travel Agents</t>
+        </is>
+      </c>
+      <c r="C927" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D927" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E927" t="inlineStr">
+        <is>
+          <t>Mon Aug 03 09:20:49 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F927" t="inlineStr">
+        <is>
+          <t>Lamentamos que no hayas obtenido una respuesta y haber tardado en responder, Ane. Debido al gran volumen de casos en las redes sociales, no hemos podido contestar hasta ahora. 
+Si deseas llamar a nuestro equipo de Atención al cliente, aquí encontrarás los datos de contacto: https://t.co/tuuNbmGVaG
+Si es sobre Vuelos, Taxis o Seguros, puedes contactar con los equipos especializados aquí: https://t.co/TBejpc4vOA
+Alternativamente, si está relacionado con una reserva de alojamiento y quieres que lo revisemos, envíanos un mensaje privado con los siguientes datos y nos pondremos en contacto contigo lo antes posible: 
+- Número de confirmación
+- Código PIN
+- Nombre del huésped en la reserva
+- Detalles de tu solicitud
+Ten en cuenta que nuestro equipo de redes sociales no trabaja en tiempo real. 
+Un saludo.</t>
+        </is>
+      </c>
+      <c r="G927" t="inlineStr"/>
+      <c r="H927" t="inlineStr"/>
+      <c r="I927" t="inlineStr"/>
+      <c r="J927" t="inlineStr"/>
+      <c r="K927" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2084207852734878128</t>
+        </is>
+      </c>
+      <c r="L927" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M927" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N927" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O927" t="inlineStr">
+        <is>
+          <t>Booking.com for Travel Agents apologized for delayed responses due to high volume of social media inquiries and provided contact details for customer support and specialized teams.</t>
+        </is>
+      </c>
+    </row>
+    <row r="928">
+      <c r="A928" t="inlineStr">
+        <is>
+          <t>Mondee</t>
+        </is>
+      </c>
+      <c r="B928" t="inlineStr">
+        <is>
+          <t>Booking.com for Travel Agents</t>
+        </is>
+      </c>
+      <c r="C928" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D928" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E928" t="inlineStr">
+        <is>
+          <t>Mon Aug 03 09:19:27 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F928" t="inlineStr">
+        <is>
+          <t>Bonjour, merci de nous avoir contactés.  
+Nous nous excusons pour le délai de réponse. Notre équipe des réseaux sociaux fait face à un volume élevé de messages en ce moment. Si votre demande est urgente, nous vous invitons à contacter notre service client (https://t.co/o8QyR8SaDb).  
+Nous regrettons de lire votre déception concernant le fait que votre réservation n’ait pas été honorée. Les disponibilités sur notre plateforme sont gérées directement par les hébergements. S’ils commettent une erreur et que vous ne pouvez pas effectuer votre enregistrement, nous vous invitons à nous appeler le jour de votre arrivée afin que nous puissions vous aider.  
+Notre équipe des réseaux sociaux peut faire un suivi de la situation. N’hésitez pas à nous envoyer un message privé avec les informations suivantes :  
+- numéro de confirmation,  
+- code confidentiel,  
+- nom complet du voyageur,  
+et nous reviendrons vers vous dès que possible.</t>
+        </is>
+      </c>
+      <c r="G928" t="inlineStr"/>
+      <c r="H928" t="inlineStr"/>
+      <c r="I928" t="inlineStr"/>
+      <c r="J928" t="inlineStr"/>
+      <c r="K928" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2084207508235620386</t>
+        </is>
+      </c>
+      <c r="L928" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M928" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N928" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O928" t="inlineStr">
+        <is>
+          <t>Booking.com for Travel Agents apologizes for delayed response and informs customers about booking issues, offering contact details for urgent assistance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="929">
+      <c r="A929" t="inlineStr">
+        <is>
+          <t>Mondee</t>
+        </is>
+      </c>
+      <c r="B929" t="inlineStr">
+        <is>
+          <t>Booking.com for Travel Agents</t>
+        </is>
+      </c>
+      <c r="C929" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D929" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E929" t="inlineStr">
+        <is>
+          <t>Mon Aug 03 09:12:09 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F929" t="inlineStr">
+        <is>
+          <t>Hi there, we regret hearing this and would like to check your booking, please send us a private message with the following details, and we'll get back to you as soon as possible: 
+- Confirmation number
+- Pin code
+- Name on the reservation (meaning the name of the traveler)
+Please bear in mind that our Social Media Team doesn't work in real time. For immediate support, please call our 24/7 Customer Service Team - our contact details can be found here: https://t.co/o8QyR8SaDb
+Also, at this time, we only offer support for accommodation bookings via social media. For questions about Flights, Taxis, or Insurance, you can reach out to the dedicated support team here: https://t.co/UfRgpDJomK</t>
+        </is>
+      </c>
+      <c r="G929" t="inlineStr"/>
+      <c r="H929" t="inlineStr"/>
+      <c r="I929" t="inlineStr"/>
+      <c r="J929" t="inlineStr"/>
+      <c r="K929" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2084205673315700810</t>
+        </is>
+      </c>
+      <c r="L929" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M929" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N929" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O929" t="inlineStr">
+        <is>
+          <t>Booking.com for Travel Agents is responding to a customer issue by directing them to private messaging for booking details and offering 24/7 phone support, while clarifying that only accommodation bookings are handled via social media.</t>
+        </is>
+      </c>
+    </row>
+    <row r="930">
+      <c r="A930" t="inlineStr">
+        <is>
+          <t>Mondee</t>
+        </is>
+      </c>
+      <c r="B930" t="inlineStr">
+        <is>
+          <t>Booking.com for Travel Agents</t>
+        </is>
+      </c>
+      <c r="C930" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D930" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E930" t="inlineStr">
+        <is>
+          <t>Mon Aug 03 09:09:37 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F930" t="inlineStr">
+        <is>
+          <t>Hello Christine, the cost may rise during the reservation process if you initially choose a particular room type and policy but later opt to change to a different category and/or policy. However, for the sake of transparency, we cannot display one price at the start and a different one at the conclusion unless there is a system error. Additionally, throughout the process, we provide a detailed breakdown of costs to help travelers comprehend the reasons behind certain prices. If you encounter any issues with your booking, please send us a direct message with the following details, and we will respond to you as quickly as we can:
+- booking number
+- pin code
+- full name of the guest on the reservation
+Regards</t>
+        </is>
+      </c>
+      <c r="G930" t="inlineStr"/>
+      <c r="H930" t="inlineStr"/>
+      <c r="I930" t="inlineStr"/>
+      <c r="J930" t="inlineStr"/>
+      <c r="K930" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2084205035596963884</t>
+        </is>
+      </c>
+      <c r="L930" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M930" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N930" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O930" t="inlineStr">
+        <is>
+          <t>Booking.com explains that price changes may occur during the reservation process if room type or policy is altered, and offers a detailed cost breakdown and direct messaging support for travelers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="931">
+      <c r="A931" t="inlineStr">
+        <is>
+          <t>Mondee</t>
+        </is>
+      </c>
+      <c r="B931" t="inlineStr">
+        <is>
+          <t>Booking.com for Travel Agents</t>
+        </is>
+      </c>
+      <c r="C931" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D931" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E931" t="inlineStr">
+        <is>
+          <t>Mon Aug 03 09:08:07 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F931" t="inlineStr">
+        <is>
+          <t>@CJackson36508 Hi Cory, we reached out to you via direct message two days ago requesting the documents we require. When you have a moment, please check it out. Thank you very much.</t>
+        </is>
+      </c>
+      <c r="G931" t="inlineStr"/>
+      <c r="H931" t="inlineStr"/>
+      <c r="I931" t="inlineStr"/>
+      <c r="J931" t="inlineStr"/>
+      <c r="K931" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2084204655525908743</t>
+        </is>
+      </c>
+      <c r="L931" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M931" t="inlineStr">
+        <is>
+          <t>Partnership and Acquisitions</t>
+        </is>
+      </c>
+      <c r="N931" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O931" t="inlineStr">
+        <is>
+          <t>Booking.com for Travel Agents is contacting a potential partner to request required documents, indicating a private outreach likely related to a partnership or collaboration.</t>
+        </is>
+      </c>
+    </row>
+    <row r="932">
+      <c r="A932" t="inlineStr">
+        <is>
+          <t>Mondee</t>
+        </is>
+      </c>
+      <c r="B932" t="inlineStr">
+        <is>
+          <t>Booking.com for Travel Agents</t>
+        </is>
+      </c>
+      <c r="C932" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D932" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E932" t="inlineStr">
+        <is>
+          <t>Mon Aug 03 09:06:15 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F932" t="inlineStr">
+        <is>
+          <t>@RichardDSo40757 Hi Richard, we replied to your DM.</t>
+        </is>
+      </c>
+      <c r="G932" t="inlineStr"/>
+      <c r="H932" t="inlineStr"/>
+      <c r="I932" t="inlineStr"/>
+      <c r="J932" t="inlineStr"/>
+      <c r="K932" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2084204187999404122</t>
+        </is>
+      </c>
+      <c r="L932" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M932" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N932" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O932" t="inlineStr">
+        <is>
+          <t>Booking.com for Travel Agents replied to a direct message from user Richard, indicating routine customer or partner engagement.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/News_Dashboard/data/social_media_posts.xlsx
+++ b/News_Dashboard/data/social_media_posts.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O932"/>
+  <dimension ref="A1:O971"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -59702,6 +59702,2506 @@
         </is>
       </c>
     </row>
+    <row r="933">
+      <c r="A933" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B933" t="inlineStr">
+        <is>
+          <t>Navan</t>
+        </is>
+      </c>
+      <c r="C933" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D933" t="inlineStr">
+        <is>
+          <t>navan</t>
+        </is>
+      </c>
+      <c r="E933" t="inlineStr">
+        <is>
+          <t>Mon Aug 03 16:57:21 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F933" t="inlineStr">
+        <is>
+          <t>Hey Chicago,
+We're giving out free matcha and cold brew at Pioneer Court today and tomorrow.
+Stop by! It's a no brainer 🧠 
+#navanatgbta https://t.co/qyTApMP17z</t>
+        </is>
+      </c>
+      <c r="G933" t="inlineStr"/>
+      <c r="H933" t="inlineStr"/>
+      <c r="I933" t="inlineStr"/>
+      <c r="J933" t="inlineStr"/>
+      <c r="K933" t="inlineStr">
+        <is>
+          <t>https://x.com/Navan/status/2084322742061474265</t>
+        </is>
+      </c>
+      <c r="L933" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M933" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N933" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O933" t="inlineStr">
+        <is>
+          <t>Navan is hosting a free matcha and cold brew promotion at Pioneer Court in Chicago to engage customers and increase brand visibility.</t>
+        </is>
+      </c>
+    </row>
+    <row r="934">
+      <c r="A934" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B934" t="inlineStr">
+        <is>
+          <t>Ramp</t>
+        </is>
+      </c>
+      <c r="C934" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D934" t="inlineStr">
+        <is>
+          <t>tryramp</t>
+        </is>
+      </c>
+      <c r="E934" t="inlineStr">
+        <is>
+          <t>Tue Aug 04 16:45:00 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F934" t="inlineStr">
+        <is>
+          <t>BREAKING: Scott Galloway will be speaking at OnRamp 2026.
+Grab your tickets to hear his mid-year predictions: https://t.co/ImRdqa0fR8 https://t.co/Ck6pMHG9qq</t>
+        </is>
+      </c>
+      <c r="G934" t="inlineStr"/>
+      <c r="H934" t="inlineStr"/>
+      <c r="I934" t="inlineStr"/>
+      <c r="J934" t="inlineStr"/>
+      <c r="K934" t="inlineStr">
+        <is>
+          <t>https://x.com/tryramp/status/2084682021784420606</t>
+        </is>
+      </c>
+      <c r="L934" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M934" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N934" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O934" t="inlineStr">
+        <is>
+          <t>Ramp is announcing that Scott Galloway will speak at OnRamp 2026 and is promoting ticket sales for the event.</t>
+        </is>
+      </c>
+    </row>
+    <row r="935">
+      <c r="A935" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B935" t="inlineStr">
+        <is>
+          <t>Ramp</t>
+        </is>
+      </c>
+      <c r="C935" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D935" t="inlineStr">
+        <is>
+          <t>tryramp</t>
+        </is>
+      </c>
+      <c r="E935" t="inlineStr">
+        <is>
+          <t>Tue Aug 04 16:27:20 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F935" t="inlineStr">
+        <is>
+          <t>Get Infinity Home Services' blueprint with the full story: 
+https://t.co/BoElv8cwKz</t>
+        </is>
+      </c>
+      <c r="G935" t="inlineStr"/>
+      <c r="H935" t="inlineStr"/>
+      <c r="I935" t="inlineStr"/>
+      <c r="J935" t="inlineStr"/>
+      <c r="K935" t="inlineStr">
+        <is>
+          <t>https://x.com/tryramp/status/2084677576723665096</t>
+        </is>
+      </c>
+      <c r="L935" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M935" t="inlineStr">
+        <is>
+          <t>Product Announcement</t>
+        </is>
+      </c>
+      <c r="N935" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O935" t="inlineStr">
+        <is>
+          <t>Ramp posts a link to a story about Infinity Home Services' blueprint, promoting the service without providing additional details.</t>
+        </is>
+      </c>
+    </row>
+    <row r="936">
+      <c r="A936" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B936" t="inlineStr">
+        <is>
+          <t>Ramp</t>
+        </is>
+      </c>
+      <c r="C936" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D936" t="inlineStr">
+        <is>
+          <t>tryramp</t>
+        </is>
+      </c>
+      <c r="E936" t="inlineStr">
+        <is>
+          <t>Tue Aug 04 15:29:26 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F936" t="inlineStr">
+        <is>
+          <t>@chaserchapman @grok cue “let’s get it started”</t>
+        </is>
+      </c>
+      <c r="G936" t="inlineStr"/>
+      <c r="H936" t="inlineStr"/>
+      <c r="I936" t="inlineStr"/>
+      <c r="J936" t="inlineStr"/>
+      <c r="K936" t="inlineStr">
+        <is>
+          <t>https://x.com/tryramp/status/2084663006432997718</t>
+        </is>
+      </c>
+      <c r="L936" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M936" t="inlineStr">
+        <is>
+          <t>Product Announcement</t>
+        </is>
+      </c>
+      <c r="N936" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O936" t="inlineStr">
+        <is>
+          <t>Ramp teases a new initiative or collaboration with @chaserchapman and @grok, hinting at upcoming activity.</t>
+        </is>
+      </c>
+    </row>
+    <row r="937">
+      <c r="A937" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B937" t="inlineStr">
+        <is>
+          <t>Ramp</t>
+        </is>
+      </c>
+      <c r="C937" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D937" t="inlineStr">
+        <is>
+          <t>tryramp</t>
+        </is>
+      </c>
+      <c r="E937" t="inlineStr">
+        <is>
+          <t>Tue Aug 04 14:35:00 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F937" t="inlineStr">
+        <is>
+          <t>In construction, precision makes the difference between profit or loss on every job site. So Infinity Home Services made their financial operations airtight across more than 20 brands with Ramp.
+Now 200+ field purchases per day get automatically coded to the right jobs and 90+ hours of AP work get automated on Bill Pay.</t>
+        </is>
+      </c>
+      <c r="G937" t="inlineStr"/>
+      <c r="H937" t="inlineStr"/>
+      <c r="I937" t="inlineStr"/>
+      <c r="J937" t="inlineStr"/>
+      <c r="K937" t="inlineStr">
+        <is>
+          <t>https://x.com/tryramp/status/2084649306561409410</t>
+        </is>
+      </c>
+      <c r="L937" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M937" t="inlineStr">
+        <is>
+          <t>Product Announcement</t>
+        </is>
+      </c>
+      <c r="N937" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O937" t="inlineStr">
+        <is>
+          <t>Ramp showcases Infinity Home Services’ success in automating field purchases and AP work across 20+ brands, highlighting the precision and efficiency gains from its platform.</t>
+        </is>
+      </c>
+    </row>
+    <row r="938">
+      <c r="A938" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B938" t="inlineStr">
+        <is>
+          <t>Ramp</t>
+        </is>
+      </c>
+      <c r="C938" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D938" t="inlineStr">
+        <is>
+          <t>tryramp</t>
+        </is>
+      </c>
+      <c r="E938" t="inlineStr">
+        <is>
+          <t>Mon Aug 03 18:18:46 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F938" t="inlineStr">
+        <is>
+          <t>@NotionHQ @michellehui @MistralAI @Newlab locked in for life</t>
+        </is>
+      </c>
+      <c r="G938" t="inlineStr"/>
+      <c r="H938" t="inlineStr"/>
+      <c r="I938" t="inlineStr"/>
+      <c r="J938" t="inlineStr"/>
+      <c r="K938" t="inlineStr">
+        <is>
+          <t>https://x.com/tryramp/status/2084343234117943538</t>
+        </is>
+      </c>
+      <c r="L938" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M938" t="inlineStr">
+        <is>
+          <t>Partnership and Acquisitions</t>
+        </is>
+      </c>
+      <c r="N938" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O938" t="inlineStr">
+        <is>
+          <t>Ramp announces long-term partnerships with NotionHQ, Michelle Hui, MistralAI, and Newlab.</t>
+        </is>
+      </c>
+    </row>
+    <row r="939">
+      <c r="A939" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B939" t="inlineStr">
+        <is>
+          <t>Ramp</t>
+        </is>
+      </c>
+      <c r="C939" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D939" t="inlineStr">
+        <is>
+          <t>tryramp</t>
+        </is>
+      </c>
+      <c r="E939" t="inlineStr">
+        <is>
+          <t>Mon Aug 03 18:15:22 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F939" t="inlineStr">
+        <is>
+          <t>Ramp is now available in ChatGPT Work with 100+ new tools.
+You can ask things like "how did our software spend change this quarter?” or "can you please do my expenses while I bask in the dappled sunlight of this wooded glen?" 
+Grab the plugin: https://t.co/YHGvV5DDpR https://t.co/sR54w4itn5</t>
+        </is>
+      </c>
+      <c r="G939" t="inlineStr"/>
+      <c r="H939" t="inlineStr"/>
+      <c r="I939" t="inlineStr"/>
+      <c r="J939" t="inlineStr"/>
+      <c r="K939" t="inlineStr">
+        <is>
+          <t>https://x.com/tryramp/status/2084342378173694166</t>
+        </is>
+      </c>
+      <c r="L939" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M939" t="inlineStr">
+        <is>
+          <t>Product Announcement</t>
+        </is>
+      </c>
+      <c r="N939" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O939" t="inlineStr">
+        <is>
+          <t>Ramp announces its integration with ChatGPT Work, offering 100+ new tools and a plugin for streamlined expense and spend queries.</t>
+        </is>
+      </c>
+    </row>
+    <row r="940">
+      <c r="A940" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B940" t="inlineStr">
+        <is>
+          <t>Ramp</t>
+        </is>
+      </c>
+      <c r="C940" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D940" t="inlineStr">
+        <is>
+          <t>tryramp</t>
+        </is>
+      </c>
+      <c r="E940" t="inlineStr">
+        <is>
+          <t>Mon Aug 03 16:08:04 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F940" t="inlineStr">
+        <is>
+          <t>@rajdtta you got this https://t.co/L7SCnh2hZE</t>
+        </is>
+      </c>
+      <c r="G940" t="inlineStr"/>
+      <c r="H940" t="inlineStr"/>
+      <c r="I940" t="inlineStr"/>
+      <c r="J940" t="inlineStr"/>
+      <c r="K940" t="inlineStr">
+        <is>
+          <t>https://x.com/tryramp/status/2084310340246855707</t>
+        </is>
+      </c>
+      <c r="L940" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M940" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N940" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O940" t="inlineStr">
+        <is>
+          <t>Ramp posts a supportive message to a user, indicating encouragement rather than a formal announcement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="941">
+      <c r="A941" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B941" t="inlineStr">
+        <is>
+          <t>Ramp</t>
+        </is>
+      </c>
+      <c r="C941" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="D941" t="inlineStr">
+        <is>
+          <t>tryramp</t>
+        </is>
+      </c>
+      <c r="E941" t="inlineStr">
+        <is>
+          <t>2026-08-04T16:18:22.000Z</t>
+        </is>
+      </c>
+      <c r="F941" t="inlineStr">
+        <is>
+          <t>In construction, precision makes the difference between profit or loss on every job site. So Infinity Home Services made their financial operations airtight across more than 20 brands with Ramp.
+Now 200+ field purchases per day get automatically coded to the right jobs and 90+ hours of AP work get automated on Bill Pay.</t>
+        </is>
+      </c>
+      <c r="G941" t="inlineStr">
+        <is>
+          <t>https://scontent-cdg4-3.cdninstagram.com/v/t51.71878-15/764217551_1578078444059243_610334106829510678_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_ht=scontent-cdg4-3.cdninstagram.com&amp;_nc_cat=111&amp;_nc_oc=Q6cZ2gFeKfM0i0wEdWBr3FToOBqpKFd0w2m1BQR8EVT3BiOzMmyMiBv0_jm0gcwxmhee1leAqsuXfFMZ0xpyicV_Y_OZ&amp;_nc_ohc=QnaayizzjowQ7kNvwFns-QU&amp;_nc_gid=EucXRHRMBGR25UhVj92qiA&amp;edm=ADp7STQBAAAA&amp;ccb=7-5&amp;oh=00_AQF4CyeBfqovwv9dYkh9lA0EOWIP29KFBi5oazt5qlcVsA&amp;oe=6A7812C5&amp;_nc_sid=c6f216</t>
+        </is>
+      </c>
+      <c r="H941" t="inlineStr">
+        <is>
+          <t>[easyocr not installed. Run 'pip install easyocr torch torchvision']</t>
+        </is>
+      </c>
+      <c r="I941" t="inlineStr">
+        <is>
+          <t>https://scontent-cdg4-2.cdninstagram.com/o1/v/t2/f2/m86/AQOKFMCpCAS34zYDBEsjhBxmLM3r2o4FHpgkXatjDFR7pi657m6iQe8_pbTgsgV8ECDxh3IRZjHWKEuXd2WA4AW4O1NOIhuxWvaS5Rc.mp4?_nc_cat=109&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-cdg4-2.cdninstagram.com&amp;_nc_ohc=o2UFqout9ngQ7kNvwFsqYrf&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uQ0xJUFMuQzMuMTE4OC5kYXNoX2Jhc2VsaW5lXzFfdjEiLCJ4cHZfYXNzZXRfaWQiOjE1NzMwNDM1NzQyNzA1MTIsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDA5OSwiZHVyYXRpb25fcyI6MTE5LCJ1cmxnZW5fc291cmNlIjoid3d3In0%3D&amp;ccb=17-1&amp;vs=50c64a2bad162f88&amp;_nc_vs=HBksFQIYUmlnX3hwdl9yZWVsc19wZXJtYW5lbnRfc3JfcHJvZC8xMTRCQ0VEN0MyQ0ExNDVGREYyRDI0NUUxMTYwRDBBOV92aWRlb19kYXNoaW5pdC5tcDQVAALIARIAFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyLzIwNDJDRDVDMjk1RjA2NzdCMjc4QzRGQzNGNDI5RUFCX2F1ZGlvX2Rhc2hpbml0Lm1wNBUCAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbgqK_3l6vLBRUCKAJDMywXQF3wAAAAAAAYEmRhc2hfYmFzZWxpbmVfMV92MREAdf4HZeadAQA&amp;_nc_gid=EucXRHRMBGR25UhVj92qiA&amp;_nc_zt=28&amp;_nc_ss=7a22e&amp;oh=00_AQEFxOiNQbSBVtQecZawNoTsG-q5YFwprp1lD7GvjnzFQQ&amp;oe=6A73F31E</t>
+        </is>
+      </c>
+      <c r="J941" t="inlineStr">
+        <is>
+          <t>[faster-whisper not installed. Run 'pip install faster-whisper']</t>
+        </is>
+      </c>
+      <c r="K941" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Dbn99W8RfyE/</t>
+        </is>
+      </c>
+      <c r="L941" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M941" t="inlineStr">
+        <is>
+          <t>Partnership and Acquisitions</t>
+        </is>
+      </c>
+      <c r="N941" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O941" t="inlineStr">
+        <is>
+          <t>Infinity Home Services partners with Ramp to automate field purchases and accounts payable, enhancing financial precision across more than 20 brands.</t>
+        </is>
+      </c>
+    </row>
+    <row r="942">
+      <c r="A942" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B942" t="inlineStr">
+        <is>
+          <t>Brex</t>
+        </is>
+      </c>
+      <c r="C942" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D942" t="inlineStr">
+        <is>
+          <t>brexhq</t>
+        </is>
+      </c>
+      <c r="E942" t="inlineStr">
+        <is>
+          <t>Tue Aug 04 17:24:14 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F942" t="inlineStr">
+        <is>
+          <t>https://t.co/Q9WxY1DdQO</t>
+        </is>
+      </c>
+      <c r="G942" t="inlineStr"/>
+      <c r="H942" t="inlineStr"/>
+      <c r="I942" t="inlineStr"/>
+      <c r="J942" t="inlineStr"/>
+      <c r="K942" t="inlineStr">
+        <is>
+          <t>https://x.com/brexHQ/status/2084691898074337673</t>
+        </is>
+      </c>
+      <c r="L942" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M942" t="inlineStr">
+        <is>
+          <t>Product Announcement</t>
+        </is>
+      </c>
+      <c r="N942" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O942" t="inlineStr">
+        <is>
+          <t>Brex shares a link to a new product or service announcement, indicating a positive development for the company.</t>
+        </is>
+      </c>
+    </row>
+    <row r="943">
+      <c r="A943" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B943" t="inlineStr">
+        <is>
+          <t>Brex</t>
+        </is>
+      </c>
+      <c r="C943" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D943" t="inlineStr">
+        <is>
+          <t>brexhq</t>
+        </is>
+      </c>
+      <c r="E943" t="inlineStr">
+        <is>
+          <t>Tue Aug 04 16:45:00 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F943" t="inlineStr">
+        <is>
+          <t>@cjgustafson breaks down what our data across thousands of companies is showing on token costs. 
+Tap in 👇</t>
+        </is>
+      </c>
+      <c r="G943" t="inlineStr"/>
+      <c r="H943" t="inlineStr"/>
+      <c r="I943" t="inlineStr"/>
+      <c r="J943" t="inlineStr"/>
+      <c r="K943" t="inlineStr">
+        <is>
+          <t>https://x.com/brexHQ/status/2084682022014910876</t>
+        </is>
+      </c>
+      <c r="L943" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M943" t="inlineStr">
+        <is>
+          <t>Tech Updates</t>
+        </is>
+      </c>
+      <c r="N943" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O943" t="inlineStr">
+        <is>
+          <t>Brex shares data-driven insights on token costs across thousands of companies, providing a technical analysis for its audience.</t>
+        </is>
+      </c>
+    </row>
+    <row r="944">
+      <c r="A944" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B944" t="inlineStr">
+        <is>
+          <t>Brex</t>
+        </is>
+      </c>
+      <c r="C944" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D944" t="inlineStr">
+        <is>
+          <t>brexhq</t>
+        </is>
+      </c>
+      <c r="E944" t="inlineStr">
+        <is>
+          <t>Mon Aug 03 22:31:38 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F944" t="inlineStr">
+        <is>
+          <t>@merge_api @meetgranola @sigmacomputing @ashbyhq @statsig @metabase Love to see it 🤝</t>
+        </is>
+      </c>
+      <c r="G944" t="inlineStr"/>
+      <c r="H944" t="inlineStr"/>
+      <c r="I944" t="inlineStr"/>
+      <c r="J944" t="inlineStr"/>
+      <c r="K944" t="inlineStr">
+        <is>
+          <t>https://x.com/brexHQ/status/2084406869737541882</t>
+        </is>
+      </c>
+      <c r="L944" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M944" t="inlineStr">
+        <is>
+          <t>Partnership and Acquisitions</t>
+        </is>
+      </c>
+      <c r="N944" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O944" t="inlineStr">
+        <is>
+          <t>Brex expresses enthusiasm for a collaboration or partnership involving Merge API, MeetGranola, Sigma Computing, AshbyHQ, Statsig, and Metabase.</t>
+        </is>
+      </c>
+    </row>
+    <row r="945">
+      <c r="A945" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B945" t="inlineStr">
+        <is>
+          <t>Brex</t>
+        </is>
+      </c>
+      <c r="C945" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D945" t="inlineStr">
+        <is>
+          <t>brexhq</t>
+        </is>
+      </c>
+      <c r="E945" t="inlineStr">
+        <is>
+          <t>Mon Aug 03 18:28:00 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F945" t="inlineStr">
+        <is>
+          <t>Nobody throws a party over an expense report getting completed on time. But maybe they should?</t>
+        </is>
+      </c>
+      <c r="G945" t="inlineStr"/>
+      <c r="H945" t="inlineStr"/>
+      <c r="I945" t="inlineStr"/>
+      <c r="J945" t="inlineStr"/>
+      <c r="K945" t="inlineStr">
+        <is>
+          <t>https://x.com/brexHQ/status/2084345554742698094</t>
+        </is>
+      </c>
+      <c r="L945" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M945" t="inlineStr">
+        <is>
+          <t>Product Announcement</t>
+        </is>
+      </c>
+      <c r="N945" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O945" t="inlineStr">
+        <is>
+          <t>Brex humorously promotes the value of completing expense reports on time, implying that such efficiency deserves celebration.</t>
+        </is>
+      </c>
+    </row>
+    <row r="946">
+      <c r="A946" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B946" t="inlineStr">
+        <is>
+          <t>Brex</t>
+        </is>
+      </c>
+      <c r="C946" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D946" t="inlineStr">
+        <is>
+          <t>brexhq</t>
+        </is>
+      </c>
+      <c r="E946" t="inlineStr">
+        <is>
+          <t>Mon Aug 03 14:57:22 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F946" t="inlineStr">
+        <is>
+          <t>By the time you're done reading this, an AI agent somewhere just handled an expense no one had to think about</t>
+        </is>
+      </c>
+      <c r="G946" t="inlineStr"/>
+      <c r="H946" t="inlineStr"/>
+      <c r="I946" t="inlineStr"/>
+      <c r="J946" t="inlineStr"/>
+      <c r="K946" t="inlineStr">
+        <is>
+          <t>https://x.com/brexHQ/status/2084292548185440669</t>
+        </is>
+      </c>
+      <c r="L946" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M946" t="inlineStr">
+        <is>
+          <t>Product Announcement</t>
+        </is>
+      </c>
+      <c r="N946" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O946" t="inlineStr">
+        <is>
+          <t>Brex highlights a new AI agent that automatically processes expenses, showcasing an advancement in their expense management capabilities.</t>
+        </is>
+      </c>
+    </row>
+    <row r="947">
+      <c r="A947" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B947" t="inlineStr">
+        <is>
+          <t>Brex</t>
+        </is>
+      </c>
+      <c r="C947" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D947" t="inlineStr">
+        <is>
+          <t>brexhq</t>
+        </is>
+      </c>
+      <c r="E947" t="inlineStr">
+        <is>
+          <t>Mon Aug 03 14:10:59 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F947" t="inlineStr">
+        <is>
+          <t>@axrahman See you on the court! 🎾</t>
+        </is>
+      </c>
+      <c r="G947" t="inlineStr"/>
+      <c r="H947" t="inlineStr"/>
+      <c r="I947" t="inlineStr"/>
+      <c r="J947" t="inlineStr"/>
+      <c r="K947" t="inlineStr">
+        <is>
+          <t>https://x.com/brexHQ/status/2084280877039677538</t>
+        </is>
+      </c>
+      <c r="L947" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M947" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N947" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O947" t="inlineStr">
+        <is>
+          <t>Brex tweets a friendly message to @axrahman about an upcoming tennis match, indicating a lighthearted engagement rather than a business announcement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="948">
+      <c r="A948" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B948" t="inlineStr">
+        <is>
+          <t>Expedia</t>
+        </is>
+      </c>
+      <c r="C948" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="D948" t="inlineStr">
+        <is>
+          <t>expedia</t>
+        </is>
+      </c>
+      <c r="E948" t="inlineStr">
+        <is>
+          <t>2026-08-04T16:00:03.000Z</t>
+        </is>
+      </c>
+      <c r="F948" t="inlineStr">
+        <is>
+          <t>An island getaway might not make you think of Norway, but it definitely should. 24 hours of sunlight at certain times of year? Yes, really. One of our top picks on the Island Hot List. 🔗 Check out other islands, link in bio.</t>
+        </is>
+      </c>
+      <c r="G948" t="inlineStr">
+        <is>
+          <t>https://scontent-yyz1-1.cdninstagram.com/v/t51.82787-15/764907986_18621031393030381_3837496416266496752_n.jpg?stp=dst-jpg_e15_fr_p1080x1080_tt6&amp;_nc_ht=scontent-yyz1-1.cdninstagram.com&amp;_nc_cat=101&amp;_nc_oc=Q6cZ2gHR43eDW45ek9RoFk7E6j5j9qZSDzZwzhbUtg4ua07t9dYR4iUZxsqUlnUPr0sFKcM&amp;_nc_ohc=axYkncCjeDEQ7kNvwEYjMCI&amp;_nc_gid=tXkYr90r7NMSwWIIdXGP5Q&amp;edm=ADp7STQBAAAA&amp;ccb=7-5&amp;oh=00_AQGMrkIgDAyWx_TFBHM0M9pPN_M0vLLLXkUDjUyWJ5ObDA&amp;oe=6A7811BA&amp;_nc_sid=c6f216</t>
+        </is>
+      </c>
+      <c r="H948" t="inlineStr">
+        <is>
+          <t>[easyocr not installed. Run 'pip install easyocr torch torchvision']</t>
+        </is>
+      </c>
+      <c r="I948" t="inlineStr">
+        <is>
+          <t>https://scontent-yyz1-1.cdninstagram.com/o1/v/t2/f2/m86/AQNxu_WHoxtJtgPVC-6cOftusfUiBDqUuz4mV9O7XnvyPJj7w-BY6dGFE8r3JUTTIAHUvTBNTxIZ91jgjhu1T5p0xKL86kzgFmbjmPE.mp4?_nc_cat=107&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-yyz1-1.cdninstagram.com&amp;_nc_ohc=KowvbZD_JBIQ7kNvwHrD9Ov&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uQ0xJUFMuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTg2MjEwMTI4OTIwMzAzODEsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDA5OSwiZHVyYXRpb25fcyI6MTIsInVybGdlbl9zb3VyY2UiOiJ3d3cifQ%3D%3D&amp;ccb=17-1&amp;vs=966813b29c9be2e3&amp;_nc_vs=HBksFQIYUmlnX3hwdl9yZWVsc19wZXJtYW5lbnRfc3JfcHJvZC8xMjRCMjVDNDBBM0Y4NUJDNEZBMzFEQTZBQUYwNzQ5OF92aWRlb19kYXNoaW5pdC5tcDQVAALIARIAFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyLzFENDAzRTVGNTlCMTU3NDY2RTAwRUI3M0NCREEzQjgxX2F1ZGlvX2Rhc2hpbml0Lm1wNBUCAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACba1sysze2TQhUCKAJDMywXQCkQ5WBBiTcYEmRhc2hfYmFzZWxpbmVfMV92MREAdf4HZeadAQA&amp;_nc_gid=tXkYr90r7NMSwWIIdXGP5Q&amp;_nc_zt=28&amp;_nc_ss=7a22e&amp;oh=00_AQEEZrgVW4IO8MsVlTRNr2gHA4R0-omugxCdL8qI_0yD0A&amp;oe=6A740FB4</t>
+        </is>
+      </c>
+      <c r="J948" t="inlineStr">
+        <is>
+          <t>[faster-whisper not installed. Run 'pip install faster-whisper']</t>
+        </is>
+      </c>
+      <c r="K948" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Dbn18YBiaZ0/</t>
+        </is>
+      </c>
+      <c r="L948" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M948" t="inlineStr">
+        <is>
+          <t>Product Announcement</t>
+        </is>
+      </c>
+      <c r="N948" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O948" t="inlineStr">
+        <is>
+          <t>Expedia promotes Norway as an unexpected island getaway, featuring it as a top pick on its Island Hot List and encouraging followers to explore more islands via the link in bio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="949">
+      <c r="A949" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B949" t="inlineStr">
+        <is>
+          <t>Expedia</t>
+        </is>
+      </c>
+      <c r="C949" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D949" t="inlineStr">
+        <is>
+          <t>Expedia</t>
+        </is>
+      </c>
+      <c r="E949" t="inlineStr">
+        <is>
+          <t>2026-08-04T14:10:13.399Z</t>
+        </is>
+      </c>
+      <c r="F949" t="inlineStr">
+        <is>
+          <t>The final whistle blew. The travel inspiration didn't. 
+Expedia data shows that the 2026 summer soccer tournament sparked a wave of travel inspiration across the U.S.  
+We're calling it the "Golden Boarding Pass": 11 destinations that turned football fever into real-world wanderlust. 
+What drove it? Not just trophies. Underdog heroics. Viral fan moments. Emotional storylines that made people think: I want to go there. 
+The biggest takeaway: when a country captures hearts on the pitch, travelers are ready to book a trip off it. 
+See the full list here: http://ms.spr.ly/6047a8C4X</t>
+        </is>
+      </c>
+      <c r="G949" t="inlineStr"/>
+      <c r="H949" t="inlineStr"/>
+      <c r="I949" t="inlineStr"/>
+      <c r="J949" t="inlineStr"/>
+      <c r="K949" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/expedia_summers-soccer-fever-powers-travel-demand-activity-7490408759790387200-SrVt</t>
+        </is>
+      </c>
+      <c r="L949" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M949" t="inlineStr">
+        <is>
+          <t>Product Announcement</t>
+        </is>
+      </c>
+      <c r="N949" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O949" t="inlineStr">
+        <is>
+          <t>Expedia capitalized on the 2026 summer soccer tournament by promoting 11 destinations—dubbed the "Golden Boarding Pass"—to inspire travel and drive bookings, highlighting underdog heroics and viral fan moments as key motivators.</t>
+        </is>
+      </c>
+    </row>
+    <row r="950">
+      <c r="A950" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B950" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C950" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D950" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E950" t="inlineStr">
+        <is>
+          <t>Tue Aug 04 15:41:51 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F950" t="inlineStr">
+        <is>
+          <t>Bonjour Elsa, merci de nous interpeller ici. Nous sommes navrés d'apprendre que vous semblez être en attente d'un remboursement de notre part.
+Pour que nous puissions nous renseigner davantage sur la situation, nous vous invitons à nous communiquer, uniquement en message privé pour des raisons de confidentialité :
+- le numéro de confirmation
+- le code confidentiel
+- le nom complet du voyageur
+Nous reviendrons ensuite au plus vite vers vous mais gardez à l'esprit que notre équipe des réseaux sociaux ne fonctionne pas en temps réel.
+Dans cette attente, nous vous souhaitons une bonne fin de journée.
+Cordialement.</t>
+        </is>
+      </c>
+      <c r="G950" t="inlineStr"/>
+      <c r="H950" t="inlineStr"/>
+      <c r="I950" t="inlineStr"/>
+      <c r="J950" t="inlineStr"/>
+      <c r="K950" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2084666129356599645</t>
+        </is>
+      </c>
+      <c r="L950" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M950" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N950" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O950" t="inlineStr">
+        <is>
+          <t>Booking.com replies to a customer complaint about a pending refund, asking for private details to investigate the issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="951">
+      <c r="A951" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B951" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C951" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D951" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E951" t="inlineStr">
+        <is>
+          <t>Tue Aug 04 14:10:55 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F951" t="inlineStr">
+        <is>
+          <t>Hi there, thanks for letting us know about this. It doesn't necessarily mean your account has been compromised. It’s possible that the person making the reservation accidentally entered a typo in their email during the booking process which our platform would recognize as yours. We’d like to reach out to the booker to correct this issue. Please DM us the following details, so we can follow up:
+Confirmation number:
+Pin code:
+Name of the Guest:</t>
+        </is>
+      </c>
+      <c r="G951" t="inlineStr"/>
+      <c r="H951" t="inlineStr"/>
+      <c r="I951" t="inlineStr"/>
+      <c r="J951" t="inlineStr"/>
+      <c r="K951" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2084643245661859996</t>
+        </is>
+      </c>
+      <c r="L951" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M951" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N951" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O951" t="inlineStr">
+        <is>
+          <t>Booking.com addresses a potential account compromise claim, explaining it could be a typo in the booking process and requests confirmation details to resolve the issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="952">
+      <c r="A952" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B952" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C952" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D952" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E952" t="inlineStr">
+        <is>
+          <t>Tue Aug 04 12:36:22 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F952" t="inlineStr">
+        <is>
+          <t>@adv_abdulazeem Hi Abdul, thanks for reaching out to us.
+We regret hearing the accommodation didn't honor your booking. Please check our reply to your DM, kind regards. https://t.co/Z89AAoEgD7</t>
+        </is>
+      </c>
+      <c r="G952" t="inlineStr"/>
+      <c r="H952" t="inlineStr"/>
+      <c r="I952" t="inlineStr"/>
+      <c r="J952" t="inlineStr"/>
+      <c r="K952" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2084619453493371194</t>
+        </is>
+      </c>
+      <c r="L952" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M952" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N952" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O952" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a user complaint about an accommodation not honoring a booking, apologizing and directing the user to a private message for resolution.</t>
+        </is>
+      </c>
+    </row>
+    <row r="953">
+      <c r="A953" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B953" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C953" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D953" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E953" t="inlineStr">
+        <is>
+          <t>Tue Aug 04 11:45:46 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F953" t="inlineStr">
+        <is>
+          <t>@Matt_FoXclan - Numéro de confirmation :
+- Code confidentiel :
+- Nom indiqué sur la réservation :
+Vous pouvez également nous appeler pour une assistance immédiate ici : https://t.co/aH74XgSLGq</t>
+        </is>
+      </c>
+      <c r="G953" t="inlineStr"/>
+      <c r="H953" t="inlineStr"/>
+      <c r="I953" t="inlineStr"/>
+      <c r="J953" t="inlineStr"/>
+      <c r="K953" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2084606720555229364</t>
+        </is>
+      </c>
+      <c r="L953" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M953" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N953" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O953" t="inlineStr">
+        <is>
+          <t>Booking.com posted a generic support message with placeholders for confirmation number, code, and name, offering immediate assistance via a link.</t>
+        </is>
+      </c>
+    </row>
+    <row r="954">
+      <c r="A954" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B954" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C954" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D954" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E954" t="inlineStr">
+        <is>
+          <t>Tue Aug 04 11:45:38 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F954" t="inlineStr">
+        <is>
+          <t>Hi Nicole, we want to emphasize that we regret to hear about your experience with your Car Rental Reservation and the purchased insurance. We've now escalated your case further to our dedicated team, who will get back to you shortly. 
+Should you have any other questions in the meantime, please don't hesitate to reach out to us again. 
+Kind regards.</t>
+        </is>
+      </c>
+      <c r="G954" t="inlineStr"/>
+      <c r="H954" t="inlineStr"/>
+      <c r="I954" t="inlineStr"/>
+      <c r="J954" t="inlineStr"/>
+      <c r="K954" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2084606684928835692</t>
+        </is>
+      </c>
+      <c r="L954" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="M954" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N954" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O954" t="inlineStr">
+        <is>
+          <t>Booking.com apologizes for a negative car rental reservation experience and escalates the case to a dedicated team.</t>
+        </is>
+      </c>
+    </row>
+    <row r="955">
+      <c r="A955" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B955" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C955" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D955" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E955" t="inlineStr">
+        <is>
+          <t>Tue Aug 04 11:45:21 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F955" t="inlineStr">
+        <is>
+          <t>@Matt_FoXclan Nous regrettons de lire votre déception concernant vos difficultés avec votre transfert depuis/vers l’aéroport.
+Afin que nous puissions vous assister davantage, merci de nous envoyer un message privé avec les informations suivantes :</t>
+        </is>
+      </c>
+      <c r="G955" t="inlineStr"/>
+      <c r="H955" t="inlineStr"/>
+      <c r="I955" t="inlineStr"/>
+      <c r="J955" t="inlineStr"/>
+      <c r="K955" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2084606612333810107</t>
+        </is>
+      </c>
+      <c r="L955" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M955" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N955" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O955" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a user’s complaint about airport transfer difficulties, offering private assistance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="956">
+      <c r="A956" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B956" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C956" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D956" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E956" t="inlineStr">
+        <is>
+          <t>Tue Aug 04 11:45:07 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F956" t="inlineStr">
+        <is>
+          <t>@Matt_FoXclan Bonjour, nous vous présentons nos excuses pour notre réponse tardive. Nous recevons actuellement un volume important de messages sur les réseaux sociaux, ce qui a retardé notre retour vers vous.</t>
+        </is>
+      </c>
+      <c r="G956" t="inlineStr"/>
+      <c r="H956" t="inlineStr"/>
+      <c r="I956" t="inlineStr"/>
+      <c r="J956" t="inlineStr"/>
+      <c r="K956" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2084606555446546525</t>
+        </is>
+      </c>
+      <c r="L956" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M956" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N956" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O956" t="inlineStr">
+        <is>
+          <t>Booking.com apologized for a delayed response to a user, citing a high volume of messages on social media.</t>
+        </is>
+      </c>
+    </row>
+    <row r="957">
+      <c r="A957" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B957" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C957" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D957" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E957" t="inlineStr">
+        <is>
+          <t>Tue Aug 04 10:57:31 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F957" t="inlineStr">
+        <is>
+          <t>@Zidedine Hola Zidane, gracias por contactarnos. Hemos respondido a tu mensaje privado, cuando tengas oportunidad, por favor revisa tu bandeja de entrada. Gracias.</t>
+        </is>
+      </c>
+      <c r="G957" t="inlineStr"/>
+      <c r="H957" t="inlineStr"/>
+      <c r="I957" t="inlineStr"/>
+      <c r="J957" t="inlineStr"/>
+      <c r="K957" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2084594577294438458</t>
+        </is>
+      </c>
+      <c r="L957" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M957" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N957" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O957" t="inlineStr">
+        <is>
+          <t>Booking.com replied to a private message from a user, confirming receipt and asking them to check their inbox.</t>
+        </is>
+      </c>
+    </row>
+    <row r="958">
+      <c r="A958" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B958" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C958" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D958" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E958" t="inlineStr">
+        <is>
+          <t>Tue Aug 04 10:46:52 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F958" t="inlineStr">
+        <is>
+          <t>Hi Mike, we regret to hear that the property wasn’t able to accommodate you. On https://t.co/fGhmZE7riF, room availability is managed directly by the property, and they’re responsible for keeping it accurate. 
+To assist you, please send us a DM with the following details, and we will get back to you as soon as possible: 
+- Confirmation number 
+- PIN code 
+- Name on the reservation 
+Best regards.</t>
+        </is>
+      </c>
+      <c r="G958" t="inlineStr"/>
+      <c r="H958" t="inlineStr"/>
+      <c r="I958" t="inlineStr"/>
+      <c r="J958" t="inlineStr"/>
+      <c r="K958" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2084591894823145769</t>
+        </is>
+      </c>
+      <c r="L958" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M958" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N958" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O958" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a customer complaint about property availability, offering to resolve the issue via direct message.</t>
+        </is>
+      </c>
+    </row>
+    <row r="959">
+      <c r="A959" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B959" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C959" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D959" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E959" t="inlineStr">
+        <is>
+          <t>Tue Aug 04 10:30:01 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F959" t="inlineStr">
+        <is>
+          <t>Hola, Carles. Lamentamos los inconvenientes. Cuéntanos, ¿en qué podemos ayudarte?. Para que podamos atender tu solicitud, envíanos un mensaje privado con los siguientes datos y te responderemos lo antes posible:
+- Número de confirmación:
+- Código PIN:
+- Nombre que aparece en la reserva:
+- Detalles de tu solicitud:
+Ten en cuenta que nuestro equipo de Redes Sociales no trabaja en tiempo real. Para recibir ayuda inmediata, llama a nuestro equipo de Atención al Cliente disponible 24/7; puedes encontrar nuestros datos de contacto aquí:  https://t.co/o8QyR8SaDb
+Un saludo.</t>
+        </is>
+      </c>
+      <c r="G959" t="inlineStr"/>
+      <c r="H959" t="inlineStr"/>
+      <c r="I959" t="inlineStr"/>
+      <c r="J959" t="inlineStr"/>
+      <c r="K959" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2084587655526785254</t>
+        </is>
+      </c>
+      <c r="L959" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M959" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N959" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O959" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a user’s complaint, offering to resolve the issue via private message and providing contact details for immediate assistance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="960">
+      <c r="A960" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B960" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C960" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D960" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E960" t="inlineStr">
+        <is>
+          <t>Tue Aug 04 10:11:58 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F960" t="inlineStr">
+        <is>
+          <t>Olá, bom dia, Agradecemos pelo seu contato, mas como este e o primeiro através deste canal, precisamos de mais informações para poder ajudar. Se o reembolso mencionado for por uma reserva de acomodação, pedimos que nos contate pelo privado com:
+• O seu número de confirmação
+• O código PIN
+• O nome do titular da reserva
+E te daremos um retorno breve. Pra suporte imediato, sugerimos o contato direto com o nosso SAC 24h através do 11 4700 3708 (ou um dos seguinte números: https://t.co/o8QyR8SaDb).
+Caso o assunto seja devido a reservas de passagens, táxi ou seguros, entre em contato com a equipe de suporte dedicada aqui: https://t.co/OVuF5pCzba, e pra suporte como uma propriedade, através da sua Extranet ou um destes números: https://t.co/cUW1kaDY9m?.</t>
+        </is>
+      </c>
+      <c r="G960" t="inlineStr"/>
+      <c r="H960" t="inlineStr"/>
+      <c r="I960" t="inlineStr"/>
+      <c r="J960" t="inlineStr"/>
+      <c r="K960" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2084583111988240745</t>
+        </is>
+      </c>
+      <c r="L960" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M960" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N960" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O960" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a customer inquiry in Portuguese, requesting additional details for a refund and providing contact options for further assistance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="961">
+      <c r="A961" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B961" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C961" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D961" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E961" t="inlineStr">
+        <is>
+          <t>Tue Aug 04 10:02:23 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F961" t="inlineStr">
+        <is>
+          <t>@ssa5555005 Hi there, we have responded to your DM.</t>
+        </is>
+      </c>
+      <c r="G961" t="inlineStr"/>
+      <c r="H961" t="inlineStr"/>
+      <c r="I961" t="inlineStr"/>
+      <c r="J961" t="inlineStr"/>
+      <c r="K961" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2084580700699681158</t>
+        </is>
+      </c>
+      <c r="L961" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M961" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N961" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O961" t="inlineStr">
+        <is>
+          <t>Booking.com replied to a user’s direct message on X.</t>
+        </is>
+      </c>
+    </row>
+    <row r="962">
+      <c r="A962" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B962" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C962" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D962" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E962" t="inlineStr">
+        <is>
+          <t>Tue Aug 04 10:00:42 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F962" t="inlineStr">
+        <is>
+          <t>@OlivierFlahaut Bonjour Olivier, nous nous excusons pour notre réponse tardive. Nous vous avons envoyé un message privé ; merci de le consulter dès que possible.</t>
+        </is>
+      </c>
+      <c r="G962" t="inlineStr"/>
+      <c r="H962" t="inlineStr"/>
+      <c r="I962" t="inlineStr"/>
+      <c r="J962" t="inlineStr"/>
+      <c r="K962" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2084580275728642299</t>
+        </is>
+      </c>
+      <c r="L962" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M962" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N962" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O962" t="inlineStr">
+        <is>
+          <t>Booking.com apologized for a delayed response and sent a private message to user Olivier Flahaut.</t>
+        </is>
+      </c>
+    </row>
+    <row r="963">
+      <c r="A963" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B963" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C963" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D963" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E963" t="inlineStr">
+        <is>
+          <t>Tue Aug 04 09:49:11 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F963" t="inlineStr">
+        <is>
+          <t>@madoublevie89 Vous pouvez également nous appeler pour une assistance immédiate ici : https://t.co/aH74XgSLGq</t>
+        </is>
+      </c>
+      <c r="G963" t="inlineStr"/>
+      <c r="H963" t="inlineStr"/>
+      <c r="I963" t="inlineStr"/>
+      <c r="J963" t="inlineStr"/>
+      <c r="K963" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2084577381050699785</t>
+        </is>
+      </c>
+      <c r="L963" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M963" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N963" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O963" t="inlineStr">
+        <is>
+          <t>Booking.com is directing users to a new contact link for immediate assistance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="964">
+      <c r="A964" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B964" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C964" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D964" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E964" t="inlineStr">
+        <is>
+          <t>Tue Aug 04 09:48:49 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F964" t="inlineStr">
+        <is>
+          <t>@madoublevie89 Afin que nous puissions vous aider ici, merci de nous envoyer un message privé avec les informations suivantes :
+- Numéro de confirmation :
+- Code confidentiel :
+- Nom indiqué sur la réservation :</t>
+        </is>
+      </c>
+      <c r="G964" t="inlineStr"/>
+      <c r="H964" t="inlineStr"/>
+      <c r="I964" t="inlineStr"/>
+      <c r="J964" t="inlineStr"/>
+      <c r="K964" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2084577287001829547</t>
+        </is>
+      </c>
+      <c r="L964" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M964" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N964" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O964" t="inlineStr">
+        <is>
+          <t>Booking.com asks a user to send private booking details via direct message for assistance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="965">
+      <c r="A965" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B965" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C965" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D965" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E965" t="inlineStr">
+        <is>
+          <t>Tue Aug 04 09:48:34 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F965" t="inlineStr">
+        <is>
+          <t>@madoublevie89 Bonjour, toutes nos excuses pour notre réponse tardive. Nous regrettons de lire votre déception.</t>
+        </is>
+      </c>
+      <c r="G965" t="inlineStr"/>
+      <c r="H965" t="inlineStr"/>
+      <c r="I965" t="inlineStr"/>
+      <c r="J965" t="inlineStr"/>
+      <c r="K965" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2084577224674398377</t>
+        </is>
+      </c>
+      <c r="L965" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="M965" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N965" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O965" t="inlineStr">
+        <is>
+          <t>Booking.com apologizes for a delayed response and expresses regret over a user's disappointment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="966">
+      <c r="A966" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B966" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C966" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D966" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E966" t="inlineStr">
+        <is>
+          <t>Tue Aug 04 09:22:23 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F966" t="inlineStr">
+        <is>
+          <t>Sentimos que tuvieras dificultades con tu reserva, no hayas recibido el reembolso y haber tardado en responder, Alejandro. Debido al gran volumen de casos en las redes sociales, no hemos podido contestar hasta ahora.  
+Entendemos que quieres resolverlo. Si deseas que lo revisemos, envíanos un mensaje privado con el código PIN de la reserva y nos pondremos en contacto contigo lo antes posible. 
+Como alternativa, si necesitas asistencia inmediata, siempre puedes llamarnos aquí: https://t.co/tuuNbmGVaG
+Un saludo.</t>
+        </is>
+      </c>
+      <c r="G966" t="inlineStr"/>
+      <c r="H966" t="inlineStr"/>
+      <c r="I966" t="inlineStr"/>
+      <c r="J966" t="inlineStr"/>
+      <c r="K966" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2084570634017767436</t>
+        </is>
+      </c>
+      <c r="L966" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M966" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N966" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O966" t="inlineStr">
+        <is>
+          <t>Booking.com apologizes for a customer’s reservation difficulties, refund delay, and slow response, offering to resolve the issue via private message with a PIN or a phone call.</t>
+        </is>
+      </c>
+    </row>
+    <row r="967">
+      <c r="A967" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B967" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C967" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D967" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E967" t="inlineStr">
+        <is>
+          <t>Tue Aug 04 09:11:47 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F967" t="inlineStr">
+        <is>
+          <t>Hi Veronique, how can we help you? If your request is related to an accommodation booking, please DM us the following details, and we'll get back to you as soon as possible: 
+- Confirmation number:
+- Pin code:
+- Name on the reservation:
+- Details on your request:
+For questions about Flights, Taxis, or Insurance, you can reach out to the dedicated support team here: https://t.co/UfRgpDJomK</t>
+        </is>
+      </c>
+      <c r="G967" t="inlineStr"/>
+      <c r="H967" t="inlineStr"/>
+      <c r="I967" t="inlineStr"/>
+      <c r="J967" t="inlineStr"/>
+      <c r="K967" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2084567966385865108</t>
+        </is>
+      </c>
+      <c r="L967" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M967" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N967" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O967" t="inlineStr">
+        <is>
+          <t>Booking.com shares a new customer support workflow for accommodation booking inquiries, directing flight, taxi, and insurance questions to a dedicated team.</t>
+        </is>
+      </c>
+    </row>
+    <row r="968">
+      <c r="A968" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B968" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C968" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D968" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E968" t="inlineStr">
+        <is>
+          <t>Tue Aug 04 07:26:01 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F968" t="inlineStr">
+        <is>
+          <t>Hola, Zazu. Lamentamos la tardanza en nuestra respuesta. Ten presente que no ofrecemos asistencia inmediata a través de las redes sociales. 
+Nos complace saber que tu solicitud ha sido resuelta. 
+Para cualquier cosa adicional que necesites, no dudes en ponerte en contacto con nosotros nuevamente.
+Un saludo.</t>
+        </is>
+      </c>
+      <c r="G968" t="inlineStr"/>
+      <c r="H968" t="inlineStr"/>
+      <c r="I968" t="inlineStr"/>
+      <c r="J968" t="inlineStr"/>
+      <c r="K968" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2084541349076897861</t>
+        </is>
+      </c>
+      <c r="L968" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M968" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N968" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O968" t="inlineStr">
+        <is>
+          <t>Booking.com apologizes for a delayed response and informs the user that immediate assistance via social media is not available, offering further contact if needed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="969">
+      <c r="A969" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B969" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C969" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D969" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E969" t="inlineStr">
+        <is>
+          <t>Tue Aug 04 07:06:43 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F969" t="inlineStr">
+        <is>
+          <t>Bonjour Amandine, merci de nous avoir contactés. Nous sommes navrés d'apprendre que vous restez dans l'attente d'une réponse de notre service client pour votre demande de remboursement. 
+Pour que nous puissions accéder à votre dossier, nous vous invitons à nous communiquer par message privé pour des raisons de confidentialité : 
+- le numéro de confirmation 
+- le code confidentiel 
+- le nom complet du voyageur 
+Nous reviendrons ensuite vers vous dès que possible. 
+Cordialement.</t>
+        </is>
+      </c>
+      <c r="G969" t="inlineStr"/>
+      <c r="H969" t="inlineStr"/>
+      <c r="I969" t="inlineStr"/>
+      <c r="J969" t="inlineStr"/>
+      <c r="K969" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2084536492429320616</t>
+        </is>
+      </c>
+      <c r="L969" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M969" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N969" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O969" t="inlineStr">
+        <is>
+          <t>Booking.com replies to a customer’s refund inquiry, apologizing for the delay and requesting private details via direct message for confidentiality.</t>
+        </is>
+      </c>
+    </row>
+    <row r="970">
+      <c r="A970" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B970" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C970" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D970" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="E970" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:03:01.464Z</t>
+        </is>
+      </c>
+      <c r="F970" t="inlineStr">
+        <is>
+          <t>What if the best engineering is the kind you never actually see? ☁️
+Join Laura and Anushka from our Manchester office as they dive into making travel effortless, taking real ownership and life inside our UK tech hub! 🇬🇧
+Anushka unwinds by baking cheesecake! 🍰
+How do you like to recharge when you close your laptop?</t>
+        </is>
+      </c>
+      <c r="G970" t="inlineStr"/>
+      <c r="H970" t="inlineStr"/>
+      <c r="I970" t="inlineStr">
+        <is>
+          <t>https://dms.licdn.com/playlist/vid/v2/D4E10AQENP6TeIRShTQ/mp4-720p-30fp-crf28/B4EZ_Lp76aIUBk-/0/1785828212022?e=1786474800&amp;v=beta&amp;t=CJKysSOZDHCsEbracxXhDe6vr605VOE_47tBi0iIfq0</t>
+        </is>
+      </c>
+      <c r="J970" t="inlineStr">
+        <is>
+          <t>[faster-whisper not installed. Run 'pip install faster-whisper']</t>
+        </is>
+      </c>
+      <c r="K970" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/booking%2Ecom_what-if-the-best-engineering-is-the-kind-activity-7490316351157391360-HV_w</t>
+        </is>
+      </c>
+      <c r="L970" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M970" t="inlineStr">
+        <is>
+          <t>Tech Updates</t>
+        </is>
+      </c>
+      <c r="N970" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O970" t="inlineStr">
+        <is>
+          <t>Booking.com showcases its Manchester tech hub, highlighting engineering culture and personal touches from team members to emphasize effortless travel and ownership.</t>
+        </is>
+      </c>
+    </row>
+    <row r="971">
+      <c r="A971" t="inlineStr">
+        <is>
+          <t>Mondee</t>
+        </is>
+      </c>
+      <c r="B971" t="inlineStr">
+        <is>
+          <t>Sky Bird Travel</t>
+        </is>
+      </c>
+      <c r="C971" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D971" t="inlineStr">
+        <is>
+          <t>Sky Bird Travel &amp; Tours</t>
+        </is>
+      </c>
+      <c r="E971" t="inlineStr">
+        <is>
+          <t>2026-08-03T22:16:03.105Z</t>
+        </is>
+      </c>
+      <c r="F971" t="inlineStr">
+        <is>
+          <t>We couldn't have won gold at last year’s Travvy Awards without you. We're nominated again for Best Airline Consolidator at the 2026 awards!  
+Voting closes on September 4, so click the link to vote for us!  https://lnkd.in/eQAs2phh
+#TravvyAwards2026  #VoteForSkyBirdSkyBird #BestAirlineConsolidator</t>
+        </is>
+      </c>
+      <c r="G971" t="inlineStr">
+        <is>
+          <t>https://media.licdn.com/dms/image/v2/D4D22AQFe96gOQLUbFA/feedshare-shrink_1280/B4DZ_Jsrl7H0AM-/0/1785795361723?e=1787184000&amp;v=beta&amp;t=y4vRvKJiMubBsNB5Mlokz37j-CvNN5RVjiqoVinJ-KM</t>
+        </is>
+      </c>
+      <c r="H971" t="inlineStr">
+        <is>
+          <t>[easyocr not installed. Run 'pip install easyocr torch torchvision']</t>
+        </is>
+      </c>
+      <c r="I971" t="inlineStr"/>
+      <c r="J971" t="inlineStr"/>
+      <c r="K971" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/sky-bird-travel-tours_travvyawards2026-voteforskybirdskybird-bestairlineconsolidator-activity-7490168634653229056-t6xH</t>
+        </is>
+      </c>
+      <c r="L971" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M971" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N971" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O971" t="inlineStr">
+        <is>
+          <t>Sky Bird Travel thanks supporters for last year’s Travvy Awards win and urges votes for its 2026 nomination as Best Airline Consolidator.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/News_Dashboard/data/social_media_posts.xlsx
+++ b/News_Dashboard/data/social_media_posts.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O971"/>
+  <dimension ref="A1:O985"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -62202,6 +62202,898 @@
         </is>
       </c>
     </row>
+    <row r="972">
+      <c r="A972" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B972" t="inlineStr">
+        <is>
+          <t>Ramp</t>
+        </is>
+      </c>
+      <c r="C972" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D972" t="inlineStr">
+        <is>
+          <t>tryramp</t>
+        </is>
+      </c>
+      <c r="E972" t="inlineStr">
+        <is>
+          <t>Wed Aug 05 15:58:37 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F972" t="inlineStr">
+        <is>
+          <t>@beehiiv ALL EYES ON THE HIIV
+https://t.co/XP5ctCojvH</t>
+        </is>
+      </c>
+      <c r="G972" t="inlineStr"/>
+      <c r="H972" t="inlineStr"/>
+      <c r="I972" t="inlineStr"/>
+      <c r="J972" t="inlineStr"/>
+      <c r="K972" t="inlineStr">
+        <is>
+          <t>https://x.com/tryramp/status/2085032739154071826</t>
+        </is>
+      </c>
+      <c r="L972" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M972" t="inlineStr">
+        <is>
+          <t>Product Announcement</t>
+        </is>
+      </c>
+      <c r="N972" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O972" t="inlineStr">
+        <is>
+          <t>Ramp highlights its new product or feature, ‘Hiiv’, in a post that draws attention from the newsletter platform Beehiiv, indicating a potential launch or marketing push.</t>
+        </is>
+      </c>
+    </row>
+    <row r="973">
+      <c r="A973" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B973" t="inlineStr">
+        <is>
+          <t>Brex</t>
+        </is>
+      </c>
+      <c r="C973" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D973" t="inlineStr">
+        <is>
+          <t>brexhq</t>
+        </is>
+      </c>
+      <c r="E973" t="inlineStr">
+        <is>
+          <t>Wed Aug 05 18:08:21 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F973" t="inlineStr">
+        <is>
+          <t>@lennysan 🤭</t>
+        </is>
+      </c>
+      <c r="G973" t="inlineStr"/>
+      <c r="H973" t="inlineStr"/>
+      <c r="I973" t="inlineStr"/>
+      <c r="J973" t="inlineStr"/>
+      <c r="K973" t="inlineStr">
+        <is>
+          <t>https://x.com/brexHQ/status/2085065385686995034</t>
+        </is>
+      </c>
+      <c r="L973" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="M973" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N973" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O973" t="inlineStr">
+        <is>
+          <t>Brex tweets a facepalm emoji in response to Lennysan, suggesting a reaction to Lennysan's recent content or statement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="974">
+      <c r="A974" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B974" t="inlineStr">
+        <is>
+          <t>Brex</t>
+        </is>
+      </c>
+      <c r="C974" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D974" t="inlineStr">
+        <is>
+          <t>brexhq</t>
+        </is>
+      </c>
+      <c r="E974" t="inlineStr">
+        <is>
+          <t>Wed Aug 05 17:49:46 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F974" t="inlineStr">
+        <is>
+          <t>@clerkyinc Here's to getting builders back to building. 🚀</t>
+        </is>
+      </c>
+      <c r="G974" t="inlineStr"/>
+      <c r="H974" t="inlineStr"/>
+      <c r="I974" t="inlineStr"/>
+      <c r="J974" t="inlineStr"/>
+      <c r="K974" t="inlineStr">
+        <is>
+          <t>https://x.com/brexHQ/status/2085060711131095093</t>
+        </is>
+      </c>
+      <c r="L974" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M974" t="inlineStr">
+        <is>
+          <t>Partnership and Acquisitions</t>
+        </is>
+      </c>
+      <c r="N974" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O974" t="inlineStr">
+        <is>
+          <t>Brex publicly acknowledges Clerky Inc. in a supportive post, encouraging builders to continue creating and building.</t>
+        </is>
+      </c>
+    </row>
+    <row r="975">
+      <c r="A975" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B975" t="inlineStr">
+        <is>
+          <t>Brex</t>
+        </is>
+      </c>
+      <c r="C975" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D975" t="inlineStr">
+        <is>
+          <t>brexhq</t>
+        </is>
+      </c>
+      <c r="E975" t="inlineStr">
+        <is>
+          <t>Wed Aug 05 17:35:54 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F975" t="inlineStr">
+        <is>
+          <t>Read the full story: https://t.co/EPgYBSS25R</t>
+        </is>
+      </c>
+      <c r="G975" t="inlineStr"/>
+      <c r="H975" t="inlineStr"/>
+      <c r="I975" t="inlineStr"/>
+      <c r="J975" t="inlineStr"/>
+      <c r="K975" t="inlineStr">
+        <is>
+          <t>https://x.com/brexHQ/status/2085057218647334967</t>
+        </is>
+      </c>
+      <c r="L975" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M975" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N975" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O975" t="inlineStr">
+        <is>
+          <t>Brex posted a link to a news article without additional context, making it unclear what specific activity is being highlighted.</t>
+        </is>
+      </c>
+    </row>
+    <row r="976">
+      <c r="A976" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B976" t="inlineStr">
+        <is>
+          <t>Brex</t>
+        </is>
+      </c>
+      <c r="C976" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D976" t="inlineStr">
+        <is>
+          <t>brexhq</t>
+        </is>
+      </c>
+      <c r="E976" t="inlineStr">
+        <is>
+          <t>Wed Aug 05 17:35:53 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F976" t="inlineStr">
+        <is>
+          <t>@lennysan, @benthompson, @GergelyOrosz, @bariweiss, @milkkarten, @Emily_Sundberg, @Noahpinion, @michaeljburry, @bhargreaves, @chrissyfarr, @CaseyNewton, @twifintech, @healthapiguy, @RyanSAdams, @TrustlessState, @bytebytego</t>
+        </is>
+      </c>
+      <c r="G976" t="inlineStr"/>
+      <c r="H976" t="inlineStr"/>
+      <c r="I976" t="inlineStr"/>
+      <c r="J976" t="inlineStr"/>
+      <c r="K976" t="inlineStr">
+        <is>
+          <t>https://x.com/brexHQ/status/2085057217296764971</t>
+        </is>
+      </c>
+      <c r="L976" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M976" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N976" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O976" t="inlineStr">
+        <is>
+          <t>Brex tags a wide array of industry influencers in a tweet, suggesting a potential collaboration or announcement, but no explicit details are provided.</t>
+        </is>
+      </c>
+    </row>
+    <row r="977">
+      <c r="A977" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B977" t="inlineStr">
+        <is>
+          <t>Brex</t>
+        </is>
+      </c>
+      <c r="C977" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D977" t="inlineStr">
+        <is>
+          <t>brexhq</t>
+        </is>
+      </c>
+      <c r="E977" t="inlineStr">
+        <is>
+          <t>Wed Aug 05 17:35:52 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F977" t="inlineStr">
+        <is>
+          <t>A newsletter used to be something you unsubscribed from for free, now it's something startups budget for. Here's what startups are actually paying to read in 2026. https://t.co/u18d2IEzMB</t>
+        </is>
+      </c>
+      <c r="G977" t="inlineStr"/>
+      <c r="H977" t="inlineStr"/>
+      <c r="I977" t="inlineStr"/>
+      <c r="J977" t="inlineStr"/>
+      <c r="K977" t="inlineStr">
+        <is>
+          <t>https://x.com/brexHQ/status/2085057213458960726</t>
+        </is>
+      </c>
+      <c r="L977" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M977" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N977" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O977" t="inlineStr">
+        <is>
+          <t>Brex notes that startups are now budgeting for paid newsletters, highlighting a shift in content monetization and startup spending priorities.</t>
+        </is>
+      </c>
+    </row>
+    <row r="978">
+      <c r="A978" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B978" t="inlineStr">
+        <is>
+          <t>Brex</t>
+        </is>
+      </c>
+      <c r="C978" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D978" t="inlineStr">
+        <is>
+          <t>brexhq</t>
+        </is>
+      </c>
+      <c r="E978" t="inlineStr">
+        <is>
+          <t>Wed Aug 05 15:02:27 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F978" t="inlineStr">
+        <is>
+          <t>@MollySOShea @nikesharora we're ready</t>
+        </is>
+      </c>
+      <c r="G978" t="inlineStr"/>
+      <c r="H978" t="inlineStr"/>
+      <c r="I978" t="inlineStr"/>
+      <c r="J978" t="inlineStr"/>
+      <c r="K978" t="inlineStr">
+        <is>
+          <t>https://x.com/brexHQ/status/2085018604198596744</t>
+        </is>
+      </c>
+      <c r="L978" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M978" t="inlineStr">
+        <is>
+          <t>Partnership and Acquisitions</t>
+        </is>
+      </c>
+      <c r="N978" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O978" t="inlineStr">
+        <is>
+          <t>Brex signals readiness for a collaboration or partnership involving Molly S. O'Shea and CEO Nikesh Harora.</t>
+        </is>
+      </c>
+    </row>
+    <row r="979">
+      <c r="A979" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B979" t="inlineStr">
+        <is>
+          <t>Brex</t>
+        </is>
+      </c>
+      <c r="C979" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D979" t="inlineStr">
+        <is>
+          <t>brexhq</t>
+        </is>
+      </c>
+      <c r="E979" t="inlineStr">
+        <is>
+          <t>Wed Aug 05 14:03:12 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F979" t="inlineStr">
+        <is>
+          <t>"it's just a few receipts"
+the few receipts: https://t.co/D5i70N7qyE</t>
+        </is>
+      </c>
+      <c r="G979" t="inlineStr"/>
+      <c r="H979" t="inlineStr"/>
+      <c r="I979" t="inlineStr"/>
+      <c r="J979" t="inlineStr"/>
+      <c r="K979" t="inlineStr">
+        <is>
+          <t>https://x.com/brexHQ/status/2085003692629991537</t>
+        </is>
+      </c>
+      <c r="L979" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M979" t="inlineStr">
+        <is>
+          <t>Product Announcement</t>
+        </is>
+      </c>
+      <c r="N979" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O979" t="inlineStr">
+        <is>
+          <t>Brex highlights a new feature that simplifies receipt handling, emphasizing its ease and minimal effort.</t>
+        </is>
+      </c>
+    </row>
+    <row r="980">
+      <c r="A980" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B980" t="inlineStr">
+        <is>
+          <t>Brex</t>
+        </is>
+      </c>
+      <c r="C980" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D980" t="inlineStr">
+        <is>
+          <t>brexhq</t>
+        </is>
+      </c>
+      <c r="E980" t="inlineStr">
+        <is>
+          <t>Tue Aug 04 21:19:17 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F980" t="inlineStr">
+        <is>
+          <t>Every vendor says they support MCP. Few will tell you how it holds up at scale. 
+Our AI Engineer, Sai Chiligireddy, on spotting the ones that do. 👇 https://t.co/c8Vr3tjwhP</t>
+        </is>
+      </c>
+      <c r="G980" t="inlineStr"/>
+      <c r="H980" t="inlineStr"/>
+      <c r="I980" t="inlineStr"/>
+      <c r="J980" t="inlineStr"/>
+      <c r="K980" t="inlineStr">
+        <is>
+          <t>https://x.com/brexHQ/status/2084751048661426622</t>
+        </is>
+      </c>
+      <c r="L980" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M980" t="inlineStr">
+        <is>
+          <t>Tech Updates</t>
+        </is>
+      </c>
+      <c r="N980" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O980" t="inlineStr">
+        <is>
+          <t>Brex showcases that their AI engineer has identified vendors that genuinely support MCP at scale, emphasizing Brex’s commitment to robust technology solutions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="981">
+      <c r="A981" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B981" t="inlineStr">
+        <is>
+          <t>Brex</t>
+        </is>
+      </c>
+      <c r="C981" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D981" t="inlineStr">
+        <is>
+          <t>brexhq</t>
+        </is>
+      </c>
+      <c r="E981" t="inlineStr">
+        <is>
+          <t>Tue Aug 04 18:30:42 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F981" t="inlineStr">
+        <is>
+          <t>Read the full story on the blimp: https://t.co/jS9M8RAo70</t>
+        </is>
+      </c>
+      <c r="G981" t="inlineStr"/>
+      <c r="H981" t="inlineStr"/>
+      <c r="I981" t="inlineStr"/>
+      <c r="J981" t="inlineStr"/>
+      <c r="K981" t="inlineStr">
+        <is>
+          <t>https://x.com/brexHQ/status/2084708623985312231</t>
+        </is>
+      </c>
+      <c r="L981" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M981" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N981" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O981" t="inlineStr">
+        <is>
+          <t>Brex shared a link to a news story about the company.</t>
+        </is>
+      </c>
+    </row>
+    <row r="982">
+      <c r="A982" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B982" t="inlineStr">
+        <is>
+          <t>Brex</t>
+        </is>
+      </c>
+      <c r="C982" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D982" t="inlineStr">
+        <is>
+          <t>brexhq</t>
+        </is>
+      </c>
+      <c r="E982" t="inlineStr">
+        <is>
+          <t>Tue Aug 04 18:30:42 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F982" t="inlineStr">
+        <is>
+          <t>Almost forgot MSG https://t.co/eoREFZjzbS</t>
+        </is>
+      </c>
+      <c r="G982" t="inlineStr"/>
+      <c r="H982" t="inlineStr"/>
+      <c r="I982" t="inlineStr"/>
+      <c r="J982" t="inlineStr"/>
+      <c r="K982" t="inlineStr">
+        <is>
+          <t>https://x.com/brexHQ/status/2084708622299205795</t>
+        </is>
+      </c>
+      <c r="L982" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M982" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N982" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O982" t="inlineStr">
+        <is>
+          <t>Brex posts a brief reminder about MSG, likely referencing a product or event, without any major announcement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="983">
+      <c r="A983" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B983" t="inlineStr">
+        <is>
+          <t>Brex</t>
+        </is>
+      </c>
+      <c r="C983" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D983" t="inlineStr">
+        <is>
+          <t>brexhq</t>
+        </is>
+      </c>
+      <c r="E983" t="inlineStr">
+        <is>
+          <t>Tue Aug 04 18:30:41 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F983" t="inlineStr">
+        <is>
+          <t>Places the Brex blimp has been:
+— RFP email threads
+— SF skies
+— Now, Forbes
+Our head of OHH Media told @Forbes how we built it with our friends at Buoyant Aero. https://t.co/IiETZIuxJD</t>
+        </is>
+      </c>
+      <c r="G983" t="inlineStr"/>
+      <c r="H983" t="inlineStr"/>
+      <c r="I983" t="inlineStr"/>
+      <c r="J983" t="inlineStr"/>
+      <c r="K983" t="inlineStr">
+        <is>
+          <t>https://x.com/brexHQ/status/2084708620789285227</t>
+        </is>
+      </c>
+      <c r="L983" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M983" t="inlineStr">
+        <is>
+          <t>Product Announcement</t>
+        </is>
+      </c>
+      <c r="N983" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O983" t="inlineStr">
+        <is>
+          <t>Brex highlights its new blimp, tracing its journey from RFP email threads to SF skies and now Forbes coverage, emphasizing collaboration with Buoyant Aero.</t>
+        </is>
+      </c>
+    </row>
+    <row r="984">
+      <c r="A984" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B984" t="inlineStr">
+        <is>
+          <t>Expedia</t>
+        </is>
+      </c>
+      <c r="C984" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="D984" t="inlineStr">
+        <is>
+          <t>expedia</t>
+        </is>
+      </c>
+      <c r="E984" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:31:25.000Z</t>
+        </is>
+      </c>
+      <c r="F984" t="inlineStr">
+        <is>
+          <t>Step inside the world of Ted Lasso with a walking tour through the real Richmond filming locations. From Ted's apartment and Richmond Green to The Prince's Head, then finish with the famous biscuits and a stay right in the heart of it all. ⚽️
+Book your tour, stay, and complete set-jetting trip on Expedia.
+📍 Richmond, London
+🎥 @benji_esca</t>
+        </is>
+      </c>
+      <c r="G984" t="inlineStr">
+        <is>
+          <t>https://scontent-lhr11-1.cdninstagram.com/v/t51.82787-15/764925705_18621392194030381_471137091644611146_n.jpg?stp=dst-jpg_e35_p1080x1080_sh2.08_tt6&amp;_nc_ht=scontent-lhr11-1.cdninstagram.com&amp;_nc_cat=101&amp;_nc_oc=Q6cZ2gF9oZslQ-oZRRjNnJKdx7PSPVd3fefm29wFWlqVv--Z4NmQHQ9bJRIiWLYx18frO63kSPDh6svo89gFNv4_WIqm&amp;_nc_ohc=H7dljndJ1XYQ7kNvwGqsZNB&amp;_nc_gid=LX-TwI515OnkPAg0I265Mw&amp;edm=ADp7STQBAAAA&amp;ccb=7-5&amp;oh=00_AQFDiah81z7qoBJc8gtaPcyLw1bfPKMLFZfrzioG9wIkyA&amp;oe=6A79507D&amp;_nc_sid=c6f216</t>
+        </is>
+      </c>
+      <c r="H984" t="inlineStr">
+        <is>
+          <t>[easyocr not installed. Run 'pip install easyocr torch torchvision']</t>
+        </is>
+      </c>
+      <c r="I984" t="inlineStr">
+        <is>
+          <t>https://scontent-lhr11-1.cdninstagram.com/o1/v/t2/f2/m86/AQObqaBkG5I1-w2CBvcILkdci-cackChkk6OkPSgQuwUwfA3H6vr-hHFZYG-XFxGhjqsh9yazuSaL0ehmnlOvoNN5Wo2Q6bFKz2eOtw.mp4?_nc_cat=100&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-lhr11-1.cdninstagram.com&amp;_nc_ohc=bpoG6rYO6iMQ7kNvwEvWNYQ&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uQ0xJUFMuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTg2MjEzODkwNjgwMzAzODEsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDA5OSwiZHVyYXRpb25fcyI6NTIsInVybGdlbl9zb3VyY2UiOiJ3d3cifQ%3D%3D&amp;ccb=17-1&amp;vs=4a77e0836332aea4&amp;_nc_vs=HBksFQIYUmlnX3hwdl9yZWVsc19wZXJtYW5lbnRfc3JfcHJvZC8wRTQzQUM3RTAzMzA4MDREN0JEQkY2NURCMjRBQjJBMV92aWRlb19kYXNoaW5pdC5tcDQVAALIARIAFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyLzlGNDI2OUY5NTdEMzJFMTU4NTFDNTc3ODc5NUQ2Q0E1X2F1ZGlvX2Rhc2hpbml0Lm1wNBUCAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbaxv6JwIOUQhUCKAJDMywXQEo7peNT988YEmRhc2hfYmFzZWxpbmVfMV92MREAdf4HZeadAQA&amp;_nc_gid=LX-TwI515OnkPAg0I265Mw&amp;_nc_zt=28&amp;_nc_ss=7a22e&amp;oh=00_AQFfk9hqP4KWO5Mvc_ob6v0Tus-ynmodgFWSCuoC7Eq2-g&amp;oe=6A756E59</t>
+        </is>
+      </c>
+      <c r="J984" t="inlineStr">
+        <is>
+          <t>[faster-whisper not installed. Run 'pip install faster-whisper']</t>
+        </is>
+      </c>
+      <c r="K984" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DbqrjNGgd0D/</t>
+        </is>
+      </c>
+      <c r="L984" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M984" t="inlineStr">
+        <is>
+          <t>Product Announcement</t>
+        </is>
+      </c>
+      <c r="N984" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O984" t="inlineStr">
+        <is>
+          <t>Expedia is promoting a Ted Lasso-themed walking tour in Richmond, London, offering a combined tour, stay, and set-jetting experience.</t>
+        </is>
+      </c>
+    </row>
+    <row r="985">
+      <c r="A985" t="inlineStr">
+        <is>
+          <t>Mondee</t>
+        </is>
+      </c>
+      <c r="B985" t="inlineStr">
+        <is>
+          <t>Sky Bird Travel</t>
+        </is>
+      </c>
+      <c r="C985" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D985" t="inlineStr">
+        <is>
+          <t>Sky Bird Travel &amp; Tours</t>
+        </is>
+      </c>
+      <c r="E985" t="inlineStr">
+        <is>
+          <t>2026-08-05T16:56:49.390Z</t>
+        </is>
+      </c>
+      <c r="F985" t="inlineStr">
+        <is>
+          <t>Travel plans can change—but peace of mind doesn’t have to. When you book with a travel advisor, you have someone in your corner before, during, and after your trip. From the latest travel updates to personalized support when plans change, we’re here to help you travel with confidence. 
+✈️ Stay informed. 
+🌎 Travel smarter. 
+❤️ Experience personalized service every step of the way. 
+#WhyUseATravelAgent #TravelAdvisor #TravelSmarter #TravelExperts #BookWithConfidence #TravelPlanning #TravelSupport #TravelAgent</t>
+        </is>
+      </c>
+      <c r="G985" t="inlineStr">
+        <is>
+          <t>https://media.licdn.com/dms/image/v2/D4D22AQFsLVIZnKLD1g/feedshare-shrink_1280/B4DZ_S2y43HQAU-/0/1785949008012?e=1787788800&amp;v=beta&amp;t=Apj8pzd-HIBrjmW8NhQPP9clfSLjYTyQ48pMgrni2sQ</t>
+        </is>
+      </c>
+      <c r="H985" t="inlineStr">
+        <is>
+          <t>[easyocr not installed. Run 'pip install easyocr torch torchvision']</t>
+        </is>
+      </c>
+      <c r="I985" t="inlineStr"/>
+      <c r="J985" t="inlineStr"/>
+      <c r="K985" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/sky-bird-travel-tours_whyuseatravelagent-traveladvisor-travelsmarter-activity-7490813073881169920-HmKi</t>
+        </is>
+      </c>
+      <c r="L985" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M985" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N985" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O985" t="inlineStr">
+        <is>
+          <t>Sky Bird Travel promotes the benefits of using a travel advisor for personalized support and peace of mind throughout the travel experience.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
